--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="F2" t="n">
-        <v>83.16</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>22.43</v>
+        <v>22.15</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -579,8 +579,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1235</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
@@ -632,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="F3" t="n">
-        <v>9.51</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -654,8 +658,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M3" t="n">
+        <v>41</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
@@ -707,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -729,8 +737,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M4" t="n">
+        <v>153.5</v>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
@@ -782,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5595</v>
+        <v>5440</v>
       </c>
       <c r="F5" t="n">
-        <v>119.81</v>
+        <v>116.49</v>
       </c>
       <c r="G5" t="n">
-        <v>34.47</v>
+        <v>33.51</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -804,8 +816,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5595</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
@@ -861,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>121.5</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>22.97</v>
+        <v>23.44</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -883,8 +899,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>121.5</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
@@ -936,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>27.4</v>
+        <v>27.29</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -958,8 +978,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100</v>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
@@ -1015,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
-        <v>22.07</v>
+        <v>21.68</v>
       </c>
       <c r="G8" t="n">
-        <v>4.83</v>
+        <v>4.75</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1037,8 +1061,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="M8" t="n">
+        <v>173</v>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
@@ -1094,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.91</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1116,8 +1144,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M9" t="n">
+        <v>106</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
@@ -1169,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F10" t="n">
-        <v>17.55</v>
+        <v>17.33</v>
       </c>
       <c r="G10" t="n">
-        <v>6.22</v>
+        <v>6.14</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1192,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.98</v>
+        <v>-1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>153.5</v>
+        <v>155</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1248,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="F11" t="n">
-        <v>24.4</v>
+        <v>24.59</v>
       </c>
       <c r="G11" t="n">
-        <v>4.63</v>
+        <v>4.67</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1270,8 +1302,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1270</v>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
@@ -1323,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="F12" t="n">
-        <v>19.51</v>
+        <v>19.64</v>
       </c>
       <c r="G12" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1345,8 +1381,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M12" t="n">
+        <v>156.5</v>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
@@ -1402,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>277.5</v>
+        <v>274</v>
       </c>
       <c r="F13" t="n">
-        <v>32.46</v>
+        <v>32.05</v>
       </c>
       <c r="G13" t="n">
-        <v>6.57</v>
+        <v>6.49</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1424,8 +1464,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M13" t="n">
+        <v>277.5</v>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
@@ -1481,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>28.19</v>
       </c>
       <c r="G14" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1503,8 +1547,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>142.5</v>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
@@ -1556,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>216.5</v>
+        <v>215.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.5</v>
+        <v>19.41</v>
       </c>
       <c r="G15" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1578,8 +1626,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="M15" t="n">
+        <v>216.5</v>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
@@ -1635,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="F16" t="n">
-        <v>164.06</v>
+        <v>154.7</v>
       </c>
       <c r="G16" t="n">
-        <v>63.69</v>
+        <v>60.06</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1657,8 +1709,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6400</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
@@ -1714,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1590</v>
+        <v>1510</v>
       </c>
       <c r="F17" t="n">
-        <v>47.04</v>
+        <v>44.67</v>
       </c>
       <c r="G17" t="n">
-        <v>9.550000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1732,8 +1788,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1590</v>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -1787,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="F18" t="n">
-        <v>66.09999999999999</v>
+        <v>64.58</v>
       </c>
       <c r="G18" t="n">
-        <v>33.85</v>
+        <v>33.07</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1805,8 +1865,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11990</v>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -1860,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="F19" t="n">
-        <v>64.03</v>
+        <v>62.5</v>
       </c>
       <c r="G19" t="n">
-        <v>12.43</v>
+        <v>12.13</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1878,8 +1942,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="M19" t="n">
+        <v>753</v>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -1933,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>84.3</v>
+        <v>81.8</v>
       </c>
       <c r="F20" t="n">
-        <v>46.32</v>
+        <v>44.95</v>
       </c>
       <c r="G20" t="n">
-        <v>6.93</v>
+        <v>6.72</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -1951,8 +2019,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.3</v>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2006,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6600</v>
+        <v>6310</v>
       </c>
       <c r="F21" t="n">
-        <v>108.06</v>
+        <v>103.31</v>
       </c>
       <c r="G21" t="n">
-        <v>27.9</v>
+        <v>26.68</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2024,8 +2096,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6600</v>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2083,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="F22" t="n">
-        <v>54.59</v>
+        <v>53.06</v>
       </c>
       <c r="G22" t="n">
-        <v>27.48</v>
+        <v>26.71</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2101,8 +2177,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2140</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2160,10 +2240,10 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.4</v>
+        <v>18.35</v>
       </c>
       <c r="F23" t="n">
-        <v>41.82</v>
+        <v>41.7</v>
       </c>
       <c r="G23" t="n">
         <v>1.69</v>
@@ -2178,8 +2258,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18.4</v>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2237,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1410</v>
+        <v>1370</v>
       </c>
       <c r="F24" t="n">
-        <v>71.61</v>
+        <v>69.58</v>
       </c>
       <c r="G24" t="n">
-        <v>17.47</v>
+        <v>16.98</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2255,8 +2339,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1410</v>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2314,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>45.15</v>
+        <v>44.95</v>
       </c>
       <c r="F25" t="n">
-        <v>55.06</v>
+        <v>54.82</v>
       </c>
       <c r="G25" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2333,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.99</v>
+        <v>-0.44</v>
       </c>
       <c r="M25" t="n">
-        <v>41.05</v>
+        <v>45.15</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2395,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2745</v>
+        <v>2675</v>
       </c>
       <c r="F26" t="n">
-        <v>236.23</v>
+        <v>230.21</v>
       </c>
       <c r="G26" t="n">
-        <v>53.81</v>
+        <v>52.44</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2411,8 +2499,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2745</v>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2470,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="F27" t="n">
-        <v>44.28</v>
+        <v>42.84</v>
       </c>
       <c r="G27" t="n">
-        <v>6.92</v>
+        <v>6.69</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2488,8 +2580,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="M27" t="n">
+        <v>612</v>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2547,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1190</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="n">
-        <v>58.28</v>
+        <v>59.01</v>
       </c>
       <c r="G28" t="n">
-        <v>12.08</v>
+        <v>12.23</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2563,8 +2659,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1190</v>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2622,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>547</v>
+        <v>509</v>
       </c>
       <c r="F29" t="n">
-        <v>89.53</v>
+        <v>83.31</v>
       </c>
       <c r="G29" t="n">
-        <v>17.54</v>
+        <v>16.32</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2640,8 +2740,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>-6.95</v>
+      </c>
+      <c r="M29" t="n">
+        <v>547</v>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2699,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3375</v>
+        <v>3255</v>
       </c>
       <c r="F30" t="n">
-        <v>79.59999999999999</v>
+        <v>76.77</v>
       </c>
       <c r="G30" t="n">
-        <v>10.97</v>
+        <v>10.58</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2717,8 +2821,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3375</v>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2776,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>509</v>
+        <v>492.5</v>
       </c>
       <c r="F31" t="n">
-        <v>103.25</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>13.28</v>
+        <v>12.85</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2792,8 +2900,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="M31" t="n">
+        <v>509</v>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -2851,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="F32" t="n">
-        <v>42.43</v>
+        <v>43.38</v>
       </c>
       <c r="G32" t="n">
-        <v>10.52</v>
+        <v>10.76</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2869,8 +2981,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M32" t="n">
+        <v>670</v>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
@@ -2924,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="F33" t="n">
-        <v>36.7</v>
+        <v>36.16</v>
       </c>
       <c r="G33" t="n">
-        <v>6.34</v>
+        <v>6.24</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -2942,8 +3058,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="M33" t="n">
+        <v>545</v>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -3001,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="F34" t="n">
-        <v>75.31</v>
+        <v>73.16</v>
       </c>
       <c r="G34" t="n">
-        <v>17.16</v>
+        <v>16.67</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3019,8 +3139,12 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4560</v>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -3078,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="F35" t="n">
-        <v>51.56</v>
+        <v>53.15</v>
       </c>
       <c r="G35" t="n">
-        <v>14.33</v>
+        <v>14.77</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3100,8 +3224,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1620</v>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
@@ -3153,10 +3281,10 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="F36" t="n">
-        <v>21.44</v>
+        <v>21.47</v>
       </c>
       <c r="G36" t="n">
         <v>1.07</v>
@@ -3175,8 +3303,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M36" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
@@ -3232,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>5820</v>
+        <v>5310</v>
       </c>
       <c r="F37" t="n">
-        <v>131.35</v>
+        <v>119.84</v>
       </c>
       <c r="G37" t="n">
-        <v>36.22</v>
+        <v>33.04</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3254,8 +3386,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>-8.76</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5820</v>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
@@ -3307,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="F38" t="n">
-        <v>83.58</v>
+        <v>79.98</v>
       </c>
       <c r="G38" t="n">
-        <v>32.83</v>
+        <v>31.42</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3329,8 +3465,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5345</v>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
@@ -3382,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="F39" t="n">
-        <v>45.62</v>
+        <v>45.42</v>
       </c>
       <c r="G39" t="n">
-        <v>23.92</v>
+        <v>23.82</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3404,8 +3544,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M39" t="n">
+        <v>697</v>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
@@ -3461,10 +3605,10 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>11.89</v>
+        <v>11.87</v>
       </c>
       <c r="G40" t="n">
         <v>1.66</v>
@@ -3483,8 +3627,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M40" t="n">
+        <v>96.8</v>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
@@ -3536,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>152.5</v>
+        <v>155</v>
       </c>
       <c r="F41" t="n">
-        <v>11.73</v>
+        <v>11.92</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3558,8 +3706,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M41" t="n">
+        <v>152.5</v>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
@@ -3615,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F42" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G42" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3637,8 +3789,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="M42" t="n">
+        <v>106.5</v>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
@@ -3690,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>954</v>
+        <v>915</v>
       </c>
       <c r="F43" t="n">
-        <v>25.81</v>
+        <v>24.76</v>
       </c>
       <c r="G43" t="n">
-        <v>3.97</v>
+        <v>3.81</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3712,8 +3868,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="M43" t="n">
+        <v>954</v>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
@@ -3769,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F44" t="n">
-        <v>27.13</v>
+        <v>26.86</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3791,8 +3951,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="M44" t="n">
+        <v>197</v>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
@@ -3848,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3590</v>
+        <v>3355</v>
       </c>
       <c r="F45" t="n">
-        <v>52.65</v>
+        <v>49.21</v>
       </c>
       <c r="G45" t="n">
-        <v>5.13</v>
+        <v>4.79</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -3870,8 +4034,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3590</v>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
@@ -3927,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>210.5</v>
+        <v>208</v>
       </c>
       <c r="F46" t="n">
-        <v>21.44</v>
+        <v>21.18</v>
       </c>
       <c r="G46" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -3945,8 +4113,12 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M46" t="n">
+        <v>210.5</v>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4018,8 +4190,12 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>222</v>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
@@ -4073,13 +4249,13 @@
         <v>61</v>
       </c>
       <c r="E48" t="n">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="F48" t="n">
-        <v>25.85</v>
+        <v>25.49</v>
       </c>
       <c r="G48" t="n">
-        <v>7.29</v>
+        <v>7.19</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4091,8 +4267,12 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="M48" t="n">
+        <v>713</v>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4150,13 +4330,13 @@
         <v>51</v>
       </c>
       <c r="E49" t="n">
-        <v>5995</v>
+        <v>6055</v>
       </c>
       <c r="F49" t="n">
-        <v>31.88</v>
+        <v>32.2</v>
       </c>
       <c r="G49" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4168,8 +4348,12 @@
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>5995</v>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4227,13 +4411,13 @@
         <v>97</v>
       </c>
       <c r="E50" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F50" t="n">
-        <v>23.55</v>
+        <v>23.46</v>
       </c>
       <c r="G50" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="H50" t="n">
         <v>29.3</v>
@@ -4249,8 +4433,12 @@
           <t>🟡未來合理</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M50" t="n">
+        <v>520</v>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
@@ -4302,13 +4490,13 @@
         <v>91</v>
       </c>
       <c r="E51" t="n">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="F51" t="n">
-        <v>41.9</v>
+        <v>40.74</v>
       </c>
       <c r="G51" t="n">
-        <v>5.62</v>
+        <v>5.47</v>
       </c>
       <c r="H51" t="n">
         <v>46.1</v>
@@ -4324,8 +4512,12 @@
           <t>🟡未來合理</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="M51" t="n">
+        <v>683</v>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
@@ -4400,10 +4592,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>58</v>
+        <v>57.4</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -4456,13 +4648,13 @@
         <v>77</v>
       </c>
       <c r="E53" t="n">
-        <v>188</v>
+        <v>183.5</v>
       </c>
       <c r="F53" t="n">
-        <v>17.17</v>
+        <v>16.76</v>
       </c>
       <c r="G53" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="H53" t="n">
         <v>15.5</v>
@@ -4478,8 +4670,12 @@
           <t>🟡未來合理</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="M53" t="n">
+        <v>188</v>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
@@ -4531,13 +4727,13 @@
         <v>96</v>
       </c>
       <c r="E54" t="n">
-        <v>326</v>
+        <v>318.5</v>
       </c>
       <c r="F54" t="n">
-        <v>16.88</v>
+        <v>16.49</v>
       </c>
       <c r="G54" t="n">
-        <v>4.79</v>
+        <v>4.68</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -4549,8 +4745,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="M54" t="n">
+        <v>326</v>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4604,13 +4804,13 @@
         <v>94</v>
       </c>
       <c r="E55" t="n">
-        <v>163.5</v>
+        <v>162</v>
       </c>
       <c r="F55" t="n">
-        <v>18.39</v>
+        <v>18.22</v>
       </c>
       <c r="G55" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -4622,8 +4822,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="M55" t="n">
+        <v>163.5</v>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4677,13 +4881,13 @@
         <v>78</v>
       </c>
       <c r="E56" t="n">
-        <v>119.5</v>
+        <v>117</v>
       </c>
       <c r="F56" t="n">
-        <v>19.43</v>
+        <v>19.02</v>
       </c>
       <c r="G56" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -4696,10 +4900,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.27</v>
+        <v>-2.09</v>
       </c>
       <c r="M56" t="n">
-        <v>118</v>
+        <v>119.5</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4754,13 +4958,13 @@
         <v>78</v>
       </c>
       <c r="E57" t="n">
-        <v>86.3</v>
+        <v>85.3</v>
       </c>
       <c r="F57" t="n">
-        <v>16.47</v>
+        <v>16.28</v>
       </c>
       <c r="G57" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4772,8 +4976,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M57" t="n">
+        <v>86.3</v>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4831,13 +5039,13 @@
         <v>77</v>
       </c>
       <c r="E58" t="n">
-        <v>152.5</v>
+        <v>154</v>
       </c>
       <c r="F58" t="n">
-        <v>17</v>
+        <v>17.17</v>
       </c>
       <c r="G58" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -4849,8 +5057,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M58" t="n">
+        <v>152.5</v>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4908,13 +5120,13 @@
         <v>76</v>
       </c>
       <c r="E59" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F59" t="n">
-        <v>14.05</v>
+        <v>14.11</v>
       </c>
       <c r="G59" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -4926,8 +5138,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M59" t="n">
+        <v>226</v>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -4981,13 +5197,13 @@
         <v>73</v>
       </c>
       <c r="E60" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F60" t="n">
-        <v>15.27</v>
+        <v>15.19</v>
       </c>
       <c r="G60" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -4999,8 +5215,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="M60" t="n">
+        <v>181</v>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -5054,13 +5274,13 @@
         <v>66</v>
       </c>
       <c r="E61" t="n">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F61" t="n">
-        <v>16.15</v>
+        <v>16.08</v>
       </c>
       <c r="G61" t="n">
-        <v>13.03</v>
+        <v>12.98</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5072,8 +5292,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M61" t="n">
+        <v>699</v>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -5131,13 +5355,13 @@
         <v>62</v>
       </c>
       <c r="E62" t="n">
-        <v>473</v>
+        <v>465.5</v>
       </c>
       <c r="F62" t="n">
-        <v>18.35</v>
+        <v>18.06</v>
       </c>
       <c r="G62" t="n">
-        <v>5.06</v>
+        <v>4.98</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -5147,8 +5371,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="M62" t="n">
+        <v>473</v>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -5206,13 +5434,13 @@
         <v>60</v>
       </c>
       <c r="E63" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="F63" t="n">
-        <v>19.68</v>
+        <v>19.78</v>
       </c>
       <c r="G63" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5225,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-0.47</v>
+        <v>0.47</v>
       </c>
       <c r="M63" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5287,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="F64" t="n">
-        <v>17.64</v>
+        <v>17.59</v>
       </c>
       <c r="G64" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5303,8 +5531,12 @@
           <t>🟡合理</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M64" t="n">
+        <v>160</v>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -5362,13 +5594,13 @@
         <v>97</v>
       </c>
       <c r="E65" t="n">
-        <v>154.5</v>
+        <v>156</v>
       </c>
       <c r="F65" t="n">
-        <v>16.23</v>
+        <v>16.39</v>
       </c>
       <c r="G65" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="H65" t="n">
         <v>14.7</v>
@@ -5385,10 +5617,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="M65" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -5441,13 +5673,13 @@
         <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F66" t="n">
-        <v>20.17</v>
+        <v>20.1</v>
       </c>
       <c r="G66" t="n">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
       <c r="H66" t="n">
         <v>17.9</v>
@@ -5463,8 +5695,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M66" t="n">
+        <v>539</v>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
@@ -5516,13 +5752,13 @@
         <v>91</v>
       </c>
       <c r="E67" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="F67" t="n">
-        <v>15.37</v>
+        <v>15.31</v>
       </c>
       <c r="G67" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="H67" t="n">
         <v>15</v>
@@ -5539,10 +5775,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.83</v>
+        <v>-0.42</v>
       </c>
       <c r="M67" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5595,13 +5831,13 @@
         <v>90</v>
       </c>
       <c r="E68" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F68" t="n">
-        <v>25.11</v>
+        <v>24.68</v>
       </c>
       <c r="G68" t="n">
-        <v>6.46</v>
+        <v>6.35</v>
       </c>
       <c r="H68" t="n">
         <v>27.5</v>
@@ -5617,8 +5853,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="M68" t="n">
+        <v>297</v>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
@@ -5670,10 +5910,10 @@
         <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>14.41</v>
+        <v>14.44</v>
       </c>
       <c r="G69" t="n">
         <v>2.04</v>
@@ -5692,8 +5932,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M69" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
@@ -5745,13 +5989,13 @@
         <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="F70" t="n">
-        <v>17.2</v>
+        <v>17.13</v>
       </c>
       <c r="G70" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="H70" t="n">
         <v>16.4</v>
@@ -5767,8 +6011,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M70" t="n">
+        <v>123.5</v>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
@@ -5824,13 +6072,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="F71" t="n">
-        <v>16.38</v>
+        <v>16.25</v>
       </c>
       <c r="G71" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H71" t="n">
         <v>15.3</v>
@@ -5846,8 +6094,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M71" t="n">
+        <v>248.5</v>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
@@ -5899,13 +6151,13 @@
         <v>76</v>
       </c>
       <c r="E72" t="n">
-        <v>1145</v>
+        <v>1065</v>
       </c>
       <c r="F72" t="n">
-        <v>48.5</v>
+        <v>45.11</v>
       </c>
       <c r="G72" t="n">
-        <v>25.9</v>
+        <v>24.09</v>
       </c>
       <c r="H72" t="n">
         <v>38.8</v>
@@ -5919,8 +6171,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1145</v>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
@@ -5976,13 +6232,13 @@
         <v>68</v>
       </c>
       <c r="E73" t="n">
-        <v>61.7</v>
+        <v>60.5</v>
       </c>
       <c r="F73" t="n">
-        <v>19.9</v>
+        <v>19.52</v>
       </c>
       <c r="G73" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="H73" t="n">
         <v>21.3</v>
@@ -5998,8 +6254,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M73" t="n">
+        <v>61.7</v>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
@@ -6055,13 +6315,13 @@
         <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="F74" t="n">
-        <v>44.12</v>
+        <v>41.52</v>
       </c>
       <c r="G74" t="n">
-        <v>23.55</v>
+        <v>22.16</v>
       </c>
       <c r="H74" t="n">
         <v>24.6</v>
@@ -6077,8 +6337,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3310</v>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
@@ -6130,13 +6394,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="F75" t="n">
-        <v>14.16</v>
+        <v>14.36</v>
       </c>
       <c r="G75" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H75" t="n">
         <v>14.2</v>
@@ -6152,8 +6416,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>703</v>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
@@ -6205,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="F76" t="n">
-        <v>27.59</v>
+        <v>27.65</v>
       </c>
       <c r="G76" t="n">
-        <v>9.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>23.6</v>
@@ -6227,8 +6495,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2380</v>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
@@ -6280,13 +6552,13 @@
         <v>97</v>
       </c>
       <c r="E77" t="n">
-        <v>116.5</v>
+        <v>118.5</v>
       </c>
       <c r="F77" t="n">
-        <v>16.62</v>
+        <v>16.9</v>
       </c>
       <c r="G77" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="H77" t="n">
         <v>12.4</v>
@@ -6303,7 +6575,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
         <v>116.5</v>
@@ -6359,13 +6631,13 @@
         <v>94</v>
       </c>
       <c r="E78" t="n">
-        <v>106.5</v>
+        <v>105.5</v>
       </c>
       <c r="F78" t="n">
-        <v>13.18</v>
+        <v>13.06</v>
       </c>
       <c r="G78" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H78" t="n">
         <v>12.3</v>
@@ -6382,10 +6654,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-1.84</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6438,13 +6710,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="F79" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
       <c r="G79" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H79" t="n">
         <v>5.9</v>
@@ -6461,10 +6733,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-2.13</v>
+        <v>-0.4</v>
       </c>
       <c r="M79" t="n">
-        <v>25.85</v>
+        <v>25.3</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6517,13 +6789,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>107.5</v>
+        <v>105.5</v>
       </c>
       <c r="F80" t="n">
-        <v>12.38</v>
+        <v>12.15</v>
       </c>
       <c r="G80" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H80" t="n">
         <v>10.7</v>
@@ -6539,8 +6811,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="M80" t="n">
+        <v>107.5</v>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
@@ -6592,13 +6868,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>177</v>
+        <v>176.5</v>
       </c>
       <c r="F81" t="n">
-        <v>12.62</v>
+        <v>12.58</v>
       </c>
       <c r="G81" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="H81" t="n">
         <v>11.4</v>
@@ -6614,8 +6890,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="L81" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M81" t="n">
+        <v>177</v>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
@@ -6667,13 +6947,13 @@
         <v>92</v>
       </c>
       <c r="E82" t="n">
-        <v>42.05</v>
+        <v>41.2</v>
       </c>
       <c r="F82" t="n">
-        <v>8.85</v>
+        <v>8.67</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H82" t="n">
         <v>7.6</v>
@@ -6689,8 +6969,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="M82" t="n">
+        <v>42.05</v>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
@@ -6742,13 +7026,13 @@
         <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="F83" t="n">
-        <v>23.22</v>
+        <v>22.91</v>
       </c>
       <c r="G83" t="n">
-        <v>8.9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H83" t="n">
         <v>25</v>
@@ -6764,8 +7048,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="M83" t="n">
+        <v>886</v>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
@@ -6817,13 +7105,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>510</v>
+        <v>490.5</v>
       </c>
       <c r="F84" t="n">
-        <v>21.85</v>
+        <v>21.02</v>
       </c>
       <c r="G84" t="n">
-        <v>4.81</v>
+        <v>4.63</v>
       </c>
       <c r="H84" t="n">
         <v>21.2</v>
@@ -6839,8 +7127,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="M84" t="n">
+        <v>510</v>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
@@ -6892,13 +7184,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F85" t="n">
-        <v>17.53</v>
+        <v>16.99</v>
       </c>
       <c r="G85" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
       <c r="H85" t="n">
         <v>14.1</v>
@@ -6914,8 +7206,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="L85" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="M85" t="n">
+        <v>163</v>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
@@ -6967,13 +7263,13 @@
         <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>38.7</v>
+        <v>38.45</v>
       </c>
       <c r="F86" t="n">
-        <v>7.98</v>
+        <v>7.93</v>
       </c>
       <c r="G86" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H86" t="n">
         <v>6.2</v>
@@ -6989,8 +7285,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="M86" t="n">
+        <v>38.7</v>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
@@ -7042,13 +7342,13 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="F87" t="n">
-        <v>29.46</v>
+        <v>28.91</v>
       </c>
       <c r="G87" t="n">
-        <v>15.18</v>
+        <v>14.9</v>
       </c>
       <c r="H87" t="n">
         <v>30.7</v>
@@ -7064,8 +7364,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1875</v>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
@@ -7121,13 +7425,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1305</v>
+        <v>1260</v>
       </c>
       <c r="F88" t="n">
-        <v>30.1</v>
+        <v>29.06</v>
       </c>
       <c r="G88" t="n">
-        <v>9.16</v>
+        <v>8.84</v>
       </c>
       <c r="H88" t="n">
         <v>21.8</v>
@@ -7143,8 +7447,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1305</v>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
@@ -7200,13 +7508,13 @@
         <v>79</v>
       </c>
       <c r="E89" t="n">
-        <v>89.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>8.789999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="G89" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="H89" t="n">
         <v>8.6</v>
@@ -7222,8 +7530,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
+      <c r="L89" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="M89" t="n">
+        <v>89.7</v>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
@@ -7279,10 +7591,10 @@
         <v>78</v>
       </c>
       <c r="E90" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="G90" t="n">
         <v>1.32</v>
@@ -7305,7 +7617,7 @@
         <v>0.19</v>
       </c>
       <c r="M90" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7384,8 +7696,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>51.2</v>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
@@ -7441,13 +7757,13 @@
         <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>332.5</v>
+        <v>333</v>
       </c>
       <c r="F92" t="n">
-        <v>14.49</v>
+        <v>14.51</v>
       </c>
       <c r="G92" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="H92" t="n">
         <v>13.2</v>
@@ -7463,8 +7779,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
+      <c r="L92" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M92" t="n">
+        <v>332.5</v>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
@@ -7520,13 +7840,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="F93" t="n">
-        <v>7.28</v>
+        <v>7.42</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="H93" t="n">
         <v>9.6</v>
@@ -7542,8 +7862,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2270</v>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
@@ -7599,13 +7923,13 @@
         <v>62</v>
       </c>
       <c r="E94" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="F94" t="n">
-        <v>14.38</v>
+        <v>14.5</v>
       </c>
       <c r="G94" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="H94" t="n">
         <v>10</v>
@@ -7621,8 +7945,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M94" t="n">
+        <v>181</v>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
@@ -7678,13 +8006,13 @@
         <v>60</v>
       </c>
       <c r="E95" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="F95" t="n">
-        <v>14.56</v>
+        <v>14.61</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H95" t="n">
         <v>11.9</v>
@@ -7700,8 +8028,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="L95" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1365</v>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
@@ -7757,13 +8089,13 @@
         <v>79</v>
       </c>
       <c r="E96" t="n">
-        <v>69.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="G96" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
@@ -7775,8 +8107,12 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M96" t="n">
+        <v>69.5</v>
+      </c>
       <c r="N96" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -7830,13 +8166,13 @@
         <v>77</v>
       </c>
       <c r="E97" t="n">
-        <v>398</v>
+        <v>388.5</v>
       </c>
       <c r="F97" t="n">
-        <v>5.14</v>
+        <v>5.02</v>
       </c>
       <c r="G97" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -7848,8 +8184,12 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="M97" t="n">
+        <v>398</v>
+      </c>
       <c r="N97" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -7907,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>23.65</v>
+        <v>23.45</v>
       </c>
       <c r="F98" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="G98" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -7926,7 +8266,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M98" t="n">
         <v>23.65</v>
@@ -7988,13 +8328,13 @@
         <v>75</v>
       </c>
       <c r="E99" t="n">
-        <v>35.75</v>
+        <v>34.85</v>
       </c>
       <c r="F99" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8006,8 +8346,12 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="M99" t="n">
+        <v>35.75</v>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -8065,13 +8409,13 @@
         <v>69</v>
       </c>
       <c r="E100" t="n">
-        <v>202</v>
+        <v>199.5</v>
       </c>
       <c r="F100" t="n">
-        <v>5.02</v>
+        <v>4.96</v>
       </c>
       <c r="G100" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8083,8 +8427,12 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="L100" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="M100" t="n">
+        <v>202</v>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -8142,13 +8490,13 @@
         <v>32</v>
       </c>
       <c r="E101" t="n">
-        <v>47.05</v>
+        <v>46.6</v>
       </c>
       <c r="F101" t="n">
-        <v>11.62</v>
+        <v>11.51</v>
       </c>
       <c r="G101" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8160,8 +8508,12 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="M101" t="n">
+        <v>47.05</v>
+      </c>
       <c r="N101" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
@@ -8350,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="F2" t="n">
-        <v>44.12</v>
+        <v>41.52</v>
       </c>
       <c r="G2" t="n">
-        <v>23.55</v>
+        <v>22.16</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8372,8 +8724,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3310</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
@@ -8425,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="F3" t="n">
-        <v>14.16</v>
+        <v>14.36</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8447,8 +8803,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>703</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
@@ -8500,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="F4" t="n">
-        <v>27.59</v>
+        <v>27.65</v>
       </c>
       <c r="G4" t="n">
-        <v>9.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8522,8 +8882,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2380</v>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
@@ -8575,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>116.5</v>
+        <v>118.5</v>
       </c>
       <c r="F5" t="n">
-        <v>16.62</v>
+        <v>16.9</v>
       </c>
       <c r="G5" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8598,7 +8962,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
         <v>116.5</v>
@@ -8654,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>106.5</v>
+        <v>105.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.18</v>
+        <v>13.06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -8677,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.84</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -8733,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="F7" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -8756,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.13</v>
+        <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>25.85</v>
+        <v>25.3</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -8812,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>107.5</v>
+        <v>105.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.38</v>
+        <v>12.15</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -8834,8 +9198,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="M8" t="n">
+        <v>107.5</v>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
@@ -8887,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>177</v>
+        <v>176.5</v>
       </c>
       <c r="F9" t="n">
-        <v>12.62</v>
+        <v>12.58</v>
       </c>
       <c r="G9" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -8909,8 +9277,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M9" t="n">
+        <v>177</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
@@ -8962,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.05</v>
+        <v>41.2</v>
       </c>
       <c r="F10" t="n">
-        <v>8.85</v>
+        <v>8.67</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -8984,8 +9356,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="M10" t="n">
+        <v>42.05</v>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
@@ -9037,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="F11" t="n">
-        <v>23.22</v>
+        <v>22.91</v>
       </c>
       <c r="G11" t="n">
-        <v>8.9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9059,8 +9435,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="M11" t="n">
+        <v>886</v>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
@@ -9112,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>490.5</v>
       </c>
       <c r="F12" t="n">
-        <v>21.85</v>
+        <v>21.02</v>
       </c>
       <c r="G12" t="n">
-        <v>4.81</v>
+        <v>4.63</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9134,8 +9514,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="M12" t="n">
+        <v>510</v>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
@@ -9187,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F13" t="n">
-        <v>17.53</v>
+        <v>16.99</v>
       </c>
       <c r="G13" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9209,8 +9593,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="M13" t="n">
+        <v>163</v>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
@@ -9262,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.7</v>
+        <v>38.45</v>
       </c>
       <c r="F14" t="n">
-        <v>7.98</v>
+        <v>7.93</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9284,8 +9672,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="M14" t="n">
+        <v>38.7</v>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
@@ -9337,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="F15" t="n">
-        <v>29.46</v>
+        <v>28.91</v>
       </c>
       <c r="G15" t="n">
-        <v>15.18</v>
+        <v>14.9</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9359,8 +9751,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1875</v>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
@@ -9416,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1305</v>
+        <v>1260</v>
       </c>
       <c r="F16" t="n">
-        <v>30.1</v>
+        <v>29.06</v>
       </c>
       <c r="G16" t="n">
-        <v>9.16</v>
+        <v>8.84</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9438,8 +9834,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1305</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
@@ -9495,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>8.789999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9517,8 +9917,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>89.7</v>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
@@ -9574,10 +9978,10 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="G18" t="n">
         <v>1.32</v>
@@ -9600,7 +10004,7 @@
         <v>0.19</v>
       </c>
       <c r="M18" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -9679,8 +10083,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>51.2</v>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
@@ -9736,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>332.5</v>
+        <v>333</v>
       </c>
       <c r="F20" t="n">
-        <v>14.49</v>
+        <v>14.51</v>
       </c>
       <c r="G20" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -9758,8 +10166,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>332.5</v>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
@@ -9815,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="F21" t="n">
-        <v>7.28</v>
+        <v>7.42</v>
       </c>
       <c r="G21" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -9837,8 +10249,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2270</v>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
@@ -9894,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.38</v>
+        <v>14.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -9916,8 +10332,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M22" t="n">
+        <v>181</v>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
@@ -9973,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="F23" t="n">
-        <v>14.56</v>
+        <v>14.61</v>
       </c>
       <c r="G23" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -9995,8 +10415,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1365</v>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
@@ -10183,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>154.5</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n">
-        <v>16.23</v>
+        <v>16.39</v>
       </c>
       <c r="G2" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10206,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="M2" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10262,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F3" t="n">
-        <v>20.17</v>
+        <v>20.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10284,8 +10708,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>539</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
@@ -10337,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="F4" t="n">
-        <v>15.37</v>
+        <v>15.31</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10360,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.83</v>
+        <v>-0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10416,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F5" t="n">
-        <v>25.11</v>
+        <v>24.68</v>
       </c>
       <c r="G5" t="n">
-        <v>6.46</v>
+        <v>6.35</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10438,8 +10866,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="M5" t="n">
+        <v>297</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
@@ -10491,10 +10923,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>14.41</v>
+        <v>14.44</v>
       </c>
       <c r="G6" t="n">
         <v>2.04</v>
@@ -10513,8 +10945,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
@@ -10566,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>17.2</v>
+        <v>17.13</v>
       </c>
       <c r="G7" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -10588,8 +11024,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>123.5</v>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
@@ -10645,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.38</v>
+        <v>16.25</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -10667,8 +11107,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>248.5</v>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
@@ -10720,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1145</v>
+        <v>1065</v>
       </c>
       <c r="F9" t="n">
-        <v>48.5</v>
+        <v>45.11</v>
       </c>
       <c r="G9" t="n">
-        <v>25.9</v>
+        <v>24.09</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -10740,8 +11184,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1145</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
@@ -10797,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.7</v>
+        <v>60.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.9</v>
+        <v>19.52</v>
       </c>
       <c r="G10" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -10819,8 +11267,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M10" t="n">
+        <v>61.7</v>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
@@ -11007,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="F2" t="n">
-        <v>83.16</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>22.43</v>
+        <v>22.15</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11029,8 +11481,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1235</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
@@ -11082,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="F3" t="n">
-        <v>9.51</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11104,8 +11560,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M3" t="n">
+        <v>41</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
@@ -11157,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11179,8 +11639,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M4" t="n">
+        <v>153.5</v>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
@@ -11232,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5595</v>
+        <v>5440</v>
       </c>
       <c r="F5" t="n">
-        <v>119.81</v>
+        <v>116.49</v>
       </c>
       <c r="G5" t="n">
-        <v>34.47</v>
+        <v>33.51</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11254,8 +11718,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5595</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
@@ -11311,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>121.5</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>22.97</v>
+        <v>23.44</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11333,8 +11801,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>121.5</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
@@ -11386,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>27.4</v>
+        <v>27.29</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11408,8 +11880,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100</v>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
@@ -11465,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
-        <v>22.07</v>
+        <v>21.68</v>
       </c>
       <c r="G8" t="n">
-        <v>4.83</v>
+        <v>4.75</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11487,8 +11963,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="M8" t="n">
+        <v>173</v>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
@@ -11544,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.91</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -11566,8 +12046,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M9" t="n">
+        <v>106</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
@@ -11619,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F10" t="n">
-        <v>17.55</v>
+        <v>17.33</v>
       </c>
       <c r="G10" t="n">
-        <v>6.22</v>
+        <v>6.14</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -11642,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.98</v>
+        <v>-1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>153.5</v>
+        <v>155</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -11698,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="F11" t="n">
-        <v>24.4</v>
+        <v>24.59</v>
       </c>
       <c r="G11" t="n">
-        <v>4.63</v>
+        <v>4.67</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -11720,8 +12204,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1270</v>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
@@ -11773,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="F12" t="n">
-        <v>19.51</v>
+        <v>19.64</v>
       </c>
       <c r="G12" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -11795,8 +12283,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M12" t="n">
+        <v>156.5</v>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
@@ -11852,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>277.5</v>
+        <v>274</v>
       </c>
       <c r="F13" t="n">
-        <v>32.46</v>
+        <v>32.05</v>
       </c>
       <c r="G13" t="n">
-        <v>6.57</v>
+        <v>6.49</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -11874,8 +12366,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M13" t="n">
+        <v>277.5</v>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
@@ -11931,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>28.19</v>
       </c>
       <c r="G14" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -11953,8 +12449,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>142.5</v>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
@@ -12006,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>216.5</v>
+        <v>215.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.5</v>
+        <v>19.41</v>
       </c>
       <c r="G15" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12028,8 +12528,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="M15" t="n">
+        <v>216.5</v>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
@@ -12085,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="F16" t="n">
-        <v>164.06</v>
+        <v>154.7</v>
       </c>
       <c r="G16" t="n">
-        <v>63.69</v>
+        <v>60.06</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12107,8 +12611,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6400</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
@@ -12295,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="F2" t="n">
-        <v>51.56</v>
+        <v>53.15</v>
       </c>
       <c r="G2" t="n">
-        <v>14.33</v>
+        <v>14.77</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12317,8 +12825,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1620</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
@@ -12370,10 +12882,10 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>21.44</v>
+        <v>21.47</v>
       </c>
       <c r="G3" t="n">
         <v>1.07</v>
@@ -12392,8 +12904,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
@@ -12449,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>5820</v>
+        <v>5310</v>
       </c>
       <c r="F4" t="n">
-        <v>131.35</v>
+        <v>119.84</v>
       </c>
       <c r="G4" t="n">
-        <v>36.22</v>
+        <v>33.04</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12471,8 +12987,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>-8.76</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5820</v>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
@@ -12524,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="F5" t="n">
-        <v>83.58</v>
+        <v>79.98</v>
       </c>
       <c r="G5" t="n">
-        <v>32.83</v>
+        <v>31.42</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -12546,8 +13066,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5345</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
@@ -12599,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="F6" t="n">
-        <v>45.62</v>
+        <v>45.42</v>
       </c>
       <c r="G6" t="n">
-        <v>23.92</v>
+        <v>23.82</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -12621,8 +13145,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M6" t="n">
+        <v>697</v>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
@@ -12678,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.89</v>
+        <v>11.87</v>
       </c>
       <c r="G7" t="n">
         <v>1.66</v>
@@ -12700,8 +13228,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M7" t="n">
+        <v>96.8</v>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
@@ -12753,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>152.5</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>11.73</v>
+        <v>11.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -12775,8 +13307,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M8" t="n">
+        <v>152.5</v>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
@@ -12832,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -12854,8 +13390,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="M9" t="n">
+        <v>106.5</v>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
@@ -12907,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>954</v>
+        <v>915</v>
       </c>
       <c r="F10" t="n">
-        <v>25.81</v>
+        <v>24.76</v>
       </c>
       <c r="G10" t="n">
-        <v>3.97</v>
+        <v>3.81</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -12929,8 +13469,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="M10" t="n">
+        <v>954</v>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
@@ -12986,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F11" t="n">
-        <v>27.13</v>
+        <v>26.86</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13008,8 +13552,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="M11" t="n">
+        <v>197</v>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
@@ -13065,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3590</v>
+        <v>3355</v>
       </c>
       <c r="F12" t="n">
-        <v>52.65</v>
+        <v>49.21</v>
       </c>
       <c r="G12" t="n">
-        <v>5.13</v>
+        <v>4.79</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13087,8 +13635,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3590</v>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="F2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>22.15</v>
+        <v>23.61</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.21</v>
+        <v>6.56</v>
       </c>
       <c r="M2" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5440</v>
+        <v>5600</v>
       </c>
       <c r="F5" t="n">
-        <v>116.49</v>
+        <v>119.91</v>
       </c>
       <c r="G5" t="n">
-        <v>33.51</v>
+        <v>34.5</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.77</v>
+        <v>2.94</v>
       </c>
       <c r="M5" t="n">
-        <v>5595</v>
+        <v>5440</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44</v>
+        <v>23.53</v>
       </c>
       <c r="G6" t="n">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.06</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>121.5</v>
+        <v>124</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F7" t="n">
-        <v>27.29</v>
+        <v>27.34</v>
       </c>
       <c r="G7" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.68</v>
+        <v>21.75</v>
       </c>
       <c r="G8" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.73</v>
+        <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>25.91</v>
+        <v>25.55</v>
       </c>
       <c r="G9" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>-1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>17.33</v>
+        <v>17.67</v>
       </c>
       <c r="G10" t="n">
-        <v>6.14</v>
+        <v>6.26</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.29</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1280</v>
+        <v>1240</v>
       </c>
       <c r="F11" t="n">
-        <v>24.59</v>
+        <v>23.82</v>
       </c>
       <c r="G11" t="n">
-        <v>4.67</v>
+        <v>4.52</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.79</v>
+        <v>-3.12</v>
       </c>
       <c r="M11" t="n">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>157.5</v>
+        <v>159</v>
       </c>
       <c r="F12" t="n">
-        <v>19.64</v>
+        <v>19.83</v>
       </c>
       <c r="G12" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="M12" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F13" t="n">
-        <v>32.05</v>
+        <v>32.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.49</v>
+        <v>6.56</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.26</v>
+        <v>1.09</v>
       </c>
       <c r="M13" t="n">
-        <v>277.5</v>
+        <v>274</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>215.5</v>
+        <v>215</v>
       </c>
       <c r="F15" t="n">
-        <v>19.41</v>
+        <v>19.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="M15" t="n">
-        <v>216.5</v>
+        <v>215.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6035</v>
+        <v>6170</v>
       </c>
       <c r="F16" t="n">
-        <v>154.7</v>
+        <v>158.16</v>
       </c>
       <c r="G16" t="n">
-        <v>60.06</v>
+        <v>61.41</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-5.7</v>
+        <v>2.24</v>
       </c>
       <c r="M16" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1510</v>
+        <v>1575</v>
       </c>
       <c r="F17" t="n">
-        <v>44.67</v>
+        <v>46.6</v>
       </c>
       <c r="G17" t="n">
-        <v>9.07</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-5.03</v>
+        <v>4.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1590</v>
+        <v>1510</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>11715</v>
+        <v>12045</v>
       </c>
       <c r="F18" t="n">
-        <v>64.58</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>33.07</v>
+        <v>34.01</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-2.29</v>
+        <v>2.82</v>
       </c>
       <c r="M18" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="F19" t="n">
-        <v>62.5</v>
+        <v>63.01</v>
       </c>
       <c r="G19" t="n">
-        <v>12.13</v>
+        <v>12.23</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-2.39</v>
+        <v>0.82</v>
       </c>
       <c r="M19" t="n">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>44.95</v>
+        <v>46.15</v>
       </c>
       <c r="G20" t="n">
-        <v>6.72</v>
+        <v>6.9</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.97</v>
+        <v>2.69</v>
       </c>
       <c r="M20" t="n">
-        <v>84.3</v>
+        <v>81.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="F21" t="n">
-        <v>103.31</v>
+        <v>101.67</v>
       </c>
       <c r="G21" t="n">
-        <v>26.68</v>
+        <v>26.25</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-4.39</v>
+        <v>-1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>6600</v>
+        <v>6310</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="F22" t="n">
-        <v>53.06</v>
+        <v>53.32</v>
       </c>
       <c r="G22" t="n">
-        <v>26.71</v>
+        <v>26.84</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.8</v>
+        <v>0.48</v>
       </c>
       <c r="M22" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.35</v>
+        <v>18.25</v>
       </c>
       <c r="F23" t="n">
-        <v>41.7</v>
+        <v>41.48</v>
       </c>
       <c r="G23" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.27</v>
+        <v>-0.54</v>
       </c>
       <c r="M23" t="n">
-        <v>18.4</v>
+        <v>18.35</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1370</v>
+        <v>1415</v>
       </c>
       <c r="F24" t="n">
-        <v>69.58</v>
+        <v>71.86</v>
       </c>
       <c r="G24" t="n">
-        <v>16.98</v>
+        <v>17.54</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-2.84</v>
+        <v>3.28</v>
       </c>
       <c r="M24" t="n">
-        <v>1410</v>
+        <v>1370</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>44.95</v>
+        <v>49.4</v>
       </c>
       <c r="F25" t="n">
-        <v>54.82</v>
+        <v>60.24</v>
       </c>
       <c r="G25" t="n">
-        <v>3.74</v>
+        <v>4.11</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-0.44</v>
+        <v>9.9</v>
       </c>
       <c r="M25" t="n">
-        <v>45.15</v>
+        <v>44.95</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2675</v>
+        <v>2805</v>
       </c>
       <c r="F26" t="n">
-        <v>230.21</v>
+        <v>241.39</v>
       </c>
       <c r="G26" t="n">
-        <v>52.44</v>
+        <v>54.99</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-2.55</v>
+        <v>4.86</v>
       </c>
       <c r="M26" t="n">
-        <v>2745</v>
+        <v>2675</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="F27" t="n">
-        <v>42.84</v>
+        <v>43.78</v>
       </c>
       <c r="G27" t="n">
-        <v>6.69</v>
+        <v>6.84</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-3.27</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1190</v>
+        <v>1205</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="F29" t="n">
-        <v>83.31</v>
+        <v>89.53</v>
       </c>
       <c r="G29" t="n">
-        <v>16.32</v>
+        <v>17.54</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-6.95</v>
+        <v>7.47</v>
       </c>
       <c r="M29" t="n">
-        <v>547</v>
+        <v>509</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3255</v>
+        <v>3230</v>
       </c>
       <c r="F30" t="n">
-        <v>76.77</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>10.58</v>
+        <v>10.5</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-3.56</v>
+        <v>-0.77</v>
       </c>
       <c r="M30" t="n">
-        <v>3375</v>
+        <v>3255</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>492.5</v>
+        <v>541</v>
       </c>
       <c r="F31" t="n">
-        <v>99.90000000000001</v>
+        <v>109.74</v>
       </c>
       <c r="G31" t="n">
-        <v>12.85</v>
+        <v>14.11</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-3.24</v>
+        <v>9.85</v>
       </c>
       <c r="M31" t="n">
-        <v>509</v>
+        <v>492.5</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="F32" t="n">
-        <v>43.38</v>
+        <v>44.02</v>
       </c>
       <c r="G32" t="n">
-        <v>10.76</v>
+        <v>10.92</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.24</v>
+        <v>1.46</v>
       </c>
       <c r="M32" t="n">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F33" t="n">
-        <v>36.16</v>
+        <v>36.09</v>
       </c>
       <c r="G33" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-1.47</v>
+        <v>-0.19</v>
       </c>
       <c r="M33" t="n">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4430</v>
+        <v>4530</v>
       </c>
       <c r="F34" t="n">
-        <v>73.16</v>
+        <v>74.81</v>
       </c>
       <c r="G34" t="n">
-        <v>16.67</v>
+        <v>17.04</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-2.85</v>
+        <v>2.26</v>
       </c>
       <c r="M34" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1670</v>
+        <v>1710</v>
       </c>
       <c r="F35" t="n">
-        <v>53.15</v>
+        <v>54.42</v>
       </c>
       <c r="G35" t="n">
-        <v>14.77</v>
+        <v>15.12</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.09</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>21.47</v>
+        <v>21.65</v>
       </c>
       <c r="G36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.14</v>
+        <v>0.82</v>
       </c>
       <c r="M36" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>5310</v>
+        <v>5240</v>
       </c>
       <c r="F37" t="n">
-        <v>119.84</v>
+        <v>118.26</v>
       </c>
       <c r="G37" t="n">
-        <v>33.04</v>
+        <v>32.61</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-8.76</v>
+        <v>-1.32</v>
       </c>
       <c r="M37" t="n">
-        <v>5820</v>
+        <v>5310</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>5115</v>
+        <v>5085</v>
       </c>
       <c r="F38" t="n">
-        <v>79.98</v>
+        <v>79.52</v>
       </c>
       <c r="G38" t="n">
-        <v>31.42</v>
+        <v>31.23</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-4.3</v>
+        <v>-0.59</v>
       </c>
       <c r="M38" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="F39" t="n">
-        <v>45.42</v>
+        <v>46.2</v>
       </c>
       <c r="G39" t="n">
-        <v>23.82</v>
+        <v>24.23</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.43</v>
+        <v>1.73</v>
       </c>
       <c r="M39" t="n">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="F40" t="n">
-        <v>11.87</v>
+        <v>11.89</v>
       </c>
       <c r="G40" t="n">
         <v>1.66</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-0.21</v>
+        <v>0.21</v>
       </c>
       <c r="M40" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F41" t="n">
-        <v>11.92</v>
+        <v>11.77</v>
       </c>
       <c r="G41" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.64</v>
+        <v>-1.29</v>
       </c>
       <c r="M41" t="n">
-        <v>152.5</v>
+        <v>155</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>915</v>
+        <v>1005</v>
       </c>
       <c r="F43" t="n">
-        <v>24.76</v>
+        <v>27.19</v>
       </c>
       <c r="G43" t="n">
-        <v>3.81</v>
+        <v>4.19</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-4.09</v>
+        <v>9.84</v>
       </c>
       <c r="M43" t="n">
-        <v>954</v>
+        <v>915</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,10 +3929,10 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>195</v>
+        <v>195.5</v>
       </c>
       <c r="F44" t="n">
-        <v>26.86</v>
+        <v>26.93</v>
       </c>
       <c r="G44" t="n">
         <v>2.63</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-1.02</v>
+        <v>0.26</v>
       </c>
       <c r="M44" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3355</v>
+        <v>3345</v>
       </c>
       <c r="F45" t="n">
-        <v>49.21</v>
+        <v>49.06</v>
       </c>
       <c r="G45" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-6.55</v>
+        <v>-0.3</v>
       </c>
       <c r="M45" t="n">
-        <v>3590</v>
+        <v>3355</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>208</v>
+        <v>210.5</v>
       </c>
       <c r="F46" t="n">
-        <v>21.18</v>
+        <v>21.44</v>
       </c>
       <c r="G46" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M46" t="n">
-        <v>210.5</v>
+        <v>208</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>63</v>
       </c>
       <c r="E47" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F47" t="n">
-        <v>24.32</v>
+        <v>23.99</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="M47" t="n">
         <v>222</v>
@@ -4249,13 +4249,13 @@
         <v>61</v>
       </c>
       <c r="E48" t="n">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="F48" t="n">
-        <v>25.49</v>
+        <v>26.11</v>
       </c>
       <c r="G48" t="n">
-        <v>7.19</v>
+        <v>7.36</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-1.4</v>
+        <v>2.42</v>
       </c>
       <c r="M48" t="n">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4313,12 +4313,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4327,20 +4327,20 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>6055</v>
+        <v>107.5</v>
       </c>
       <c r="F49" t="n">
-        <v>32.2</v>
+        <v>20.06</v>
       </c>
       <c r="G49" t="n">
-        <v>4.13</v>
+        <v>2.49</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>186.3</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="M49" t="n">
-        <v>5995</v>
+        <v>106</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4361,28 +4361,28 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="R49" t="n">
-        <v>6.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S49" t="n">
-        <v>41.8</v>
+        <v>37</v>
       </c>
       <c r="T49" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4394,71 +4394,73 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="E50" t="n">
-        <v>518</v>
+        <v>6225</v>
       </c>
       <c r="F50" t="n">
-        <v>23.46</v>
+        <v>33.11</v>
       </c>
       <c r="G50" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="H50" t="n">
-        <v>29.3</v>
-      </c>
+        <v>4.25</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.87</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-0.38</v>
+        <v>2.81</v>
       </c>
       <c r="M50" t="n">
-        <v>520</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+        <v>6055</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P50" t="n">
-        <v>19.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.94</v>
+        <v>1.21</v>
       </c>
       <c r="R50" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="S50" t="n">
-        <v>64.90000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="T50" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.87</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4466,19 +4468,19 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4487,25 +4489,25 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E51" t="n">
-        <v>664</v>
+        <v>521</v>
       </c>
       <c r="F51" t="n">
-        <v>40.74</v>
+        <v>23.6</v>
       </c>
       <c r="G51" t="n">
-        <v>5.47</v>
+        <v>6.43</v>
       </c>
       <c r="H51" t="n">
-        <v>46.1</v>
+        <v>29.3</v>
       </c>
       <c r="I51" t="n">
-        <v>30.6</v>
+        <v>18.6</v>
       </c>
       <c r="J51" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4513,78 +4515,78 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-2.78</v>
+        <v>0.58</v>
       </c>
       <c r="M51" t="n">
-        <v>683</v>
+        <v>518</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R51" t="n">
-        <v>24.8</v>
+        <v>10.6</v>
       </c>
       <c r="S51" t="n">
-        <v>1.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T51" t="n">
-        <v>60.2</v>
+        <v>34.7</v>
       </c>
       <c r="U51" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E52" t="n">
-        <v>57.4</v>
+        <v>671</v>
       </c>
       <c r="F52" t="n">
-        <v>15.77</v>
+        <v>41.17</v>
       </c>
       <c r="G52" t="n">
-        <v>2.4</v>
+        <v>5.52</v>
       </c>
       <c r="H52" t="n">
-        <v>17.3</v>
+        <v>46.1</v>
       </c>
       <c r="I52" t="n">
-        <v>11.8</v>
+        <v>30.6</v>
       </c>
       <c r="J52" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4592,30 +4594,30 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M52" t="n">
-        <v>57.4</v>
+        <v>664</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>11.3</v>
+        <v>15.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="R52" t="n">
-        <v>4.4</v>
+        <v>24.8</v>
       </c>
       <c r="S52" t="n">
-        <v>768.2</v>
+        <v>1.5</v>
       </c>
       <c r="T52" t="n">
-        <v>19.4</v>
+        <v>60.2</v>
       </c>
       <c r="U52" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -4624,19 +4626,19 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4645,25 +4647,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E53" t="n">
-        <v>183.5</v>
+        <v>58.5</v>
       </c>
       <c r="F53" t="n">
-        <v>16.76</v>
+        <v>16.07</v>
       </c>
       <c r="G53" t="n">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="H53" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="I53" t="n">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="J53" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4671,34 +4673,34 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-2.39</v>
+        <v>1.92</v>
       </c>
       <c r="M53" t="n">
-        <v>188</v>
+        <v>57.4</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.03</v>
+        <v>1.15</v>
       </c>
       <c r="R53" t="n">
-        <v>30.2</v>
+        <v>4.4</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>768.2</v>
       </c>
       <c r="T53" t="n">
-        <v>16.9</v>
+        <v>19.4</v>
       </c>
       <c r="U53" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -4710,89 +4712,91 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E54" t="n">
-        <v>318.5</v>
+        <v>181</v>
       </c>
       <c r="F54" t="n">
-        <v>16.49</v>
+        <v>16.53</v>
       </c>
       <c r="G54" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I54" t="n">
-        <v>49</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-2.3</v>
+        <v>-1.36</v>
       </c>
       <c r="M54" t="n">
-        <v>326</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>183.5</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.09</v>
+        <v>4.03</v>
       </c>
       <c r="R54" t="n">
-        <v>24.2</v>
+        <v>30.2</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="n">
-        <v>24</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4801,20 +4805,20 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E55" t="n">
-        <v>162</v>
+        <v>326.5</v>
       </c>
       <c r="F55" t="n">
-        <v>18.22</v>
+        <v>16.91</v>
       </c>
       <c r="G55" t="n">
-        <v>3.84</v>
+        <v>4.79</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>57.1</v>
+        <v>49</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -4823,10 +4827,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.92</v>
+        <v>2.51</v>
       </c>
       <c r="M55" t="n">
-        <v>163.5</v>
+        <v>318.5</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4835,24 +4839,24 @@
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>18.6</v>
+        <v>29.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="R55" t="n">
-        <v>11.1</v>
+        <v>24.2</v>
       </c>
       <c r="S55" t="n">
-        <v>3.6</v>
+        <v>25</v>
       </c>
       <c r="T55" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -4864,34 +4868,34 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E56" t="n">
-        <v>117</v>
+        <v>162.5</v>
       </c>
       <c r="F56" t="n">
-        <v>19.02</v>
+        <v>18.28</v>
       </c>
       <c r="G56" t="n">
-        <v>2.81</v>
+        <v>3.86</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>11</v>
+        <v>57.1</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -4900,10 +4904,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-2.09</v>
+        <v>0.31</v>
       </c>
       <c r="M56" t="n">
-        <v>119.5</v>
+        <v>162</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4912,24 +4916,24 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>10.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.4</v>
+        <v>2.74</v>
       </c>
       <c r="R56" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="S56" t="n">
-        <v>48.7</v>
+        <v>3.6</v>
       </c>
       <c r="T56" t="n">
-        <v>28.4</v>
+        <v>22</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -4941,12 +4945,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4958,17 +4962,17 @@
         <v>78</v>
       </c>
       <c r="E57" t="n">
-        <v>85.3</v>
+        <v>117.5</v>
       </c>
       <c r="F57" t="n">
-        <v>16.28</v>
+        <v>19.11</v>
       </c>
       <c r="G57" t="n">
-        <v>1.66</v>
+        <v>2.82</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4977,40 +4981,36 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-1.16</v>
+        <v>0.43</v>
       </c>
       <c r="M57" t="n">
-        <v>86.3</v>
+        <v>117</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S57" t="n">
-        <v>-2.7</v>
+        <v>48.7</v>
       </c>
       <c r="T57" t="n">
-        <v>20.3</v>
+        <v>28.4</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5022,12 +5022,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5036,20 +5036,20 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>154</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>17.17</v>
+        <v>16.87</v>
       </c>
       <c r="G58" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.98</v>
+        <v>3.63</v>
       </c>
       <c r="M58" t="n">
-        <v>152.5</v>
+        <v>85.3</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5070,23 +5070,23 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>ROE5低</t>
+          <t>月營收轉負-3%</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>5.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="R58" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>14.6</v>
+        <v>-2.7</v>
       </c>
       <c r="T58" t="n">
-        <v>34.2</v>
+        <v>20.3</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
@@ -5103,12 +5103,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5117,20 +5117,20 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>227</v>
+        <v>156.5</v>
       </c>
       <c r="F59" t="n">
-        <v>14.11</v>
+        <v>17.45</v>
       </c>
       <c r="G59" t="n">
-        <v>5.13</v>
+        <v>1.72</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5139,36 +5139,40 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.44</v>
+        <v>1.62</v>
       </c>
       <c r="M59" t="n">
-        <v>226</v>
+        <v>154</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P59" t="n">
-        <v>30.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="R59" t="n">
-        <v>20.4</v>
+        <v>22.1</v>
       </c>
       <c r="S59" t="n">
-        <v>812.4</v>
+        <v>14.6</v>
       </c>
       <c r="T59" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -5180,12 +5184,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5194,20 +5198,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>180</v>
+        <v>233</v>
       </c>
       <c r="F60" t="n">
-        <v>15.19</v>
+        <v>14.48</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81</v>
+        <v>5.26</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>49.2</v>
+        <v>9.6</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5216,10 +5220,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-0.55</v>
+        <v>2.64</v>
       </c>
       <c r="M60" t="n">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5228,24 +5232,24 @@
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>14.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>20.4</v>
       </c>
       <c r="S60" t="n">
-        <v>10.3</v>
+        <v>812.4</v>
       </c>
       <c r="T60" t="n">
-        <v>20.2</v>
+        <v>34.6</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5257,12 +5261,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5271,20 +5275,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>696</v>
+        <v>184</v>
       </c>
       <c r="F61" t="n">
-        <v>16.08</v>
+        <v>15.53</v>
       </c>
       <c r="G61" t="n">
-        <v>12.98</v>
+        <v>1.85</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>-8.1</v>
+        <v>49.2</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -5293,35 +5297,31 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-0.43</v>
+        <v>2.22</v>
       </c>
       <c r="M61" t="n">
-        <v>699</v>
+        <v>180</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>94.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="R61" t="n">
-        <v>18.2</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="T61" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
@@ -5338,33 +5338,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>465.5</v>
+        <v>708</v>
       </c>
       <c r="F62" t="n">
-        <v>18.06</v>
+        <v>16.36</v>
       </c>
       <c r="G62" t="n">
-        <v>4.98</v>
+        <v>13.2</v>
       </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>-8.1</v>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
@@ -5372,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-1.59</v>
+        <v>1.72</v>
       </c>
       <c r="M62" t="n">
-        <v>473</v>
+        <v>696</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5384,28 +5386,28 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>17.9</v>
+        <v>94.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="R62" t="n">
-        <v>-6.1</v>
+        <v>18.2</v>
       </c>
       <c r="S62" t="n">
-        <v>730.1</v>
+        <v>12</v>
       </c>
       <c r="T62" t="n">
-        <v>45.2</v>
+        <v>19.6</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5417,12 +5419,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5431,21 +5433,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>106</v>
+        <v>492.5</v>
       </c>
       <c r="F63" t="n">
-        <v>19.78</v>
+        <v>19.11</v>
       </c>
       <c r="G63" t="n">
-        <v>2.46</v>
+        <v>5.27</v>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
-        <v>186.3</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.47</v>
+        <v>5.8</v>
       </c>
       <c r="M63" t="n">
-        <v>105.5</v>
+        <v>465.5</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>10.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="R63" t="n">
-        <v>-3.4</v>
+        <v>-6.1</v>
       </c>
       <c r="S63" t="n">
-        <v>37</v>
+        <v>730.1</v>
       </c>
       <c r="T63" t="n">
-        <v>35.8</v>
+        <v>45.2</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>159.5</v>
+        <v>169</v>
       </c>
       <c r="F64" t="n">
-        <v>17.59</v>
+        <v>18.63</v>
       </c>
       <c r="G64" t="n">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-0.31</v>
+        <v>5.96</v>
       </c>
       <c r="M64" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>97</v>
       </c>
       <c r="E65" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F65" t="n">
-        <v>16.39</v>
+        <v>16.7</v>
       </c>
       <c r="G65" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="H65" t="n">
         <v>14.7</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.97</v>
+        <v>1.92</v>
       </c>
       <c r="M65" t="n">
-        <v>154.5</v>
+        <v>156</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5752,13 +5752,13 @@
         <v>91</v>
       </c>
       <c r="E67" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="F67" t="n">
-        <v>15.31</v>
+        <v>15.37</v>
       </c>
       <c r="G67" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="H67" t="n">
         <v>15</v>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="M67" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5831,13 +5831,13 @@
         <v>90</v>
       </c>
       <c r="E68" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F68" t="n">
-        <v>24.68</v>
+        <v>24.94</v>
       </c>
       <c r="G68" t="n">
-        <v>6.35</v>
+        <v>6.41</v>
       </c>
       <c r="H68" t="n">
         <v>27.5</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.68</v>
+        <v>1.03</v>
       </c>
       <c r="M68" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5910,10 +5910,10 @@
         <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
       <c r="G69" t="n">
         <v>2.04</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.24</v>
+        <v>-0.24</v>
       </c>
       <c r="M69" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5989,13 +5989,13 @@
         <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F70" t="n">
-        <v>17.13</v>
+        <v>17.41</v>
       </c>
       <c r="G70" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="H70" t="n">
         <v>16.4</v>
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-0.4</v>
+        <v>1.63</v>
       </c>
       <c r="M70" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
@@ -6072,13 +6072,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>246.5</v>
+        <v>248</v>
       </c>
       <c r="F71" t="n">
-        <v>16.25</v>
+        <v>16.35</v>
       </c>
       <c r="G71" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H71" t="n">
         <v>15.3</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.8</v>
+        <v>0.61</v>
       </c>
       <c r="M71" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>76</v>
       </c>
       <c r="E72" t="n">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="F72" t="n">
-        <v>45.11</v>
+        <v>44.47</v>
       </c>
       <c r="G72" t="n">
-        <v>24.09</v>
+        <v>23.75</v>
       </c>
       <c r="H72" t="n">
         <v>38.8</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-6.99</v>
+        <v>-1.41</v>
       </c>
       <c r="M72" t="n">
-        <v>1145</v>
+        <v>1065</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6232,13 +6232,13 @@
         <v>68</v>
       </c>
       <c r="E73" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="F73" t="n">
-        <v>19.52</v>
+        <v>19.9</v>
       </c>
       <c r="G73" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="H73" t="n">
         <v>21.3</v>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1.94</v>
+        <v>1.98</v>
       </c>
       <c r="M73" t="n">
-        <v>61.7</v>
+        <v>60.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6315,13 +6315,13 @@
         <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>3115</v>
+        <v>3175</v>
       </c>
       <c r="F74" t="n">
-        <v>41.52</v>
+        <v>42.32</v>
       </c>
       <c r="G74" t="n">
-        <v>22.16</v>
+        <v>22.59</v>
       </c>
       <c r="H74" t="n">
         <v>24.6</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-5.89</v>
+        <v>1.93</v>
       </c>
       <c r="M74" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -6394,13 +6394,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="F75" t="n">
-        <v>14.36</v>
+        <v>14.24</v>
       </c>
       <c r="G75" t="n">
-        <v>8.119999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H75" t="n">
         <v>14.2</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.42</v>
+        <v>-0.84</v>
       </c>
       <c r="M75" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6473,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2385</v>
+        <v>2380</v>
       </c>
       <c r="F76" t="n">
-        <v>27.65</v>
+        <v>27.59</v>
       </c>
       <c r="G76" t="n">
-        <v>9.609999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="H76" t="n">
         <v>23.6</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.21</v>
+        <v>-0.21</v>
       </c>
       <c r="M76" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6552,13 +6552,13 @@
         <v>97</v>
       </c>
       <c r="E77" t="n">
-        <v>118.5</v>
+        <v>119.5</v>
       </c>
       <c r="F77" t="n">
-        <v>16.9</v>
+        <v>17.05</v>
       </c>
       <c r="G77" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="H77" t="n">
         <v>12.4</v>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>0.84</v>
       </c>
       <c r="M77" t="n">
-        <v>116.5</v>
+        <v>118.5</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6631,13 +6631,13 @@
         <v>94</v>
       </c>
       <c r="E78" t="n">
-        <v>105.5</v>
+        <v>108</v>
       </c>
       <c r="F78" t="n">
-        <v>13.06</v>
+        <v>13.37</v>
       </c>
       <c r="G78" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H78" t="n">
         <v>12.3</v>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="M78" t="n">
-        <v>106.5</v>
+        <v>105.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>25.2</v>
+        <v>25.15</v>
       </c>
       <c r="F79" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="G79" t="n">
         <v>0.97</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="M79" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6789,13 +6789,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="F80" t="n">
-        <v>12.15</v>
+        <v>12.21</v>
       </c>
       <c r="G80" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H80" t="n">
         <v>10.7</v>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-1.86</v>
+        <v>0.47</v>
       </c>
       <c r="M80" t="n">
-        <v>107.5</v>
+        <v>105.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6868,13 +6868,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="F81" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="G81" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="H81" t="n">
         <v>11.4</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.28</v>
+        <v>0.85</v>
       </c>
       <c r="M81" t="n">
-        <v>177</v>
+        <v>176.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         <v>92</v>
       </c>
       <c r="E82" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="F82" t="n">
-        <v>8.67</v>
+        <v>8.69</v>
       </c>
       <c r="G82" t="n">
         <v>1.6</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-2.02</v>
+        <v>0.24</v>
       </c>
       <c r="M82" t="n">
-        <v>42.05</v>
+        <v>41.2</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7026,13 +7026,13 @@
         <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="F83" t="n">
-        <v>22.91</v>
+        <v>23.15</v>
       </c>
       <c r="G83" t="n">
-        <v>8.779999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H83" t="n">
         <v>25</v>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.35</v>
+        <v>1.03</v>
       </c>
       <c r="M83" t="n">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7105,13 +7105,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>490.5</v>
+        <v>504</v>
       </c>
       <c r="F84" t="n">
-        <v>21.02</v>
+        <v>21.59</v>
       </c>
       <c r="G84" t="n">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="H84" t="n">
         <v>21.2</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-3.82</v>
+        <v>2.75</v>
       </c>
       <c r="M84" t="n">
-        <v>510</v>
+        <v>490.5</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7184,13 +7184,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>158</v>
+        <v>160.5</v>
       </c>
       <c r="F85" t="n">
-        <v>16.99</v>
+        <v>17.26</v>
       </c>
       <c r="G85" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="H85" t="n">
         <v>14.1</v>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-3.07</v>
+        <v>1.58</v>
       </c>
       <c r="M85" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7263,10 +7263,10 @@
         <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>38.45</v>
+        <v>38.55</v>
       </c>
       <c r="F86" t="n">
-        <v>7.93</v>
+        <v>7.95</v>
       </c>
       <c r="G86" t="n">
         <v>1.09</v>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-0.65</v>
+        <v>0.26</v>
       </c>
       <c r="M86" t="n">
-        <v>38.7</v>
+        <v>38.45</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-1.87</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
@@ -7425,13 +7425,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1260</v>
+        <v>1360</v>
       </c>
       <c r="F88" t="n">
-        <v>29.06</v>
+        <v>31.37</v>
       </c>
       <c r="G88" t="n">
-        <v>8.84</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H88" t="n">
         <v>21.8</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-3.45</v>
+        <v>7.94</v>
       </c>
       <c r="M88" t="n">
-        <v>1305</v>
+        <v>1260</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7508,10 +7508,10 @@
         <v>79</v>
       </c>
       <c r="E89" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="F89" t="n">
-        <v>8.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G89" t="n">
         <v>2.13</v>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-1.23</v>
+        <v>0.23</v>
       </c>
       <c r="M89" t="n">
-        <v>89.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7591,13 +7591,13 @@
         <v>78</v>
       </c>
       <c r="E90" t="n">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="F90" t="n">
-        <v>8.01</v>
+        <v>8.18</v>
       </c>
       <c r="G90" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="H90" t="n">
         <v>6.8</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.19</v>
+        <v>2.07</v>
       </c>
       <c r="M90" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7757,13 +7757,13 @@
         <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>333</v>
+        <v>340.5</v>
       </c>
       <c r="F92" t="n">
-        <v>14.51</v>
+        <v>14.84</v>
       </c>
       <c r="G92" t="n">
-        <v>5.27</v>
+        <v>5.39</v>
       </c>
       <c r="H92" t="n">
         <v>13.2</v>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.15</v>
+        <v>2.25</v>
       </c>
       <c r="M92" t="n">
-        <v>332.5</v>
+        <v>333</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7840,13 +7840,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>2315</v>
+        <v>2165</v>
       </c>
       <c r="F93" t="n">
-        <v>7.42</v>
+        <v>6.94</v>
       </c>
       <c r="G93" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="H93" t="n">
         <v>9.6</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.98</v>
+        <v>-6.48</v>
       </c>
       <c r="M93" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7923,13 +7923,13 @@
         <v>62</v>
       </c>
       <c r="E94" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="F94" t="n">
-        <v>14.5</v>
+        <v>14.54</v>
       </c>
       <c r="G94" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="H94" t="n">
         <v>10</v>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.83</v>
+        <v>0.27</v>
       </c>
       <c r="M94" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8006,13 +8006,13 @@
         <v>60</v>
       </c>
       <c r="E95" t="n">
-        <v>1370</v>
+        <v>1475</v>
       </c>
       <c r="F95" t="n">
-        <v>14.61</v>
+        <v>15.73</v>
       </c>
       <c r="G95" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="H95" t="n">
         <v>11.9</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.37</v>
+        <v>7.66</v>
       </c>
       <c r="M95" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8089,13 +8089,13 @@
         <v>79</v>
       </c>
       <c r="E96" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="F96" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="G96" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-0.58</v>
+        <v>0.14</v>
       </c>
       <c r="M96" t="n">
-        <v>69.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         <v>77</v>
       </c>
       <c r="E97" t="n">
-        <v>388.5</v>
+        <v>399.5</v>
       </c>
       <c r="F97" t="n">
-        <v>5.02</v>
+        <v>5.16</v>
       </c>
       <c r="G97" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-2.39</v>
+        <v>2.83</v>
       </c>
       <c r="M97" t="n">
-        <v>398</v>
+        <v>388.5</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>23.45</v>
+        <v>23.65</v>
       </c>
       <c r="F98" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="G98" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="M98" t="n">
-        <v>23.65</v>
+        <v>23.45</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>75</v>
       </c>
       <c r="E99" t="n">
-        <v>34.85</v>
+        <v>34.8</v>
       </c>
       <c r="F99" t="n">
         <v>3.75</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-2.52</v>
+        <v>-0.14</v>
       </c>
       <c r="M99" t="n">
-        <v>35.75</v>
+        <v>34.85</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>69</v>
       </c>
       <c r="E100" t="n">
-        <v>199.5</v>
+        <v>210</v>
       </c>
       <c r="F100" t="n">
-        <v>4.96</v>
+        <v>5.22</v>
       </c>
       <c r="G100" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-1.24</v>
+        <v>5.26</v>
       </c>
       <c r="M100" t="n">
-        <v>202</v>
+        <v>199.5</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>32</v>
       </c>
       <c r="E101" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="F101" t="n">
-        <v>11.51</v>
+        <v>11.53</v>
       </c>
       <c r="G101" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-0.96</v>
+        <v>0.21</v>
       </c>
       <c r="M101" t="n">
-        <v>47.05</v>
+        <v>46.6</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3115</v>
+        <v>3175</v>
       </c>
       <c r="F2" t="n">
-        <v>41.52</v>
+        <v>42.32</v>
       </c>
       <c r="G2" t="n">
-        <v>22.16</v>
+        <v>22.59</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-5.89</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="F3" t="n">
-        <v>14.36</v>
+        <v>14.24</v>
       </c>
       <c r="G3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>-0.84</v>
       </c>
       <c r="M3" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2385</v>
+        <v>2380</v>
       </c>
       <c r="F4" t="n">
-        <v>27.65</v>
+        <v>27.59</v>
       </c>
       <c r="G4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.21</v>
+        <v>-0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>118.5</v>
+        <v>119.5</v>
       </c>
       <c r="F5" t="n">
-        <v>16.9</v>
+        <v>17.05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>0.84</v>
       </c>
       <c r="M5" t="n">
-        <v>116.5</v>
+        <v>118.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>105.5</v>
+        <v>108</v>
       </c>
       <c r="F6" t="n">
-        <v>13.06</v>
+        <v>13.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.37</v>
       </c>
       <c r="M6" t="n">
-        <v>106.5</v>
+        <v>105.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,10 +9097,10 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.2</v>
+        <v>25.15</v>
       </c>
       <c r="F7" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="G7" t="n">
         <v>0.97</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
-        <v>12.15</v>
+        <v>12.21</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.86</v>
+        <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>107.5</v>
+        <v>105.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="F9" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.28</v>
+        <v>0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>177</v>
+        <v>176.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,10 +9334,10 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="F10" t="n">
-        <v>8.67</v>
+        <v>8.69</v>
       </c>
       <c r="G10" t="n">
         <v>1.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.02</v>
+        <v>0.24</v>
       </c>
       <c r="M10" t="n">
-        <v>42.05</v>
+        <v>41.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="F11" t="n">
-        <v>22.91</v>
+        <v>23.15</v>
       </c>
       <c r="G11" t="n">
-        <v>8.779999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.35</v>
+        <v>1.03</v>
       </c>
       <c r="M11" t="n">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>490.5</v>
+        <v>504</v>
       </c>
       <c r="F12" t="n">
-        <v>21.02</v>
+        <v>21.59</v>
       </c>
       <c r="G12" t="n">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-3.82</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>510</v>
+        <v>490.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>158</v>
+        <v>160.5</v>
       </c>
       <c r="F13" t="n">
-        <v>16.99</v>
+        <v>17.26</v>
       </c>
       <c r="G13" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-3.07</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.45</v>
+        <v>38.55</v>
       </c>
       <c r="F14" t="n">
-        <v>7.93</v>
+        <v>7.95</v>
       </c>
       <c r="G14" t="n">
         <v>1.09</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.65</v>
+        <v>0.26</v>
       </c>
       <c r="M14" t="n">
-        <v>38.7</v>
+        <v>38.45</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.87</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1260</v>
+        <v>1360</v>
       </c>
       <c r="F16" t="n">
-        <v>29.06</v>
+        <v>31.37</v>
       </c>
       <c r="G16" t="n">
-        <v>8.84</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-3.45</v>
+        <v>7.94</v>
       </c>
       <c r="M16" t="n">
-        <v>1305</v>
+        <v>1260</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,10 +9895,10 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="F17" t="n">
-        <v>8.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>2.13</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-1.23</v>
+        <v>0.23</v>
       </c>
       <c r="M17" t="n">
-        <v>89.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="F18" t="n">
-        <v>8.01</v>
+        <v>8.18</v>
       </c>
       <c r="G18" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.19</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>333</v>
+        <v>340.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.51</v>
+        <v>14.84</v>
       </c>
       <c r="G20" t="n">
-        <v>5.27</v>
+        <v>5.39</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.15</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>332.5</v>
+        <v>333</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2315</v>
+        <v>2165</v>
       </c>
       <c r="F21" t="n">
-        <v>7.42</v>
+        <v>6.94</v>
       </c>
       <c r="G21" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.98</v>
+        <v>-6.48</v>
       </c>
       <c r="M21" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="F22" t="n">
-        <v>14.5</v>
+        <v>14.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.83</v>
+        <v>0.27</v>
       </c>
       <c r="M22" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1370</v>
+        <v>1475</v>
       </c>
       <c r="F23" t="n">
-        <v>14.61</v>
+        <v>15.73</v>
       </c>
       <c r="G23" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.37</v>
+        <v>7.66</v>
       </c>
       <c r="M23" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F2" t="n">
-        <v>16.39</v>
+        <v>16.7</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.97</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>154.5</v>
+        <v>156</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>15.31</v>
+        <v>15.37</v>
       </c>
       <c r="G4" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>119</v>
+        <v>118.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F5" t="n">
-        <v>24.68</v>
+        <v>24.94</v>
       </c>
       <c r="G5" t="n">
-        <v>6.35</v>
+        <v>6.41</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.68</v>
+        <v>1.03</v>
       </c>
       <c r="M5" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,10 +10923,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
       <c r="G6" t="n">
         <v>2.04</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.24</v>
+        <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>17.13</v>
+        <v>17.41</v>
       </c>
       <c r="G7" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.4</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>246.5</v>
+        <v>248</v>
       </c>
       <c r="F8" t="n">
-        <v>16.25</v>
+        <v>16.35</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.8</v>
+        <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="F9" t="n">
-        <v>45.11</v>
+        <v>44.47</v>
       </c>
       <c r="G9" t="n">
-        <v>24.09</v>
+        <v>23.75</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-6.99</v>
+        <v>-1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1145</v>
+        <v>1065</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="F10" t="n">
-        <v>19.52</v>
+        <v>19.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.94</v>
+        <v>1.98</v>
       </c>
       <c r="M10" t="n">
-        <v>61.7</v>
+        <v>60.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="F2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>22.15</v>
+        <v>23.61</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.21</v>
+        <v>6.56</v>
       </c>
       <c r="M2" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5440</v>
+        <v>5600</v>
       </c>
       <c r="F5" t="n">
-        <v>116.49</v>
+        <v>119.91</v>
       </c>
       <c r="G5" t="n">
-        <v>33.51</v>
+        <v>34.5</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.77</v>
+        <v>2.94</v>
       </c>
       <c r="M5" t="n">
-        <v>5595</v>
+        <v>5440</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44</v>
+        <v>23.53</v>
       </c>
       <c r="G6" t="n">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.06</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>121.5</v>
+        <v>124</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F7" t="n">
-        <v>27.29</v>
+        <v>27.34</v>
       </c>
       <c r="G7" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.68</v>
+        <v>21.75</v>
       </c>
       <c r="G8" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.73</v>
+        <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>25.91</v>
+        <v>25.55</v>
       </c>
       <c r="G9" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>-1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>17.33</v>
+        <v>17.67</v>
       </c>
       <c r="G10" t="n">
-        <v>6.14</v>
+        <v>6.26</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.29</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1280</v>
+        <v>1240</v>
       </c>
       <c r="F11" t="n">
-        <v>24.59</v>
+        <v>23.82</v>
       </c>
       <c r="G11" t="n">
-        <v>4.67</v>
+        <v>4.52</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.79</v>
+        <v>-3.12</v>
       </c>
       <c r="M11" t="n">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>157.5</v>
+        <v>159</v>
       </c>
       <c r="F12" t="n">
-        <v>19.64</v>
+        <v>19.83</v>
       </c>
       <c r="G12" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="M12" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F13" t="n">
-        <v>32.05</v>
+        <v>32.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.49</v>
+        <v>6.56</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.26</v>
+        <v>1.09</v>
       </c>
       <c r="M13" t="n">
-        <v>277.5</v>
+        <v>274</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>215.5</v>
+        <v>215</v>
       </c>
       <c r="F15" t="n">
-        <v>19.41</v>
+        <v>19.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="M15" t="n">
-        <v>216.5</v>
+        <v>215.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6035</v>
+        <v>6170</v>
       </c>
       <c r="F16" t="n">
-        <v>154.7</v>
+        <v>158.16</v>
       </c>
       <c r="G16" t="n">
-        <v>60.06</v>
+        <v>61.41</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-5.7</v>
+        <v>2.24</v>
       </c>
       <c r="M16" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1670</v>
+        <v>1710</v>
       </c>
       <c r="F2" t="n">
-        <v>53.15</v>
+        <v>54.42</v>
       </c>
       <c r="G2" t="n">
-        <v>14.77</v>
+        <v>15.12</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.09</v>
+        <v>2.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>21.47</v>
+        <v>21.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>0.82</v>
       </c>
       <c r="M3" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>5310</v>
+        <v>5240</v>
       </c>
       <c r="F4" t="n">
-        <v>119.84</v>
+        <v>118.26</v>
       </c>
       <c r="G4" t="n">
-        <v>33.04</v>
+        <v>32.61</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-8.76</v>
+        <v>-1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>5820</v>
+        <v>5310</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5115</v>
+        <v>5085</v>
       </c>
       <c r="F5" t="n">
-        <v>79.98</v>
+        <v>79.52</v>
       </c>
       <c r="G5" t="n">
-        <v>31.42</v>
+        <v>31.23</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-4.3</v>
+        <v>-0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="F6" t="n">
-        <v>45.42</v>
+        <v>46.2</v>
       </c>
       <c r="G6" t="n">
-        <v>23.82</v>
+        <v>24.23</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.43</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="F7" t="n">
-        <v>11.87</v>
+        <v>11.89</v>
       </c>
       <c r="G7" t="n">
         <v>1.66</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.21</v>
+        <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>11.92</v>
+        <v>11.77</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.64</v>
+        <v>-1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>152.5</v>
+        <v>155</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>915</v>
+        <v>1005</v>
       </c>
       <c r="F10" t="n">
-        <v>24.76</v>
+        <v>27.19</v>
       </c>
       <c r="G10" t="n">
-        <v>3.81</v>
+        <v>4.19</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-4.09</v>
+        <v>9.84</v>
       </c>
       <c r="M10" t="n">
-        <v>954</v>
+        <v>915</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,10 +13530,10 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>195</v>
+        <v>195.5</v>
       </c>
       <c r="F11" t="n">
-        <v>26.86</v>
+        <v>26.93</v>
       </c>
       <c r="G11" t="n">
         <v>2.63</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.02</v>
+        <v>0.26</v>
       </c>
       <c r="M11" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3355</v>
+        <v>3345</v>
       </c>
       <c r="F12" t="n">
-        <v>49.21</v>
+        <v>49.06</v>
       </c>
       <c r="G12" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-6.55</v>
+        <v>-0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3590</v>
+        <v>3355</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="F3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="M3" t="n">
         <v>40.8</v>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="F5" t="n">
-        <v>119.91</v>
+        <v>117.77</v>
       </c>
       <c r="G5" t="n">
-        <v>34.5</v>
+        <v>33.88</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.94</v>
+        <v>-1.79</v>
       </c>
       <c r="M5" t="n">
-        <v>5440</v>
+        <v>5600</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124.5</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>23.53</v>
+        <v>23.44</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>99.8</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
-        <v>27.34</v>
+        <v>27.67</v>
       </c>
       <c r="G7" t="n">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>170.5</v>
+        <v>172.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.75</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>1.17</v>
       </c>
       <c r="M8" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.55</v>
+        <v>25.91</v>
       </c>
       <c r="G9" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>156.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.67</v>
+        <v>17.72</v>
       </c>
       <c r="G10" t="n">
-        <v>6.26</v>
+        <v>6.28</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>0.32</v>
       </c>
       <c r="M10" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="F11" t="n">
-        <v>23.82</v>
+        <v>23.92</v>
       </c>
       <c r="G11" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-3.12</v>
+        <v>0.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1280</v>
+        <v>1240</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F12" t="n">
-        <v>19.83</v>
+        <v>20.32</v>
       </c>
       <c r="G12" t="n">
-        <v>4.17</v>
+        <v>4.28</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.95</v>
+        <v>2.52</v>
       </c>
       <c r="M12" t="n">
-        <v>157.5</v>
+        <v>159</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F13" t="n">
-        <v>32.4</v>
+        <v>32.51</v>
       </c>
       <c r="G13" t="n">
-        <v>6.56</v>
+        <v>6.58</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
       <c r="M13" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>143.5</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>28.19</v>
+        <v>28.49</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M14" t="n">
         <v>143.5</v>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>215</v>
+        <v>217.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.37</v>
+        <v>19.59</v>
       </c>
       <c r="G15" t="n">
-        <v>5.46</v>
+        <v>5.52</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.23</v>
+        <v>1.16</v>
       </c>
       <c r="M15" t="n">
-        <v>215.5</v>
+        <v>215</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6170</v>
+        <v>6500</v>
       </c>
       <c r="F16" t="n">
-        <v>158.16</v>
+        <v>166.62</v>
       </c>
       <c r="G16" t="n">
-        <v>61.41</v>
+        <v>64.69</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.24</v>
+        <v>5.35</v>
       </c>
       <c r="M16" t="n">
-        <v>6035</v>
+        <v>6170</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1575</v>
+        <v>1510</v>
       </c>
       <c r="F17" t="n">
-        <v>46.6</v>
+        <v>44.67</v>
       </c>
       <c r="G17" t="n">
-        <v>9.460000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.3</v>
+        <v>-4.13</v>
       </c>
       <c r="M17" t="n">
-        <v>1510</v>
+        <v>1575</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12045</v>
+        <v>12295</v>
       </c>
       <c r="F18" t="n">
-        <v>66.40000000000001</v>
+        <v>67.78</v>
       </c>
       <c r="G18" t="n">
-        <v>34.01</v>
+        <v>34.71</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.82</v>
+        <v>2.08</v>
       </c>
       <c r="M18" t="n">
-        <v>11715</v>
+        <v>12045</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>741</v>
+        <v>815</v>
       </c>
       <c r="F19" t="n">
-        <v>63.01</v>
+        <v>69.3</v>
       </c>
       <c r="G19" t="n">
-        <v>12.23</v>
+        <v>13.45</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.82</v>
+        <v>9.99</v>
       </c>
       <c r="M19" t="n">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>81.5</v>
       </c>
       <c r="F20" t="n">
-        <v>46.15</v>
+        <v>44.78</v>
       </c>
       <c r="G20" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.69</v>
+        <v>-2.98</v>
       </c>
       <c r="M20" t="n">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6210</v>
+        <v>6120</v>
       </c>
       <c r="F21" t="n">
-        <v>101.67</v>
+        <v>100.2</v>
       </c>
       <c r="G21" t="n">
-        <v>26.25</v>
+        <v>25.87</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.58</v>
+        <v>-1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="F22" t="n">
-        <v>53.32</v>
+        <v>53.19</v>
       </c>
       <c r="G22" t="n">
-        <v>26.84</v>
+        <v>26.77</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.48</v>
+        <v>-0.24</v>
       </c>
       <c r="M22" t="n">
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.25</v>
+        <v>18.45</v>
       </c>
       <c r="F23" t="n">
-        <v>41.48</v>
+        <v>41.93</v>
       </c>
       <c r="G23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.54</v>
+        <v>1.1</v>
       </c>
       <c r="M23" t="n">
-        <v>18.35</v>
+        <v>18.25</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1415</v>
+        <v>1320</v>
       </c>
       <c r="F24" t="n">
-        <v>71.86</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>17.54</v>
+        <v>16.36</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.28</v>
+        <v>-6.71</v>
       </c>
       <c r="M24" t="n">
-        <v>1370</v>
+        <v>1415</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>49.4</v>
+        <v>54.3</v>
       </c>
       <c r="F25" t="n">
-        <v>60.24</v>
+        <v>66.22</v>
       </c>
       <c r="G25" t="n">
-        <v>4.11</v>
+        <v>4.52</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.9</v>
+        <v>9.92</v>
       </c>
       <c r="M25" t="n">
-        <v>44.95</v>
+        <v>49.4</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2805</v>
+        <v>2720</v>
       </c>
       <c r="F26" t="n">
-        <v>241.39</v>
+        <v>234.08</v>
       </c>
       <c r="G26" t="n">
-        <v>54.99</v>
+        <v>53.32</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.86</v>
+        <v>-3.03</v>
       </c>
       <c r="M26" t="n">
-        <v>2675</v>
+        <v>2805</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="F27" t="n">
-        <v>43.78</v>
+        <v>44.43</v>
       </c>
       <c r="G27" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="F28" t="n">
-        <v>59.01</v>
+        <v>58.52</v>
       </c>
       <c r="G28" t="n">
-        <v>12.23</v>
+        <v>12.13</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="M28" t="n">
         <v>1205</v>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="F29" t="n">
-        <v>89.53</v>
+        <v>91</v>
       </c>
       <c r="G29" t="n">
-        <v>17.54</v>
+        <v>17.83</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>7.47</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3230</v>
+        <v>3200</v>
       </c>
       <c r="F30" t="n">
-        <v>76.18000000000001</v>
+        <v>75.47</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5</v>
+        <v>10.41</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-0.77</v>
+        <v>-0.93</v>
       </c>
       <c r="M30" t="n">
-        <v>3255</v>
+        <v>3230</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="F31" t="n">
-        <v>109.74</v>
+        <v>106.49</v>
       </c>
       <c r="G31" t="n">
-        <v>14.11</v>
+        <v>13.69</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>9.85</v>
+        <v>-2.96</v>
       </c>
       <c r="M31" t="n">
-        <v>492.5</v>
+        <v>541</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="F32" t="n">
-        <v>44.02</v>
+        <v>43.45</v>
       </c>
       <c r="G32" t="n">
-        <v>10.92</v>
+        <v>10.77</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.46</v>
+        <v>-1.29</v>
       </c>
       <c r="M32" t="n">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="F33" t="n">
-        <v>36.09</v>
+        <v>35.62</v>
       </c>
       <c r="G33" t="n">
-        <v>6.23</v>
+        <v>6.15</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-0.19</v>
+        <v>-1.31</v>
       </c>
       <c r="M33" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4530</v>
+        <v>4500</v>
       </c>
       <c r="F34" t="n">
-        <v>74.81</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>17.04</v>
+        <v>16.93</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.26</v>
+        <v>-0.66</v>
       </c>
       <c r="M34" t="n">
-        <v>4430</v>
+        <v>4530</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1710</v>
+        <v>1685</v>
       </c>
       <c r="F35" t="n">
-        <v>54.42</v>
+        <v>53.63</v>
       </c>
       <c r="G35" t="n">
-        <v>15.12</v>
+        <v>14.9</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>-1.46</v>
       </c>
       <c r="M35" t="n">
-        <v>1670</v>
+        <v>1710</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>21.65</v>
+        <v>21.35</v>
       </c>
       <c r="G36" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.82</v>
+        <v>-1.36</v>
       </c>
       <c r="M36" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>5240</v>
+        <v>5355</v>
       </c>
       <c r="F37" t="n">
-        <v>118.26</v>
+        <v>120.85</v>
       </c>
       <c r="G37" t="n">
-        <v>32.61</v>
+        <v>33.33</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1.32</v>
+        <v>2.19</v>
       </c>
       <c r="M37" t="n">
-        <v>5310</v>
+        <v>5240</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>5085</v>
+        <v>4695</v>
       </c>
       <c r="F38" t="n">
-        <v>79.52</v>
+        <v>73.42</v>
       </c>
       <c r="G38" t="n">
-        <v>31.23</v>
+        <v>28.84</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-0.59</v>
+        <v>-7.67</v>
       </c>
       <c r="M38" t="n">
-        <v>5115</v>
+        <v>5085</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F39" t="n">
-        <v>46.2</v>
+        <v>46.14</v>
       </c>
       <c r="G39" t="n">
-        <v>24.23</v>
+        <v>24.19</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.73</v>
+        <v>-0.14</v>
       </c>
       <c r="M39" t="n">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,13 +3605,13 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>11.89</v>
+        <v>11.99</v>
       </c>
       <c r="G40" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H40" t="n">
         <v>11</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.21</v>
+        <v>0.83</v>
       </c>
       <c r="M40" t="n">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" t="n">
-        <v>11.77</v>
+        <v>11.85</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-1.29</v>
+        <v>0.65</v>
       </c>
       <c r="M41" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>1005</v>
+        <v>965</v>
       </c>
       <c r="F43" t="n">
-        <v>27.19</v>
+        <v>26.11</v>
       </c>
       <c r="G43" t="n">
-        <v>4.19</v>
+        <v>4.02</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9.84</v>
+        <v>-3.98</v>
       </c>
       <c r="M43" t="n">
-        <v>915</v>
+        <v>1005</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>195.5</v>
+        <v>197.5</v>
       </c>
       <c r="F44" t="n">
-        <v>26.93</v>
+        <v>27.2</v>
       </c>
       <c r="G44" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.26</v>
+        <v>1.02</v>
       </c>
       <c r="M44" t="n">
-        <v>195</v>
+        <v>195.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3345</v>
+        <v>3295</v>
       </c>
       <c r="F45" t="n">
-        <v>49.06</v>
+        <v>48.33</v>
       </c>
       <c r="G45" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-0.3</v>
+        <v>-1.49</v>
       </c>
       <c r="M45" t="n">
-        <v>3355</v>
+        <v>3345</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>210.5</v>
+        <v>208.5</v>
       </c>
       <c r="F46" t="n">
-        <v>21.44</v>
+        <v>21.23</v>
       </c>
       <c r="G46" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.2</v>
+        <v>-0.95</v>
       </c>
       <c r="M46" t="n">
-        <v>208</v>
+        <v>210.5</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>63</v>
       </c>
       <c r="E47" t="n">
-        <v>219</v>
+        <v>226.5</v>
       </c>
       <c r="F47" t="n">
-        <v>23.99</v>
+        <v>24.81</v>
       </c>
       <c r="G47" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-1.35</v>
+        <v>3.42</v>
       </c>
       <c r="M47" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4249,13 +4249,13 @@
         <v>61</v>
       </c>
       <c r="E48" t="n">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="F48" t="n">
-        <v>26.11</v>
+        <v>25.92</v>
       </c>
       <c r="G48" t="n">
-        <v>7.36</v>
+        <v>7.31</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.42</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4330,13 +4330,13 @@
         <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="F49" t="n">
-        <v>20.06</v>
+        <v>20.15</v>
       </c>
       <c r="G49" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.42</v>
+        <v>0.47</v>
       </c>
       <c r="M49" t="n">
-        <v>106</v>
+        <v>107.5</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4411,13 +4411,13 @@
         <v>51</v>
       </c>
       <c r="E50" t="n">
-        <v>6225</v>
+        <v>6020</v>
       </c>
       <c r="F50" t="n">
-        <v>33.11</v>
+        <v>32.02</v>
       </c>
       <c r="G50" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.81</v>
+        <v>-3.29</v>
       </c>
       <c r="M50" t="n">
-        <v>6055</v>
+        <v>6225</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4492,13 +4492,13 @@
         <v>97</v>
       </c>
       <c r="E51" t="n">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F51" t="n">
-        <v>23.6</v>
+        <v>23.37</v>
       </c>
       <c r="G51" t="n">
-        <v>6.43</v>
+        <v>6.36</v>
       </c>
       <c r="H51" t="n">
         <v>29.3</v>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.58</v>
+        <v>-0.96</v>
       </c>
       <c r="M51" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -4571,13 +4571,13 @@
         <v>91</v>
       </c>
       <c r="E52" t="n">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="F52" t="n">
-        <v>41.17</v>
+        <v>42.21</v>
       </c>
       <c r="G52" t="n">
-        <v>5.52</v>
+        <v>5.66</v>
       </c>
       <c r="H52" t="n">
         <v>46.1</v>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.05</v>
+        <v>2.53</v>
       </c>
       <c r="M52" t="n">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -4650,13 +4650,13 @@
         <v>79</v>
       </c>
       <c r="E53" t="n">
-        <v>58.5</v>
+        <v>58.8</v>
       </c>
       <c r="F53" t="n">
-        <v>16.07</v>
+        <v>16.15</v>
       </c>
       <c r="G53" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H53" t="n">
         <v>17.3</v>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.92</v>
+        <v>0.51</v>
       </c>
       <c r="M53" t="n">
-        <v>57.4</v>
+        <v>58.5</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4729,13 +4729,13 @@
         <v>77</v>
       </c>
       <c r="E54" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F54" t="n">
-        <v>16.53</v>
+        <v>16.26</v>
       </c>
       <c r="G54" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H54" t="n">
         <v>15.5</v>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1.36</v>
+        <v>-1.66</v>
       </c>
       <c r="M54" t="n">
-        <v>183.5</v>
+        <v>181</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4808,13 +4808,13 @@
         <v>96</v>
       </c>
       <c r="E55" t="n">
-        <v>326.5</v>
+        <v>324.5</v>
       </c>
       <c r="F55" t="n">
-        <v>16.91</v>
+        <v>16.8</v>
       </c>
       <c r="G55" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.51</v>
+        <v>-0.61</v>
       </c>
       <c r="M55" t="n">
-        <v>318.5</v>
+        <v>326.5</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4885,13 +4885,13 @@
         <v>94</v>
       </c>
       <c r="E56" t="n">
-        <v>162.5</v>
+        <v>165</v>
       </c>
       <c r="F56" t="n">
-        <v>18.28</v>
+        <v>18.56</v>
       </c>
       <c r="G56" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.31</v>
+        <v>1.54</v>
       </c>
       <c r="M56" t="n">
-        <v>162</v>
+        <v>162.5</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4962,13 +4962,13 @@
         <v>78</v>
       </c>
       <c r="E57" t="n">
-        <v>117.5</v>
+        <v>119.5</v>
       </c>
       <c r="F57" t="n">
-        <v>19.11</v>
+        <v>19.43</v>
       </c>
       <c r="G57" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.43</v>
+        <v>1.7</v>
       </c>
       <c r="M57" t="n">
-        <v>117</v>
+        <v>117.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5039,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>88.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="F58" t="n">
-        <v>16.87</v>
+        <v>16.95</v>
       </c>
       <c r="G58" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.63</v>
+        <v>0.45</v>
       </c>
       <c r="M58" t="n">
-        <v>85.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5120,13 +5120,13 @@
         <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>156.5</v>
+        <v>153</v>
       </c>
       <c r="F59" t="n">
-        <v>17.45</v>
+        <v>17.06</v>
       </c>
       <c r="G59" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.62</v>
+        <v>-2.24</v>
       </c>
       <c r="M59" t="n">
-        <v>154</v>
+        <v>156.5</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5201,13 +5201,13 @@
         <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>233</v>
+        <v>232.5</v>
       </c>
       <c r="F60" t="n">
-        <v>14.48</v>
+        <v>14.45</v>
       </c>
       <c r="G60" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.64</v>
+        <v>-0.21</v>
       </c>
       <c r="M60" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5278,13 +5278,13 @@
         <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>184</v>
+        <v>182.5</v>
       </c>
       <c r="F61" t="n">
-        <v>15.53</v>
+        <v>15.4</v>
       </c>
       <c r="G61" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.22</v>
+        <v>-0.82</v>
       </c>
       <c r="M61" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="F62" t="n">
-        <v>16.36</v>
+        <v>16.75</v>
       </c>
       <c r="G62" t="n">
-        <v>13.2</v>
+        <v>13.52</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="M62" t="n">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>492.5</v>
+        <v>488</v>
       </c>
       <c r="F63" t="n">
-        <v>19.11</v>
+        <v>18.94</v>
       </c>
       <c r="G63" t="n">
-        <v>5.27</v>
+        <v>5.22</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>5.8</v>
+        <v>-0.91</v>
       </c>
       <c r="M63" t="n">
-        <v>465.5</v>
+        <v>492.5</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F64" t="n">
-        <v>18.63</v>
+        <v>18.74</v>
       </c>
       <c r="G64" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5.96</v>
+        <v>0.59</v>
       </c>
       <c r="M64" t="n">
-        <v>159.5</v>
+        <v>169</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>97</v>
       </c>
       <c r="E65" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F65" t="n">
-        <v>16.7</v>
+        <v>18.07</v>
       </c>
       <c r="G65" t="n">
-        <v>4.71</v>
+        <v>5.09</v>
       </c>
       <c r="H65" t="n">
         <v>14.7</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.92</v>
+        <v>8.18</v>
       </c>
       <c r="M65" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -5673,13 +5673,13 @@
         <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="F66" t="n">
-        <v>20.1</v>
+        <v>19.84</v>
       </c>
       <c r="G66" t="n">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="H66" t="n">
         <v>17.9</v>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="M66" t="n">
         <v>537</v>
@@ -5752,13 +5752,13 @@
         <v>91</v>
       </c>
       <c r="E67" t="n">
-        <v>119</v>
+        <v>119.5</v>
       </c>
       <c r="F67" t="n">
-        <v>15.37</v>
+        <v>15.44</v>
       </c>
       <c r="G67" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="H67" t="n">
         <v>15</v>
@@ -5778,7 +5778,7 @@
         <v>0.42</v>
       </c>
       <c r="M67" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5831,13 +5831,13 @@
         <v>90</v>
       </c>
       <c r="E68" t="n">
-        <v>295</v>
+        <v>304.5</v>
       </c>
       <c r="F68" t="n">
-        <v>24.94</v>
+        <v>25.74</v>
       </c>
       <c r="G68" t="n">
-        <v>6.41</v>
+        <v>6.62</v>
       </c>
       <c r="H68" t="n">
         <v>27.5</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.03</v>
+        <v>3.22</v>
       </c>
       <c r="M68" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5910,13 +5910,13 @@
         <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="F69" t="n">
-        <v>14.41</v>
+        <v>14.39</v>
       </c>
       <c r="G69" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H69" t="n">
         <v>16.7</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.24</v>
+        <v>-0.12</v>
       </c>
       <c r="M69" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5989,13 +5989,13 @@
         <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>125</v>
+        <v>125.5</v>
       </c>
       <c r="F70" t="n">
-        <v>17.41</v>
+        <v>17.48</v>
       </c>
       <c r="G70" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="H70" t="n">
         <v>16.4</v>
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.63</v>
+        <v>0.4</v>
       </c>
       <c r="M70" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
@@ -6072,13 +6072,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>248</v>
+        <v>250.5</v>
       </c>
       <c r="F71" t="n">
-        <v>16.35</v>
+        <v>16.51</v>
       </c>
       <c r="G71" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H71" t="n">
         <v>15.3</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>246.5</v>
+        <v>248</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>76</v>
       </c>
       <c r="E72" t="n">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="F72" t="n">
-        <v>44.47</v>
+        <v>45.74</v>
       </c>
       <c r="G72" t="n">
-        <v>23.75</v>
+        <v>24.43</v>
       </c>
       <c r="H72" t="n">
         <v>38.8</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.41</v>
+        <v>2.86</v>
       </c>
       <c r="M72" t="n">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6232,13 +6232,13 @@
         <v>68</v>
       </c>
       <c r="E73" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="F73" t="n">
-        <v>19.9</v>
+        <v>19.84</v>
       </c>
       <c r="G73" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="H73" t="n">
         <v>21.3</v>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.98</v>
+        <v>-0.32</v>
       </c>
       <c r="M73" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6315,13 +6315,13 @@
         <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>3175</v>
+        <v>3185</v>
       </c>
       <c r="F74" t="n">
-        <v>42.32</v>
+        <v>42.46</v>
       </c>
       <c r="G74" t="n">
-        <v>22.59</v>
+        <v>22.66</v>
       </c>
       <c r="H74" t="n">
         <v>24.6</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.93</v>
+        <v>0.31</v>
       </c>
       <c r="M74" t="n">
-        <v>3115</v>
+        <v>3175</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -6394,13 +6394,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="F75" t="n">
-        <v>14.24</v>
+        <v>14.02</v>
       </c>
       <c r="G75" t="n">
-        <v>8.050000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="H75" t="n">
         <v>14.2</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-0.84</v>
+        <v>-1.56</v>
       </c>
       <c r="M75" t="n">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6473,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2380</v>
+        <v>2425</v>
       </c>
       <c r="F76" t="n">
-        <v>27.59</v>
+        <v>28.11</v>
       </c>
       <c r="G76" t="n">
-        <v>9.59</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>23.6</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-0.21</v>
+        <v>1.89</v>
       </c>
       <c r="M76" t="n">
-        <v>2385</v>
+        <v>2380</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6552,13 +6552,13 @@
         <v>97</v>
       </c>
       <c r="E77" t="n">
-        <v>119.5</v>
+        <v>116</v>
       </c>
       <c r="F77" t="n">
-        <v>17.05</v>
+        <v>16.55</v>
       </c>
       <c r="G77" t="n">
-        <v>3.77</v>
+        <v>3.66</v>
       </c>
       <c r="H77" t="n">
         <v>12.4</v>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.84</v>
+        <v>-2.93</v>
       </c>
       <c r="M77" t="n">
-        <v>118.5</v>
+        <v>119.5</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>105.5</v>
+        <v>108</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6710,13 +6710,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>25.15</v>
+        <v>25.25</v>
       </c>
       <c r="F79" t="n">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="G79" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H79" t="n">
         <v>5.9</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M79" t="n">
-        <v>25.2</v>
+        <v>25.15</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6789,13 +6789,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F80" t="n">
-        <v>12.21</v>
+        <v>12.33</v>
       </c>
       <c r="G80" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H80" t="n">
         <v>10.7</v>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6868,13 +6868,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>178</v>
+        <v>178.5</v>
       </c>
       <c r="F81" t="n">
-        <v>12.69</v>
+        <v>12.72</v>
       </c>
       <c r="G81" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="H81" t="n">
         <v>11.4</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.85</v>
+        <v>0.28</v>
       </c>
       <c r="M81" t="n">
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6947,13 +6947,13 @@
         <v>92</v>
       </c>
       <c r="E82" t="n">
-        <v>41.3</v>
+        <v>42.05</v>
       </c>
       <c r="F82" t="n">
-        <v>8.69</v>
+        <v>8.85</v>
       </c>
       <c r="G82" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H82" t="n">
         <v>7.6</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.24</v>
+        <v>1.82</v>
       </c>
       <c r="M82" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7026,13 +7026,13 @@
         <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="F83" t="n">
-        <v>23.15</v>
+        <v>23.36</v>
       </c>
       <c r="G83" t="n">
-        <v>8.869999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H83" t="n">
         <v>25</v>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="M83" t="n">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7105,13 +7105,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F84" t="n">
-        <v>21.59</v>
+        <v>21.51</v>
       </c>
       <c r="G84" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="H84" t="n">
         <v>21.2</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.75</v>
+        <v>-0.4</v>
       </c>
       <c r="M84" t="n">
-        <v>490.5</v>
+        <v>504</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7184,13 +7184,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>160.5</v>
+        <v>162</v>
       </c>
       <c r="F85" t="n">
-        <v>17.26</v>
+        <v>17.42</v>
       </c>
       <c r="G85" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="H85" t="n">
         <v>14.1</v>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.58</v>
+        <v>0.93</v>
       </c>
       <c r="M85" t="n">
-        <v>158</v>
+        <v>160.5</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7263,13 +7263,13 @@
         <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>38.55</v>
+        <v>38.95</v>
       </c>
       <c r="F86" t="n">
-        <v>7.95</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H86" t="n">
         <v>6.2</v>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.26</v>
+        <v>1.04</v>
       </c>
       <c r="M86" t="n">
-        <v>38.45</v>
+        <v>38.55</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7342,13 +7342,13 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>1840</v>
+        <v>1800</v>
       </c>
       <c r="F87" t="n">
-        <v>28.91</v>
+        <v>28.28</v>
       </c>
       <c r="G87" t="n">
-        <v>14.9</v>
+        <v>14.57</v>
       </c>
       <c r="H87" t="n">
         <v>30.7</v>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>-2.17</v>
       </c>
       <c r="M87" t="n">
         <v>1840</v>
@@ -7425,13 +7425,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1360</v>
+        <v>1385</v>
       </c>
       <c r="F88" t="n">
-        <v>31.37</v>
+        <v>31.94</v>
       </c>
       <c r="G88" t="n">
-        <v>9.539999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H88" t="n">
         <v>21.8</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7.94</v>
+        <v>1.84</v>
       </c>
       <c r="M88" t="n">
-        <v>1260</v>
+        <v>1360</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7508,13 +7508,13 @@
         <v>79</v>
       </c>
       <c r="E89" t="n">
-        <v>88.8</v>
+        <v>89.7</v>
       </c>
       <c r="F89" t="n">
-        <v>8.699999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H89" t="n">
         <v>8.6</v>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.23</v>
+        <v>1.01</v>
       </c>
       <c r="M89" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7591,13 +7591,13 @@
         <v>78</v>
       </c>
       <c r="E90" t="n">
-        <v>54.3</v>
+        <v>54.7</v>
       </c>
       <c r="F90" t="n">
-        <v>8.18</v>
+        <v>8.24</v>
       </c>
       <c r="G90" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H90" t="n">
         <v>6.8</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.07</v>
+        <v>0.74</v>
       </c>
       <c r="M90" t="n">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7674,13 +7674,13 @@
         <v>77</v>
       </c>
       <c r="E91" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="F91" t="n">
-        <v>7.1</v>
+        <v>7.12</v>
       </c>
       <c r="G91" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H91" t="n">
         <v>10.4</v>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M91" t="n">
         <v>51.2</v>
@@ -7757,13 +7757,13 @@
         <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>340.5</v>
+        <v>344</v>
       </c>
       <c r="F92" t="n">
-        <v>14.84</v>
+        <v>14.99</v>
       </c>
       <c r="G92" t="n">
-        <v>5.39</v>
+        <v>5.44</v>
       </c>
       <c r="H92" t="n">
         <v>13.2</v>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.25</v>
+        <v>1.03</v>
       </c>
       <c r="M92" t="n">
-        <v>333</v>
+        <v>340.5</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7840,13 +7840,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>2165</v>
+        <v>2135</v>
       </c>
       <c r="F93" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
       <c r="G93" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="H93" t="n">
         <v>9.6</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-6.48</v>
+        <v>-1.39</v>
       </c>
       <c r="M93" t="n">
-        <v>2315</v>
+        <v>2165</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7923,13 +7923,13 @@
         <v>62</v>
       </c>
       <c r="E94" t="n">
-        <v>183</v>
+        <v>186.5</v>
       </c>
       <c r="F94" t="n">
-        <v>14.54</v>
+        <v>14.81</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="H94" t="n">
         <v>10</v>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.27</v>
+        <v>1.91</v>
       </c>
       <c r="M94" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8006,13 +8006,13 @@
         <v>60</v>
       </c>
       <c r="E95" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="F95" t="n">
-        <v>15.73</v>
+        <v>15.78</v>
       </c>
       <c r="G95" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H95" t="n">
         <v>11.9</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>7.66</v>
+        <v>0.34</v>
       </c>
       <c r="M95" t="n">
-        <v>1370</v>
+        <v>1475</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8089,10 +8089,10 @@
         <v>79</v>
       </c>
       <c r="E96" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="F96" t="n">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="G96" t="n">
         <v>1.09</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.14</v>
+        <v>0.72</v>
       </c>
       <c r="M96" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         <v>77</v>
       </c>
       <c r="E97" t="n">
-        <v>399.5</v>
+        <v>395</v>
       </c>
       <c r="F97" t="n">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
       <c r="G97" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.83</v>
+        <v>-1.13</v>
       </c>
       <c r="M97" t="n">
-        <v>388.5</v>
+        <v>399.5</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>23.65</v>
+        <v>23.9</v>
       </c>
       <c r="F98" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="G98" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.85</v>
+        <v>1.06</v>
       </c>
       <c r="M98" t="n">
-        <v>23.45</v>
+        <v>23.65</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>75</v>
       </c>
       <c r="E99" t="n">
-        <v>34.8</v>
+        <v>34.85</v>
       </c>
       <c r="F99" t="n">
         <v>3.75</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-0.14</v>
+        <v>0.14</v>
       </c>
       <c r="M99" t="n">
-        <v>34.85</v>
+        <v>34.8</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>69</v>
       </c>
       <c r="E100" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F100" t="n">
-        <v>5.22</v>
+        <v>5.07</v>
       </c>
       <c r="G100" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>5.26</v>
+        <v>-2.86</v>
       </c>
       <c r="M100" t="n">
-        <v>199.5</v>
+        <v>210</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>32</v>
       </c>
       <c r="E101" t="n">
-        <v>46.7</v>
+        <v>47.4</v>
       </c>
       <c r="F101" t="n">
-        <v>11.53</v>
+        <v>11.7</v>
       </c>
       <c r="G101" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.21</v>
+        <v>1.5</v>
       </c>
       <c r="M101" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3175</v>
+        <v>3185</v>
       </c>
       <c r="F2" t="n">
-        <v>42.32</v>
+        <v>42.46</v>
       </c>
       <c r="G2" t="n">
-        <v>22.59</v>
+        <v>22.66</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>3115</v>
+        <v>3175</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="F3" t="n">
-        <v>14.24</v>
+        <v>14.02</v>
       </c>
       <c r="G3" t="n">
-        <v>8.050000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.84</v>
+        <v>-1.56</v>
       </c>
       <c r="M3" t="n">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2380</v>
+        <v>2425</v>
       </c>
       <c r="F4" t="n">
-        <v>27.59</v>
+        <v>28.11</v>
       </c>
       <c r="G4" t="n">
-        <v>9.59</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.21</v>
+        <v>1.89</v>
       </c>
       <c r="M4" t="n">
-        <v>2385</v>
+        <v>2380</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>119.5</v>
+        <v>116</v>
       </c>
       <c r="F5" t="n">
-        <v>17.05</v>
+        <v>16.55</v>
       </c>
       <c r="G5" t="n">
-        <v>3.77</v>
+        <v>3.66</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.84</v>
+        <v>-2.93</v>
       </c>
       <c r="M5" t="n">
-        <v>118.5</v>
+        <v>119.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>105.5</v>
+        <v>108</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.15</v>
+        <v>25.25</v>
       </c>
       <c r="F7" t="n">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>25.2</v>
+        <v>25.15</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
-        <v>12.21</v>
+        <v>12.33</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>105.5</v>
+        <v>106</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>178</v>
+        <v>178.5</v>
       </c>
       <c r="F9" t="n">
-        <v>12.69</v>
+        <v>12.72</v>
       </c>
       <c r="G9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.85</v>
+        <v>0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.3</v>
+        <v>42.05</v>
       </c>
       <c r="F10" t="n">
-        <v>8.69</v>
+        <v>8.85</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.24</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="F11" t="n">
-        <v>23.15</v>
+        <v>23.36</v>
       </c>
       <c r="G11" t="n">
-        <v>8.869999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="M11" t="n">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F12" t="n">
-        <v>21.59</v>
+        <v>21.51</v>
       </c>
       <c r="G12" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>-0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>490.5</v>
+        <v>504</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>160.5</v>
+        <v>162</v>
       </c>
       <c r="F13" t="n">
-        <v>17.26</v>
+        <v>17.42</v>
       </c>
       <c r="G13" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>0.93</v>
       </c>
       <c r="M13" t="n">
-        <v>158</v>
+        <v>160.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.55</v>
+        <v>38.95</v>
       </c>
       <c r="F14" t="n">
-        <v>7.95</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.26</v>
+        <v>1.04</v>
       </c>
       <c r="M14" t="n">
-        <v>38.45</v>
+        <v>38.55</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1840</v>
+        <v>1800</v>
       </c>
       <c r="F15" t="n">
-        <v>28.91</v>
+        <v>28.28</v>
       </c>
       <c r="G15" t="n">
-        <v>14.9</v>
+        <v>14.57</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-2.17</v>
       </c>
       <c r="M15" t="n">
         <v>1840</v>
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1360</v>
+        <v>1385</v>
       </c>
       <c r="F16" t="n">
-        <v>31.37</v>
+        <v>31.94</v>
       </c>
       <c r="G16" t="n">
-        <v>9.539999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.94</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>1260</v>
+        <v>1360</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.8</v>
+        <v>89.7</v>
       </c>
       <c r="F17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.23</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>54.3</v>
+        <v>54.7</v>
       </c>
       <c r="F18" t="n">
-        <v>8.18</v>
+        <v>8.24</v>
       </c>
       <c r="G18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>0.74</v>
       </c>
       <c r="M18" t="n">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="F19" t="n">
-        <v>7.1</v>
+        <v>7.12</v>
       </c>
       <c r="G19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M19" t="n">
         <v>51.2</v>
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>340.5</v>
+        <v>344</v>
       </c>
       <c r="F20" t="n">
-        <v>14.84</v>
+        <v>14.99</v>
       </c>
       <c r="G20" t="n">
-        <v>5.39</v>
+        <v>5.44</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.03</v>
       </c>
       <c r="M20" t="n">
-        <v>333</v>
+        <v>340.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2165</v>
+        <v>2135</v>
       </c>
       <c r="F21" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
       <c r="G21" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-6.48</v>
+        <v>-1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>2315</v>
+        <v>2165</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>183</v>
+        <v>186.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.54</v>
+        <v>14.81</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.27</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="F23" t="n">
-        <v>15.73</v>
+        <v>15.78</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7.66</v>
+        <v>0.34</v>
       </c>
       <c r="M23" t="n">
-        <v>1370</v>
+        <v>1475</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F2" t="n">
-        <v>16.7</v>
+        <v>18.07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.71</v>
+        <v>5.09</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>8.18</v>
       </c>
       <c r="M2" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="F3" t="n">
-        <v>20.1</v>
+        <v>19.84</v>
       </c>
       <c r="G3" t="n">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="M3" t="n">
         <v>537</v>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>119.5</v>
       </c>
       <c r="F4" t="n">
-        <v>15.37</v>
+        <v>15.44</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10791,7 +10791,7 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>118.5</v>
+        <v>119</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>295</v>
+        <v>304.5</v>
       </c>
       <c r="F5" t="n">
-        <v>24.94</v>
+        <v>25.74</v>
       </c>
       <c r="G5" t="n">
-        <v>6.41</v>
+        <v>6.62</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.03</v>
+        <v>3.22</v>
       </c>
       <c r="M5" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14.41</v>
+        <v>14.39</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.24</v>
+        <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>125</v>
+        <v>125.5</v>
       </c>
       <c r="F7" t="n">
-        <v>17.41</v>
+        <v>17.48</v>
       </c>
       <c r="G7" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>248</v>
+        <v>250.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.35</v>
+        <v>16.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>246.5</v>
+        <v>248</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="F9" t="n">
-        <v>44.47</v>
+        <v>45.74</v>
       </c>
       <c r="G9" t="n">
-        <v>23.75</v>
+        <v>24.43</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.41</v>
+        <v>2.86</v>
       </c>
       <c r="M9" t="n">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.9</v>
+        <v>19.84</v>
       </c>
       <c r="G10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.98</v>
+        <v>-0.32</v>
       </c>
       <c r="M10" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="F3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="M3" t="n">
         <v>40.8</v>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="F5" t="n">
-        <v>119.91</v>
+        <v>117.77</v>
       </c>
       <c r="G5" t="n">
-        <v>34.5</v>
+        <v>33.88</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.94</v>
+        <v>-1.79</v>
       </c>
       <c r="M5" t="n">
-        <v>5440</v>
+        <v>5600</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124.5</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>23.53</v>
+        <v>23.44</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>99.8</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
-        <v>27.34</v>
+        <v>27.67</v>
       </c>
       <c r="G7" t="n">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>170.5</v>
+        <v>172.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.75</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>1.17</v>
       </c>
       <c r="M8" t="n">
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.55</v>
+        <v>25.91</v>
       </c>
       <c r="G9" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>156.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.67</v>
+        <v>17.72</v>
       </c>
       <c r="G10" t="n">
-        <v>6.26</v>
+        <v>6.28</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>0.32</v>
       </c>
       <c r="M10" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="F11" t="n">
-        <v>23.82</v>
+        <v>23.92</v>
       </c>
       <c r="G11" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-3.12</v>
+        <v>0.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1280</v>
+        <v>1240</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F12" t="n">
-        <v>19.83</v>
+        <v>20.32</v>
       </c>
       <c r="G12" t="n">
-        <v>4.17</v>
+        <v>4.28</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.95</v>
+        <v>2.52</v>
       </c>
       <c r="M12" t="n">
-        <v>157.5</v>
+        <v>159</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F13" t="n">
-        <v>32.4</v>
+        <v>32.51</v>
       </c>
       <c r="G13" t="n">
-        <v>6.56</v>
+        <v>6.58</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
       <c r="M13" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>143.5</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>28.19</v>
+        <v>28.49</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M14" t="n">
         <v>143.5</v>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>215</v>
+        <v>217.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.37</v>
+        <v>19.59</v>
       </c>
       <c r="G15" t="n">
-        <v>5.46</v>
+        <v>5.52</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.23</v>
+        <v>1.16</v>
       </c>
       <c r="M15" t="n">
-        <v>215.5</v>
+        <v>215</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6170</v>
+        <v>6500</v>
       </c>
       <c r="F16" t="n">
-        <v>158.16</v>
+        <v>166.62</v>
       </c>
       <c r="G16" t="n">
-        <v>61.41</v>
+        <v>64.69</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.24</v>
+        <v>5.35</v>
       </c>
       <c r="M16" t="n">
-        <v>6035</v>
+        <v>6170</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1710</v>
+        <v>1685</v>
       </c>
       <c r="F2" t="n">
-        <v>54.42</v>
+        <v>53.63</v>
       </c>
       <c r="G2" t="n">
-        <v>15.12</v>
+        <v>14.9</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.4</v>
+        <v>-1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1670</v>
+        <v>1710</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>21.65</v>
+        <v>21.35</v>
       </c>
       <c r="G3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.82</v>
+        <v>-1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>5240</v>
+        <v>5355</v>
       </c>
       <c r="F4" t="n">
-        <v>118.26</v>
+        <v>120.85</v>
       </c>
       <c r="G4" t="n">
-        <v>32.61</v>
+        <v>33.33</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.32</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>5310</v>
+        <v>5240</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5085</v>
+        <v>4695</v>
       </c>
       <c r="F5" t="n">
-        <v>79.52</v>
+        <v>73.42</v>
       </c>
       <c r="G5" t="n">
-        <v>31.23</v>
+        <v>28.84</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.59</v>
+        <v>-7.67</v>
       </c>
       <c r="M5" t="n">
-        <v>5115</v>
+        <v>5085</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F6" t="n">
-        <v>46.2</v>
+        <v>46.14</v>
       </c>
       <c r="G6" t="n">
-        <v>24.23</v>
+        <v>24.19</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.73</v>
+        <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.89</v>
+        <v>11.99</v>
       </c>
       <c r="G7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.21</v>
+        <v>0.83</v>
       </c>
       <c r="M7" t="n">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F8" t="n">
-        <v>11.77</v>
+        <v>11.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.29</v>
+        <v>0.65</v>
       </c>
       <c r="M8" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>1005</v>
+        <v>965</v>
       </c>
       <c r="F10" t="n">
-        <v>27.19</v>
+        <v>26.11</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19</v>
+        <v>4.02</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9.84</v>
+        <v>-3.98</v>
       </c>
       <c r="M10" t="n">
-        <v>915</v>
+        <v>1005</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>195.5</v>
+        <v>197.5</v>
       </c>
       <c r="F11" t="n">
-        <v>26.93</v>
+        <v>27.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.26</v>
+        <v>1.02</v>
       </c>
       <c r="M11" t="n">
-        <v>195</v>
+        <v>195.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3345</v>
+        <v>3295</v>
       </c>
       <c r="F12" t="n">
-        <v>49.06</v>
+        <v>48.33</v>
       </c>
       <c r="G12" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.3</v>
+        <v>-1.49</v>
       </c>
       <c r="M12" t="n">
-        <v>3355</v>
+        <v>3345</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1300</v>
+        <v>1430</v>
       </c>
       <c r="F2" t="n">
-        <v>87.54000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="G2" t="n">
-        <v>23.61</v>
+        <v>25.97</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>1300</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>155.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.22</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="F5" t="n">
-        <v>117.77</v>
+        <v>124.2</v>
       </c>
       <c r="G5" t="n">
-        <v>33.88</v>
+        <v>35.73</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.79</v>
+        <v>5.45</v>
       </c>
       <c r="M5" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>124.5</v>
+        <v>124</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.67</v>
+        <v>27.81</v>
       </c>
       <c r="G7" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8</v>
+        <v>101</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172.5</v>
+        <v>174</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>22.19</v>
       </c>
       <c r="G8" t="n">
-        <v>4.82</v>
+        <v>4.86</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="M8" t="n">
-        <v>170.5</v>
+        <v>172.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="F9" t="n">
-        <v>25.91</v>
+        <v>26.03</v>
       </c>
       <c r="G9" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.72</v>
+        <v>17.84</v>
       </c>
       <c r="G10" t="n">
-        <v>6.28</v>
+        <v>6.32</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>156</v>
+        <v>156.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1245</v>
+        <v>1220</v>
       </c>
       <c r="F11" t="n">
-        <v>23.92</v>
+        <v>23.44</v>
       </c>
       <c r="G11" t="n">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>-2.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>163</v>
+        <v>163.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.32</v>
+        <v>20.39</v>
       </c>
       <c r="G12" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.52</v>
+        <v>0.31</v>
       </c>
       <c r="M12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F13" t="n">
-        <v>32.51</v>
+        <v>32.98</v>
       </c>
       <c r="G13" t="n">
-        <v>6.58</v>
+        <v>6.68</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.36</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.49</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.05</v>
+        <v>0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>143.5</v>
+        <v>145</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>217.5</v>
+        <v>216.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.59</v>
+        <v>19.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.52</v>
+        <v>5.49</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.16</v>
+        <v>-0.46</v>
       </c>
       <c r="M15" t="n">
-        <v>215</v>
+        <v>217.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6500</v>
+        <v>7150</v>
       </c>
       <c r="F16" t="n">
-        <v>166.62</v>
+        <v>183.29</v>
       </c>
       <c r="G16" t="n">
-        <v>64.69</v>
+        <v>71.16</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.35</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>6170</v>
+        <v>6500</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1510</v>
+        <v>1575</v>
       </c>
       <c r="F17" t="n">
-        <v>44.67</v>
+        <v>46.6</v>
       </c>
       <c r="G17" t="n">
-        <v>9.07</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-4.13</v>
+        <v>4.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1575</v>
+        <v>1510</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12295</v>
+        <v>12495</v>
       </c>
       <c r="F18" t="n">
-        <v>67.78</v>
+        <v>68.88</v>
       </c>
       <c r="G18" t="n">
-        <v>34.71</v>
+        <v>35.28</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>12045</v>
+        <v>12295</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>815</v>
+        <v>896</v>
       </c>
       <c r="F19" t="n">
-        <v>69.3</v>
+        <v>76.19</v>
       </c>
       <c r="G19" t="n">
-        <v>13.45</v>
+        <v>14.79</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.99</v>
+        <v>9.94</v>
       </c>
       <c r="M19" t="n">
-        <v>741</v>
+        <v>815</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>81.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>44.78</v>
+        <v>45.66</v>
       </c>
       <c r="G20" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.98</v>
+        <v>1.96</v>
       </c>
       <c r="M20" t="n">
-        <v>84</v>
+        <v>81.5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6120</v>
+        <v>6435</v>
       </c>
       <c r="F21" t="n">
-        <v>100.2</v>
+        <v>105.35</v>
       </c>
       <c r="G21" t="n">
-        <v>25.87</v>
+        <v>27.21</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.45</v>
+        <v>5.15</v>
       </c>
       <c r="M21" t="n">
-        <v>6210</v>
+        <v>6120</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2085</v>
+        <v>2290</v>
       </c>
       <c r="F22" t="n">
-        <v>53.19</v>
+        <v>58.42</v>
       </c>
       <c r="G22" t="n">
-        <v>26.77</v>
+        <v>29.4</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.24</v>
+        <v>9.83</v>
       </c>
       <c r="M22" t="n">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.45</v>
+        <v>18.5</v>
       </c>
       <c r="F23" t="n">
-        <v>41.93</v>
+        <v>42.05</v>
       </c>
       <c r="G23" t="n">
         <v>1.7</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.1</v>
+        <v>0.27</v>
       </c>
       <c r="M23" t="n">
-        <v>18.25</v>
+        <v>18.45</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1320</v>
+        <v>1370</v>
       </c>
       <c r="F24" t="n">
-        <v>67.04000000000001</v>
+        <v>69.58</v>
       </c>
       <c r="G24" t="n">
-        <v>16.36</v>
+        <v>16.98</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-6.71</v>
+        <v>3.79</v>
       </c>
       <c r="M24" t="n">
-        <v>1415</v>
+        <v>1320</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>54.3</v>
+        <v>58.7</v>
       </c>
       <c r="F25" t="n">
-        <v>66.22</v>
+        <v>71.59</v>
       </c>
       <c r="G25" t="n">
-        <v>4.52</v>
+        <v>4.88</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.92</v>
+        <v>8.1</v>
       </c>
       <c r="M25" t="n">
-        <v>49.4</v>
+        <v>54.3</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2720</v>
+        <v>2880</v>
       </c>
       <c r="F26" t="n">
-        <v>234.08</v>
+        <v>247.85</v>
       </c>
       <c r="G26" t="n">
-        <v>53.32</v>
+        <v>56.46</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-3.03</v>
+        <v>5.88</v>
       </c>
       <c r="M26" t="n">
-        <v>2805</v>
+        <v>2720</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="F27" t="n">
-        <v>44.43</v>
+        <v>46.16</v>
       </c>
       <c r="G27" t="n">
-        <v>6.94</v>
+        <v>7.21</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.49</v>
+        <v>3.91</v>
       </c>
       <c r="M27" t="n">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1195</v>
+        <v>1180</v>
       </c>
       <c r="F28" t="n">
-        <v>58.52</v>
+        <v>57.79</v>
       </c>
       <c r="G28" t="n">
-        <v>12.13</v>
+        <v>11.97</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-0.83</v>
+        <v>-1.26</v>
       </c>
       <c r="M28" t="n">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>556</v>
+        <v>611</v>
       </c>
       <c r="F29" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>17.83</v>
+        <v>19.6</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3200</v>
+        <v>3520</v>
       </c>
       <c r="F30" t="n">
-        <v>75.47</v>
+        <v>83.02</v>
       </c>
       <c r="G30" t="n">
-        <v>10.41</v>
+        <v>11.45</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-0.93</v>
+        <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>3230</v>
+        <v>3200</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="F31" t="n">
-        <v>106.49</v>
+        <v>109.13</v>
       </c>
       <c r="G31" t="n">
-        <v>13.69</v>
+        <v>14.03</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-2.96</v>
+        <v>2.48</v>
       </c>
       <c r="M31" t="n">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="F32" t="n">
-        <v>43.45</v>
+        <v>43.7</v>
       </c>
       <c r="G32" t="n">
-        <v>10.77</v>
+        <v>10.84</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-1.29</v>
+        <v>0.58</v>
       </c>
       <c r="M32" t="n">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="F33" t="n">
-        <v>35.62</v>
+        <v>37.04</v>
       </c>
       <c r="G33" t="n">
-        <v>6.15</v>
+        <v>6.39</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-1.31</v>
+        <v>3.97</v>
       </c>
       <c r="M33" t="n">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4500</v>
+        <v>4710</v>
       </c>
       <c r="F34" t="n">
-        <v>74.31999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>16.93</v>
+        <v>17.72</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-0.66</v>
+        <v>4.67</v>
       </c>
       <c r="M34" t="n">
-        <v>4530</v>
+        <v>4500</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1685</v>
+        <v>1735</v>
       </c>
       <c r="F35" t="n">
-        <v>53.63</v>
+        <v>55.22</v>
       </c>
       <c r="G35" t="n">
-        <v>14.9</v>
+        <v>15.34</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1.46</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>1710</v>
+        <v>1685</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>21.35</v>
+        <v>21.21</v>
       </c>
       <c r="G36" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-1.36</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>5355</v>
+        <v>5525</v>
       </c>
       <c r="F37" t="n">
-        <v>120.85</v>
+        <v>124.69</v>
       </c>
       <c r="G37" t="n">
-        <v>33.33</v>
+        <v>34.38</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.19</v>
+        <v>3.17</v>
       </c>
       <c r="M37" t="n">
-        <v>5240</v>
+        <v>5355</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>4695</v>
+        <v>4890</v>
       </c>
       <c r="F38" t="n">
-        <v>73.42</v>
+        <v>76.47</v>
       </c>
       <c r="G38" t="n">
-        <v>28.84</v>
+        <v>30.04</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-7.67</v>
+        <v>4.15</v>
       </c>
       <c r="M38" t="n">
-        <v>5085</v>
+        <v>4695</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="F39" t="n">
-        <v>46.14</v>
+        <v>47.19</v>
       </c>
       <c r="G39" t="n">
-        <v>24.19</v>
+        <v>24.74</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.14</v>
+        <v>2.27</v>
       </c>
       <c r="M39" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F40" t="n">
-        <v>11.99</v>
+        <v>11.98</v>
       </c>
       <c r="G40" t="n">
         <v>1.68</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.83</v>
+        <v>-0.1</v>
       </c>
       <c r="M40" t="n">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>154</v>
+        <v>155.5</v>
       </c>
       <c r="F41" t="n">
-        <v>11.85</v>
+        <v>11.96</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="M41" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>106</v>
+        <v>108.5</v>
       </c>
       <c r="F42" t="n">
-        <v>15.45</v>
+        <v>15.82</v>
       </c>
       <c r="G42" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M42" t="n">
         <v>106</v>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="F43" t="n">
-        <v>26.11</v>
+        <v>26.3</v>
       </c>
       <c r="G43" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-3.98</v>
+        <v>0.73</v>
       </c>
       <c r="M43" t="n">
-        <v>1005</v>
+        <v>965</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>197.5</v>
+        <v>199.5</v>
       </c>
       <c r="F44" t="n">
-        <v>27.2</v>
+        <v>27.48</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>195.5</v>
+        <v>197.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3295</v>
+        <v>3540</v>
       </c>
       <c r="F45" t="n">
-        <v>48.33</v>
+        <v>51.92</v>
       </c>
       <c r="G45" t="n">
-        <v>4.71</v>
+        <v>5.06</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-1.49</v>
+        <v>7.44</v>
       </c>
       <c r="M45" t="n">
-        <v>3345</v>
+        <v>3295</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>208.5</v>
+        <v>216</v>
       </c>
       <c r="F46" t="n">
-        <v>21.23</v>
+        <v>22</v>
       </c>
       <c r="G46" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-0.95</v>
+        <v>3.6</v>
       </c>
       <c r="M46" t="n">
-        <v>210.5</v>
+        <v>208.5</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4155,34 +4155,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>226.5</v>
+        <v>124</v>
       </c>
       <c r="F47" t="n">
-        <v>24.81</v>
+        <v>20.16</v>
       </c>
       <c r="G47" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>-15.3</v>
+        <v>11</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -4191,31 +4191,31 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="M47" t="n">
-        <v>219</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>EPS單期衰退</t>
-        </is>
-      </c>
+        <v>119.5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.72</v>
+        <v>1.4</v>
       </c>
       <c r="R47" t="n">
-        <v>13.2</v>
+        <v>3.8</v>
       </c>
       <c r="S47" t="n">
-        <v>34.8</v>
+        <v>48.7</v>
       </c>
       <c r="T47" t="n">
-        <v>34.5</v>
+        <v>28.4</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
@@ -4225,19 +4225,19 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4246,20 +4246,20 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>715</v>
+        <v>227.5</v>
       </c>
       <c r="F48" t="n">
-        <v>25.92</v>
+        <v>24.92</v>
       </c>
       <c r="G48" t="n">
-        <v>7.31</v>
+        <v>3.07</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>-15.3</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4268,35 +4268,31 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="M48" t="n">
-        <v>720</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>226.5</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>31.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="R48" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="S48" t="n">
-        <v>21.9</v>
+        <v>34.8</v>
       </c>
       <c r="T48" t="n">
-        <v>32.2</v>
+        <v>34.5</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -4306,19 +4302,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4327,21 +4323,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E49" t="n">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="F49" t="n">
-        <v>20.15</v>
+        <v>20.37</v>
       </c>
       <c r="G49" t="n">
-        <v>2.5</v>
+        <v>5.62</v>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="n">
-        <v>186.3</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
@@ -4349,10 +4343,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.47</v>
+        <v>7.58</v>
       </c>
       <c r="M49" t="n">
-        <v>107.5</v>
+        <v>488</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4361,28 +4355,28 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>10.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="R49" t="n">
-        <v>-3.4</v>
+        <v>-6.1</v>
       </c>
       <c r="S49" t="n">
-        <v>37</v>
+        <v>730.1</v>
       </c>
       <c r="T49" t="n">
-        <v>35.8</v>
+        <v>45.2</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4394,12 +4388,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4408,20 +4402,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>6020</v>
+        <v>727</v>
       </c>
       <c r="F50" t="n">
-        <v>32.02</v>
+        <v>26.36</v>
       </c>
       <c r="G50" t="n">
-        <v>4.11</v>
+        <v>7.43</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4430,10 +4424,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-3.29</v>
+        <v>1.68</v>
       </c>
       <c r="M50" t="n">
-        <v>6225</v>
+        <v>715</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4442,23 +4436,23 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>11.4</v>
+        <v>31.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="R50" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="S50" t="n">
-        <v>41.8</v>
+        <v>21.9</v>
       </c>
       <c r="T50" t="n">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4475,197 +4469,201 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>516</v>
+        <v>111</v>
       </c>
       <c r="F51" t="n">
-        <v>23.37</v>
+        <v>20.71</v>
       </c>
       <c r="G51" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="H51" t="n">
-        <v>29.3</v>
-      </c>
+        <v>2.57</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.87</v>
-      </c>
+        <v>186.3</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-0.96</v>
+        <v>2.78</v>
       </c>
       <c r="M51" t="n">
-        <v>521</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>19.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="R51" t="n">
-        <v>10.6</v>
+        <v>-3.4</v>
       </c>
       <c r="S51" t="n">
-        <v>64.90000000000001</v>
+        <v>37</v>
       </c>
       <c r="T51" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.87</v>
-      </c>
+        <v>35.8</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>688</v>
+        <v>6430</v>
       </c>
       <c r="F52" t="n">
-        <v>42.21</v>
+        <v>34.2</v>
       </c>
       <c r="G52" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="H52" t="n">
-        <v>46.1</v>
-      </c>
+        <v>4.39</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.97</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.53</v>
+        <v>6.81</v>
       </c>
       <c r="M52" t="n">
-        <v>671</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+        <v>6020</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P52" t="n">
-        <v>15.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="R52" t="n">
-        <v>24.8</v>
+        <v>6.8</v>
       </c>
       <c r="S52" t="n">
-        <v>1.5</v>
+        <v>41.8</v>
       </c>
       <c r="T52" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.97</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>58.8</v>
+        <v>540</v>
       </c>
       <c r="F53" t="n">
-        <v>16.15</v>
+        <v>24.46</v>
       </c>
       <c r="G53" t="n">
-        <v>2.46</v>
+        <v>6.66</v>
       </c>
       <c r="H53" t="n">
-        <v>17.3</v>
+        <v>29.3</v>
       </c>
       <c r="I53" t="n">
-        <v>11.8</v>
+        <v>18.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4673,78 +4671,78 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.51</v>
+        <v>4.65</v>
       </c>
       <c r="M53" t="n">
-        <v>58.5</v>
+        <v>516</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>11.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="R53" t="n">
-        <v>4.4</v>
+        <v>10.6</v>
       </c>
       <c r="S53" t="n">
-        <v>768.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>19.4</v>
+        <v>34.7</v>
       </c>
       <c r="U53" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E54" t="n">
-        <v>178</v>
+        <v>702</v>
       </c>
       <c r="F54" t="n">
-        <v>16.26</v>
+        <v>43.07</v>
       </c>
       <c r="G54" t="n">
-        <v>1.77</v>
+        <v>5.78</v>
       </c>
       <c r="H54" t="n">
-        <v>15.5</v>
+        <v>46.1</v>
       </c>
       <c r="I54" t="n">
-        <v>8.6</v>
+        <v>30.6</v>
       </c>
       <c r="J54" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4752,227 +4750,231 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1.66</v>
+        <v>2.03</v>
       </c>
       <c r="M54" t="n">
-        <v>181</v>
+        <v>688</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.03</v>
+        <v>1.83</v>
       </c>
       <c r="R54" t="n">
-        <v>30.2</v>
+        <v>24.8</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="T54" t="n">
-        <v>16.9</v>
+        <v>60.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>324.5</v>
+        <v>59.8</v>
       </c>
       <c r="F55" t="n">
-        <v>16.8</v>
+        <v>16.43</v>
       </c>
       <c r="G55" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>17.3</v>
+      </c>
       <c r="I55" t="n">
-        <v>49</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.64</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.61</v>
+        <v>1.7</v>
       </c>
       <c r="M55" t="n">
-        <v>326.5</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>58.8</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>29.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="R55" t="n">
-        <v>24.2</v>
+        <v>4.4</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>768.2</v>
       </c>
       <c r="T55" t="n">
-        <v>24</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.64</v>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>165</v>
+        <v>186.5</v>
       </c>
       <c r="F56" t="n">
-        <v>18.56</v>
+        <v>17.03</v>
       </c>
       <c r="G56" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>1.85</v>
+      </c>
+      <c r="H56" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I56" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.54</v>
+        <v>4.78</v>
       </c>
       <c r="M56" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>18.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.74</v>
+        <v>4.03</v>
       </c>
       <c r="R56" t="n">
-        <v>11.1</v>
+        <v>30.2</v>
       </c>
       <c r="S56" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>22</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>119.5</v>
+        <v>341.5</v>
       </c>
       <c r="F57" t="n">
-        <v>19.43</v>
+        <v>17.69</v>
       </c>
       <c r="G57" t="n">
-        <v>2.87</v>
+        <v>5.01</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4981,10 +4983,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.7</v>
+        <v>5.24</v>
       </c>
       <c r="M57" t="n">
-        <v>117.5</v>
+        <v>324.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4993,19 +4995,19 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="R57" t="n">
-        <v>3.8</v>
+        <v>24.2</v>
       </c>
       <c r="S57" t="n">
-        <v>48.7</v>
+        <v>25</v>
       </c>
       <c r="T57" t="n">
-        <v>28.4</v>
+        <v>24</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
@@ -5022,34 +5024,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>88.8</v>
+        <v>167</v>
       </c>
       <c r="F58" t="n">
-        <v>16.95</v>
+        <v>18.79</v>
       </c>
       <c r="G58" t="n">
-        <v>1.73</v>
+        <v>3.96</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>11.3</v>
+        <v>57.1</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5058,35 +5060,31 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.45</v>
+        <v>1.21</v>
       </c>
       <c r="M58" t="n">
-        <v>88.40000000000001</v>
+        <v>165</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>9.5</v>
+        <v>18.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.99</v>
+        <v>2.74</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="S58" t="n">
-        <v>-2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T58" t="n">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
@@ -5103,12 +5101,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5117,20 +5115,20 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>153</v>
+        <v>90.3</v>
       </c>
       <c r="F59" t="n">
-        <v>17.06</v>
+        <v>17.23</v>
       </c>
       <c r="G59" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5139,10 +5137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-2.24</v>
+        <v>1.69</v>
       </c>
       <c r="M59" t="n">
-        <v>156.5</v>
+        <v>88.8</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5151,23 +5149,23 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>ROE5低</t>
+          <t>月營收轉負-3%</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>5.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="R59" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>14.6</v>
+        <v>-2.7</v>
       </c>
       <c r="T59" t="n">
-        <v>34.2</v>
+        <v>20.3</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
@@ -5184,12 +5182,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5198,20 +5196,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>232.5</v>
+        <v>157</v>
       </c>
       <c r="F60" t="n">
-        <v>14.45</v>
+        <v>17.5</v>
       </c>
       <c r="G60" t="n">
-        <v>5.25</v>
+        <v>1.73</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5220,36 +5218,40 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-0.21</v>
+        <v>2.61</v>
       </c>
       <c r="M60" t="n">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P60" t="n">
-        <v>30.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="R60" t="n">
-        <v>20.4</v>
+        <v>22.1</v>
       </c>
       <c r="S60" t="n">
-        <v>812.4</v>
+        <v>14.6</v>
       </c>
       <c r="T60" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5261,12 +5263,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5275,20 +5277,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>182.5</v>
+        <v>242.5</v>
       </c>
       <c r="F61" t="n">
-        <v>15.4</v>
+        <v>15.07</v>
       </c>
       <c r="G61" t="n">
-        <v>1.83</v>
+        <v>5.48</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>49.2</v>
+        <v>9.6</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -5297,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-0.82</v>
+        <v>4.3</v>
       </c>
       <c r="M61" t="n">
-        <v>184</v>
+        <v>232.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5309,24 +5311,24 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>14.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>20.4</v>
       </c>
       <c r="S61" t="n">
-        <v>10.3</v>
+        <v>812.4</v>
       </c>
       <c r="T61" t="n">
-        <v>20.2</v>
+        <v>34.6</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5338,12 +5340,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5352,20 +5354,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>725</v>
+        <v>186</v>
       </c>
       <c r="F62" t="n">
-        <v>16.75</v>
+        <v>15.7</v>
       </c>
       <c r="G62" t="n">
-        <v>13.52</v>
+        <v>1.87</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>-8.1</v>
+        <v>49.2</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5374,35 +5376,31 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="M62" t="n">
-        <v>708</v>
+        <v>182.5</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>94.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="R62" t="n">
-        <v>18.2</v>
+        <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="T62" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
@@ -5419,33 +5417,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>488</v>
+        <v>729</v>
       </c>
       <c r="F63" t="n">
-        <v>18.94</v>
+        <v>16.84</v>
       </c>
       <c r="G63" t="n">
-        <v>5.22</v>
+        <v>13.59</v>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>-8.1</v>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-0.91</v>
+        <v>0.55</v>
       </c>
       <c r="M63" t="n">
-        <v>492.5</v>
+        <v>725</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>17.9</v>
+        <v>94.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="R63" t="n">
-        <v>-6.1</v>
+        <v>18.2</v>
       </c>
       <c r="S63" t="n">
-        <v>730.1</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>45.2</v>
+        <v>19.6</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>170</v>
+        <v>179.5</v>
       </c>
       <c r="F64" t="n">
-        <v>18.74</v>
+        <v>19.79</v>
       </c>
       <c r="G64" t="n">
-        <v>4.64</v>
+        <v>4.9</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.59</v>
+        <v>5.59</v>
       </c>
       <c r="M64" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>97</v>
       </c>
       <c r="E65" t="n">
-        <v>172</v>
+        <v>170.5</v>
       </c>
       <c r="F65" t="n">
-        <v>18.07</v>
+        <v>17.91</v>
       </c>
       <c r="G65" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="H65" t="n">
         <v>14.7</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>8.18</v>
+        <v>-0.87</v>
       </c>
       <c r="M65" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -5673,13 +5673,13 @@
         <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="F66" t="n">
-        <v>19.84</v>
+        <v>20.21</v>
       </c>
       <c r="G66" t="n">
-        <v>4.68</v>
+        <v>4.77</v>
       </c>
       <c r="H66" t="n">
         <v>17.9</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1.3</v>
+        <v>1.89</v>
       </c>
       <c r="M66" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>119</v>
+        <v>119.5</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5831,13 +5831,13 @@
         <v>90</v>
       </c>
       <c r="E68" t="n">
-        <v>304.5</v>
+        <v>320.5</v>
       </c>
       <c r="F68" t="n">
-        <v>25.74</v>
+        <v>27.09</v>
       </c>
       <c r="G68" t="n">
-        <v>6.62</v>
+        <v>6.97</v>
       </c>
       <c r="H68" t="n">
         <v>27.5</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.22</v>
+        <v>5.25</v>
       </c>
       <c r="M68" t="n">
-        <v>295</v>
+        <v>304.5</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5910,13 +5910,13 @@
         <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="F69" t="n">
-        <v>14.39</v>
+        <v>14.51</v>
       </c>
       <c r="G69" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H69" t="n">
         <v>16.7</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.12</v>
+        <v>0.85</v>
       </c>
       <c r="M69" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5989,13 +5989,13 @@
         <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>125.5</v>
+        <v>129</v>
       </c>
       <c r="F70" t="n">
-        <v>17.48</v>
+        <v>17.97</v>
       </c>
       <c r="G70" t="n">
-        <v>4.34</v>
+        <v>4.46</v>
       </c>
       <c r="H70" t="n">
         <v>16.4</v>
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.4</v>
+        <v>2.79</v>
       </c>
       <c r="M70" t="n">
-        <v>125</v>
+        <v>125.5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>248</v>
+        <v>250.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>76</v>
       </c>
       <c r="E72" t="n">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="F72" t="n">
-        <v>45.74</v>
+        <v>48.71</v>
       </c>
       <c r="G72" t="n">
-        <v>24.43</v>
+        <v>26.01</v>
       </c>
       <c r="H72" t="n">
         <v>38.8</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.86</v>
+        <v>6.48</v>
       </c>
       <c r="M72" t="n">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6232,13 +6232,13 @@
         <v>68</v>
       </c>
       <c r="E73" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="F73" t="n">
-        <v>19.84</v>
+        <v>19.9</v>
       </c>
       <c r="G73" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="H73" t="n">
         <v>21.3</v>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-0.32</v>
+        <v>0.33</v>
       </c>
       <c r="M73" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6315,13 +6315,13 @@
         <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>3185</v>
+        <v>3430</v>
       </c>
       <c r="F74" t="n">
-        <v>42.46</v>
+        <v>45.72</v>
       </c>
       <c r="G74" t="n">
-        <v>22.66</v>
+        <v>24.4</v>
       </c>
       <c r="H74" t="n">
         <v>24.6</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.31</v>
+        <v>7.69</v>
       </c>
       <c r="M74" t="n">
-        <v>3175</v>
+        <v>3185</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -6394,13 +6394,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="F75" t="n">
-        <v>14.02</v>
+        <v>14.77</v>
       </c>
       <c r="G75" t="n">
-        <v>7.92</v>
+        <v>8.34</v>
       </c>
       <c r="H75" t="n">
         <v>14.2</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.56</v>
+        <v>5.32</v>
       </c>
       <c r="M75" t="n">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6473,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2425</v>
+        <v>2460</v>
       </c>
       <c r="F76" t="n">
-        <v>28.11</v>
+        <v>28.52</v>
       </c>
       <c r="G76" t="n">
-        <v>9.779999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="H76" t="n">
         <v>23.6</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M76" t="n">
-        <v>2380</v>
+        <v>2425</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6552,13 +6552,13 @@
         <v>97</v>
       </c>
       <c r="E77" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F77" t="n">
-        <v>16.55</v>
+        <v>17.83</v>
       </c>
       <c r="G77" t="n">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="H77" t="n">
         <v>12.4</v>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-2.93</v>
+        <v>7.76</v>
       </c>
       <c r="M77" t="n">
-        <v>119.5</v>
+        <v>116</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6631,13 +6631,13 @@
         <v>94</v>
       </c>
       <c r="E78" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="F78" t="n">
-        <v>13.37</v>
+        <v>13.55</v>
       </c>
       <c r="G78" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H78" t="n">
         <v>12.3</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M78" t="n">
         <v>108</v>
@@ -6710,13 +6710,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>25.25</v>
+        <v>26.35</v>
       </c>
       <c r="F79" t="n">
-        <v>5.07</v>
+        <v>5.29</v>
       </c>
       <c r="G79" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="H79" t="n">
         <v>5.9</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.4</v>
+        <v>4.36</v>
       </c>
       <c r="M79" t="n">
-        <v>25.15</v>
+        <v>25.25</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6789,13 +6789,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>107</v>
+        <v>109.5</v>
       </c>
       <c r="F80" t="n">
-        <v>12.33</v>
+        <v>12.62</v>
       </c>
       <c r="G80" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="H80" t="n">
         <v>10.7</v>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="M80" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6868,13 +6868,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>178.5</v>
+        <v>180</v>
       </c>
       <c r="F81" t="n">
-        <v>12.72</v>
+        <v>12.83</v>
       </c>
       <c r="G81" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="H81" t="n">
         <v>11.4</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.28</v>
+        <v>0.84</v>
       </c>
       <c r="M81" t="n">
-        <v>178</v>
+        <v>178.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6947,13 +6947,13 @@
         <v>92</v>
       </c>
       <c r="E82" t="n">
-        <v>42.05</v>
+        <v>41.75</v>
       </c>
       <c r="F82" t="n">
-        <v>8.85</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H82" t="n">
         <v>7.6</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.82</v>
+        <v>-0.71</v>
       </c>
       <c r="M82" t="n">
-        <v>41.3</v>
+        <v>42.05</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7026,13 +7026,13 @@
         <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="F83" t="n">
-        <v>23.36</v>
+        <v>23.64</v>
       </c>
       <c r="G83" t="n">
-        <v>8.949999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="H83" t="n">
         <v>25</v>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.91</v>
+        <v>1.23</v>
       </c>
       <c r="M83" t="n">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7105,13 +7105,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="F84" t="n">
-        <v>21.51</v>
+        <v>22.19</v>
       </c>
       <c r="G84" t="n">
-        <v>4.74</v>
+        <v>4.89</v>
       </c>
       <c r="H84" t="n">
         <v>21.2</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.4</v>
+        <v>3.19</v>
       </c>
       <c r="M84" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7184,13 +7184,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F85" t="n">
-        <v>17.42</v>
+        <v>17.96</v>
       </c>
       <c r="G85" t="n">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="H85" t="n">
         <v>14.1</v>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.93</v>
+        <v>3.09</v>
       </c>
       <c r="M85" t="n">
-        <v>160.5</v>
+        <v>162</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7263,13 +7263,13 @@
         <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>38.95</v>
+        <v>39.35</v>
       </c>
       <c r="F86" t="n">
-        <v>8.029999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H86" t="n">
         <v>6.2</v>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="M86" t="n">
-        <v>38.55</v>
+        <v>38.95</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7342,13 +7342,13 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>1800</v>
+        <v>1855</v>
       </c>
       <c r="F87" t="n">
-        <v>28.28</v>
+        <v>29.14</v>
       </c>
       <c r="G87" t="n">
-        <v>14.57</v>
+        <v>15.02</v>
       </c>
       <c r="H87" t="n">
         <v>30.7</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-2.17</v>
+        <v>3.06</v>
       </c>
       <c r="M87" t="n">
-        <v>1840</v>
+        <v>1800</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
@@ -7425,13 +7425,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1385</v>
+        <v>1480</v>
       </c>
       <c r="F88" t="n">
-        <v>31.94</v>
+        <v>34.13</v>
       </c>
       <c r="G88" t="n">
-        <v>9.720000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="H88" t="n">
         <v>21.8</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.84</v>
+        <v>6.86</v>
       </c>
       <c r="M88" t="n">
-        <v>1360</v>
+        <v>1385</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7508,13 +7508,13 @@
         <v>79</v>
       </c>
       <c r="E89" t="n">
-        <v>89.7</v>
+        <v>90.3</v>
       </c>
       <c r="F89" t="n">
-        <v>8.789999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="G89" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="H89" t="n">
         <v>8.6</v>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="M89" t="n">
-        <v>88.8</v>
+        <v>89.7</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7591,13 +7591,13 @@
         <v>78</v>
       </c>
       <c r="E90" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="F90" t="n">
-        <v>8.24</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H90" t="n">
         <v>6.8</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="M90" t="n">
-        <v>54.3</v>
+        <v>54.7</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7674,13 +7674,13 @@
         <v>77</v>
       </c>
       <c r="E91" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F91" t="n">
-        <v>7.12</v>
+        <v>7.21</v>
       </c>
       <c r="G91" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H91" t="n">
         <v>10.4</v>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.2</v>
+        <v>1.36</v>
       </c>
       <c r="M91" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7757,13 +7757,13 @@
         <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F92" t="n">
-        <v>14.99</v>
+        <v>14.95</v>
       </c>
       <c r="G92" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="H92" t="n">
         <v>13.2</v>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.03</v>
+        <v>-0.29</v>
       </c>
       <c r="M92" t="n">
-        <v>340.5</v>
+        <v>344</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7840,10 +7840,10 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="F93" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
       <c r="G93" t="n">
         <v>2.91</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1.39</v>
+        <v>0.23</v>
       </c>
       <c r="M93" t="n">
-        <v>2165</v>
+        <v>2135</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>183</v>
+        <v>186.5</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8006,13 +8006,13 @@
         <v>60</v>
       </c>
       <c r="E95" t="n">
-        <v>1480</v>
+        <v>1495</v>
       </c>
       <c r="F95" t="n">
-        <v>15.78</v>
+        <v>15.94</v>
       </c>
       <c r="G95" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="H95" t="n">
         <v>11.9</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.34</v>
+        <v>1.01</v>
       </c>
       <c r="M95" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8089,13 +8089,13 @@
         <v>79</v>
       </c>
       <c r="E96" t="n">
-        <v>69.7</v>
+        <v>70.3</v>
       </c>
       <c r="F96" t="n">
-        <v>4.88</v>
+        <v>4.93</v>
       </c>
       <c r="G96" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="M96" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         <v>77</v>
       </c>
       <c r="E97" t="n">
-        <v>395</v>
+        <v>396.5</v>
       </c>
       <c r="F97" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="G97" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-1.13</v>
+        <v>0.38</v>
       </c>
       <c r="M97" t="n">
-        <v>399.5</v>
+        <v>395</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="F98" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="G98" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
       <c r="M98" t="n">
-        <v>23.65</v>
+        <v>23.9</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>75</v>
       </c>
       <c r="E99" t="n">
-        <v>34.85</v>
+        <v>35.7</v>
       </c>
       <c r="F99" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="G99" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.14</v>
+        <v>2.44</v>
       </c>
       <c r="M99" t="n">
-        <v>34.8</v>
+        <v>34.85</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>69</v>
       </c>
       <c r="E100" t="n">
-        <v>204</v>
+        <v>205.5</v>
       </c>
       <c r="F100" t="n">
-        <v>5.07</v>
+        <v>5.11</v>
       </c>
       <c r="G100" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-2.86</v>
+        <v>0.74</v>
       </c>
       <c r="M100" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>32</v>
       </c>
       <c r="E101" t="n">
-        <v>47.4</v>
+        <v>48.15</v>
       </c>
       <c r="F101" t="n">
-        <v>11.7</v>
+        <v>11.89</v>
       </c>
       <c r="G101" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M101" t="n">
-        <v>46.7</v>
+        <v>47.4</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3185</v>
+        <v>3430</v>
       </c>
       <c r="F2" t="n">
-        <v>42.46</v>
+        <v>45.72</v>
       </c>
       <c r="G2" t="n">
-        <v>22.66</v>
+        <v>24.4</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.31</v>
+        <v>7.69</v>
       </c>
       <c r="M2" t="n">
-        <v>3175</v>
+        <v>3185</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="F3" t="n">
-        <v>14.02</v>
+        <v>14.77</v>
       </c>
       <c r="G3" t="n">
-        <v>7.92</v>
+        <v>8.34</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.56</v>
+        <v>5.32</v>
       </c>
       <c r="M3" t="n">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2425</v>
+        <v>2460</v>
       </c>
       <c r="F4" t="n">
-        <v>28.11</v>
+        <v>28.52</v>
       </c>
       <c r="G4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>2380</v>
+        <v>2425</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>16.55</v>
+        <v>17.83</v>
       </c>
       <c r="G5" t="n">
-        <v>3.66</v>
+        <v>3.95</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.93</v>
+        <v>7.76</v>
       </c>
       <c r="M5" t="n">
-        <v>119.5</v>
+        <v>116</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.37</v>
+        <v>13.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>108</v>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.25</v>
+        <v>26.35</v>
       </c>
       <c r="F7" t="n">
-        <v>5.07</v>
+        <v>5.29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>4.36</v>
       </c>
       <c r="M7" t="n">
-        <v>25.15</v>
+        <v>25.25</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>109.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.33</v>
+        <v>12.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="M8" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>178.5</v>
+        <v>180</v>
       </c>
       <c r="F9" t="n">
-        <v>12.72</v>
+        <v>12.83</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.28</v>
+        <v>0.84</v>
       </c>
       <c r="M9" t="n">
-        <v>178</v>
+        <v>178.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.05</v>
+        <v>41.75</v>
       </c>
       <c r="F10" t="n">
-        <v>8.85</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>-0.71</v>
       </c>
       <c r="M10" t="n">
-        <v>41.3</v>
+        <v>42.05</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="F11" t="n">
-        <v>23.36</v>
+        <v>23.64</v>
       </c>
       <c r="G11" t="n">
-        <v>8.949999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.91</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="F12" t="n">
-        <v>21.51</v>
+        <v>22.19</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74</v>
+        <v>4.89</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.4</v>
+        <v>3.19</v>
       </c>
       <c r="M12" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F13" t="n">
-        <v>17.42</v>
+        <v>17.96</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.93</v>
+        <v>3.09</v>
       </c>
       <c r="M13" t="n">
-        <v>160.5</v>
+        <v>162</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.95</v>
+        <v>39.35</v>
       </c>
       <c r="F14" t="n">
-        <v>8.029999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="M14" t="n">
-        <v>38.55</v>
+        <v>38.95</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1800</v>
+        <v>1855</v>
       </c>
       <c r="F15" t="n">
-        <v>28.28</v>
+        <v>29.14</v>
       </c>
       <c r="G15" t="n">
-        <v>14.57</v>
+        <v>15.02</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-2.17</v>
+        <v>3.06</v>
       </c>
       <c r="M15" t="n">
-        <v>1840</v>
+        <v>1800</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1385</v>
+        <v>1480</v>
       </c>
       <c r="F16" t="n">
-        <v>31.94</v>
+        <v>34.13</v>
       </c>
       <c r="G16" t="n">
-        <v>9.720000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>6.86</v>
       </c>
       <c r="M16" t="n">
-        <v>1360</v>
+        <v>1385</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.7</v>
+        <v>90.3</v>
       </c>
       <c r="F17" t="n">
-        <v>8.789999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="M17" t="n">
-        <v>88.8</v>
+        <v>89.7</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="F18" t="n">
-        <v>8.24</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="M18" t="n">
-        <v>54.3</v>
+        <v>54.7</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
-        <v>7.12</v>
+        <v>7.21</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.2</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F20" t="n">
-        <v>14.99</v>
+        <v>14.95</v>
       </c>
       <c r="G20" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.03</v>
+        <v>-0.29</v>
       </c>
       <c r="M20" t="n">
-        <v>340.5</v>
+        <v>344</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,10 +10227,10 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="F21" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
       <c r="G21" t="n">
         <v>2.91</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.39</v>
+        <v>0.23</v>
       </c>
       <c r="M21" t="n">
-        <v>2165</v>
+        <v>2135</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>183</v>
+        <v>186.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1480</v>
+        <v>1495</v>
       </c>
       <c r="F23" t="n">
-        <v>15.78</v>
+        <v>15.94</v>
       </c>
       <c r="G23" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.34</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>172</v>
+        <v>170.5</v>
       </c>
       <c r="F2" t="n">
-        <v>18.07</v>
+        <v>17.91</v>
       </c>
       <c r="G2" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8.18</v>
+        <v>-0.87</v>
       </c>
       <c r="M2" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="F3" t="n">
-        <v>19.84</v>
+        <v>20.21</v>
       </c>
       <c r="G3" t="n">
-        <v>4.68</v>
+        <v>4.77</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.3</v>
+        <v>1.89</v>
       </c>
       <c r="M3" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>119</v>
+        <v>119.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>304.5</v>
+        <v>320.5</v>
       </c>
       <c r="F5" t="n">
-        <v>25.74</v>
+        <v>27.09</v>
       </c>
       <c r="G5" t="n">
-        <v>6.62</v>
+        <v>6.97</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.22</v>
+        <v>5.25</v>
       </c>
       <c r="M5" t="n">
-        <v>295</v>
+        <v>304.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="F6" t="n">
-        <v>14.39</v>
+        <v>14.51</v>
       </c>
       <c r="G6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.12</v>
+        <v>0.85</v>
       </c>
       <c r="M6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>125.5</v>
+        <v>129</v>
       </c>
       <c r="F7" t="n">
-        <v>17.48</v>
+        <v>17.97</v>
       </c>
       <c r="G7" t="n">
-        <v>4.34</v>
+        <v>4.46</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>2.79</v>
       </c>
       <c r="M7" t="n">
-        <v>125</v>
+        <v>125.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>248</v>
+        <v>250.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="F9" t="n">
-        <v>45.74</v>
+        <v>48.71</v>
       </c>
       <c r="G9" t="n">
-        <v>24.43</v>
+        <v>26.01</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.86</v>
+        <v>6.48</v>
       </c>
       <c r="M9" t="n">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="F10" t="n">
-        <v>19.84</v>
+        <v>19.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.32</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>61.7</v>
+        <v>61.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1300</v>
+        <v>1430</v>
       </c>
       <c r="F2" t="n">
-        <v>87.54000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="G2" t="n">
-        <v>23.61</v>
+        <v>25.97</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>1300</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>155.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.22</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="F5" t="n">
-        <v>117.77</v>
+        <v>124.2</v>
       </c>
       <c r="G5" t="n">
-        <v>33.88</v>
+        <v>35.73</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.79</v>
+        <v>5.45</v>
       </c>
       <c r="M5" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>124.5</v>
+        <v>124</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.67</v>
+        <v>27.81</v>
       </c>
       <c r="G7" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8</v>
+        <v>101</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172.5</v>
+        <v>174</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>22.19</v>
       </c>
       <c r="G8" t="n">
-        <v>4.82</v>
+        <v>4.86</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="M8" t="n">
-        <v>170.5</v>
+        <v>172.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="F9" t="n">
-        <v>25.91</v>
+        <v>26.03</v>
       </c>
       <c r="G9" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.72</v>
+        <v>17.84</v>
       </c>
       <c r="G10" t="n">
-        <v>6.28</v>
+        <v>6.32</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>156</v>
+        <v>156.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1245</v>
+        <v>1220</v>
       </c>
       <c r="F11" t="n">
-        <v>23.92</v>
+        <v>23.44</v>
       </c>
       <c r="G11" t="n">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>-2.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>163</v>
+        <v>163.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.32</v>
+        <v>20.39</v>
       </c>
       <c r="G12" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.52</v>
+        <v>0.31</v>
       </c>
       <c r="M12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F13" t="n">
-        <v>32.51</v>
+        <v>32.98</v>
       </c>
       <c r="G13" t="n">
-        <v>6.58</v>
+        <v>6.68</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.36</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.49</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.05</v>
+        <v>0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>143.5</v>
+        <v>145</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>217.5</v>
+        <v>216.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.59</v>
+        <v>19.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.52</v>
+        <v>5.49</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.16</v>
+        <v>-0.46</v>
       </c>
       <c r="M15" t="n">
-        <v>215</v>
+        <v>217.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>6500</v>
+        <v>7150</v>
       </c>
       <c r="F16" t="n">
-        <v>166.62</v>
+        <v>183.29</v>
       </c>
       <c r="G16" t="n">
-        <v>64.69</v>
+        <v>71.16</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.35</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>6170</v>
+        <v>6500</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1685</v>
+        <v>1735</v>
       </c>
       <c r="F2" t="n">
-        <v>53.63</v>
+        <v>55.22</v>
       </c>
       <c r="G2" t="n">
-        <v>14.9</v>
+        <v>15.34</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.46</v>
+        <v>2.97</v>
       </c>
       <c r="M2" t="n">
-        <v>1710</v>
+        <v>1685</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>21.35</v>
+        <v>21.21</v>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.36</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>5355</v>
+        <v>5525</v>
       </c>
       <c r="F4" t="n">
-        <v>120.85</v>
+        <v>124.69</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33</v>
+        <v>34.38</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>3.17</v>
       </c>
       <c r="M4" t="n">
-        <v>5240</v>
+        <v>5355</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4695</v>
+        <v>4890</v>
       </c>
       <c r="F5" t="n">
-        <v>73.42</v>
+        <v>76.47</v>
       </c>
       <c r="G5" t="n">
-        <v>28.84</v>
+        <v>30.04</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-7.67</v>
+        <v>4.15</v>
       </c>
       <c r="M5" t="n">
-        <v>5085</v>
+        <v>4695</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="F6" t="n">
-        <v>46.14</v>
+        <v>47.19</v>
       </c>
       <c r="G6" t="n">
-        <v>24.19</v>
+        <v>24.74</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.14</v>
+        <v>2.27</v>
       </c>
       <c r="M6" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.99</v>
+        <v>11.98</v>
       </c>
       <c r="G7" t="n">
         <v>1.68</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.83</v>
+        <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>154</v>
+        <v>155.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.85</v>
+        <v>11.96</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="M8" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>108.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.45</v>
+        <v>15.82</v>
       </c>
       <c r="G9" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>106</v>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="F10" t="n">
-        <v>26.11</v>
+        <v>26.3</v>
       </c>
       <c r="G10" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3.98</v>
+        <v>0.73</v>
       </c>
       <c r="M10" t="n">
-        <v>1005</v>
+        <v>965</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>197.5</v>
+        <v>199.5</v>
       </c>
       <c r="F11" t="n">
-        <v>27.2</v>
+        <v>27.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>195.5</v>
+        <v>197.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3295</v>
+        <v>3540</v>
       </c>
       <c r="F12" t="n">
-        <v>48.33</v>
+        <v>51.92</v>
       </c>
       <c r="G12" t="n">
-        <v>4.71</v>
+        <v>5.06</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.49</v>
+        <v>7.44</v>
       </c>
       <c r="M12" t="n">
-        <v>3345</v>
+        <v>3295</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1430</v>
+        <v>1505</v>
       </c>
       <c r="F2" t="n">
-        <v>96.3</v>
+        <v>101.35</v>
       </c>
       <c r="G2" t="n">
-        <v>25.97</v>
+        <v>27.33</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>5.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1300</v>
+        <v>1430</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.7</v>
+        <v>40.75</v>
       </c>
       <c r="F3" t="n">
-        <v>9.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.81</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M3" t="n">
         <v>40.7</v>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>155.5</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.22</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>155.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5800</v>
+        <v>5495</v>
       </c>
       <c r="F5" t="n">
-        <v>124.2</v>
+        <v>117.67</v>
       </c>
       <c r="G5" t="n">
-        <v>35.73</v>
+        <v>33.85</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.45</v>
+        <v>-5.26</v>
       </c>
       <c r="M5" t="n">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44</v>
+        <v>23.53</v>
       </c>
       <c r="G6" t="n">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
         <v>124</v>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.81</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.99</v>
       </c>
       <c r="M7" t="n">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8" t="n">
-        <v>22.19</v>
+        <v>22.32</v>
       </c>
       <c r="G8" t="n">
-        <v>4.86</v>
+        <v>4.89</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.87</v>
+        <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>172.5</v>
+        <v>174</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>26.03</v>
+        <v>25.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>-0.93</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>157.5</v>
+        <v>158.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.84</v>
+        <v>17.95</v>
       </c>
       <c r="G10" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="M10" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1220</v>
+        <v>1240</v>
       </c>
       <c r="F11" t="n">
-        <v>23.44</v>
+        <v>23.82</v>
       </c>
       <c r="G11" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>1245</v>
+        <v>1220</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>163.5</v>
+        <v>161.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.39</v>
+        <v>20.14</v>
       </c>
       <c r="G12" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.31</v>
+        <v>-1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>163</v>
+        <v>163.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>282</v>
+        <v>288.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.98</v>
+        <v>33.74</v>
       </c>
       <c r="G13" t="n">
-        <v>6.68</v>
+        <v>6.83</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>144.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.39</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.34</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>216.5</v>
+        <v>215</v>
       </c>
       <c r="F15" t="n">
-        <v>19.5</v>
+        <v>19.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.46</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>217.5</v>
+        <v>216.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7150</v>
+        <v>7615</v>
       </c>
       <c r="F16" t="n">
-        <v>183.29</v>
+        <v>195.21</v>
       </c>
       <c r="G16" t="n">
-        <v>71.16</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="M16" t="n">
-        <v>6500</v>
+        <v>7150</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1575</v>
+        <v>1525</v>
       </c>
       <c r="F17" t="n">
-        <v>46.6</v>
+        <v>45.12</v>
       </c>
       <c r="G17" t="n">
-        <v>9.460000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.3</v>
+        <v>-3.17</v>
       </c>
       <c r="M17" t="n">
-        <v>1510</v>
+        <v>1575</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12495</v>
+        <v>12800</v>
       </c>
       <c r="F18" t="n">
-        <v>68.88</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>35.28</v>
+        <v>36.14</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>12295</v>
+        <v>12495</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="F19" t="n">
-        <v>76.19</v>
+        <v>77.72</v>
       </c>
       <c r="G19" t="n">
-        <v>14.79</v>
+        <v>15.08</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.94</v>
+        <v>2.01</v>
       </c>
       <c r="M19" t="n">
-        <v>815</v>
+        <v>896</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>83.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>45.66</v>
+        <v>45.05</v>
       </c>
       <c r="G20" t="n">
-        <v>6.83</v>
+        <v>6.74</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.96</v>
+        <v>-1.32</v>
       </c>
       <c r="M20" t="n">
-        <v>81.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6435</v>
+        <v>5795</v>
       </c>
       <c r="F21" t="n">
-        <v>105.35</v>
+        <v>94.88</v>
       </c>
       <c r="G21" t="n">
-        <v>27.21</v>
+        <v>24.5</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.15</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>6120</v>
+        <v>6435</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2290</v>
+        <v>2375</v>
       </c>
       <c r="F22" t="n">
-        <v>58.42</v>
+        <v>60.59</v>
       </c>
       <c r="G22" t="n">
-        <v>29.4</v>
+        <v>30.5</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>9.83</v>
+        <v>3.71</v>
       </c>
       <c r="M22" t="n">
-        <v>2085</v>
+        <v>2290</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="F23" t="n">
-        <v>42.05</v>
+        <v>41.82</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.27</v>
+        <v>-0.54</v>
       </c>
       <c r="M23" t="n">
-        <v>18.45</v>
+        <v>18.5</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1370</v>
+        <v>1435</v>
       </c>
       <c r="F24" t="n">
-        <v>69.58</v>
+        <v>72.88</v>
       </c>
       <c r="G24" t="n">
-        <v>16.98</v>
+        <v>17.78</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.79</v>
+        <v>4.74</v>
       </c>
       <c r="M24" t="n">
-        <v>1320</v>
+        <v>1370</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="F25" t="n">
-        <v>71.59</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>8.1</v>
+        <v>0.17</v>
       </c>
       <c r="M25" t="n">
-        <v>54.3</v>
+        <v>58.7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="F26" t="n">
-        <v>247.85</v>
+        <v>247.42</v>
       </c>
       <c r="G26" t="n">
-        <v>56.46</v>
+        <v>56.36</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.88</v>
+        <v>-0.17</v>
       </c>
       <c r="M26" t="n">
-        <v>2720</v>
+        <v>2880</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="F27" t="n">
-        <v>46.16</v>
+        <v>47.97</v>
       </c>
       <c r="G27" t="n">
-        <v>7.21</v>
+        <v>7.49</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="M27" t="n">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1180</v>
+        <v>1150</v>
       </c>
       <c r="F28" t="n">
-        <v>57.79</v>
+        <v>56.32</v>
       </c>
       <c r="G28" t="n">
-        <v>11.97</v>
+        <v>11.67</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-1.26</v>
+        <v>-2.54</v>
       </c>
       <c r="M28" t="n">
-        <v>1195</v>
+        <v>1180</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>101.15</v>
       </c>
       <c r="G29" t="n">
-        <v>19.6</v>
+        <v>19.82</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>9.890000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="M29" t="n">
-        <v>556</v>
+        <v>611</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3520</v>
+        <v>3485</v>
       </c>
       <c r="F30" t="n">
-        <v>83.02</v>
+        <v>82.19</v>
       </c>
       <c r="G30" t="n">
-        <v>11.45</v>
+        <v>11.33</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>10</v>
+        <v>-0.99</v>
       </c>
       <c r="M30" t="n">
-        <v>3200</v>
+        <v>3520</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="F31" t="n">
-        <v>109.13</v>
+        <v>110.55</v>
       </c>
       <c r="G31" t="n">
-        <v>14.03</v>
+        <v>14.21</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.48</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="F32" t="n">
-        <v>43.7</v>
+        <v>44.71</v>
       </c>
       <c r="G32" t="n">
-        <v>10.84</v>
+        <v>11.09</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.58</v>
+        <v>2.32</v>
       </c>
       <c r="M32" t="n">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="F33" t="n">
-        <v>37.04</v>
+        <v>37.51</v>
       </c>
       <c r="G33" t="n">
-        <v>6.39</v>
+        <v>6.48</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.97</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4710</v>
+        <v>5010</v>
       </c>
       <c r="F34" t="n">
-        <v>77.79000000000001</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>17.72</v>
+        <v>18.85</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.67</v>
+        <v>6.37</v>
       </c>
       <c r="M34" t="n">
-        <v>4500</v>
+        <v>4710</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1735</v>
+        <v>1875</v>
       </c>
       <c r="F35" t="n">
-        <v>55.22</v>
+        <v>59.68</v>
       </c>
       <c r="G35" t="n">
-        <v>15.34</v>
+        <v>16.58</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>8.07</v>
       </c>
       <c r="M35" t="n">
-        <v>1685</v>
+        <v>1735</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>72.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="F36" t="n">
-        <v>21.21</v>
+        <v>20.97</v>
       </c>
       <c r="G36" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.11</v>
       </c>
       <c r="M36" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>5525</v>
+        <v>5790</v>
       </c>
       <c r="F37" t="n">
-        <v>124.69</v>
+        <v>130.67</v>
       </c>
       <c r="G37" t="n">
-        <v>34.38</v>
+        <v>36.03</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.17</v>
+        <v>4.8</v>
       </c>
       <c r="M37" t="n">
-        <v>5355</v>
+        <v>5525</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>4890</v>
+        <v>4895</v>
       </c>
       <c r="F38" t="n">
-        <v>76.47</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>30.04</v>
+        <v>30.07</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.15</v>
+        <v>0.1</v>
       </c>
       <c r="M38" t="n">
-        <v>4695</v>
+        <v>4890</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F39" t="n">
-        <v>47.19</v>
+        <v>46.99</v>
       </c>
       <c r="G39" t="n">
-        <v>24.74</v>
+        <v>24.64</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.27</v>
+        <v>-0.42</v>
       </c>
       <c r="M39" t="n">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,13 +3605,13 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="F40" t="n">
-        <v>11.98</v>
+        <v>11.95</v>
       </c>
       <c r="G40" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H40" t="n">
         <v>11</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="M40" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,10 +3684,10 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>155.5</v>
+        <v>155</v>
       </c>
       <c r="F41" t="n">
-        <v>11.96</v>
+        <v>11.92</v>
       </c>
       <c r="G41" t="n">
         <v>2.08</v>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.97</v>
+        <v>-0.32</v>
       </c>
       <c r="M41" t="n">
-        <v>154</v>
+        <v>155.5</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="F42" t="n">
-        <v>15.82</v>
+        <v>15.52</v>
       </c>
       <c r="G42" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.36</v>
+        <v>-1.84</v>
       </c>
       <c r="M42" t="n">
-        <v>106</v>
+        <v>108.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="F43" t="n">
-        <v>26.3</v>
+        <v>25.76</v>
       </c>
       <c r="G43" t="n">
-        <v>4.05</v>
+        <v>3.97</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.73</v>
+        <v>-2.06</v>
       </c>
       <c r="M43" t="n">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>199.5</v>
+        <v>198.5</v>
       </c>
       <c r="F44" t="n">
-        <v>27.48</v>
+        <v>27.34</v>
       </c>
       <c r="G44" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>-0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>197.5</v>
+        <v>199.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3540</v>
+        <v>3665</v>
       </c>
       <c r="F45" t="n">
-        <v>51.92</v>
+        <v>53.75</v>
       </c>
       <c r="G45" t="n">
-        <v>5.06</v>
+        <v>5.24</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>7.44</v>
+        <v>3.53</v>
       </c>
       <c r="M45" t="n">
-        <v>3295</v>
+        <v>3540</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F46" t="n">
-        <v>22</v>
+        <v>21.69</v>
       </c>
       <c r="G46" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.6</v>
+        <v>-1.39</v>
       </c>
       <c r="M46" t="n">
-        <v>208.5</v>
+        <v>216</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="F47" t="n">
-        <v>20.16</v>
+        <v>20.24</v>
       </c>
       <c r="G47" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.77</v>
+        <v>0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>119.5</v>
+        <v>124</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4249,13 +4249,13 @@
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>227.5</v>
+        <v>234</v>
       </c>
       <c r="F48" t="n">
-        <v>24.92</v>
+        <v>25.63</v>
       </c>
       <c r="G48" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.44</v>
+        <v>2.86</v>
       </c>
       <c r="M48" t="n">
-        <v>226.5</v>
+        <v>227.5</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4326,13 +4326,13 @@
         <v>62</v>
       </c>
       <c r="E49" t="n">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="F49" t="n">
-        <v>20.37</v>
+        <v>20.02</v>
       </c>
       <c r="G49" t="n">
-        <v>5.62</v>
+        <v>5.52</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>7.58</v>
+        <v>-1.71</v>
       </c>
       <c r="M49" t="n">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4405,13 +4405,13 @@
         <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="F50" t="n">
-        <v>26.36</v>
+        <v>26.83</v>
       </c>
       <c r="G50" t="n">
-        <v>7.43</v>
+        <v>7.56</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4486,13 +4486,13 @@
         <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>111</v>
+        <v>109.5</v>
       </c>
       <c r="F51" t="n">
-        <v>20.71</v>
+        <v>20.43</v>
       </c>
       <c r="G51" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.78</v>
+        <v>-1.35</v>
       </c>
       <c r="M51" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>6430</v>
+        <v>6400</v>
       </c>
       <c r="F52" t="n">
-        <v>34.2</v>
+        <v>34.04</v>
       </c>
       <c r="G52" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>6.81</v>
+        <v>-0.47</v>
       </c>
       <c r="M52" t="n">
-        <v>6020</v>
+        <v>6430</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="F53" t="n">
-        <v>24.46</v>
+        <v>24.23</v>
       </c>
       <c r="G53" t="n">
-        <v>6.66</v>
+        <v>6.6</v>
       </c>
       <c r="H53" t="n">
         <v>29.3</v>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.65</v>
+        <v>-0.93</v>
       </c>
       <c r="M53" t="n">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4806,13 +4806,13 @@
         <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="F55" t="n">
-        <v>16.43</v>
+        <v>16.35</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="H55" t="n">
         <v>17.3</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.7</v>
+        <v>-0.5</v>
       </c>
       <c r="M55" t="n">
-        <v>58.8</v>
+        <v>59.8</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4885,13 +4885,13 @@
         <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>186.5</v>
+        <v>180.5</v>
       </c>
       <c r="F56" t="n">
-        <v>17.03</v>
+        <v>16.48</v>
       </c>
       <c r="G56" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="H56" t="n">
         <v>15.5</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4.78</v>
+        <v>-3.22</v>
       </c>
       <c r="M56" t="n">
-        <v>178</v>
+        <v>186.5</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>324.5</v>
+        <v>341.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5041,13 +5041,13 @@
         <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>167</v>
+        <v>166.5</v>
       </c>
       <c r="F58" t="n">
-        <v>18.79</v>
+        <v>18.73</v>
       </c>
       <c r="G58" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.21</v>
+        <v>-0.3</v>
       </c>
       <c r="M58" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="F59" t="n">
-        <v>17.23</v>
+        <v>17.14</v>
       </c>
       <c r="G59" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.69</v>
+        <v>-0.55</v>
       </c>
       <c r="M59" t="n">
-        <v>88.8</v>
+        <v>90.3</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>157</v>
+        <v>154.5</v>
       </c>
       <c r="F60" t="n">
-        <v>17.5</v>
+        <v>17.22</v>
       </c>
       <c r="G60" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.61</v>
+        <v>-1.59</v>
       </c>
       <c r="M60" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5280,13 +5280,13 @@
         <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>242.5</v>
+        <v>238</v>
       </c>
       <c r="F61" t="n">
-        <v>15.07</v>
+        <v>14.79</v>
       </c>
       <c r="G61" t="n">
-        <v>5.48</v>
+        <v>5.38</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.3</v>
+        <v>-1.86</v>
       </c>
       <c r="M61" t="n">
-        <v>232.5</v>
+        <v>242.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5357,13 +5357,13 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F62" t="n">
-        <v>15.7</v>
+        <v>15.53</v>
       </c>
       <c r="G62" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.92</v>
+        <v>-1.08</v>
       </c>
       <c r="M62" t="n">
-        <v>182.5</v>
+        <v>186</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5434,13 +5434,13 @@
         <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="F63" t="n">
-        <v>16.84</v>
+        <v>16.73</v>
       </c>
       <c r="G63" t="n">
-        <v>13.59</v>
+        <v>13.5</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.55</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>179.5</v>
+        <v>174</v>
       </c>
       <c r="F64" t="n">
-        <v>19.79</v>
+        <v>19.18</v>
       </c>
       <c r="G64" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5.59</v>
+        <v>-3.06</v>
       </c>
       <c r="M64" t="n">
-        <v>170</v>
+        <v>179.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>97</v>
       </c>
       <c r="E65" t="n">
-        <v>170.5</v>
+        <v>166</v>
       </c>
       <c r="F65" t="n">
-        <v>17.91</v>
+        <v>17.44</v>
       </c>
       <c r="G65" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="H65" t="n">
         <v>14.7</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-0.87</v>
+        <v>-2.64</v>
       </c>
       <c r="M65" t="n">
-        <v>172</v>
+        <v>170.5</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -5673,13 +5673,13 @@
         <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F66" t="n">
-        <v>20.21</v>
+        <v>20.1</v>
       </c>
       <c r="G66" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="H66" t="n">
         <v>17.9</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.89</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M66" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5752,13 +5752,13 @@
         <v>91</v>
       </c>
       <c r="E67" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="F67" t="n">
-        <v>15.44</v>
+        <v>15.37</v>
       </c>
       <c r="G67" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H67" t="n">
         <v>15</v>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M67" t="n">
         <v>119.5</v>
@@ -5831,13 +5831,13 @@
         <v>90</v>
       </c>
       <c r="E68" t="n">
-        <v>320.5</v>
+        <v>322</v>
       </c>
       <c r="F68" t="n">
-        <v>27.09</v>
+        <v>27.22</v>
       </c>
       <c r="G68" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="H68" t="n">
         <v>27.5</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.25</v>
+        <v>0.47</v>
       </c>
       <c r="M68" t="n">
-        <v>304.5</v>
+        <v>320.5</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5910,13 +5910,13 @@
         <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="F69" t="n">
-        <v>14.51</v>
+        <v>14.42</v>
       </c>
       <c r="G69" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H69" t="n">
         <v>16.7</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.85</v>
+        <v>-0.6</v>
       </c>
       <c r="M69" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5989,13 +5989,13 @@
         <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F70" t="n">
-        <v>17.97</v>
+        <v>17.69</v>
       </c>
       <c r="G70" t="n">
-        <v>4.46</v>
+        <v>4.39</v>
       </c>
       <c r="H70" t="n">
         <v>16.4</v>
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.79</v>
+        <v>-1.55</v>
       </c>
       <c r="M70" t="n">
-        <v>125.5</v>
+        <v>129</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
@@ -6072,10 +6072,10 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>250.5</v>
+        <v>250</v>
       </c>
       <c r="F71" t="n">
-        <v>16.51</v>
+        <v>16.48</v>
       </c>
       <c r="G71" t="n">
         <v>1.84</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M71" t="n">
         <v>250.5</v>
@@ -6151,13 +6151,13 @@
         <v>76</v>
       </c>
       <c r="E72" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="F72" t="n">
-        <v>48.71</v>
+        <v>46.59</v>
       </c>
       <c r="G72" t="n">
-        <v>26.01</v>
+        <v>24.88</v>
       </c>
       <c r="H72" t="n">
         <v>38.8</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>6.48</v>
+        <v>-4.35</v>
       </c>
       <c r="M72" t="n">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6232,10 +6232,10 @@
         <v>68</v>
       </c>
       <c r="E73" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="F73" t="n">
-        <v>19.9</v>
+        <v>19.94</v>
       </c>
       <c r="G73" t="n">
         <v>2.85</v>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="M73" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6315,13 +6315,13 @@
         <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>3430</v>
+        <v>3415</v>
       </c>
       <c r="F74" t="n">
-        <v>45.72</v>
+        <v>45.52</v>
       </c>
       <c r="G74" t="n">
-        <v>24.4</v>
+        <v>24.29</v>
       </c>
       <c r="H74" t="n">
         <v>24.6</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>7.69</v>
+        <v>-0.44</v>
       </c>
       <c r="M74" t="n">
-        <v>3185</v>
+        <v>3430</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -6394,13 +6394,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="F75" t="n">
-        <v>14.77</v>
+        <v>14.46</v>
       </c>
       <c r="G75" t="n">
-        <v>8.34</v>
+        <v>8.17</v>
       </c>
       <c r="H75" t="n">
         <v>14.2</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>5.32</v>
+        <v>-2.05</v>
       </c>
       <c r="M75" t="n">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6473,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2460</v>
+        <v>2480</v>
       </c>
       <c r="F76" t="n">
-        <v>28.52</v>
+        <v>28.75</v>
       </c>
       <c r="G76" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="H76" t="n">
         <v>23.6</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.44</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M76" t="n">
-        <v>2425</v>
+        <v>2460</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6552,13 +6552,13 @@
         <v>97</v>
       </c>
       <c r="E77" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F77" t="n">
-        <v>17.83</v>
+        <v>17.26</v>
       </c>
       <c r="G77" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="H77" t="n">
         <v>12.4</v>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>7.76</v>
+        <v>-3.2</v>
       </c>
       <c r="M77" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6710,13 +6710,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>26.35</v>
+        <v>25.95</v>
       </c>
       <c r="F79" t="n">
-        <v>5.29</v>
+        <v>5.21</v>
       </c>
       <c r="G79" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>5.9</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.36</v>
+        <v>-1.52</v>
       </c>
       <c r="M79" t="n">
-        <v>25.25</v>
+        <v>26.35</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6789,13 +6789,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>109.5</v>
+        <v>107.5</v>
       </c>
       <c r="F80" t="n">
-        <v>12.62</v>
+        <v>12.38</v>
       </c>
       <c r="G80" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="H80" t="n">
         <v>10.7</v>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.34</v>
+        <v>-1.83</v>
       </c>
       <c r="M80" t="n">
-        <v>107</v>
+        <v>109.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6868,13 +6868,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="F81" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="G81" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="H81" t="n">
         <v>11.4</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.84</v>
+        <v>-0.28</v>
       </c>
       <c r="M81" t="n">
-        <v>178.5</v>
+        <v>180</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6947,13 +6947,13 @@
         <v>92</v>
       </c>
       <c r="E82" t="n">
-        <v>41.75</v>
+        <v>41.95</v>
       </c>
       <c r="F82" t="n">
-        <v>8.789999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="G82" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H82" t="n">
         <v>7.6</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-0.71</v>
+        <v>0.48</v>
       </c>
       <c r="M82" t="n">
-        <v>42.05</v>
+        <v>41.75</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7026,13 +7026,13 @@
         <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="F83" t="n">
-        <v>23.64</v>
+        <v>23.59</v>
       </c>
       <c r="G83" t="n">
-        <v>9.06</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H83" t="n">
         <v>25</v>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.23</v>
+        <v>-0.22</v>
       </c>
       <c r="M83" t="n">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7105,13 +7105,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F84" t="n">
-        <v>22.19</v>
+        <v>22.45</v>
       </c>
       <c r="G84" t="n">
-        <v>4.89</v>
+        <v>4.94</v>
       </c>
       <c r="H84" t="n">
         <v>21.2</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.19</v>
+        <v>1.16</v>
       </c>
       <c r="M84" t="n">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7184,13 +7184,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>167</v>
+        <v>166.5</v>
       </c>
       <c r="F85" t="n">
-        <v>17.96</v>
+        <v>17.9</v>
       </c>
       <c r="G85" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="H85" t="n">
         <v>14.1</v>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.09</v>
+        <v>-0.3</v>
       </c>
       <c r="M85" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7263,13 +7263,13 @@
         <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>39.35</v>
+        <v>39.05</v>
       </c>
       <c r="F86" t="n">
-        <v>8.109999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H86" t="n">
         <v>6.2</v>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.03</v>
+        <v>-0.76</v>
       </c>
       <c r="M86" t="n">
-        <v>38.95</v>
+        <v>39.35</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7342,13 +7342,13 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>1855</v>
+        <v>1840</v>
       </c>
       <c r="F87" t="n">
-        <v>29.14</v>
+        <v>28.91</v>
       </c>
       <c r="G87" t="n">
-        <v>15.02</v>
+        <v>14.9</v>
       </c>
       <c r="H87" t="n">
         <v>30.7</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.06</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>1800</v>
+        <v>1855</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
@@ -7425,13 +7425,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="F88" t="n">
-        <v>34.13</v>
+        <v>35.06</v>
       </c>
       <c r="G88" t="n">
-        <v>10.39</v>
+        <v>10.67</v>
       </c>
       <c r="H88" t="n">
         <v>21.8</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>6.86</v>
+        <v>2.7</v>
       </c>
       <c r="M88" t="n">
-        <v>1385</v>
+        <v>1480</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7508,13 +7508,13 @@
         <v>79</v>
       </c>
       <c r="E89" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="F89" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="H89" t="n">
         <v>8.6</v>
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.67</v>
+        <v>-0.55</v>
       </c>
       <c r="M89" t="n">
-        <v>89.7</v>
+        <v>90.3</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7591,13 +7591,13 @@
         <v>78</v>
       </c>
       <c r="E90" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="F90" t="n">
-        <v>8.300000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H90" t="n">
         <v>6.8</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="M90" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7674,13 +7674,13 @@
         <v>77</v>
       </c>
       <c r="E91" t="n">
-        <v>52</v>
+        <v>52.7</v>
       </c>
       <c r="F91" t="n">
-        <v>7.21</v>
+        <v>7.31</v>
       </c>
       <c r="G91" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H91" t="n">
         <v>10.4</v>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M91" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7757,13 +7757,13 @@
         <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>343</v>
+        <v>344.5</v>
       </c>
       <c r="F92" t="n">
-        <v>14.95</v>
+        <v>15.01</v>
       </c>
       <c r="G92" t="n">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="H92" t="n">
         <v>13.2</v>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.29</v>
+        <v>0.44</v>
       </c>
       <c r="M92" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7840,13 +7840,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="F93" t="n">
-        <v>6.86</v>
+        <v>6.89</v>
       </c>
       <c r="G93" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="H93" t="n">
         <v>9.6</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="M93" t="n">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -8006,13 +8006,13 @@
         <v>60</v>
       </c>
       <c r="E95" t="n">
-        <v>1495</v>
+        <v>1475</v>
       </c>
       <c r="F95" t="n">
-        <v>15.94</v>
+        <v>15.73</v>
       </c>
       <c r="G95" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="H95" t="n">
         <v>11.9</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.01</v>
+        <v>-1.34</v>
       </c>
       <c r="M95" t="n">
-        <v>1480</v>
+        <v>1495</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8089,13 +8089,13 @@
         <v>79</v>
       </c>
       <c r="E96" t="n">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
       <c r="F96" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="G96" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.86</v>
+        <v>-1.14</v>
       </c>
       <c r="M96" t="n">
-        <v>69.7</v>
+        <v>70.3</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         <v>77</v>
       </c>
       <c r="E97" t="n">
-        <v>396.5</v>
+        <v>389</v>
       </c>
       <c r="F97" t="n">
-        <v>5.13</v>
+        <v>5.03</v>
       </c>
       <c r="G97" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.38</v>
+        <v>-1.89</v>
       </c>
       <c r="M97" t="n">
-        <v>395</v>
+        <v>396.5</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="F98" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="G98" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.42</v>
+        <v>-1.25</v>
       </c>
       <c r="M98" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>75</v>
       </c>
       <c r="E99" t="n">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="F99" t="n">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.44</v>
+        <v>-1.4</v>
       </c>
       <c r="M99" t="n">
-        <v>34.85</v>
+        <v>35.7</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>69</v>
       </c>
       <c r="E100" t="n">
-        <v>205.5</v>
+        <v>204</v>
       </c>
       <c r="F100" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="G100" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="M100" t="n">
-        <v>204</v>
+        <v>205.5</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,10 +8490,10 @@
         <v>32</v>
       </c>
       <c r="E101" t="n">
-        <v>48.15</v>
+        <v>48.25</v>
       </c>
       <c r="F101" t="n">
-        <v>11.89</v>
+        <v>11.91</v>
       </c>
       <c r="G101" t="n">
         <v>2.1</v>
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.58</v>
+        <v>0.21</v>
       </c>
       <c r="M101" t="n">
-        <v>47.4</v>
+        <v>48.15</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3430</v>
+        <v>3415</v>
       </c>
       <c r="F2" t="n">
-        <v>45.72</v>
+        <v>45.52</v>
       </c>
       <c r="G2" t="n">
-        <v>24.4</v>
+        <v>24.29</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.69</v>
+        <v>-0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>3185</v>
+        <v>3430</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="F3" t="n">
-        <v>14.77</v>
+        <v>14.46</v>
       </c>
       <c r="G3" t="n">
-        <v>8.34</v>
+        <v>8.17</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.32</v>
+        <v>-2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2460</v>
+        <v>2480</v>
       </c>
       <c r="F4" t="n">
-        <v>28.52</v>
+        <v>28.75</v>
       </c>
       <c r="G4" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2425</v>
+        <v>2460</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F5" t="n">
-        <v>17.83</v>
+        <v>17.26</v>
       </c>
       <c r="G5" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.76</v>
+        <v>-3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>26.35</v>
+        <v>25.95</v>
       </c>
       <c r="F7" t="n">
-        <v>5.29</v>
+        <v>5.21</v>
       </c>
       <c r="G7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.36</v>
+        <v>-1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>25.25</v>
+        <v>26.35</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>109.5</v>
+        <v>107.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.62</v>
+        <v>12.38</v>
       </c>
       <c r="G8" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.34</v>
+        <v>-1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>107</v>
+        <v>109.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="F9" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="G9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.84</v>
+        <v>-0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>178.5</v>
+        <v>180</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.75</v>
+        <v>41.95</v>
       </c>
       <c r="F10" t="n">
-        <v>8.789999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.71</v>
+        <v>0.48</v>
       </c>
       <c r="M10" t="n">
-        <v>42.05</v>
+        <v>41.75</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="F11" t="n">
-        <v>23.64</v>
+        <v>23.59</v>
       </c>
       <c r="G11" t="n">
-        <v>9.06</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>-0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F12" t="n">
-        <v>22.19</v>
+        <v>22.45</v>
       </c>
       <c r="G12" t="n">
-        <v>4.89</v>
+        <v>4.94</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.19</v>
+        <v>1.16</v>
       </c>
       <c r="M12" t="n">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>167</v>
+        <v>166.5</v>
       </c>
       <c r="F13" t="n">
-        <v>17.96</v>
+        <v>17.9</v>
       </c>
       <c r="G13" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.09</v>
+        <v>-0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>39.35</v>
+        <v>39.05</v>
       </c>
       <c r="F14" t="n">
-        <v>8.109999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.03</v>
+        <v>-0.76</v>
       </c>
       <c r="M14" t="n">
-        <v>38.95</v>
+        <v>39.35</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1855</v>
+        <v>1840</v>
       </c>
       <c r="F15" t="n">
-        <v>29.14</v>
+        <v>28.91</v>
       </c>
       <c r="G15" t="n">
-        <v>15.02</v>
+        <v>14.9</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.06</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>1800</v>
+        <v>1855</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="F16" t="n">
-        <v>34.13</v>
+        <v>35.06</v>
       </c>
       <c r="G16" t="n">
-        <v>10.39</v>
+        <v>10.67</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.86</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>1385</v>
+        <v>1480</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="F17" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.67</v>
+        <v>-0.55</v>
       </c>
       <c r="M17" t="n">
-        <v>89.7</v>
+        <v>90.3</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="F18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="M18" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>52.7</v>
       </c>
       <c r="F19" t="n">
-        <v>7.21</v>
+        <v>7.31</v>
       </c>
       <c r="G19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>343</v>
+        <v>344.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.95</v>
+        <v>15.01</v>
       </c>
       <c r="G20" t="n">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.29</v>
+        <v>0.44</v>
       </c>
       <c r="M20" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="F21" t="n">
-        <v>6.86</v>
+        <v>6.89</v>
       </c>
       <c r="G21" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="M21" t="n">
-        <v>2135</v>
+        <v>2140</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1495</v>
+        <v>1475</v>
       </c>
       <c r="F23" t="n">
-        <v>15.94</v>
+        <v>15.73</v>
       </c>
       <c r="G23" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>-1.34</v>
       </c>
       <c r="M23" t="n">
-        <v>1480</v>
+        <v>1495</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>170.5</v>
+        <v>166</v>
       </c>
       <c r="F2" t="n">
-        <v>17.91</v>
+        <v>17.44</v>
       </c>
       <c r="G2" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.87</v>
+        <v>-2.64</v>
       </c>
       <c r="M2" t="n">
-        <v>172</v>
+        <v>170.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F3" t="n">
-        <v>20.21</v>
+        <v>20.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.89</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>15.44</v>
+        <v>15.37</v>
       </c>
       <c r="G4" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M4" t="n">
         <v>119.5</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>320.5</v>
+        <v>322</v>
       </c>
       <c r="F5" t="n">
-        <v>27.09</v>
+        <v>27.22</v>
       </c>
       <c r="G5" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.25</v>
+        <v>0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>304.5</v>
+        <v>320.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="F6" t="n">
-        <v>14.51</v>
+        <v>14.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.85</v>
+        <v>-0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
-        <v>17.97</v>
+        <v>17.69</v>
       </c>
       <c r="G7" t="n">
-        <v>4.46</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.79</v>
+        <v>-1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>125.5</v>
+        <v>129</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,10 +11085,10 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>250.5</v>
+        <v>250</v>
       </c>
       <c r="F8" t="n">
-        <v>16.51</v>
+        <v>16.48</v>
       </c>
       <c r="G8" t="n">
         <v>1.84</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M8" t="n">
         <v>250.5</v>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="F9" t="n">
-        <v>48.71</v>
+        <v>46.59</v>
       </c>
       <c r="G9" t="n">
-        <v>26.01</v>
+        <v>24.88</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.48</v>
+        <v>-4.35</v>
       </c>
       <c r="M9" t="n">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,10 +11245,10 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="F10" t="n">
-        <v>19.9</v>
+        <v>19.94</v>
       </c>
       <c r="G10" t="n">
         <v>2.85</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="M10" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1430</v>
+        <v>1505</v>
       </c>
       <c r="F2" t="n">
-        <v>96.3</v>
+        <v>101.35</v>
       </c>
       <c r="G2" t="n">
-        <v>25.97</v>
+        <v>27.33</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>5.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1300</v>
+        <v>1430</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,10 +11538,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.7</v>
+        <v>40.75</v>
       </c>
       <c r="F3" t="n">
-        <v>9.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1.81</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M3" t="n">
         <v>40.7</v>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>155.5</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.22</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>155.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5800</v>
+        <v>5495</v>
       </c>
       <c r="F5" t="n">
-        <v>124.2</v>
+        <v>117.67</v>
       </c>
       <c r="G5" t="n">
-        <v>35.73</v>
+        <v>33.85</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.45</v>
+        <v>-5.26</v>
       </c>
       <c r="M5" t="n">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44</v>
+        <v>23.53</v>
       </c>
       <c r="G6" t="n">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
         <v>124</v>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.81</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.99</v>
       </c>
       <c r="M7" t="n">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8" t="n">
-        <v>22.19</v>
+        <v>22.32</v>
       </c>
       <c r="G8" t="n">
-        <v>4.86</v>
+        <v>4.89</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.87</v>
+        <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>172.5</v>
+        <v>174</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>26.03</v>
+        <v>25.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>-0.93</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>157.5</v>
+        <v>158.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.84</v>
+        <v>17.95</v>
       </c>
       <c r="G10" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="M10" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1220</v>
+        <v>1240</v>
       </c>
       <c r="F11" t="n">
-        <v>23.44</v>
+        <v>23.82</v>
       </c>
       <c r="G11" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>1245</v>
+        <v>1220</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>163.5</v>
+        <v>161.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.39</v>
+        <v>20.14</v>
       </c>
       <c r="G12" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.31</v>
+        <v>-1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>163</v>
+        <v>163.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>282</v>
+        <v>288.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.98</v>
+        <v>33.74</v>
       </c>
       <c r="G13" t="n">
-        <v>6.68</v>
+        <v>6.83</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>144.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.39</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.34</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>216.5</v>
+        <v>215</v>
       </c>
       <c r="F15" t="n">
-        <v>19.5</v>
+        <v>19.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.46</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>217.5</v>
+        <v>216.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7150</v>
+        <v>7615</v>
       </c>
       <c r="F16" t="n">
-        <v>183.29</v>
+        <v>195.21</v>
       </c>
       <c r="G16" t="n">
-        <v>71.16</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="M16" t="n">
-        <v>6500</v>
+        <v>7150</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1735</v>
+        <v>1875</v>
       </c>
       <c r="F2" t="n">
-        <v>55.22</v>
+        <v>59.68</v>
       </c>
       <c r="G2" t="n">
-        <v>15.34</v>
+        <v>16.58</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.97</v>
+        <v>8.07</v>
       </c>
       <c r="M2" t="n">
-        <v>1685</v>
+        <v>1735</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>72.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="F3" t="n">
-        <v>21.21</v>
+        <v>20.97</v>
       </c>
       <c r="G3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.11</v>
       </c>
       <c r="M3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>5525</v>
+        <v>5790</v>
       </c>
       <c r="F4" t="n">
-        <v>124.69</v>
+        <v>130.67</v>
       </c>
       <c r="G4" t="n">
-        <v>34.38</v>
+        <v>36.03</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.17</v>
+        <v>4.8</v>
       </c>
       <c r="M4" t="n">
-        <v>5355</v>
+        <v>5525</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4890</v>
+        <v>4895</v>
       </c>
       <c r="F5" t="n">
-        <v>76.47</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>30.04</v>
+        <v>30.07</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.15</v>
+        <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4695</v>
+        <v>4890</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F6" t="n">
-        <v>47.19</v>
+        <v>46.99</v>
       </c>
       <c r="G6" t="n">
-        <v>24.74</v>
+        <v>24.64</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.27</v>
+        <v>-0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="F7" t="n">
-        <v>11.98</v>
+        <v>11.95</v>
       </c>
       <c r="G7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,10 +13285,10 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>155.5</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>11.96</v>
+        <v>11.92</v>
       </c>
       <c r="G8" t="n">
         <v>2.08</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.97</v>
+        <v>-0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>154</v>
+        <v>155.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.82</v>
+        <v>15.52</v>
       </c>
       <c r="G9" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>-1.84</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>108.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="F10" t="n">
-        <v>26.3</v>
+        <v>25.76</v>
       </c>
       <c r="G10" t="n">
-        <v>4.05</v>
+        <v>3.97</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.73</v>
+        <v>-2.06</v>
       </c>
       <c r="M10" t="n">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>199.5</v>
+        <v>198.5</v>
       </c>
       <c r="F11" t="n">
-        <v>27.48</v>
+        <v>27.34</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>197.5</v>
+        <v>199.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3540</v>
+        <v>3665</v>
       </c>
       <c r="F12" t="n">
-        <v>51.92</v>
+        <v>53.75</v>
       </c>
       <c r="G12" t="n">
-        <v>5.06</v>
+        <v>5.24</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7.44</v>
+        <v>3.53</v>
       </c>
       <c r="M12" t="n">
-        <v>3295</v>
+        <v>3540</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1505</v>
+        <v>1655</v>
       </c>
       <c r="F2" t="n">
-        <v>101.35</v>
+        <v>111.45</v>
       </c>
       <c r="G2" t="n">
-        <v>27.33</v>
+        <v>30.05</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.24</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>1430</v>
+        <v>1505</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="F3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -662,7 +662,7 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>40.7</v>
+        <v>40.75</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>155.5</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5495</v>
+        <v>5345</v>
       </c>
       <c r="F5" t="n">
-        <v>117.67</v>
+        <v>114.45</v>
       </c>
       <c r="G5" t="n">
-        <v>33.85</v>
+        <v>32.93</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-5.26</v>
+        <v>-2.73</v>
       </c>
       <c r="M5" t="n">
-        <v>5800</v>
+        <v>5495</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124.5</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>23.53</v>
+        <v>23.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51</v>
+        <v>4.45</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.99</v>
+        <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>172.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22.32</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>4.89</v>
+        <v>4.82</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>-1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="F10" t="n">
-        <v>17.95</v>
+        <v>17.78</v>
       </c>
       <c r="G10" t="n">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.63</v>
+        <v>-0.95</v>
       </c>
       <c r="M10" t="n">
-        <v>157.5</v>
+        <v>158.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="F11" t="n">
-        <v>23.82</v>
+        <v>24.21</v>
       </c>
       <c r="G11" t="n">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>1220</v>
+        <v>1240</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>161.5</v>
+        <v>162</v>
       </c>
       <c r="F12" t="n">
-        <v>20.14</v>
+        <v>20.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.22</v>
+        <v>0.31</v>
       </c>
       <c r="M12" t="n">
-        <v>163.5</v>
+        <v>161.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>288.5</v>
+        <v>284.5</v>
       </c>
       <c r="F13" t="n">
-        <v>33.74</v>
+        <v>33.27</v>
       </c>
       <c r="G13" t="n">
-        <v>6.83</v>
+        <v>6.74</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>-1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>282</v>
+        <v>288.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>144.5</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>28.39</v>
+        <v>28.49</v>
       </c>
       <c r="G14" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>144.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F15" t="n">
-        <v>19.37</v>
+        <v>19.28</v>
       </c>
       <c r="G15" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.47</v>
       </c>
       <c r="M15" t="n">
-        <v>216.5</v>
+        <v>215</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7615</v>
+        <v>8375</v>
       </c>
       <c r="F16" t="n">
-        <v>195.21</v>
+        <v>214.69</v>
       </c>
       <c r="G16" t="n">
-        <v>75.79000000000001</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.5</v>
+        <v>9.98</v>
       </c>
       <c r="M16" t="n">
-        <v>7150</v>
+        <v>7615</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1525</v>
+        <v>1510</v>
       </c>
       <c r="F17" t="n">
-        <v>45.12</v>
+        <v>44.67</v>
       </c>
       <c r="G17" t="n">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-3.17</v>
+        <v>-0.98</v>
       </c>
       <c r="M17" t="n">
-        <v>1575</v>
+        <v>1525</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12800</v>
+        <v>12670</v>
       </c>
       <c r="F18" t="n">
-        <v>70.56999999999999</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>36.14</v>
+        <v>35.77</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.44</v>
+        <v>-1.02</v>
       </c>
       <c r="M18" t="n">
-        <v>12495</v>
+        <v>12800</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>914</v>
+        <v>950</v>
       </c>
       <c r="F19" t="n">
-        <v>77.72</v>
+        <v>80.78</v>
       </c>
       <c r="G19" t="n">
-        <v>15.08</v>
+        <v>15.68</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.01</v>
+        <v>3.94</v>
       </c>
       <c r="M19" t="n">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>83.2</v>
       </c>
       <c r="F20" t="n">
-        <v>45.05</v>
+        <v>45.71</v>
       </c>
       <c r="G20" t="n">
-        <v>6.74</v>
+        <v>6.84</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1.32</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
-        <v>83.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5795</v>
+        <v>5765</v>
       </c>
       <c r="F21" t="n">
-        <v>94.88</v>
+        <v>94.38</v>
       </c>
       <c r="G21" t="n">
-        <v>24.5</v>
+        <v>24.37</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-9.949999999999999</v>
+        <v>-0.52</v>
       </c>
       <c r="M21" t="n">
-        <v>6435</v>
+        <v>5795</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2375</v>
+        <v>2440</v>
       </c>
       <c r="F22" t="n">
-        <v>60.59</v>
+        <v>62.24</v>
       </c>
       <c r="G22" t="n">
-        <v>30.5</v>
+        <v>31.33</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.71</v>
+        <v>2.74</v>
       </c>
       <c r="M22" t="n">
-        <v>2290</v>
+        <v>2375</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.4</v>
+        <v>18.45</v>
       </c>
       <c r="F23" t="n">
-        <v>41.82</v>
+        <v>41.93</v>
       </c>
       <c r="G23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.54</v>
+        <v>0.27</v>
       </c>
       <c r="M23" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="F24" t="n">
-        <v>72.88</v>
+        <v>73.13</v>
       </c>
       <c r="G24" t="n">
-        <v>17.78</v>
+        <v>17.85</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.74</v>
+        <v>0.35</v>
       </c>
       <c r="M24" t="n">
-        <v>1370</v>
+        <v>1435</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="F25" t="n">
-        <v>71.70999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="G25" t="n">
-        <v>4.89</v>
+        <v>4.99</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.17</v>
+        <v>2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2875</v>
+        <v>2825</v>
       </c>
       <c r="F26" t="n">
-        <v>247.42</v>
+        <v>243.12</v>
       </c>
       <c r="G26" t="n">
-        <v>56.36</v>
+        <v>55.38</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-0.17</v>
+        <v>-1.74</v>
       </c>
       <c r="M26" t="n">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="F27" t="n">
-        <v>47.97</v>
+        <v>50.14</v>
       </c>
       <c r="G27" t="n">
-        <v>7.49</v>
+        <v>7.83</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.92</v>
+        <v>4.52</v>
       </c>
       <c r="M27" t="n">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="F28" t="n">
-        <v>56.32</v>
+        <v>56.81</v>
       </c>
       <c r="G28" t="n">
-        <v>11.67</v>
+        <v>11.77</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-2.54</v>
+        <v>0.87</v>
       </c>
       <c r="M28" t="n">
-        <v>1180</v>
+        <v>1150</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="F29" t="n">
-        <v>101.15</v>
+        <v>99.02</v>
       </c>
       <c r="G29" t="n">
-        <v>19.82</v>
+        <v>19.4</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.15</v>
+        <v>-2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3485</v>
+        <v>3700</v>
       </c>
       <c r="F30" t="n">
-        <v>82.19</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>11.33</v>
+        <v>12.03</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-0.99</v>
+        <v>6.17</v>
       </c>
       <c r="M30" t="n">
-        <v>3520</v>
+        <v>3485</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="F31" t="n">
-        <v>110.55</v>
+        <v>106.69</v>
       </c>
       <c r="G31" t="n">
-        <v>14.21</v>
+        <v>13.72</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>-3.49</v>
       </c>
       <c r="M31" t="n">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F32" t="n">
-        <v>44.71</v>
+        <v>44.52</v>
       </c>
       <c r="G32" t="n">
-        <v>11.09</v>
+        <v>11.04</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.32</v>
+        <v>-0.42</v>
       </c>
       <c r="M32" t="n">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="F33" t="n">
-        <v>37.51</v>
+        <v>38.45</v>
       </c>
       <c r="G33" t="n">
-        <v>6.48</v>
+        <v>6.64</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.27</v>
+        <v>2.51</v>
       </c>
       <c r="M33" t="n">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>5010</v>
+        <v>5180</v>
       </c>
       <c r="F34" t="n">
-        <v>82.73999999999999</v>
+        <v>85.55</v>
       </c>
       <c r="G34" t="n">
-        <v>18.85</v>
+        <v>19.49</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6.37</v>
+        <v>3.39</v>
       </c>
       <c r="M34" t="n">
-        <v>4710</v>
+        <v>5010</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="F35" t="n">
-        <v>59.68</v>
+        <v>60.47</v>
       </c>
       <c r="G35" t="n">
-        <v>16.58</v>
+        <v>16.8</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>8.07</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
-        <v>1735</v>
+        <v>1875</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="F36" t="n">
-        <v>20.97</v>
+        <v>20.79</v>
       </c>
       <c r="G36" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-1.11</v>
+        <v>-0.84</v>
       </c>
       <c r="M36" t="n">
-        <v>72.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>5790</v>
+        <v>5830</v>
       </c>
       <c r="F37" t="n">
-        <v>130.67</v>
+        <v>131.57</v>
       </c>
       <c r="G37" t="n">
-        <v>36.03</v>
+        <v>36.28</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>5525</v>
+        <v>5790</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>4895</v>
+        <v>4860</v>
       </c>
       <c r="F38" t="n">
-        <v>76.54000000000001</v>
+        <v>76</v>
       </c>
       <c r="G38" t="n">
-        <v>30.07</v>
+        <v>29.85</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.1</v>
+        <v>-0.72</v>
       </c>
       <c r="M38" t="n">
-        <v>4890</v>
+        <v>4895</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="F39" t="n">
-        <v>46.99</v>
+        <v>46.6</v>
       </c>
       <c r="G39" t="n">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="M39" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>11.95</v>
+        <v>11.93</v>
       </c>
       <c r="G40" t="n">
         <v>1.67</v>
@@ -3631,7 +3631,7 @@
         <v>-0.21</v>
       </c>
       <c r="M40" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>155</v>
+        <v>154.5</v>
       </c>
       <c r="F41" t="n">
-        <v>11.92</v>
+        <v>11.88</v>
       </c>
       <c r="G41" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3710,7 +3710,7 @@
         <v>-0.32</v>
       </c>
       <c r="M41" t="n">
-        <v>155.5</v>
+        <v>155</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F42" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G42" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-1.84</v>
+        <v>-0.47</v>
       </c>
       <c r="M42" t="n">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>952</v>
+        <v>923</v>
       </c>
       <c r="F43" t="n">
-        <v>25.76</v>
+        <v>24.97</v>
       </c>
       <c r="G43" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-2.06</v>
+        <v>-3.05</v>
       </c>
       <c r="M43" t="n">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>198.5</v>
+        <v>197</v>
       </c>
       <c r="F44" t="n">
-        <v>27.34</v>
+        <v>27.13</v>
       </c>
       <c r="G44" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-0.5</v>
+        <v>-0.76</v>
       </c>
       <c r="M44" t="n">
-        <v>199.5</v>
+        <v>198.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3665</v>
+        <v>3715</v>
       </c>
       <c r="F45" t="n">
-        <v>53.75</v>
+        <v>54.49</v>
       </c>
       <c r="G45" t="n">
-        <v>5.24</v>
+        <v>5.31</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.53</v>
+        <v>1.36</v>
       </c>
       <c r="M45" t="n">
-        <v>3540</v>
+        <v>3665</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>213</v>
+        <v>217.5</v>
       </c>
       <c r="F46" t="n">
-        <v>21.69</v>
+        <v>22.15</v>
       </c>
       <c r="G46" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-1.39</v>
+        <v>2.11</v>
       </c>
       <c r="M46" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>124.5</v>
+        <v>123.5</v>
       </c>
       <c r="F47" t="n">
-        <v>20.24</v>
+        <v>20.08</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="M47" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4249,13 +4249,13 @@
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>234</v>
+        <v>233.5</v>
       </c>
       <c r="F48" t="n">
-        <v>25.63</v>
+        <v>25.58</v>
       </c>
       <c r="G48" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.86</v>
+        <v>-0.21</v>
       </c>
       <c r="M48" t="n">
-        <v>227.5</v>
+        <v>234</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4323,19 +4323,21 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E49" t="n">
-        <v>516</v>
+        <v>755</v>
       </c>
       <c r="F49" t="n">
-        <v>20.02</v>
+        <v>27.37</v>
       </c>
       <c r="G49" t="n">
-        <v>5.52</v>
+        <v>7.72</v>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>27</v>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
@@ -4343,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-1.71</v>
+        <v>2.03</v>
       </c>
       <c r="M49" t="n">
-        <v>525</v>
+        <v>740</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4355,23 +4357,23 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>17.9</v>
+        <v>31.7</v>
       </c>
       <c r="Q49" t="n">
         <v>1.5</v>
       </c>
       <c r="R49" t="n">
-        <v>-6.1</v>
+        <v>3.8</v>
       </c>
       <c r="S49" t="n">
-        <v>730.1</v>
+        <v>21.9</v>
       </c>
       <c r="T49" t="n">
-        <v>45.2</v>
+        <v>32.2</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
@@ -4388,12 +4390,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4402,20 +4404,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>740</v>
+        <v>110</v>
       </c>
       <c r="F50" t="n">
-        <v>26.83</v>
+        <v>20.52</v>
       </c>
       <c r="G50" t="n">
-        <v>7.56</v>
+        <v>2.55</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>186.3</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4424,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>0.46</v>
       </c>
       <c r="M50" t="n">
-        <v>727</v>
+        <v>109.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4436,28 +4438,28 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>31.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="R50" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S50" t="n">
-        <v>21.9</v>
+        <v>37</v>
       </c>
       <c r="T50" t="n">
-        <v>32.2</v>
+        <v>35.8</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4469,12 +4471,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4483,20 +4485,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E51" t="n">
-        <v>109.5</v>
+        <v>6405</v>
       </c>
       <c r="F51" t="n">
-        <v>20.43</v>
+        <v>34.07</v>
       </c>
       <c r="G51" t="n">
-        <v>2.54</v>
+        <v>4.37</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>186.3</v>
+        <v>9</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4505,10 +4507,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1.35</v>
+        <v>0.08</v>
       </c>
       <c r="M51" t="n">
-        <v>111</v>
+        <v>6400</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4517,28 +4519,28 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="R51" t="n">
-        <v>-3.4</v>
+        <v>6.8</v>
       </c>
       <c r="S51" t="n">
-        <v>37</v>
+        <v>41.8</v>
       </c>
       <c r="T51" t="n">
-        <v>35.8</v>
+        <v>32.9</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4550,73 +4552,71 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E52" t="n">
-        <v>6400</v>
+        <v>535</v>
       </c>
       <c r="F52" t="n">
-        <v>34.04</v>
+        <v>24.23</v>
       </c>
       <c r="G52" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>6.6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I52" t="n">
-        <v>9</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>6430</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="R52" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="S52" t="n">
-        <v>41.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4624,19 +4624,19 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4645,25 +4645,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E53" t="n">
-        <v>535</v>
+        <v>704</v>
       </c>
       <c r="F53" t="n">
-        <v>24.23</v>
+        <v>43.19</v>
       </c>
       <c r="G53" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H53" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I53" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4671,78 +4671,78 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-0.93</v>
+        <v>0.28</v>
       </c>
       <c r="M53" t="n">
-        <v>540</v>
+        <v>702</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R53" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S53" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>702</v>
+        <v>58.7</v>
       </c>
       <c r="F54" t="n">
-        <v>43.07</v>
+        <v>16.13</v>
       </c>
       <c r="G54" t="n">
-        <v>5.78</v>
+        <v>2.45</v>
       </c>
       <c r="H54" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I54" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J54" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4750,30 +4750,30 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-1.34</v>
       </c>
       <c r="M54" t="n">
-        <v>702</v>
+        <v>59.5</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R54" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S54" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T54" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U54" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4803,25 +4803,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E55" t="n">
-        <v>59.5</v>
+        <v>180</v>
       </c>
       <c r="F55" t="n">
-        <v>16.35</v>
+        <v>16.44</v>
       </c>
       <c r="G55" t="n">
-        <v>2.49</v>
+        <v>1.79</v>
       </c>
       <c r="H55" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I55" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J55" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4829,34 +4829,34 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.5</v>
+        <v>-0.28</v>
       </c>
       <c r="M55" t="n">
-        <v>59.8</v>
+        <v>180.5</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R55" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S55" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U55" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -4868,91 +4868,89 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E56" t="n">
-        <v>180.5</v>
+        <v>336.5</v>
       </c>
       <c r="F56" t="n">
-        <v>16.48</v>
+        <v>17.43</v>
       </c>
       <c r="G56" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H56" t="n">
-        <v>15.5</v>
-      </c>
+        <v>4.94</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.95</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-3.22</v>
+        <v>-1.46</v>
       </c>
       <c r="M56" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
+        <v>341.5</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.03</v>
+        <v>1.09</v>
       </c>
       <c r="R56" t="n">
-        <v>30.2</v>
+        <v>24.2</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4961,20 +4959,20 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E57" t="n">
-        <v>341.5</v>
+        <v>166</v>
       </c>
       <c r="F57" t="n">
-        <v>17.69</v>
+        <v>18.67</v>
       </c>
       <c r="G57" t="n">
-        <v>5.01</v>
+        <v>3.94</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>49</v>
+        <v>57.1</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4983,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="M57" t="n">
-        <v>341.5</v>
+        <v>166.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4995,24 +4993,24 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>29.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="R57" t="n">
-        <v>24.2</v>
+        <v>11.1</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="T57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5024,34 +5022,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>166.5</v>
+        <v>88.5</v>
       </c>
       <c r="F58" t="n">
-        <v>18.73</v>
+        <v>16.89</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95</v>
+        <v>1.72</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>57.1</v>
+        <v>11.3</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5060,31 +5058,35 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-0.3</v>
+        <v>-1.45</v>
       </c>
       <c r="M58" t="n">
-        <v>167</v>
+        <v>89.8</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P58" t="n">
-        <v>18.6</v>
+        <v>9.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.74</v>
+        <v>1.99</v>
       </c>
       <c r="R58" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>3.6</v>
+        <v>-2.7</v>
       </c>
       <c r="T58" t="n">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
@@ -5101,12 +5103,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5115,20 +5117,20 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>89.8</v>
+        <v>155</v>
       </c>
       <c r="F59" t="n">
-        <v>17.14</v>
+        <v>17.28</v>
       </c>
       <c r="G59" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5137,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-0.55</v>
+        <v>0.32</v>
       </c>
       <c r="M59" t="n">
-        <v>90.3</v>
+        <v>154.5</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5149,23 +5151,23 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="S59" t="n">
-        <v>-2.7</v>
+        <v>14.6</v>
       </c>
       <c r="T59" t="n">
-        <v>20.3</v>
+        <v>34.2</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
@@ -5182,12 +5184,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5196,20 +5198,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>154.5</v>
+        <v>232</v>
       </c>
       <c r="F60" t="n">
-        <v>17.22</v>
+        <v>14.42</v>
       </c>
       <c r="G60" t="n">
-        <v>1.7</v>
+        <v>5.24</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5218,40 +5220,36 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1.59</v>
+        <v>-2.52</v>
       </c>
       <c r="M60" t="n">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>5.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="R60" t="n">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
       <c r="S60" t="n">
-        <v>14.6</v>
+        <v>812.4</v>
       </c>
       <c r="T60" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5263,12 +5261,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5277,20 +5275,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="F61" t="n">
-        <v>14.79</v>
+        <v>15.53</v>
       </c>
       <c r="G61" t="n">
-        <v>5.38</v>
+        <v>1.85</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>9.6</v>
+        <v>49.2</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -5299,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-1.86</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>242.5</v>
+        <v>184</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5311,24 +5309,24 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>30.7</v>
+        <v>14.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R61" t="n">
-        <v>20.4</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>812.4</v>
+        <v>10.3</v>
       </c>
       <c r="T61" t="n">
-        <v>34.6</v>
+        <v>20.2</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5340,12 +5338,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5354,20 +5352,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>184</v>
+        <v>727</v>
       </c>
       <c r="F62" t="n">
-        <v>15.53</v>
+        <v>16.8</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85</v>
+        <v>13.55</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>49.2</v>
+        <v>-8.1</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5376,31 +5374,35 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-1.08</v>
+        <v>0.41</v>
       </c>
       <c r="M62" t="n">
-        <v>186</v>
+        <v>724</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P62" t="n">
-        <v>14.4</v>
+        <v>94.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>18.2</v>
       </c>
       <c r="S62" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="T62" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
@@ -5417,35 +5419,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>724</v>
+        <v>497</v>
       </c>
       <c r="F63" t="n">
-        <v>16.73</v>
+        <v>19.29</v>
       </c>
       <c r="G63" t="n">
-        <v>13.5</v>
+        <v>5.32</v>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
-        <v>-8.1</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.68</v>
       </c>
       <c r="M63" t="n">
-        <v>729</v>
+        <v>516</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>94.5</v>
+        <v>17.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="R63" t="n">
-        <v>18.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>730.1</v>
       </c>
       <c r="T63" t="n">
-        <v>19.6</v>
+        <v>45.2</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F64" t="n">
-        <v>19.18</v>
+        <v>18.85</v>
       </c>
       <c r="G64" t="n">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-3.06</v>
+        <v>-1.72</v>
       </c>
       <c r="M64" t="n">
-        <v>179.5</v>
+        <v>174</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>97</v>
       </c>
       <c r="E65" t="n">
-        <v>166</v>
+        <v>159.5</v>
       </c>
       <c r="F65" t="n">
-        <v>17.44</v>
+        <v>16.75</v>
       </c>
       <c r="G65" t="n">
-        <v>4.91</v>
+        <v>4.72</v>
       </c>
       <c r="H65" t="n">
         <v>14.7</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-2.64</v>
+        <v>-3.92</v>
       </c>
       <c r="M65" t="n">
-        <v>170.5</v>
+        <v>166</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -5673,13 +5673,13 @@
         <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F66" t="n">
-        <v>20.1</v>
+        <v>19.99</v>
       </c>
       <c r="G66" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="H66" t="n">
         <v>17.9</v>
@@ -5699,7 +5699,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M66" t="n">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5752,13 +5752,13 @@
         <v>91</v>
       </c>
       <c r="E67" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F67" t="n">
-        <v>15.37</v>
+        <v>15.25</v>
       </c>
       <c r="G67" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="H67" t="n">
         <v>15</v>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="M67" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5831,13 +5831,13 @@
         <v>90</v>
       </c>
       <c r="E68" t="n">
-        <v>322</v>
+        <v>317.5</v>
       </c>
       <c r="F68" t="n">
-        <v>27.22</v>
+        <v>26.84</v>
       </c>
       <c r="G68" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H68" t="n">
         <v>27.5</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.47</v>
+        <v>-1.4</v>
       </c>
       <c r="M68" t="n">
-        <v>320.5</v>
+        <v>322</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5910,13 +5910,13 @@
         <v>87</v>
       </c>
       <c r="E69" t="n">
-        <v>82.5</v>
+        <v>82</v>
       </c>
       <c r="F69" t="n">
-        <v>14.42</v>
+        <v>14.34</v>
       </c>
       <c r="G69" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H69" t="n">
         <v>16.7</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="M69" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5989,13 +5989,13 @@
         <v>77</v>
       </c>
       <c r="E70" t="n">
-        <v>127</v>
+        <v>126.5</v>
       </c>
       <c r="F70" t="n">
-        <v>17.69</v>
+        <v>17.62</v>
       </c>
       <c r="G70" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="H70" t="n">
         <v>16.4</v>
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1.55</v>
+        <v>-0.39</v>
       </c>
       <c r="M70" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
@@ -6072,13 +6072,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F71" t="n">
-        <v>16.48</v>
+        <v>16.68</v>
       </c>
       <c r="G71" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H71" t="n">
         <v>15.3</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="M71" t="n">
-        <v>250.5</v>
+        <v>250</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
@@ -6151,13 +6151,13 @@
         <v>76</v>
       </c>
       <c r="E72" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="F72" t="n">
-        <v>46.59</v>
+        <v>45.74</v>
       </c>
       <c r="G72" t="n">
-        <v>24.88</v>
+        <v>24.43</v>
       </c>
       <c r="H72" t="n">
         <v>38.8</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-4.35</v>
+        <v>-1.82</v>
       </c>
       <c r="M72" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
@@ -6232,13 +6232,13 @@
         <v>68</v>
       </c>
       <c r="E73" t="n">
-        <v>61.8</v>
+        <v>61.2</v>
       </c>
       <c r="F73" t="n">
-        <v>19.94</v>
+        <v>19.74</v>
       </c>
       <c r="G73" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="H73" t="n">
         <v>21.3</v>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.16</v>
+        <v>-0.97</v>
       </c>
       <c r="M73" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6315,13 +6315,13 @@
         <v>100</v>
       </c>
       <c r="E74" t="n">
-        <v>3415</v>
+        <v>3390</v>
       </c>
       <c r="F74" t="n">
-        <v>45.52</v>
+        <v>45.19</v>
       </c>
       <c r="G74" t="n">
-        <v>24.29</v>
+        <v>24.12</v>
       </c>
       <c r="H74" t="n">
         <v>24.6</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-0.44</v>
+        <v>-0.73</v>
       </c>
       <c r="M74" t="n">
-        <v>3430</v>
+        <v>3415</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -6394,13 +6394,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F75" t="n">
-        <v>14.46</v>
+        <v>14.4</v>
       </c>
       <c r="G75" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H75" t="n">
         <v>14.2</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-2.05</v>
+        <v>-0.42</v>
       </c>
       <c r="M75" t="n">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6473,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2480</v>
+        <v>2460</v>
       </c>
       <c r="F76" t="n">
-        <v>28.75</v>
+        <v>28.52</v>
       </c>
       <c r="G76" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="H76" t="n">
         <v>23.6</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M76" t="n">
-        <v>2460</v>
+        <v>2480</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-3.2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6631,13 +6631,13 @@
         <v>94</v>
       </c>
       <c r="E78" t="n">
-        <v>109.5</v>
+        <v>108</v>
       </c>
       <c r="F78" t="n">
-        <v>13.55</v>
+        <v>13.37</v>
       </c>
       <c r="G78" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H78" t="n">
         <v>12.3</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>-1.37</v>
       </c>
       <c r="M78" t="n">
         <v>109.5</v>
@@ -6710,10 +6710,10 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>25.95</v>
+        <v>25.8</v>
       </c>
       <c r="F79" t="n">
-        <v>5.21</v>
+        <v>5.18</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-1.52</v>
+        <v>-0.58</v>
       </c>
       <c r="M79" t="n">
-        <v>26.35</v>
+        <v>25.95</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6789,13 +6789,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>107.5</v>
+        <v>105</v>
       </c>
       <c r="F80" t="n">
-        <v>12.38</v>
+        <v>12.1</v>
       </c>
       <c r="G80" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="H80" t="n">
         <v>10.7</v>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-1.83</v>
+        <v>-2.33</v>
       </c>
       <c r="M80" t="n">
-        <v>109.5</v>
+        <v>107.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6868,13 +6868,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>179.5</v>
+        <v>181</v>
       </c>
       <c r="F81" t="n">
-        <v>12.79</v>
+        <v>12.9</v>
       </c>
       <c r="G81" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="H81" t="n">
         <v>11.4</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.28</v>
+        <v>0.84</v>
       </c>
       <c r="M81" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6947,13 +6947,13 @@
         <v>92</v>
       </c>
       <c r="E82" t="n">
-        <v>41.95</v>
+        <v>42.5</v>
       </c>
       <c r="F82" t="n">
-        <v>8.83</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H82" t="n">
         <v>7.6</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.48</v>
+        <v>1.31</v>
       </c>
       <c r="M82" t="n">
-        <v>41.75</v>
+        <v>41.95</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7026,13 +7026,13 @@
         <v>90</v>
       </c>
       <c r="E83" t="n">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="F83" t="n">
-        <v>23.59</v>
+        <v>23.54</v>
       </c>
       <c r="G83" t="n">
-        <v>9.039999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="H83" t="n">
         <v>25</v>
@@ -7052,7 +7052,7 @@
         <v>-0.22</v>
       </c>
       <c r="M83" t="n">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7105,13 +7105,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="F84" t="n">
-        <v>22.45</v>
+        <v>23.09</v>
       </c>
       <c r="G84" t="n">
-        <v>4.94</v>
+        <v>5.08</v>
       </c>
       <c r="H84" t="n">
         <v>21.2</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.16</v>
+        <v>2.86</v>
       </c>
       <c r="M84" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7184,13 +7184,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>166.5</v>
+        <v>167</v>
       </c>
       <c r="F85" t="n">
-        <v>17.9</v>
+        <v>17.96</v>
       </c>
       <c r="G85" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="H85" t="n">
         <v>14.1</v>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="M85" t="n">
-        <v>167</v>
+        <v>166.5</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7263,10 +7263,10 @@
         <v>84</v>
       </c>
       <c r="E86" t="n">
-        <v>39.05</v>
+        <v>39.2</v>
       </c>
       <c r="F86" t="n">
-        <v>8.050000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="G86" t="n">
         <v>1.11</v>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-0.76</v>
+        <v>0.38</v>
       </c>
       <c r="M86" t="n">
-        <v>39.35</v>
+        <v>39.05</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7342,13 +7342,13 @@
         <v>80</v>
       </c>
       <c r="E87" t="n">
-        <v>1840</v>
+        <v>1915</v>
       </c>
       <c r="F87" t="n">
-        <v>28.91</v>
+        <v>30.09</v>
       </c>
       <c r="G87" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="H87" t="n">
         <v>30.7</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.08</v>
       </c>
       <c r="M87" t="n">
-        <v>1855</v>
+        <v>1840</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
@@ -7425,13 +7425,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1520</v>
+        <v>1600</v>
       </c>
       <c r="F88" t="n">
-        <v>35.06</v>
+        <v>36.9</v>
       </c>
       <c r="G88" t="n">
-        <v>10.67</v>
+        <v>11.23</v>
       </c>
       <c r="H88" t="n">
         <v>21.8</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
       <c r="M88" t="n">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7591,13 +7591,13 @@
         <v>78</v>
       </c>
       <c r="E90" t="n">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="F90" t="n">
-        <v>8.390000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="G90" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H90" t="n">
         <v>6.8</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
       <c r="M90" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7674,10 +7674,10 @@
         <v>77</v>
       </c>
       <c r="E91" t="n">
-        <v>52.7</v>
+        <v>53.1</v>
       </c>
       <c r="F91" t="n">
-        <v>7.31</v>
+        <v>7.36</v>
       </c>
       <c r="G91" t="n">
         <v>1.13</v>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.35</v>
+        <v>0.76</v>
       </c>
       <c r="M91" t="n">
-        <v>52</v>
+        <v>52.7</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7757,13 +7757,13 @@
         <v>65</v>
       </c>
       <c r="E92" t="n">
-        <v>344.5</v>
+        <v>342</v>
       </c>
       <c r="F92" t="n">
-        <v>15.01</v>
+        <v>14.9</v>
       </c>
       <c r="G92" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="H92" t="n">
         <v>13.2</v>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.44</v>
+        <v>-0.73</v>
       </c>
       <c r="M92" t="n">
-        <v>343</v>
+        <v>344.5</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7840,13 +7840,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>2150</v>
+        <v>2115</v>
       </c>
       <c r="F93" t="n">
-        <v>6.89</v>
+        <v>6.78</v>
       </c>
       <c r="G93" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="H93" t="n">
         <v>9.6</v>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.47</v>
+        <v>-1.63</v>
       </c>
       <c r="M93" t="n">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7923,13 +7923,13 @@
         <v>62</v>
       </c>
       <c r="E94" t="n">
-        <v>186.5</v>
+        <v>180.5</v>
       </c>
       <c r="F94" t="n">
-        <v>14.81</v>
+        <v>14.34</v>
       </c>
       <c r="G94" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="H94" t="n">
         <v>10</v>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>-3.22</v>
       </c>
       <c r="M94" t="n">
         <v>186.5</v>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1495</v>
+        <v>1475</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8089,10 +8089,10 @@
         <v>79</v>
       </c>
       <c r="E96" t="n">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
       <c r="F96" t="n">
-        <v>4.87</v>
+        <v>4.86</v>
       </c>
       <c r="G96" t="n">
         <v>1.09</v>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-1.14</v>
+        <v>-0.29</v>
       </c>
       <c r="M96" t="n">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         <v>77</v>
       </c>
       <c r="E97" t="n">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F97" t="n">
-        <v>5.03</v>
+        <v>4.96</v>
       </c>
       <c r="G97" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-1.89</v>
+        <v>-1.29</v>
       </c>
       <c r="M97" t="n">
-        <v>396.5</v>
+        <v>389</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="F98" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="G98" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-1.25</v>
+        <v>-0.84</v>
       </c>
       <c r="M98" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>75</v>
       </c>
       <c r="E99" t="n">
-        <v>35.2</v>
+        <v>34.65</v>
       </c>
       <c r="F99" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="G99" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-1.4</v>
+        <v>-1.56</v>
       </c>
       <c r="M99" t="n">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>69</v>
       </c>
       <c r="E100" t="n">
-        <v>204</v>
+        <v>201.5</v>
       </c>
       <c r="F100" t="n">
-        <v>5.07</v>
+        <v>5.01</v>
       </c>
       <c r="G100" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-0.73</v>
+        <v>-1.23</v>
       </c>
       <c r="M100" t="n">
-        <v>205.5</v>
+        <v>204</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>32</v>
       </c>
       <c r="E101" t="n">
-        <v>48.25</v>
+        <v>48</v>
       </c>
       <c r="F101" t="n">
-        <v>11.91</v>
+        <v>11.85</v>
       </c>
       <c r="G101" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.21</v>
+        <v>-0.52</v>
       </c>
       <c r="M101" t="n">
-        <v>48.15</v>
+        <v>48.25</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3415</v>
+        <v>3390</v>
       </c>
       <c r="F2" t="n">
-        <v>45.52</v>
+        <v>45.19</v>
       </c>
       <c r="G2" t="n">
-        <v>24.29</v>
+        <v>24.12</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.44</v>
+        <v>-0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>3430</v>
+        <v>3415</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F3" t="n">
-        <v>14.46</v>
+        <v>14.4</v>
       </c>
       <c r="G3" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-2.05</v>
+        <v>-0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2480</v>
+        <v>2460</v>
       </c>
       <c r="F4" t="n">
-        <v>28.75</v>
+        <v>28.52</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2460</v>
+        <v>2480</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-3.2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>109.5</v>
+        <v>108</v>
       </c>
       <c r="F6" t="n">
-        <v>13.55</v>
+        <v>13.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.37</v>
       </c>
       <c r="M6" t="n">
         <v>109.5</v>
@@ -9097,10 +9097,10 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.95</v>
+        <v>25.8</v>
       </c>
       <c r="F7" t="n">
-        <v>5.21</v>
+        <v>5.18</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.52</v>
+        <v>-0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>26.35</v>
+        <v>25.95</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>107.5</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>12.38</v>
+        <v>12.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.83</v>
+        <v>-2.33</v>
       </c>
       <c r="M8" t="n">
-        <v>109.5</v>
+        <v>107.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>179.5</v>
+        <v>181</v>
       </c>
       <c r="F9" t="n">
-        <v>12.79</v>
+        <v>12.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.28</v>
+        <v>0.84</v>
       </c>
       <c r="M9" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.95</v>
+        <v>42.5</v>
       </c>
       <c r="F10" t="n">
-        <v>8.83</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.48</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>41.75</v>
+        <v>41.95</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="F11" t="n">
-        <v>23.59</v>
+        <v>23.54</v>
       </c>
       <c r="G11" t="n">
-        <v>9.039999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9439,7 +9439,7 @@
         <v>-0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="F12" t="n">
-        <v>22.45</v>
+        <v>23.09</v>
       </c>
       <c r="G12" t="n">
-        <v>4.94</v>
+        <v>5.08</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.16</v>
+        <v>2.86</v>
       </c>
       <c r="M12" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>166.5</v>
+        <v>167</v>
       </c>
       <c r="F13" t="n">
-        <v>17.9</v>
+        <v>17.96</v>
       </c>
       <c r="G13" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>167</v>
+        <v>166.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>39.05</v>
+        <v>39.2</v>
       </c>
       <c r="F14" t="n">
-        <v>8.050000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="G14" t="n">
         <v>1.11</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.76</v>
+        <v>0.38</v>
       </c>
       <c r="M14" t="n">
-        <v>39.35</v>
+        <v>39.05</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1840</v>
+        <v>1915</v>
       </c>
       <c r="F15" t="n">
-        <v>28.91</v>
+        <v>30.09</v>
       </c>
       <c r="G15" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.08</v>
       </c>
       <c r="M15" t="n">
-        <v>1855</v>
+        <v>1840</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1520</v>
+        <v>1600</v>
       </c>
       <c r="F16" t="n">
-        <v>35.06</v>
+        <v>36.9</v>
       </c>
       <c r="G16" t="n">
-        <v>10.67</v>
+        <v>11.23</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
       <c r="M16" t="n">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="F18" t="n">
-        <v>8.390000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="G18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
       <c r="M18" t="n">
-        <v>55.1</v>
+        <v>55.7</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,10 +10061,10 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>52.7</v>
+        <v>53.1</v>
       </c>
       <c r="F19" t="n">
-        <v>7.31</v>
+        <v>7.36</v>
       </c>
       <c r="G19" t="n">
         <v>1.13</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>0.76</v>
       </c>
       <c r="M19" t="n">
-        <v>52</v>
+        <v>52.7</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>344.5</v>
+        <v>342</v>
       </c>
       <c r="F20" t="n">
-        <v>15.01</v>
+        <v>14.9</v>
       </c>
       <c r="G20" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.44</v>
+        <v>-0.73</v>
       </c>
       <c r="M20" t="n">
-        <v>343</v>
+        <v>344.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2150</v>
+        <v>2115</v>
       </c>
       <c r="F21" t="n">
-        <v>6.89</v>
+        <v>6.78</v>
       </c>
       <c r="G21" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.47</v>
+        <v>-1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>186.5</v>
+        <v>180.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.81</v>
+        <v>14.34</v>
       </c>
       <c r="G22" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-3.22</v>
       </c>
       <c r="M22" t="n">
         <v>186.5</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1495</v>
+        <v>1475</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>166</v>
+        <v>159.5</v>
       </c>
       <c r="F2" t="n">
-        <v>17.44</v>
+        <v>16.75</v>
       </c>
       <c r="G2" t="n">
-        <v>4.91</v>
+        <v>4.72</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.64</v>
+        <v>-3.92</v>
       </c>
       <c r="M2" t="n">
-        <v>170.5</v>
+        <v>166</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F3" t="n">
-        <v>20.1</v>
+        <v>19.99</v>
       </c>
       <c r="G3" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10712,7 +10712,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>15.37</v>
+        <v>15.25</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="M4" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>322</v>
+        <v>317.5</v>
       </c>
       <c r="F5" t="n">
-        <v>27.22</v>
+        <v>26.84</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.47</v>
+        <v>-1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>320.5</v>
+        <v>322</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.5</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>14.42</v>
+        <v>14.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>126.5</v>
       </c>
       <c r="F7" t="n">
-        <v>17.69</v>
+        <v>17.62</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.55</v>
+        <v>-0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F8" t="n">
-        <v>16.48</v>
+        <v>16.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>250.5</v>
+        <v>250</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="F9" t="n">
-        <v>46.59</v>
+        <v>45.74</v>
       </c>
       <c r="G9" t="n">
-        <v>24.88</v>
+        <v>24.43</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-4.35</v>
+        <v>-1.82</v>
       </c>
       <c r="M9" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.8</v>
+        <v>61.2</v>
       </c>
       <c r="F10" t="n">
-        <v>19.94</v>
+        <v>19.74</v>
       </c>
       <c r="G10" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.16</v>
+        <v>-0.97</v>
       </c>
       <c r="M10" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1505</v>
+        <v>1655</v>
       </c>
       <c r="F2" t="n">
-        <v>101.35</v>
+        <v>111.45</v>
       </c>
       <c r="G2" t="n">
-        <v>27.33</v>
+        <v>30.05</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.24</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>1430</v>
+        <v>1505</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="F3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11564,7 +11564,7 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>40.7</v>
+        <v>40.75</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>155.5</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5495</v>
+        <v>5345</v>
       </c>
       <c r="F5" t="n">
-        <v>117.67</v>
+        <v>114.45</v>
       </c>
       <c r="G5" t="n">
-        <v>33.85</v>
+        <v>32.93</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-5.26</v>
+        <v>-2.73</v>
       </c>
       <c r="M5" t="n">
-        <v>5800</v>
+        <v>5495</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124.5</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>23.53</v>
+        <v>23.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51</v>
+        <v>4.45</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.99</v>
+        <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>172.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22.32</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>4.89</v>
+        <v>4.82</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>-1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="F10" t="n">
-        <v>17.95</v>
+        <v>17.78</v>
       </c>
       <c r="G10" t="n">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.63</v>
+        <v>-0.95</v>
       </c>
       <c r="M10" t="n">
-        <v>157.5</v>
+        <v>158.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="F11" t="n">
-        <v>23.82</v>
+        <v>24.21</v>
       </c>
       <c r="G11" t="n">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>1220</v>
+        <v>1240</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>161.5</v>
+        <v>162</v>
       </c>
       <c r="F12" t="n">
-        <v>20.14</v>
+        <v>20.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.22</v>
+        <v>0.31</v>
       </c>
       <c r="M12" t="n">
-        <v>163.5</v>
+        <v>161.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>288.5</v>
+        <v>284.5</v>
       </c>
       <c r="F13" t="n">
-        <v>33.74</v>
+        <v>33.27</v>
       </c>
       <c r="G13" t="n">
-        <v>6.83</v>
+        <v>6.74</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>-1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>282</v>
+        <v>288.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>144.5</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>28.39</v>
+        <v>28.49</v>
       </c>
       <c r="G14" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>144.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F15" t="n">
-        <v>19.37</v>
+        <v>19.28</v>
       </c>
       <c r="G15" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.47</v>
       </c>
       <c r="M15" t="n">
-        <v>216.5</v>
+        <v>215</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7615</v>
+        <v>8375</v>
       </c>
       <c r="F16" t="n">
-        <v>195.21</v>
+        <v>214.69</v>
       </c>
       <c r="G16" t="n">
-        <v>75.79000000000001</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.5</v>
+        <v>9.98</v>
       </c>
       <c r="M16" t="n">
-        <v>7150</v>
+        <v>7615</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="F2" t="n">
-        <v>59.68</v>
+        <v>60.47</v>
       </c>
       <c r="G2" t="n">
-        <v>16.58</v>
+        <v>16.8</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8.07</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1735</v>
+        <v>1875</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="F3" t="n">
-        <v>20.97</v>
+        <v>20.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.11</v>
+        <v>-0.84</v>
       </c>
       <c r="M3" t="n">
-        <v>72.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>5790</v>
+        <v>5830</v>
       </c>
       <c r="F4" t="n">
-        <v>130.67</v>
+        <v>131.57</v>
       </c>
       <c r="G4" t="n">
-        <v>36.03</v>
+        <v>36.28</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>5525</v>
+        <v>5790</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4895</v>
+        <v>4860</v>
       </c>
       <c r="F5" t="n">
-        <v>76.54000000000001</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>30.07</v>
+        <v>29.85</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>-0.72</v>
       </c>
       <c r="M5" t="n">
-        <v>4890</v>
+        <v>4895</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="F6" t="n">
-        <v>46.99</v>
+        <v>46.6</v>
       </c>
       <c r="G6" t="n">
-        <v>24.64</v>
+        <v>24.43</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="M6" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.95</v>
+        <v>11.93</v>
       </c>
       <c r="G7" t="n">
         <v>1.67</v>
@@ -13232,7 +13232,7 @@
         <v>-0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>154.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.92</v>
+        <v>11.88</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13311,7 +13311,7 @@
         <v>-0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>155.5</v>
+        <v>155</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.84</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>108.5</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>952</v>
+        <v>923</v>
       </c>
       <c r="F10" t="n">
-        <v>25.76</v>
+        <v>24.97</v>
       </c>
       <c r="G10" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.06</v>
+        <v>-3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>198.5</v>
+        <v>197</v>
       </c>
       <c r="F11" t="n">
-        <v>27.34</v>
+        <v>27.13</v>
       </c>
       <c r="G11" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.5</v>
+        <v>-0.76</v>
       </c>
       <c r="M11" t="n">
-        <v>199.5</v>
+        <v>198.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3665</v>
+        <v>3715</v>
       </c>
       <c r="F12" t="n">
-        <v>53.75</v>
+        <v>54.49</v>
       </c>
       <c r="G12" t="n">
-        <v>5.24</v>
+        <v>5.31</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.53</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>3540</v>
+        <v>3665</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1655</v>
+        <v>1540</v>
       </c>
       <c r="F2" t="n">
-        <v>111.45</v>
+        <v>103.7</v>
       </c>
       <c r="G2" t="n">
-        <v>30.05</v>
+        <v>27.96</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.970000000000001</v>
+        <v>-6.95</v>
       </c>
       <c r="M2" t="n">
-        <v>1505</v>
+        <v>1655</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="F3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="G3" t="n">
         <v>1.82</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5345</v>
+        <v>5620</v>
       </c>
       <c r="F5" t="n">
-        <v>114.45</v>
+        <v>120.34</v>
       </c>
       <c r="G5" t="n">
-        <v>32.93</v>
+        <v>34.62</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.73</v>
+        <v>5.14</v>
       </c>
       <c r="M5" t="n">
-        <v>5495</v>
+        <v>5345</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>124.5</v>
+        <v>123</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.77</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.51</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.49</v>
+        <v>2.94</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172.5</v>
+        <v>172</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>21.94</v>
       </c>
       <c r="G8" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.43</v>
+        <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>175</v>
+        <v>172.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1260</v>
+        <v>1230</v>
       </c>
       <c r="F11" t="n">
-        <v>24.21</v>
+        <v>23.63</v>
       </c>
       <c r="G11" t="n">
-        <v>4.6</v>
+        <v>4.49</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.61</v>
+        <v>-2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
-        <v>20.2</v>
+        <v>20.57</v>
       </c>
       <c r="G12" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.31</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>161.5</v>
+        <v>162</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>284.5</v>
+        <v>283.5</v>
       </c>
       <c r="F13" t="n">
-        <v>33.27</v>
+        <v>33.16</v>
       </c>
       <c r="G13" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.39</v>
+        <v>-0.35</v>
       </c>
       <c r="M13" t="n">
-        <v>288.5</v>
+        <v>284.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.49</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>144.5</v>
+        <v>145</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F15" t="n">
-        <v>19.28</v>
+        <v>19.19</v>
       </c>
       <c r="G15" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1630,7 +1630,7 @@
         <v>-0.47</v>
       </c>
       <c r="M15" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8375</v>
+        <v>8385</v>
       </c>
       <c r="F16" t="n">
-        <v>214.69</v>
+        <v>214.94</v>
       </c>
       <c r="G16" t="n">
-        <v>83.34999999999999</v>
+        <v>83.45</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.98</v>
+        <v>0.12</v>
       </c>
       <c r="M16" t="n">
-        <v>7615</v>
+        <v>8375</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="F17" t="n">
-        <v>44.67</v>
+        <v>44.82</v>
       </c>
       <c r="G17" t="n">
-        <v>9.07</v>
+        <v>9.1</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.98</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>1525</v>
+        <v>1510</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12670</v>
+        <v>12390</v>
       </c>
       <c r="F18" t="n">
-        <v>69.84999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="G18" t="n">
-        <v>35.77</v>
+        <v>34.98</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.02</v>
+        <v>-2.21</v>
       </c>
       <c r="M18" t="n">
-        <v>12800</v>
+        <v>12670</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="F19" t="n">
-        <v>80.78</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>15.68</v>
+        <v>15.76</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.94</v>
+        <v>0.53</v>
       </c>
       <c r="M19" t="n">
-        <v>914</v>
+        <v>950</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>83.2</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
-        <v>45.71</v>
+        <v>45.05</v>
       </c>
       <c r="G20" t="n">
-        <v>6.84</v>
+        <v>6.74</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>-1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>82</v>
+        <v>83.2</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5765</v>
+        <v>5995</v>
       </c>
       <c r="F21" t="n">
-        <v>94.38</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>24.37</v>
+        <v>25.35</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-0.52</v>
+        <v>3.99</v>
       </c>
       <c r="M21" t="n">
-        <v>5795</v>
+        <v>5765</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2440</v>
+        <v>2325</v>
       </c>
       <c r="F22" t="n">
-        <v>62.24</v>
+        <v>59.31</v>
       </c>
       <c r="G22" t="n">
-        <v>31.33</v>
+        <v>29.85</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.74</v>
+        <v>-4.71</v>
       </c>
       <c r="M22" t="n">
-        <v>2375</v>
+        <v>2440</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>18.4</v>
+        <v>18.45</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1440</v>
+        <v>1460</v>
       </c>
       <c r="F24" t="n">
-        <v>73.13</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>17.85</v>
+        <v>18.09</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.35</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="F25" t="n">
-        <v>73.17</v>
+        <v>77.56</v>
       </c>
       <c r="G25" t="n">
-        <v>4.99</v>
+        <v>5.29</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2825</v>
+        <v>2680</v>
       </c>
       <c r="F26" t="n">
-        <v>243.12</v>
+        <v>230.64</v>
       </c>
       <c r="G26" t="n">
-        <v>55.38</v>
+        <v>52.54</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-1.74</v>
+        <v>-5.13</v>
       </c>
       <c r="M26" t="n">
-        <v>2875</v>
+        <v>2825</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1160</v>
+        <v>1175</v>
       </c>
       <c r="F28" t="n">
-        <v>56.81</v>
+        <v>57.54</v>
       </c>
       <c r="G28" t="n">
-        <v>11.77</v>
+        <v>11.92</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.87</v>
+        <v>1.29</v>
       </c>
       <c r="M28" t="n">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="F29" t="n">
-        <v>99.02</v>
+        <v>96.56</v>
       </c>
       <c r="G29" t="n">
-        <v>19.4</v>
+        <v>18.92</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-2.1</v>
+        <v>-2.48</v>
       </c>
       <c r="M29" t="n">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3700</v>
+        <v>3475</v>
       </c>
       <c r="F30" t="n">
-        <v>87.26000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>12.03</v>
+        <v>11.3</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6.17</v>
+        <v>-6.08</v>
       </c>
       <c r="M30" t="n">
-        <v>3485</v>
+        <v>3700</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F31" t="n">
-        <v>106.69</v>
+        <v>105.48</v>
       </c>
       <c r="G31" t="n">
-        <v>13.72</v>
+        <v>13.56</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-3.49</v>
+        <v>-1.14</v>
       </c>
       <c r="M31" t="n">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F32" t="n">
-        <v>44.52</v>
+        <v>44.4</v>
       </c>
       <c r="G32" t="n">
-        <v>11.04</v>
+        <v>11.01</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.42</v>
+        <v>-0.28</v>
       </c>
       <c r="M32" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F33" t="n">
-        <v>38.45</v>
+        <v>38.59</v>
       </c>
       <c r="G33" t="n">
-        <v>6.64</v>
+        <v>6.66</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.51</v>
+        <v>0.35</v>
       </c>
       <c r="M33" t="n">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>5180</v>
+        <v>5185</v>
       </c>
       <c r="F34" t="n">
-        <v>85.55</v>
+        <v>85.63</v>
       </c>
       <c r="G34" t="n">
-        <v>19.49</v>
+        <v>19.51</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.39</v>
+        <v>0.1</v>
       </c>
       <c r="M34" t="n">
-        <v>5010</v>
+        <v>5180</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="F36" t="n">
-        <v>20.79</v>
+        <v>20.82</v>
       </c>
       <c r="G36" t="n">
         <v>1.04</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-0.84</v>
+        <v>0.14</v>
       </c>
       <c r="M36" t="n">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>5830</v>
+        <v>6410</v>
       </c>
       <c r="F37" t="n">
-        <v>131.57</v>
+        <v>144.66</v>
       </c>
       <c r="G37" t="n">
-        <v>36.28</v>
+        <v>39.89</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>5790</v>
+        <v>5830</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>4860</v>
+        <v>5020</v>
       </c>
       <c r="F38" t="n">
-        <v>76</v>
+        <v>78.5</v>
       </c>
       <c r="G38" t="n">
-        <v>29.85</v>
+        <v>30.84</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-0.72</v>
+        <v>3.29</v>
       </c>
       <c r="M38" t="n">
-        <v>4895</v>
+        <v>4860</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="F39" t="n">
-        <v>46.6</v>
+        <v>46.07</v>
       </c>
       <c r="G39" t="n">
-        <v>24.43</v>
+        <v>24.16</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.84</v>
+        <v>-1.12</v>
       </c>
       <c r="M39" t="n">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="F40" t="n">
-        <v>11.93</v>
+        <v>11.92</v>
       </c>
       <c r="G40" t="n">
         <v>1.67</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-0.21</v>
+        <v>-0.1</v>
       </c>
       <c r="M40" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="F41" t="n">
-        <v>11.88</v>
+        <v>11.69</v>
       </c>
       <c r="G41" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-0.32</v>
+        <v>-1.62</v>
       </c>
       <c r="M41" t="n">
-        <v>155</v>
+        <v>154.5</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="F42" t="n">
-        <v>15.45</v>
+        <v>15.52</v>
       </c>
       <c r="G42" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.47</v>
+        <v>0.47</v>
       </c>
       <c r="M42" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="F43" t="n">
-        <v>24.97</v>
+        <v>24.49</v>
       </c>
       <c r="G43" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-3.05</v>
+        <v>-1.95</v>
       </c>
       <c r="M43" t="n">
-        <v>952</v>
+        <v>923</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,10 +3929,10 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>197</v>
+        <v>196.5</v>
       </c>
       <c r="F44" t="n">
-        <v>27.13</v>
+        <v>27.07</v>
       </c>
       <c r="G44" t="n">
         <v>2.65</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="M44" t="n">
-        <v>198.5</v>
+        <v>197</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3715</v>
+        <v>3760</v>
       </c>
       <c r="F45" t="n">
-        <v>54.49</v>
+        <v>55.15</v>
       </c>
       <c r="G45" t="n">
-        <v>5.31</v>
+        <v>5.37</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="M45" t="n">
-        <v>3665</v>
+        <v>3715</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>217.5</v>
+        <v>216.5</v>
       </c>
       <c r="F46" t="n">
-        <v>22.15</v>
+        <v>22.05</v>
       </c>
       <c r="G46" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.11</v>
+        <v>-0.46</v>
       </c>
       <c r="M46" t="n">
-        <v>213</v>
+        <v>217.5</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4155,34 +4155,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E47" t="n">
-        <v>123.5</v>
+        <v>230</v>
       </c>
       <c r="F47" t="n">
-        <v>20.08</v>
+        <v>25.19</v>
       </c>
       <c r="G47" t="n">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>-15.3</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -4191,31 +4191,31 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+        <v>233.5</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>EPS單期衰退</t>
+        </is>
+      </c>
       <c r="P47" t="n">
-        <v>10.8</v>
+        <v>9.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.4</v>
+        <v>0.72</v>
       </c>
       <c r="R47" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="S47" t="n">
-        <v>48.7</v>
+        <v>34.8</v>
       </c>
       <c r="T47" t="n">
-        <v>28.4</v>
+        <v>34.5</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
@@ -4225,19 +4225,19 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4246,20 +4246,20 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E48" t="n">
-        <v>233.5</v>
+        <v>761</v>
       </c>
       <c r="F48" t="n">
-        <v>25.58</v>
+        <v>27.59</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15</v>
+        <v>7.78</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>-15.3</v>
+        <v>27</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4268,31 +4268,35 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-0.21</v>
+        <v>0.79</v>
       </c>
       <c r="M48" t="n">
-        <v>234</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>755</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>9.4</v>
+        <v>31.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="R48" t="n">
-        <v>13.2</v>
+        <v>3.8</v>
       </c>
       <c r="S48" t="n">
-        <v>34.8</v>
+        <v>21.9</v>
       </c>
       <c r="T48" t="n">
-        <v>34.5</v>
+        <v>32.2</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -4302,19 +4306,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4323,20 +4327,20 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>755</v>
+        <v>109</v>
       </c>
       <c r="F49" t="n">
-        <v>27.37</v>
+        <v>20.34</v>
       </c>
       <c r="G49" t="n">
-        <v>7.72</v>
+        <v>2.53</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>186.3</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4345,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.03</v>
+        <v>-0.91</v>
       </c>
       <c r="M49" t="n">
-        <v>740</v>
+        <v>110</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4357,28 +4361,28 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>31.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="R49" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S49" t="n">
-        <v>21.9</v>
+        <v>37</v>
       </c>
       <c r="T49" t="n">
-        <v>32.2</v>
+        <v>35.8</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4390,12 +4394,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4404,20 +4408,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E50" t="n">
-        <v>110</v>
+        <v>6190</v>
       </c>
       <c r="F50" t="n">
-        <v>20.52</v>
+        <v>32.92</v>
       </c>
       <c r="G50" t="n">
-        <v>2.55</v>
+        <v>4.23</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>186.3</v>
+        <v>9</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4426,10 +4430,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.46</v>
+        <v>-3.36</v>
       </c>
       <c r="M50" t="n">
-        <v>109.5</v>
+        <v>6405</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4438,28 +4442,28 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="R50" t="n">
-        <v>-3.4</v>
+        <v>6.8</v>
       </c>
       <c r="S50" t="n">
-        <v>37</v>
+        <v>41.8</v>
       </c>
       <c r="T50" t="n">
-        <v>35.8</v>
+        <v>32.9</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4471,73 +4475,71 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E51" t="n">
-        <v>6405</v>
+        <v>549</v>
       </c>
       <c r="F51" t="n">
-        <v>34.07</v>
+        <v>24.86</v>
       </c>
       <c r="G51" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>6.77</v>
+      </c>
+      <c r="H51" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I51" t="n">
-        <v>9</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.08</v>
+        <v>2.62</v>
       </c>
       <c r="M51" t="n">
-        <v>6400</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="R51" t="n">
-        <v>6.8</v>
+        <v>10.6</v>
       </c>
       <c r="S51" t="n">
-        <v>41.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T51" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="U51" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4545,19 +4547,19 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4566,25 +4568,25 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E52" t="n">
-        <v>535</v>
+        <v>691</v>
       </c>
       <c r="F52" t="n">
-        <v>24.23</v>
+        <v>42.39</v>
       </c>
       <c r="G52" t="n">
-        <v>6.6</v>
+        <v>5.69</v>
       </c>
       <c r="H52" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I52" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J52" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4592,78 +4594,78 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-1.85</v>
       </c>
       <c r="M52" t="n">
-        <v>535</v>
+        <v>704</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R52" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S52" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T52" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U52" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E53" t="n">
-        <v>704</v>
+        <v>58.4</v>
       </c>
       <c r="F53" t="n">
-        <v>43.19</v>
+        <v>16.04</v>
       </c>
       <c r="G53" t="n">
-        <v>5.8</v>
+        <v>2.44</v>
       </c>
       <c r="H53" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I53" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J53" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4671,30 +4673,30 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.28</v>
+        <v>-0.51</v>
       </c>
       <c r="M53" t="n">
-        <v>702</v>
+        <v>58.7</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R53" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S53" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T53" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U53" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -4703,19 +4705,19 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4724,25 +4726,25 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E54" t="n">
-        <v>58.7</v>
+        <v>178.5</v>
       </c>
       <c r="F54" t="n">
-        <v>16.13</v>
+        <v>16.3</v>
       </c>
       <c r="G54" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="H54" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I54" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J54" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4750,34 +4752,34 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1.34</v>
+        <v>-0.83</v>
       </c>
       <c r="M54" t="n">
-        <v>59.5</v>
+        <v>180</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R54" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S54" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T54" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U54" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -4789,91 +4791,89 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E55" t="n">
-        <v>180</v>
+        <v>336</v>
       </c>
       <c r="F55" t="n">
-        <v>16.44</v>
+        <v>17.4</v>
       </c>
       <c r="G55" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H55" t="n">
-        <v>15.5</v>
-      </c>
+        <v>4.93</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.95</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.28</v>
+        <v>-0.15</v>
       </c>
       <c r="M55" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
+        <v>336.5</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.03</v>
+        <v>1.09</v>
       </c>
       <c r="R55" t="n">
-        <v>30.2</v>
+        <v>24.2</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4882,20 +4882,20 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E56" t="n">
-        <v>336.5</v>
+        <v>165.5</v>
       </c>
       <c r="F56" t="n">
-        <v>17.43</v>
+        <v>18.62</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94</v>
+        <v>3.93</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>49</v>
+        <v>57.1</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-1.46</v>
+        <v>-0.3</v>
       </c>
       <c r="M56" t="n">
-        <v>341.5</v>
+        <v>166</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4916,24 +4916,24 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>29.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="R56" t="n">
-        <v>24.2</v>
+        <v>11.1</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="T56" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -4945,34 +4945,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E57" t="n">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="F57" t="n">
-        <v>18.67</v>
+        <v>19.84</v>
       </c>
       <c r="G57" t="n">
-        <v>3.94</v>
+        <v>2.93</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>57.1</v>
+        <v>11</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-0.3</v>
+        <v>-1.21</v>
       </c>
       <c r="M57" t="n">
-        <v>166.5</v>
+        <v>123.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4993,24 +4993,24 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>18.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="R57" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="S57" t="n">
-        <v>3.6</v>
+        <v>48.7</v>
       </c>
       <c r="T57" t="n">
-        <v>22</v>
+        <v>28.4</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5039,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>88.5</v>
+        <v>87.5</v>
       </c>
       <c r="F58" t="n">
-        <v>16.89</v>
+        <v>16.7</v>
       </c>
       <c r="G58" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-1.45</v>
+        <v>-1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>89.8</v>
+        <v>88.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5120,13 +5120,13 @@
         <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F59" t="n">
-        <v>17.28</v>
+        <v>17.17</v>
       </c>
       <c r="G59" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.32</v>
+        <v>-0.65</v>
       </c>
       <c r="M59" t="n">
-        <v>154.5</v>
+        <v>155</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5201,13 +5201,13 @@
         <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>232</v>
+        <v>234.5</v>
       </c>
       <c r="F60" t="n">
-        <v>14.42</v>
+        <v>14.57</v>
       </c>
       <c r="G60" t="n">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-2.52</v>
+        <v>1.08</v>
       </c>
       <c r="M60" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5278,13 +5278,13 @@
         <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>184</v>
+        <v>185.5</v>
       </c>
       <c r="F61" t="n">
-        <v>15.53</v>
+        <v>15.65</v>
       </c>
       <c r="G61" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="M61" t="n">
         <v>184</v>
@@ -5355,13 +5355,13 @@
         <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F62" t="n">
-        <v>16.8</v>
+        <v>16.84</v>
       </c>
       <c r="G62" t="n">
-        <v>13.55</v>
+        <v>13.59</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="M62" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="F63" t="n">
-        <v>19.29</v>
+        <v>19.98</v>
       </c>
       <c r="G63" t="n">
-        <v>5.32</v>
+        <v>5.51</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-3.68</v>
+        <v>3.62</v>
       </c>
       <c r="M63" t="n">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>171</v>
+        <v>172.5</v>
       </c>
       <c r="F64" t="n">
-        <v>18.85</v>
+        <v>19.02</v>
       </c>
       <c r="G64" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1.72</v>
+        <v>0.88</v>
       </c>
       <c r="M64" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5577,71 +5577,73 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>159.5</v>
+        <v>49.1</v>
       </c>
       <c r="F65" t="n">
-        <v>16.75</v>
+        <v>12.12</v>
       </c>
       <c r="G65" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="H65" t="n">
-        <v>14.7</v>
-      </c>
+        <v>2.14</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1.29</v>
-      </c>
+        <v>-15.4</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-3.92</v>
+        <v>2.29</v>
       </c>
       <c r="M65" t="n">
-        <v>166</v>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
+        </is>
+      </c>
       <c r="P65" t="n">
-        <v>27.9</v>
+        <v>11.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.34</v>
+        <v>0.58</v>
       </c>
       <c r="R65" t="n">
-        <v>10.8</v>
+        <v>-2.2</v>
       </c>
       <c r="S65" t="n">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="T65" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.29</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -5649,19 +5651,19 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5670,25 +5672,25 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>534</v>
+        <v>157.5</v>
       </c>
       <c r="F66" t="n">
-        <v>19.99</v>
+        <v>16.54</v>
       </c>
       <c r="G66" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="H66" t="n">
-        <v>17.9</v>
+        <v>14.7</v>
       </c>
       <c r="I66" t="n">
-        <v>19.1</v>
+        <v>12.8</v>
       </c>
       <c r="J66" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5696,51 +5698,51 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.25</v>
       </c>
       <c r="M66" t="n">
-        <v>537</v>
+        <v>159.5</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>23.5</v>
+        <v>27.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="R66" t="n">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="S66" t="n">
-        <v>18.6</v>
+        <v>7.7</v>
       </c>
       <c r="T66" t="n">
-        <v>21.3</v>
+        <v>16.5</v>
       </c>
       <c r="U66" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5749,25 +5751,25 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>118</v>
+        <v>542</v>
       </c>
       <c r="F67" t="n">
-        <v>15.25</v>
+        <v>20.28</v>
       </c>
       <c r="G67" t="n">
-        <v>3.66</v>
+        <v>4.79</v>
       </c>
       <c r="H67" t="n">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="I67" t="n">
-        <v>13.5</v>
+        <v>19.1</v>
       </c>
       <c r="J67" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5775,34 +5777,34 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.84</v>
+        <v>1.5</v>
       </c>
       <c r="M67" t="n">
-        <v>119</v>
+        <v>534</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>19.8</v>
+        <v>23.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="R67" t="n">
-        <v>7</v>
+        <v>12.2</v>
       </c>
       <c r="S67" t="n">
-        <v>0.6</v>
+        <v>18.6</v>
       </c>
       <c r="T67" t="n">
-        <v>17.1</v>
+        <v>21.3</v>
       </c>
       <c r="U67" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -5814,12 +5816,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5828,25 +5830,25 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E68" t="n">
-        <v>317.5</v>
+        <v>118</v>
       </c>
       <c r="F68" t="n">
-        <v>26.84</v>
+        <v>15.25</v>
       </c>
       <c r="G68" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="H68" t="n">
-        <v>27.5</v>
+        <v>15</v>
       </c>
       <c r="I68" t="n">
-        <v>29.1</v>
+        <v>13.5</v>
       </c>
       <c r="J68" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5854,51 +5856,51 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>322</v>
+        <v>118</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>27.3</v>
+        <v>19.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.83</v>
+        <v>1.28</v>
       </c>
       <c r="R68" t="n">
-        <v>18.3</v>
+        <v>7</v>
       </c>
       <c r="S68" t="n">
-        <v>41.8</v>
+        <v>0.6</v>
       </c>
       <c r="T68" t="n">
-        <v>35.5</v>
+        <v>17.1</v>
       </c>
       <c r="U68" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5907,25 +5909,25 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>82</v>
+        <v>316.5</v>
       </c>
       <c r="F69" t="n">
-        <v>14.34</v>
+        <v>26.75</v>
       </c>
       <c r="G69" t="n">
-        <v>2.03</v>
+        <v>6.88</v>
       </c>
       <c r="H69" t="n">
-        <v>16.7</v>
+        <v>27.5</v>
       </c>
       <c r="I69" t="n">
-        <v>14.1</v>
+        <v>29.1</v>
       </c>
       <c r="J69" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5933,78 +5935,78 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.61</v>
+        <v>-0.31</v>
       </c>
       <c r="M69" t="n">
-        <v>82.5</v>
+        <v>317.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>10.8</v>
+        <v>27.3</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.1</v>
+        <v>0.83</v>
       </c>
       <c r="R69" t="n">
-        <v>21.7</v>
+        <v>18.3</v>
       </c>
       <c r="S69" t="n">
-        <v>19.5</v>
+        <v>41.8</v>
       </c>
       <c r="T69" t="n">
-        <v>19.1</v>
+        <v>35.5</v>
       </c>
       <c r="U69" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>126.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>17.62</v>
+        <v>14.49</v>
       </c>
       <c r="G70" t="n">
-        <v>4.37</v>
+        <v>2.05</v>
       </c>
       <c r="H70" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="I70" t="n">
-        <v>17.2</v>
+        <v>14.1</v>
       </c>
       <c r="J70" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6012,38 +6014,34 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-0.39</v>
+        <v>1.1</v>
       </c>
       <c r="M70" t="n">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>含金量-0.3差</t>
-        </is>
-      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>34.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q70" t="n">
-        <v>-0.28</v>
+        <v>2.1</v>
       </c>
       <c r="R70" t="n">
-        <v>17.8</v>
+        <v>21.7</v>
       </c>
       <c r="S70" t="n">
-        <v>17.6</v>
+        <v>19.5</v>
       </c>
       <c r="T70" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="U70" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -6055,12 +6053,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6072,22 +6070,22 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>253</v>
+        <v>129</v>
       </c>
       <c r="F71" t="n">
-        <v>16.68</v>
+        <v>17.97</v>
       </c>
       <c r="G71" t="n">
-        <v>1.86</v>
+        <v>4.46</v>
       </c>
       <c r="H71" t="n">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="I71" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="J71" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6095,30 +6093,34 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="M71" t="n">
-        <v>250</v>
+        <v>126.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>含金量-0.3差</t>
+        </is>
+      </c>
       <c r="P71" t="n">
-        <v>11.4</v>
+        <v>34.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.24</v>
+        <v>-0.28</v>
       </c>
       <c r="R71" t="n">
-        <v>7.8</v>
+        <v>17.8</v>
       </c>
       <c r="S71" t="n">
-        <v>39.6</v>
+        <v>17.6</v>
       </c>
       <c r="T71" t="n">
-        <v>17.6</v>
+        <v>19.2</v>
       </c>
       <c r="U71" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -6134,12 +6136,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6148,23 +6150,25 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>1080</v>
+        <v>256</v>
       </c>
       <c r="F72" t="n">
-        <v>45.74</v>
+        <v>16.88</v>
       </c>
       <c r="G72" t="n">
-        <v>24.43</v>
+        <v>1.88</v>
       </c>
       <c r="H72" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
+        <v>15.3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>15.2</v>
+      </c>
       <c r="J72" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6172,34 +6176,30 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.82</v>
+        <v>1.19</v>
       </c>
       <c r="M72" t="n">
-        <v>1100</v>
+        <v>253</v>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>EPS資料不足</t>
-        </is>
-      </c>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>52.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="R72" t="n">
-        <v>97.59999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="S72" t="n">
-        <v>99.3</v>
+        <v>39.6</v>
       </c>
       <c r="T72" t="n">
-        <v>62</v>
+        <v>17.6</v>
       </c>
       <c r="U72" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -6208,19 +6208,19 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6229,25 +6229,23 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>61.2</v>
+        <v>1060</v>
       </c>
       <c r="F73" t="n">
-        <v>19.74</v>
+        <v>44.9</v>
       </c>
       <c r="G73" t="n">
-        <v>2.83</v>
+        <v>23.98</v>
       </c>
       <c r="H73" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I73" t="n">
-        <v>18.7</v>
-      </c>
+        <v>38.8</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6255,34 +6253,34 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-0.97</v>
+        <v>-1.85</v>
       </c>
       <c r="M73" t="n">
-        <v>61.8</v>
+        <v>1080</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>⚠️高槓桿(負債81%)</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>13.6</v>
+        <v>52.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="R73" t="n">
-        <v>7.4</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S73" t="n">
-        <v>35.3</v>
+        <v>99.3</v>
       </c>
       <c r="T73" t="n">
-        <v>25.2</v>
+        <v>62</v>
       </c>
       <c r="U73" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -6291,98 +6289,102 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>3390</v>
+        <v>61</v>
       </c>
       <c r="F74" t="n">
-        <v>45.19</v>
+        <v>19.68</v>
       </c>
       <c r="G74" t="n">
-        <v>24.12</v>
+        <v>2.82</v>
       </c>
       <c r="H74" t="n">
-        <v>24.6</v>
+        <v>21.3</v>
       </c>
       <c r="I74" t="n">
-        <v>86.7</v>
+        <v>18.7</v>
       </c>
       <c r="J74" t="n">
-        <v>0.66</v>
+        <v>1.35</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-0.73</v>
+        <v>-0.33</v>
       </c>
       <c r="M74" t="n">
-        <v>3415</v>
+        <v>61.2</v>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>⚠️高槓桿(負債81%)</t>
+        </is>
+      </c>
       <c r="P74" t="n">
-        <v>50.9</v>
+        <v>13.6</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.81</v>
+        <v>1.09</v>
       </c>
       <c r="R74" t="n">
-        <v>31.1</v>
+        <v>7.4</v>
       </c>
       <c r="S74" t="n">
-        <v>60.6</v>
+        <v>35.3</v>
       </c>
       <c r="T74" t="n">
-        <v>39.3</v>
+        <v>25.2</v>
       </c>
       <c r="U74" t="n">
-        <v>0.66</v>
+        <v>1.35</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6394,22 +6396,22 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>715</v>
+        <v>3470</v>
       </c>
       <c r="F75" t="n">
-        <v>14.4</v>
+        <v>46.25</v>
       </c>
       <c r="G75" t="n">
-        <v>8.140000000000001</v>
+        <v>24.69</v>
       </c>
       <c r="H75" t="n">
-        <v>14.2</v>
+        <v>24.6</v>
       </c>
       <c r="I75" t="n">
-        <v>54.3</v>
+        <v>86.7</v>
       </c>
       <c r="J75" t="n">
-        <v>0.4</v>
+        <v>0.66</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6417,34 +6419,34 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-0.42</v>
+        <v>2.36</v>
       </c>
       <c r="M75" t="n">
-        <v>718</v>
+        <v>3390</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
-        <v>37.1</v>
+        <v>50.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="R75" t="n">
-        <v>34.4</v>
+        <v>31.1</v>
       </c>
       <c r="S75" t="n">
-        <v>103.3</v>
+        <v>60.6</v>
       </c>
       <c r="T75" t="n">
-        <v>21.9</v>
+        <v>39.3</v>
       </c>
       <c r="U75" t="n">
-        <v>0.4</v>
+        <v>0.66</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -6456,12 +6458,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6473,22 +6475,22 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>2460</v>
+        <v>736</v>
       </c>
       <c r="F76" t="n">
-        <v>28.52</v>
+        <v>14.83</v>
       </c>
       <c r="G76" t="n">
-        <v>9.92</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>23.6</v>
+        <v>14.2</v>
       </c>
       <c r="I76" t="n">
-        <v>43.1</v>
+        <v>54.3</v>
       </c>
       <c r="J76" t="n">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6496,30 +6498,30 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="M76" t="n">
-        <v>2480</v>
+        <v>715</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>32.5</v>
+        <v>37.1</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="R76" t="n">
-        <v>24.5</v>
+        <v>34.4</v>
       </c>
       <c r="S76" t="n">
-        <v>30.1</v>
+        <v>103.3</v>
       </c>
       <c r="T76" t="n">
-        <v>33.7</v>
+        <v>21.9</v>
       </c>
       <c r="U76" t="n">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -6535,12 +6537,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6549,25 +6551,25 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>121</v>
+        <v>2500</v>
       </c>
       <c r="F77" t="n">
-        <v>17.26</v>
+        <v>28.98</v>
       </c>
       <c r="G77" t="n">
-        <v>3.82</v>
+        <v>10.08</v>
       </c>
       <c r="H77" t="n">
-        <v>12.4</v>
+        <v>23.6</v>
       </c>
       <c r="I77" t="n">
-        <v>20.6</v>
+        <v>43.1</v>
       </c>
       <c r="J77" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6575,34 +6577,34 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M77" t="n">
-        <v>121</v>
+        <v>2460</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>20.9</v>
+        <v>32.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="R77" t="n">
-        <v>17.9</v>
+        <v>24.5</v>
       </c>
       <c r="S77" t="n">
-        <v>27.4</v>
+        <v>30.1</v>
       </c>
       <c r="T77" t="n">
-        <v>14.9</v>
+        <v>33.7</v>
       </c>
       <c r="U77" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -6614,12 +6616,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6628,25 +6630,25 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>108</v>
+        <v>118.5</v>
       </c>
       <c r="F78" t="n">
-        <v>13.37</v>
+        <v>16.9</v>
       </c>
       <c r="G78" t="n">
-        <v>1.94</v>
+        <v>3.74</v>
       </c>
       <c r="H78" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="I78" t="n">
-        <v>23.9</v>
+        <v>20.6</v>
       </c>
       <c r="J78" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6654,30 +6656,30 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-1.37</v>
+        <v>-2.07</v>
       </c>
       <c r="M78" t="n">
-        <v>109.5</v>
+        <v>121</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>17</v>
+        <v>20.9</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="R78" t="n">
-        <v>5.7</v>
+        <v>17.9</v>
       </c>
       <c r="S78" t="n">
-        <v>20.2</v>
+        <v>27.4</v>
       </c>
       <c r="T78" t="n">
-        <v>15.2</v>
+        <v>14.9</v>
       </c>
       <c r="U78" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -6693,12 +6695,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6710,22 +6712,22 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>25.8</v>
+        <v>109.5</v>
       </c>
       <c r="F79" t="n">
-        <v>5.18</v>
+        <v>13.55</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>1.97</v>
       </c>
       <c r="H79" t="n">
-        <v>5.9</v>
+        <v>12.3</v>
       </c>
       <c r="I79" t="n">
-        <v>16.1</v>
+        <v>23.9</v>
       </c>
       <c r="J79" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6733,34 +6735,34 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.58</v>
+        <v>1.39</v>
       </c>
       <c r="M79" t="n">
-        <v>25.95</v>
+        <v>108</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>19.4</v>
+        <v>17</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.89</v>
+        <v>1.36</v>
       </c>
       <c r="R79" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="S79" t="n">
-        <v>88.7</v>
+        <v>20.2</v>
       </c>
       <c r="T79" t="n">
-        <v>6.8</v>
+        <v>15.2</v>
       </c>
       <c r="U79" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -6772,12 +6774,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6789,22 +6791,22 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>105</v>
+        <v>25.5</v>
       </c>
       <c r="F80" t="n">
-        <v>12.1</v>
+        <v>5.12</v>
       </c>
       <c r="G80" t="n">
-        <v>2.83</v>
+        <v>0.99</v>
       </c>
       <c r="H80" t="n">
-        <v>10.7</v>
+        <v>5.9</v>
       </c>
       <c r="I80" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="J80" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6812,30 +6814,30 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-2.33</v>
+        <v>-1.16</v>
       </c>
       <c r="M80" t="n">
-        <v>107.5</v>
+        <v>25.8</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
-        <v>24.9</v>
+        <v>19.4</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="R80" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="S80" t="n">
-        <v>1.7</v>
+        <v>88.7</v>
       </c>
       <c r="T80" t="n">
-        <v>12.4</v>
+        <v>6.8</v>
       </c>
       <c r="U80" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -6851,12 +6853,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6868,22 +6870,22 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>181</v>
+        <v>105.5</v>
       </c>
       <c r="F81" t="n">
-        <v>12.9</v>
+        <v>12.15</v>
       </c>
       <c r="G81" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="H81" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="I81" t="n">
-        <v>24.1</v>
+        <v>16.2</v>
       </c>
       <c r="J81" t="n">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6891,30 +6893,30 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="M81" t="n">
-        <v>179.5</v>
+        <v>105</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>22.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="R81" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="S81" t="n">
-        <v>13.3</v>
+        <v>1.7</v>
       </c>
       <c r="T81" t="n">
-        <v>14.1</v>
+        <v>12.4</v>
       </c>
       <c r="U81" t="n">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -6930,12 +6932,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6944,25 +6946,25 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>42.5</v>
+        <v>180</v>
       </c>
       <c r="F82" t="n">
-        <v>8.949999999999999</v>
+        <v>12.83</v>
       </c>
       <c r="G82" t="n">
-        <v>1.65</v>
+        <v>3.18</v>
       </c>
       <c r="H82" t="n">
-        <v>7.6</v>
+        <v>11.4</v>
       </c>
       <c r="I82" t="n">
-        <v>9.9</v>
+        <v>24.1</v>
       </c>
       <c r="J82" t="n">
-        <v>0.84</v>
+        <v>0.59</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6970,30 +6972,30 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.31</v>
+        <v>-0.55</v>
       </c>
       <c r="M82" t="n">
-        <v>41.95</v>
+        <v>181</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>20.9</v>
+        <v>22.1</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="R82" t="n">
-        <v>20.7</v>
+        <v>10.2</v>
       </c>
       <c r="S82" t="n">
-        <v>22.1</v>
+        <v>13.3</v>
       </c>
       <c r="T82" t="n">
-        <v>8.300000000000001</v>
+        <v>14.1</v>
       </c>
       <c r="U82" t="n">
-        <v>0.84</v>
+        <v>0.59</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -7009,12 +7011,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7023,25 +7025,25 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>898</v>
+        <v>42.85</v>
       </c>
       <c r="F83" t="n">
-        <v>23.54</v>
+        <v>9.02</v>
       </c>
       <c r="G83" t="n">
-        <v>9.02</v>
+        <v>1.66</v>
       </c>
       <c r="H83" t="n">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="I83" t="n">
-        <v>79.40000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J83" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7049,34 +7051,34 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-0.22</v>
+        <v>0.82</v>
       </c>
       <c r="M83" t="n">
-        <v>900</v>
+        <v>42.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>33.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q83" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R83" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S83" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U83" t="n">
         <v>0.84</v>
       </c>
-      <c r="R83" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="S83" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="T83" t="n">
-        <v>40</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0.67</v>
-      </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -7088,12 +7090,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7105,22 +7107,22 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>539</v>
+        <v>892</v>
       </c>
       <c r="F84" t="n">
-        <v>23.09</v>
+        <v>23.38</v>
       </c>
       <c r="G84" t="n">
-        <v>5.08</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>21.2</v>
+        <v>25</v>
       </c>
       <c r="I84" t="n">
-        <v>29.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7128,30 +7130,30 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.86</v>
+        <v>-0.67</v>
       </c>
       <c r="M84" t="n">
-        <v>524</v>
+        <v>898</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>18.5</v>
+        <v>33.9</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.13</v>
+        <v>0.84</v>
       </c>
       <c r="R84" t="n">
-        <v>3.9</v>
+        <v>23.6</v>
       </c>
       <c r="S84" t="n">
-        <v>46.6</v>
+        <v>37.3</v>
       </c>
       <c r="T84" t="n">
-        <v>27.5</v>
+        <v>40</v>
       </c>
       <c r="U84" t="n">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -7167,12 +7169,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7184,22 +7186,22 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>167</v>
+        <v>543</v>
       </c>
       <c r="F85" t="n">
-        <v>17.96</v>
+        <v>23.26</v>
       </c>
       <c r="G85" t="n">
-        <v>4.54</v>
+        <v>5.12</v>
       </c>
       <c r="H85" t="n">
-        <v>14.1</v>
+        <v>21.2</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>29.8</v>
       </c>
       <c r="J85" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7207,34 +7209,34 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.3</v>
+        <v>0.74</v>
       </c>
       <c r="M85" t="n">
-        <v>166.5</v>
+        <v>539</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>20.7</v>
+        <v>18.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="R85" t="n">
-        <v>8.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="S85" t="n">
-        <v>14.9</v>
+        <v>46.6</v>
       </c>
       <c r="T85" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="U85" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -7246,12 +7248,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7260,25 +7262,25 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>39.2</v>
+        <v>163</v>
       </c>
       <c r="F86" t="n">
-        <v>8.08</v>
+        <v>17.53</v>
       </c>
       <c r="G86" t="n">
-        <v>1.11</v>
+        <v>4.43</v>
       </c>
       <c r="H86" t="n">
-        <v>6.2</v>
+        <v>14.1</v>
       </c>
       <c r="I86" t="n">
-        <v>44.7</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7286,30 +7288,30 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.38</v>
+        <v>-2.4</v>
       </c>
       <c r="M86" t="n">
-        <v>39.05</v>
+        <v>167</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>13.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.89</v>
+        <v>1.16</v>
       </c>
       <c r="R86" t="n">
-        <v>14.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S86" t="n">
-        <v>153.2</v>
+        <v>14.9</v>
       </c>
       <c r="T86" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="U86" t="n">
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -7325,12 +7327,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7339,25 +7341,25 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>1915</v>
+        <v>38.85</v>
       </c>
       <c r="F87" t="n">
-        <v>30.09</v>
+        <v>8.01</v>
       </c>
       <c r="G87" t="n">
-        <v>15.5</v>
+        <v>1.1</v>
       </c>
       <c r="H87" t="n">
-        <v>30.7</v>
+        <v>6.2</v>
       </c>
       <c r="I87" t="n">
-        <v>71.7</v>
+        <v>44.7</v>
       </c>
       <c r="J87" t="n">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7365,38 +7367,34 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.08</v>
+        <v>-0.89</v>
       </c>
       <c r="M87" t="n">
-        <v>1840</v>
+        <v>39.2</v>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
-        <v>45.1</v>
+        <v>13.6</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="R87" t="n">
-        <v>42.9</v>
+        <v>14.5</v>
       </c>
       <c r="S87" t="n">
-        <v>56.6</v>
+        <v>153.2</v>
       </c>
       <c r="T87" t="n">
-        <v>49.1</v>
+        <v>9</v>
       </c>
       <c r="U87" t="n">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -7408,12 +7406,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7425,22 +7423,22 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1600</v>
+        <v>1890</v>
       </c>
       <c r="F88" t="n">
-        <v>36.9</v>
+        <v>29.69</v>
       </c>
       <c r="G88" t="n">
-        <v>11.23</v>
+        <v>15.3</v>
       </c>
       <c r="H88" t="n">
-        <v>21.8</v>
+        <v>30.7</v>
       </c>
       <c r="I88" t="n">
-        <v>40.5</v>
+        <v>71.7</v>
       </c>
       <c r="J88" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7448,38 +7446,38 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>5.26</v>
+        <v>-1.31</v>
       </c>
       <c r="M88" t="n">
-        <v>1520</v>
+        <v>1915</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>含金量-0.1差</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>24.6</v>
+        <v>45.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>-0.08</v>
+        <v>0.92</v>
       </c>
       <c r="R88" t="n">
-        <v>13.1</v>
+        <v>42.9</v>
       </c>
       <c r="S88" t="n">
-        <v>93.8</v>
+        <v>56.6</v>
       </c>
       <c r="T88" t="n">
-        <v>30.6</v>
+        <v>49.1</v>
       </c>
       <c r="U88" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -7491,39 +7489,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>89.8</v>
+        <v>1595</v>
       </c>
       <c r="F89" t="n">
-        <v>8.800000000000001</v>
+        <v>36.79</v>
       </c>
       <c r="G89" t="n">
-        <v>2.16</v>
+        <v>11.19</v>
       </c>
       <c r="H89" t="n">
-        <v>8.6</v>
+        <v>21.8</v>
       </c>
       <c r="I89" t="n">
-        <v>31.3</v>
+        <v>40.5</v>
       </c>
       <c r="J89" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7531,38 +7529,38 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="M89" t="n">
-        <v>89.8</v>
+        <v>1600</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>含金量-0.1差</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>20.9</v>
+        <v>24.6</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.28</v>
+        <v>-0.08</v>
       </c>
       <c r="R89" t="n">
-        <v>10.5</v>
+        <v>13.1</v>
       </c>
       <c r="S89" t="n">
-        <v>1.5</v>
+        <v>93.8</v>
       </c>
       <c r="T89" t="n">
-        <v>11.2</v>
+        <v>30.6</v>
       </c>
       <c r="U89" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -7574,12 +7572,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7588,25 +7586,25 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>55.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>8.42</v>
+        <v>8.81</v>
       </c>
       <c r="G90" t="n">
-        <v>1.39</v>
+        <v>2.16</v>
       </c>
       <c r="H90" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="I90" t="n">
-        <v>13.7</v>
+        <v>31.3</v>
       </c>
       <c r="J90" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7614,38 +7612,38 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.36</v>
+        <v>0.11</v>
       </c>
       <c r="M90" t="n">
-        <v>55.7</v>
+        <v>89.8</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>含金量0.5弱</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>23.3</v>
+        <v>20.9</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.52</v>
+        <v>2.28</v>
       </c>
       <c r="R90" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="S90" t="n">
-        <v>11.8</v>
+        <v>1.5</v>
       </c>
       <c r="T90" t="n">
-        <v>7.7</v>
+        <v>11.2</v>
       </c>
       <c r="U90" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -7657,12 +7655,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7671,25 +7669,25 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>53.1</v>
+        <v>56.2</v>
       </c>
       <c r="F91" t="n">
-        <v>7.36</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="H91" t="n">
-        <v>10.4</v>
+        <v>6.8</v>
       </c>
       <c r="I91" t="n">
-        <v>17.1</v>
+        <v>13.7</v>
       </c>
       <c r="J91" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7697,34 +7695,34 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="M91" t="n">
-        <v>52.7</v>
+        <v>55.9</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>月營收轉負-10%</t>
+          <t>含金量0.5弱</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>17.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="R91" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="S91" t="n">
-        <v>-10.5</v>
+        <v>11.8</v>
       </c>
       <c r="T91" t="n">
-        <v>12.2</v>
+        <v>7.7</v>
       </c>
       <c r="U91" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -7740,12 +7738,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7754,25 +7752,25 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>342</v>
+        <v>53.1</v>
       </c>
       <c r="F92" t="n">
-        <v>14.9</v>
+        <v>7.36</v>
       </c>
       <c r="G92" t="n">
-        <v>5.41</v>
+        <v>1.13</v>
       </c>
       <c r="H92" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="I92" t="n">
-        <v>37.4</v>
+        <v>17.1</v>
       </c>
       <c r="J92" t="n">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7780,38 +7778,38 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>344.5</v>
+        <v>53.1</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>含金量-0.9差、⚠️高槓桿(負債87%)</t>
+          <t>月營收轉負-10%</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>35.3</v>
+        <v>17.5</v>
       </c>
       <c r="Q92" t="n">
-        <v>-0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R92" t="n">
-        <v>17.1</v>
+        <v>6.2</v>
       </c>
       <c r="S92" t="n">
-        <v>94.40000000000001</v>
+        <v>-10.5</v>
       </c>
       <c r="T92" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="U92" t="n">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -7823,12 +7821,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7840,22 +7838,22 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>2115</v>
+        <v>341.5</v>
       </c>
       <c r="F93" t="n">
-        <v>6.78</v>
+        <v>14.88</v>
       </c>
       <c r="G93" t="n">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="H93" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="I93" t="n">
-        <v>99.8</v>
+        <v>37.4</v>
       </c>
       <c r="J93" t="n">
-        <v>0.26</v>
+        <v>0.49</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7863,38 +7861,38 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1.63</v>
+        <v>-0.15</v>
       </c>
       <c r="M93" t="n">
-        <v>2150</v>
+        <v>342</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>含金量0.2差、毛利壓歷史低檔、⚠️存貨爆衝(存85%vs營18%)</t>
+          <t>含金量-0.9差、⚠️高槓桿(負債87%)</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>39.6</v>
+        <v>35.3</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.16</v>
+        <v>-0.87</v>
       </c>
       <c r="R93" t="n">
-        <v>49</v>
+        <v>17.1</v>
       </c>
       <c r="S93" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="T93" t="n">
         <v>18.2</v>
       </c>
-      <c r="T93" t="n">
-        <v>15.3</v>
-      </c>
       <c r="U93" t="n">
-        <v>0.26</v>
+        <v>0.49</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -7906,39 +7904,39 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>180.5</v>
+        <v>2105</v>
       </c>
       <c r="F94" t="n">
-        <v>14.34</v>
+        <v>6.75</v>
       </c>
       <c r="G94" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="H94" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I94" t="n">
-        <v>48.9</v>
+        <v>99.8</v>
       </c>
       <c r="J94" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7946,38 +7944,38 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-3.22</v>
+        <v>-0.47</v>
       </c>
       <c r="M94" t="n">
-        <v>186.5</v>
+        <v>2115</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>含金量-3.4差、毛利壓歷史低檔、⚠️高槓桿(負債81%)</t>
+          <t>含金量0.2差、毛利壓歷史低檔、⚠️存貨爆衝(存85%vs營18%)</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>23.5</v>
+        <v>39.6</v>
       </c>
       <c r="Q94" t="n">
-        <v>-3.39</v>
+        <v>0.16</v>
       </c>
       <c r="R94" t="n">
-        <v>26.2</v>
+        <v>49</v>
       </c>
       <c r="S94" t="n">
-        <v>39.2</v>
+        <v>18.2</v>
       </c>
       <c r="T94" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="U94" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -7989,12 +7987,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8003,25 +8001,25 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>1475</v>
+        <v>180</v>
       </c>
       <c r="F95" t="n">
-        <v>15.73</v>
+        <v>14.3</v>
       </c>
       <c r="G95" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="H95" t="n">
-        <v>11.9</v>
+        <v>10</v>
       </c>
       <c r="I95" t="n">
-        <v>50.3</v>
+        <v>48.9</v>
       </c>
       <c r="J95" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -8029,38 +8027,38 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="M95" t="n">
-        <v>1475</v>
+        <v>180.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔、月營收轉負-19%</t>
+          <t>含金量-3.4差、毛利壓歷史低檔、⚠️高槓桿(負債81%)</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>16.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.9</v>
+        <v>-3.39</v>
       </c>
       <c r="R95" t="n">
-        <v>22.2</v>
+        <v>26.2</v>
       </c>
       <c r="S95" t="n">
-        <v>-19.4</v>
+        <v>39.2</v>
       </c>
       <c r="T95" t="n">
-        <v>17.9</v>
+        <v>15</v>
       </c>
       <c r="U95" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -8072,89 +8070,95 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>69.3</v>
+        <v>1480</v>
       </c>
       <c r="F96" t="n">
-        <v>4.86</v>
+        <v>15.78</v>
       </c>
       <c r="G96" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>3.06</v>
+      </c>
+      <c r="H96" t="n">
+        <v>11.9</v>
+      </c>
       <c r="I96" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J96" t="inlineStr"/>
+        <v>50.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.36</v>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1475</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔、月營收轉負-19%</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R96" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S96" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="T96" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L96" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="M96" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="R96" t="n">
-        <v>23</v>
-      </c>
-      <c r="S96" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="T96" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8163,20 +8167,20 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>384</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="G97" t="n">
-        <v>3.16</v>
+        <v>1.1</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>110.7</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -8185,40 +8189,36 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-1.29</v>
+        <v>0.87</v>
       </c>
       <c r="M97" t="n">
-        <v>389</v>
+        <v>69.3</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>含金量-0.5差</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>55.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q97" t="n">
-        <v>-0.46</v>
+        <v>0.99</v>
       </c>
       <c r="R97" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="S97" t="n">
-        <v>210.4</v>
+        <v>13.7</v>
       </c>
       <c r="T97" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -8230,12 +8230,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8247,17 +8247,17 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>23.5</v>
+        <v>383</v>
       </c>
       <c r="F98" t="n">
-        <v>3.32</v>
+        <v>4.95</v>
       </c>
       <c r="G98" t="n">
-        <v>1.32</v>
+        <v>3.15</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>40.9</v>
+        <v>110.7</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-0.84</v>
+        <v>-0.26</v>
       </c>
       <c r="M98" t="n">
-        <v>23.7</v>
+        <v>384</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8278,28 +8278,28 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>含金量0.4差</t>
+          <t>含金量-0.5差</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>51.6</v>
+        <v>55.8</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.39</v>
+        <v>-0.46</v>
       </c>
       <c r="R98" t="n">
-        <v>30.3</v>
+        <v>7.6</v>
       </c>
       <c r="S98" t="n">
-        <v>826.2</v>
+        <v>210.4</v>
       </c>
       <c r="T98" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -8311,12 +8311,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8325,20 +8325,20 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>34.65</v>
+        <v>23.5</v>
       </c>
       <c r="F99" t="n">
-        <v>3.73</v>
+        <v>3.32</v>
       </c>
       <c r="G99" t="n">
-        <v>0.97</v>
+        <v>1.32</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>147.4</v>
+        <v>40.9</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>35.2</v>
+        <v>23.5</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8359,28 +8359,28 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>含金量0.0差</t>
+          <t>含金量0.4差</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>29.2</v>
+        <v>51.6</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.04</v>
+        <v>0.39</v>
       </c>
       <c r="R99" t="n">
-        <v>36.1</v>
+        <v>30.3</v>
       </c>
       <c r="S99" t="n">
-        <v>0.4</v>
+        <v>826.2</v>
       </c>
       <c r="T99" t="n">
-        <v>14.4</v>
+        <v>3.9</v>
       </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -8392,12 +8392,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8406,20 +8406,20 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>201.5</v>
+        <v>34.65</v>
       </c>
       <c r="F100" t="n">
-        <v>5.01</v>
+        <v>3.73</v>
       </c>
       <c r="G100" t="n">
-        <v>2.75</v>
+        <v>0.97</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>21.9</v>
+        <v>147.4</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-1.23</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>204</v>
+        <v>34.65</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8440,28 +8440,28 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>含金量-1.3差</t>
+          <t>含金量0.0差</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>41.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q100" t="n">
-        <v>-1.31</v>
+        <v>0.04</v>
       </c>
       <c r="R100" t="n">
-        <v>6.4</v>
+        <v>36.1</v>
       </c>
       <c r="S100" t="n">
-        <v>224.4</v>
+        <v>0.4</v>
       </c>
       <c r="T100" t="n">
-        <v>10.5</v>
+        <v>14.4</v>
       </c>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -8473,34 +8473,34 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>48</v>
+        <v>200.5</v>
       </c>
       <c r="F101" t="n">
-        <v>11.85</v>
+        <v>4.99</v>
       </c>
       <c r="G101" t="n">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>-15.4</v>
+        <v>21.9</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="M101" t="n">
-        <v>48.25</v>
+        <v>201.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8521,23 +8521,23 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>EPS連年衰退、含金量0.6弱、營收5年萎縮-2%</t>
+          <t>含金量-1.3差</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>11.5</v>
+        <v>41.3</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.58</v>
+        <v>-1.31</v>
       </c>
       <c r="R101" t="n">
-        <v>-2.2</v>
+        <v>6.4</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>224.4</v>
       </c>
       <c r="T101" t="n">
-        <v>19.9</v>
+        <v>10.5</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3390</v>
+        <v>3470</v>
       </c>
       <c r="F2" t="n">
-        <v>45.19</v>
+        <v>46.25</v>
       </c>
       <c r="G2" t="n">
-        <v>24.12</v>
+        <v>24.69</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.73</v>
+        <v>2.36</v>
       </c>
       <c r="M2" t="n">
-        <v>3415</v>
+        <v>3390</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="F3" t="n">
-        <v>14.4</v>
+        <v>14.83</v>
       </c>
       <c r="G3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.42</v>
+        <v>2.94</v>
       </c>
       <c r="M3" t="n">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2460</v>
+        <v>2500</v>
       </c>
       <c r="F4" t="n">
-        <v>28.52</v>
+        <v>28.98</v>
       </c>
       <c r="G4" t="n">
-        <v>9.92</v>
+        <v>10.08</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="M4" t="n">
-        <v>2480</v>
+        <v>2460</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>121</v>
+        <v>118.5</v>
       </c>
       <c r="F5" t="n">
-        <v>17.26</v>
+        <v>16.9</v>
       </c>
       <c r="G5" t="n">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-2.07</v>
       </c>
       <c r="M5" t="n">
         <v>121</v>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.37</v>
+        <v>13.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>109.5</v>
+        <v>108</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5.18</v>
+        <v>5.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.58</v>
+        <v>-1.16</v>
       </c>
       <c r="M7" t="n">
-        <v>25.95</v>
+        <v>25.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1</v>
+        <v>12.15</v>
       </c>
       <c r="G8" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-2.33</v>
+        <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>107.5</v>
+        <v>105</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F9" t="n">
-        <v>12.9</v>
+        <v>12.83</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.84</v>
+        <v>-0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>179.5</v>
+        <v>181</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.5</v>
+        <v>42.85</v>
       </c>
       <c r="F10" t="n">
-        <v>8.949999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="M10" t="n">
-        <v>41.95</v>
+        <v>42.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="F11" t="n">
-        <v>23.54</v>
+        <v>23.38</v>
       </c>
       <c r="G11" t="n">
-        <v>9.02</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.22</v>
+        <v>-0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F12" t="n">
-        <v>23.09</v>
+        <v>23.26</v>
       </c>
       <c r="G12" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.86</v>
+        <v>0.74</v>
       </c>
       <c r="M12" t="n">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F13" t="n">
-        <v>17.96</v>
+        <v>17.53</v>
       </c>
       <c r="G13" t="n">
-        <v>4.54</v>
+        <v>4.43</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>166.5</v>
+        <v>167</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>39.2</v>
+        <v>38.85</v>
       </c>
       <c r="F14" t="n">
-        <v>8.08</v>
+        <v>8.01</v>
       </c>
       <c r="G14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.38</v>
+        <v>-0.89</v>
       </c>
       <c r="M14" t="n">
-        <v>39.05</v>
+        <v>39.2</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1915</v>
+        <v>1890</v>
       </c>
       <c r="F15" t="n">
-        <v>30.09</v>
+        <v>29.69</v>
       </c>
       <c r="G15" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.08</v>
+        <v>-1.31</v>
       </c>
       <c r="M15" t="n">
-        <v>1840</v>
+        <v>1915</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="F16" t="n">
-        <v>36.9</v>
+        <v>36.79</v>
       </c>
       <c r="G16" t="n">
-        <v>11.23</v>
+        <v>11.19</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.26</v>
+        <v>-0.31</v>
       </c>
       <c r="M16" t="n">
-        <v>1520</v>
+        <v>1600</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,10 +9895,10 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="G17" t="n">
         <v>2.16</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M17" t="n">
         <v>89.8</v>
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="F18" t="n">
-        <v>8.42</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="M18" t="n">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>52.7</v>
+        <v>53.1</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>342</v>
+        <v>341.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.9</v>
+        <v>14.88</v>
       </c>
       <c r="G20" t="n">
-        <v>5.41</v>
+        <v>5.4</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.73</v>
+        <v>-0.15</v>
       </c>
       <c r="M20" t="n">
-        <v>344.5</v>
+        <v>342</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2115</v>
+        <v>2105</v>
       </c>
       <c r="F21" t="n">
-        <v>6.78</v>
+        <v>6.75</v>
       </c>
       <c r="G21" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.63</v>
+        <v>-0.47</v>
       </c>
       <c r="M21" t="n">
-        <v>2150</v>
+        <v>2115</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>180.5</v>
+        <v>180</v>
       </c>
       <c r="F22" t="n">
-        <v>14.34</v>
+        <v>14.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-3.22</v>
+        <v>-0.28</v>
       </c>
       <c r="M22" t="n">
-        <v>186.5</v>
+        <v>180.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="F23" t="n">
-        <v>15.73</v>
+        <v>15.78</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="M23" t="n">
         <v>1475</v>
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16.75</v>
+        <v>16.54</v>
       </c>
       <c r="G2" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.92</v>
+        <v>-1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>166</v>
+        <v>159.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="F3" t="n">
-        <v>19.99</v>
+        <v>20.28</v>
       </c>
       <c r="G3" t="n">
-        <v>4.71</v>
+        <v>4.79</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>317.5</v>
+        <v>316.5</v>
       </c>
       <c r="F5" t="n">
-        <v>26.84</v>
+        <v>26.75</v>
       </c>
       <c r="G5" t="n">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.4</v>
+        <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>322</v>
+        <v>317.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>14.34</v>
+        <v>14.49</v>
       </c>
       <c r="G6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.61</v>
+        <v>1.1</v>
       </c>
       <c r="M6" t="n">
-        <v>82.5</v>
+        <v>82</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>126.5</v>
+        <v>129</v>
       </c>
       <c r="F7" t="n">
-        <v>17.62</v>
+        <v>17.97</v>
       </c>
       <c r="G7" t="n">
-        <v>4.37</v>
+        <v>4.46</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.39</v>
+        <v>1.98</v>
       </c>
       <c r="M7" t="n">
-        <v>127</v>
+        <v>126.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F8" t="n">
-        <v>16.68</v>
+        <v>16.88</v>
       </c>
       <c r="G8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="F9" t="n">
-        <v>45.74</v>
+        <v>44.9</v>
       </c>
       <c r="G9" t="n">
-        <v>24.43</v>
+        <v>23.98</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.82</v>
+        <v>-1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61.2</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>19.74</v>
+        <v>19.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.97</v>
+        <v>-0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>61.8</v>
+        <v>61.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1655</v>
+        <v>1540</v>
       </c>
       <c r="F2" t="n">
-        <v>111.45</v>
+        <v>103.7</v>
       </c>
       <c r="G2" t="n">
-        <v>30.05</v>
+        <v>27.96</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.970000000000001</v>
+        <v>-6.95</v>
       </c>
       <c r="M2" t="n">
-        <v>1505</v>
+        <v>1655</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,10 +11538,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="F3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="G3" t="n">
         <v>1.82</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>40.75</v>
+        <v>40.8</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5345</v>
+        <v>5620</v>
       </c>
       <c r="F5" t="n">
-        <v>114.45</v>
+        <v>120.34</v>
       </c>
       <c r="G5" t="n">
-        <v>32.93</v>
+        <v>34.62</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.73</v>
+        <v>5.14</v>
       </c>
       <c r="M5" t="n">
-        <v>5495</v>
+        <v>5345</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>124.5</v>
+        <v>123</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.77</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.51</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.49</v>
+        <v>2.94</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172.5</v>
+        <v>172</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>21.94</v>
       </c>
       <c r="G8" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.43</v>
+        <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>175</v>
+        <v>172.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1260</v>
+        <v>1230</v>
       </c>
       <c r="F11" t="n">
-        <v>24.21</v>
+        <v>23.63</v>
       </c>
       <c r="G11" t="n">
-        <v>4.6</v>
+        <v>4.49</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.61</v>
+        <v>-2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
-        <v>20.2</v>
+        <v>20.57</v>
       </c>
       <c r="G12" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.31</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>161.5</v>
+        <v>162</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>284.5</v>
+        <v>283.5</v>
       </c>
       <c r="F13" t="n">
-        <v>33.27</v>
+        <v>33.16</v>
       </c>
       <c r="G13" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.39</v>
+        <v>-0.35</v>
       </c>
       <c r="M13" t="n">
-        <v>288.5</v>
+        <v>284.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.49</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>144.5</v>
+        <v>145</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F15" t="n">
-        <v>19.28</v>
+        <v>19.19</v>
       </c>
       <c r="G15" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12532,7 +12532,7 @@
         <v>-0.47</v>
       </c>
       <c r="M15" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8375</v>
+        <v>8385</v>
       </c>
       <c r="F16" t="n">
-        <v>214.69</v>
+        <v>214.94</v>
       </c>
       <c r="G16" t="n">
-        <v>83.34999999999999</v>
+        <v>83.45</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.98</v>
+        <v>0.12</v>
       </c>
       <c r="M16" t="n">
-        <v>7615</v>
+        <v>8375</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,10 +12882,10 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="F3" t="n">
-        <v>20.79</v>
+        <v>20.82</v>
       </c>
       <c r="G3" t="n">
         <v>1.04</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.84</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>5830</v>
+        <v>6410</v>
       </c>
       <c r="F4" t="n">
-        <v>131.57</v>
+        <v>144.66</v>
       </c>
       <c r="G4" t="n">
-        <v>36.28</v>
+        <v>39.89</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>5790</v>
+        <v>5830</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4860</v>
+        <v>5020</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>78.5</v>
       </c>
       <c r="G5" t="n">
-        <v>29.85</v>
+        <v>30.84</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.72</v>
+        <v>3.29</v>
       </c>
       <c r="M5" t="n">
-        <v>4895</v>
+        <v>4860</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="F6" t="n">
-        <v>46.6</v>
+        <v>46.07</v>
       </c>
       <c r="G6" t="n">
-        <v>24.43</v>
+        <v>24.16</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.84</v>
+        <v>-1.12</v>
       </c>
       <c r="M6" t="n">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>11.93</v>
+        <v>11.92</v>
       </c>
       <c r="G7" t="n">
         <v>1.67</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.21</v>
+        <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="F8" t="n">
-        <v>11.88</v>
+        <v>11.69</v>
       </c>
       <c r="G8" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.32</v>
+        <v>-1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>155</v>
+        <v>154.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.45</v>
+        <v>15.52</v>
       </c>
       <c r="G9" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="F10" t="n">
-        <v>24.97</v>
+        <v>24.49</v>
       </c>
       <c r="G10" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3.05</v>
+        <v>-1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>952</v>
+        <v>923</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,10 +13530,10 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>197</v>
+        <v>196.5</v>
       </c>
       <c r="F11" t="n">
-        <v>27.13</v>
+        <v>27.07</v>
       </c>
       <c r="G11" t="n">
         <v>2.65</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="M11" t="n">
-        <v>198.5</v>
+        <v>197</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3715</v>
+        <v>3760</v>
       </c>
       <c r="F12" t="n">
-        <v>54.49</v>
+        <v>55.15</v>
       </c>
       <c r="G12" t="n">
-        <v>5.31</v>
+        <v>5.37</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
-        <v>3665</v>
+        <v>3715</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="F2" t="n">
-        <v>103.7</v>
+        <v>103.03</v>
       </c>
       <c r="G2" t="n">
-        <v>27.96</v>
+        <v>27.78</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-6.95</v>
+        <v>-0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>1655</v>
+        <v>1540</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.9</v>
+        <v>40.85</v>
       </c>
       <c r="F3" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
       <c r="G3" t="n">
         <v>1.82</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>-0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5620</v>
+        <v>5415</v>
       </c>
       <c r="F5" t="n">
-        <v>120.34</v>
+        <v>115.95</v>
       </c>
       <c r="G5" t="n">
-        <v>34.62</v>
+        <v>33.36</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.14</v>
+        <v>-3.65</v>
       </c>
       <c r="M5" t="n">
-        <v>5345</v>
+        <v>5620</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.25</v>
+        <v>23.16</v>
       </c>
       <c r="G6" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="M6" t="n">
         <v>123</v>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.77</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.94</v>
+        <v>-2.86</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>172.5</v>
+        <v>172</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1230</v>
+        <v>1210</v>
       </c>
       <c r="F11" t="n">
-        <v>23.63</v>
+        <v>23.25</v>
       </c>
       <c r="G11" t="n">
-        <v>4.49</v>
+        <v>4.41</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.38</v>
+        <v>-1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>1260</v>
+        <v>1230</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.57</v>
+        <v>20.51</v>
       </c>
       <c r="G12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>-0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>283.5</v>
+        <v>287</v>
       </c>
       <c r="F13" t="n">
-        <v>33.16</v>
+        <v>33.57</v>
       </c>
       <c r="G13" t="n">
-        <v>6.71</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.35</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
-        <v>284.5</v>
+        <v>283.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.49</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>213</v>
+        <v>212.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.19</v>
+        <v>19.14</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="M15" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8385</v>
+        <v>8525</v>
       </c>
       <c r="F16" t="n">
-        <v>214.94</v>
+        <v>218.53</v>
       </c>
       <c r="G16" t="n">
-        <v>83.45</v>
+        <v>84.84</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.12</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>8375</v>
+        <v>8385</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1515</v>
+        <v>1530</v>
       </c>
       <c r="F17" t="n">
-        <v>44.82</v>
+        <v>45.27</v>
       </c>
       <c r="G17" t="n">
-        <v>9.1</v>
+        <v>9.19</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.33</v>
+        <v>0.99</v>
       </c>
       <c r="M17" t="n">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12390</v>
+        <v>12350</v>
       </c>
       <c r="F18" t="n">
-        <v>68.31</v>
+        <v>68.09</v>
       </c>
       <c r="G18" t="n">
-        <v>34.98</v>
+        <v>34.87</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-2.21</v>
+        <v>-0.32</v>
       </c>
       <c r="M18" t="n">
-        <v>12670</v>
+        <v>12390</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="F19" t="n">
-        <v>81.20999999999999</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>15.76</v>
+        <v>16.02</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.53</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>81.3</v>
       </c>
       <c r="F20" t="n">
-        <v>45.05</v>
+        <v>44.67</v>
       </c>
       <c r="G20" t="n">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1.44</v>
+        <v>-0.85</v>
       </c>
       <c r="M20" t="n">
-        <v>83.2</v>
+        <v>82</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5995</v>
+        <v>5850</v>
       </c>
       <c r="F21" t="n">
-        <v>98.15000000000001</v>
+        <v>95.78</v>
       </c>
       <c r="G21" t="n">
-        <v>25.35</v>
+        <v>24.73</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.99</v>
+        <v>-2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>5765</v>
+        <v>5995</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2325</v>
+        <v>2295</v>
       </c>
       <c r="F22" t="n">
-        <v>59.31</v>
+        <v>58.55</v>
       </c>
       <c r="G22" t="n">
-        <v>29.85</v>
+        <v>29.47</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-4.71</v>
+        <v>-1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>2440</v>
+        <v>2325</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.45</v>
+        <v>18.3</v>
       </c>
       <c r="F23" t="n">
-        <v>41.93</v>
+        <v>41.59</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>18.45</v>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1460</v>
+        <v>1495</v>
       </c>
       <c r="F24" t="n">
-        <v>74.15000000000001</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>18.09</v>
+        <v>18.53</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>1440</v>
+        <v>1460</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>63.6</v>
+        <v>62.9</v>
       </c>
       <c r="F25" t="n">
-        <v>77.56</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>-1.1</v>
       </c>
       <c r="M25" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2680</v>
+        <v>2700</v>
       </c>
       <c r="F26" t="n">
-        <v>230.64</v>
+        <v>232.36</v>
       </c>
       <c r="G26" t="n">
-        <v>52.54</v>
+        <v>52.93</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-5.13</v>
+        <v>0.75</v>
       </c>
       <c r="M26" t="n">
-        <v>2825</v>
+        <v>2680</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="F27" t="n">
-        <v>50.14</v>
+        <v>50.58</v>
       </c>
       <c r="G27" t="n">
-        <v>7.83</v>
+        <v>7.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M27" t="n">
         <v>693</v>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1175</v>
+        <v>1155</v>
       </c>
       <c r="F28" t="n">
-        <v>57.54</v>
+        <v>56.56</v>
       </c>
       <c r="G28" t="n">
-        <v>11.92</v>
+        <v>11.72</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.29</v>
+        <v>-1.7</v>
       </c>
       <c r="M28" t="n">
-        <v>1160</v>
+        <v>1175</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="F29" t="n">
-        <v>96.56</v>
+        <v>92.14</v>
       </c>
       <c r="G29" t="n">
-        <v>18.92</v>
+        <v>18.06</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-2.48</v>
+        <v>-4.58</v>
       </c>
       <c r="M29" t="n">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3475</v>
+        <v>3310</v>
       </c>
       <c r="F30" t="n">
-        <v>81.95999999999999</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>11.3</v>
+        <v>10.76</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-6.08</v>
+        <v>-4.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3700</v>
+        <v>3475</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="F31" t="n">
-        <v>105.48</v>
+        <v>104.06</v>
       </c>
       <c r="G31" t="n">
-        <v>13.56</v>
+        <v>13.38</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-1.14</v>
+        <v>-1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="F32" t="n">
-        <v>44.4</v>
+        <v>45.73</v>
       </c>
       <c r="G32" t="n">
-        <v>11.01</v>
+        <v>11.34</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.28</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="F33" t="n">
-        <v>38.59</v>
+        <v>39.06</v>
       </c>
       <c r="G33" t="n">
-        <v>6.66</v>
+        <v>6.74</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.35</v>
+        <v>1.22</v>
       </c>
       <c r="M33" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>5185</v>
+        <v>5285</v>
       </c>
       <c r="F34" t="n">
-        <v>85.63</v>
+        <v>87.28</v>
       </c>
       <c r="G34" t="n">
-        <v>19.51</v>
+        <v>19.89</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.1</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
-        <v>5180</v>
+        <v>5185</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="F35" t="n">
-        <v>60.47</v>
+        <v>60.79</v>
       </c>
       <c r="G35" t="n">
-        <v>16.8</v>
+        <v>16.89</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M35" t="n">
         <v>1900</v>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>70.8</v>
+        <v>69.3</v>
       </c>
       <c r="F36" t="n">
-        <v>20.82</v>
+        <v>20.38</v>
       </c>
       <c r="G36" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.14</v>
+        <v>-2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>6410</v>
+        <v>6920</v>
       </c>
       <c r="F37" t="n">
-        <v>144.66</v>
+        <v>156.17</v>
       </c>
       <c r="G37" t="n">
-        <v>39.89</v>
+        <v>43.06</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9.949999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="M37" t="n">
-        <v>5830</v>
+        <v>6410</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>5020</v>
+        <v>5050</v>
       </c>
       <c r="F38" t="n">
-        <v>78.5</v>
+        <v>78.97</v>
       </c>
       <c r="G38" t="n">
-        <v>30.84</v>
+        <v>31.02</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.29</v>
+        <v>0.6</v>
       </c>
       <c r="M38" t="n">
-        <v>4860</v>
+        <v>5020</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F39" t="n">
-        <v>46.07</v>
+        <v>45.75</v>
       </c>
       <c r="G39" t="n">
-        <v>24.16</v>
+        <v>23.99</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-1.12</v>
+        <v>-0.71</v>
       </c>
       <c r="M39" t="n">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>152</v>
+        <v>153.5</v>
       </c>
       <c r="F41" t="n">
-        <v>11.69</v>
+        <v>11.81</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-1.62</v>
+        <v>0.99</v>
       </c>
       <c r="M41" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F42" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G42" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.47</v>
+        <v>-0.47</v>
       </c>
       <c r="M42" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="F43" t="n">
-        <v>24.49</v>
+        <v>24.38</v>
       </c>
       <c r="G43" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-1.95</v>
+        <v>-0.44</v>
       </c>
       <c r="M43" t="n">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>196.5</v>
+        <v>196</v>
       </c>
       <c r="F44" t="n">
-        <v>27.07</v>
+        <v>27</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3955,7 +3955,7 @@
         <v>-0.25</v>
       </c>
       <c r="M44" t="n">
-        <v>197</v>
+        <v>196.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3760</v>
+        <v>3770</v>
       </c>
       <c r="F45" t="n">
-        <v>55.15</v>
+        <v>55.29</v>
       </c>
       <c r="G45" t="n">
-        <v>5.37</v>
+        <v>5.39</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.21</v>
+        <v>0.27</v>
       </c>
       <c r="M45" t="n">
-        <v>3715</v>
+        <v>3760</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>216.5</v>
+        <v>218.5</v>
       </c>
       <c r="F46" t="n">
-        <v>22.05</v>
+        <v>22.25</v>
       </c>
       <c r="G46" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-0.46</v>
+        <v>0.92</v>
       </c>
       <c r="M46" t="n">
-        <v>217.5</v>
+        <v>216.5</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>63</v>
       </c>
       <c r="E47" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F47" t="n">
-        <v>25.19</v>
+        <v>26.07</v>
       </c>
       <c r="G47" t="n">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-1.5</v>
+        <v>3.48</v>
       </c>
       <c r="M47" t="n">
-        <v>233.5</v>
+        <v>230</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4249,13 +4249,13 @@
         <v>61</v>
       </c>
       <c r="E48" t="n">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="F48" t="n">
-        <v>27.59</v>
+        <v>27.16</v>
       </c>
       <c r="G48" t="n">
-        <v>7.78</v>
+        <v>7.66</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.79</v>
+        <v>-1.58</v>
       </c>
       <c r="M48" t="n">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4330,13 +4330,13 @@
         <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>109</v>
+        <v>110.5</v>
       </c>
       <c r="F49" t="n">
-        <v>20.34</v>
+        <v>20.62</v>
       </c>
       <c r="G49" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-0.91</v>
+        <v>1.38</v>
       </c>
       <c r="M49" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4411,13 +4411,13 @@
         <v>51</v>
       </c>
       <c r="E50" t="n">
-        <v>6190</v>
+        <v>6245</v>
       </c>
       <c r="F50" t="n">
-        <v>32.92</v>
+        <v>33.21</v>
       </c>
       <c r="G50" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-3.36</v>
+        <v>0.89</v>
       </c>
       <c r="M50" t="n">
-        <v>6405</v>
+        <v>6190</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4492,13 +4492,13 @@
         <v>97</v>
       </c>
       <c r="E51" t="n">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="F51" t="n">
-        <v>24.86</v>
+        <v>25.59</v>
       </c>
       <c r="G51" t="n">
-        <v>6.77</v>
+        <v>6.97</v>
       </c>
       <c r="H51" t="n">
         <v>29.3</v>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="M51" t="n">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -4571,13 +4571,13 @@
         <v>91</v>
       </c>
       <c r="E52" t="n">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="F52" t="n">
-        <v>42.39</v>
+        <v>42.82</v>
       </c>
       <c r="G52" t="n">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
       <c r="H52" t="n">
         <v>46.1</v>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.85</v>
+        <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -4650,13 +4650,13 @@
         <v>79</v>
       </c>
       <c r="E53" t="n">
-        <v>58.4</v>
+        <v>58.8</v>
       </c>
       <c r="F53" t="n">
-        <v>16.04</v>
+        <v>16.15</v>
       </c>
       <c r="G53" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H53" t="n">
         <v>17.3</v>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-0.51</v>
+        <v>0.68</v>
       </c>
       <c r="M53" t="n">
-        <v>58.7</v>
+        <v>58.4</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4729,13 +4729,13 @@
         <v>77</v>
       </c>
       <c r="E54" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="F54" t="n">
-        <v>16.3</v>
+        <v>16.35</v>
       </c>
       <c r="G54" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H54" t="n">
         <v>15.5</v>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-0.83</v>
+        <v>0.28</v>
       </c>
       <c r="M54" t="n">
-        <v>180</v>
+        <v>178.5</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4808,13 +4808,13 @@
         <v>96</v>
       </c>
       <c r="E55" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F55" t="n">
-        <v>17.4</v>
+        <v>17.56</v>
       </c>
       <c r="G55" t="n">
-        <v>4.93</v>
+        <v>4.98</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.15</v>
+        <v>0.89</v>
       </c>
       <c r="M55" t="n">
-        <v>336.5</v>
+        <v>336</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4885,13 +4885,13 @@
         <v>94</v>
       </c>
       <c r="E56" t="n">
-        <v>165.5</v>
+        <v>166</v>
       </c>
       <c r="F56" t="n">
-        <v>18.62</v>
+        <v>18.67</v>
       </c>
       <c r="G56" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="M56" t="n">
-        <v>166</v>
+        <v>165.5</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4962,13 +4962,13 @@
         <v>78</v>
       </c>
       <c r="E57" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="F57" t="n">
-        <v>19.84</v>
+        <v>19.92</v>
       </c>
       <c r="G57" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-1.21</v>
+        <v>0.41</v>
       </c>
       <c r="M57" t="n">
-        <v>123.5</v>
+        <v>122</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5039,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="G58" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-1.13</v>
+        <v>1.83</v>
       </c>
       <c r="M58" t="n">
-        <v>88.5</v>
+        <v>87.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5120,13 +5120,13 @@
         <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F59" t="n">
-        <v>17.17</v>
+        <v>17.28</v>
       </c>
       <c r="G59" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-0.65</v>
+        <v>0.65</v>
       </c>
       <c r="M59" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5201,13 +5201,13 @@
         <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>234.5</v>
+        <v>243</v>
       </c>
       <c r="F60" t="n">
-        <v>14.57</v>
+        <v>15.1</v>
       </c>
       <c r="G60" t="n">
-        <v>5.3</v>
+        <v>5.49</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.08</v>
+        <v>3.62</v>
       </c>
       <c r="M60" t="n">
-        <v>232</v>
+        <v>234.5</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5278,13 +5278,13 @@
         <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>185.5</v>
+        <v>183.5</v>
       </c>
       <c r="F61" t="n">
-        <v>15.65</v>
+        <v>15.49</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.82</v>
+        <v>-1.08</v>
       </c>
       <c r="M61" t="n">
-        <v>184</v>
+        <v>185.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="F62" t="n">
-        <v>16.84</v>
+        <v>17.58</v>
       </c>
       <c r="G62" t="n">
-        <v>13.59</v>
+        <v>14.19</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.28</v>
+        <v>4.39</v>
       </c>
       <c r="M62" t="n">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
         <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="F63" t="n">
-        <v>19.98</v>
+        <v>19.52</v>
       </c>
       <c r="G63" t="n">
-        <v>5.51</v>
+        <v>5.38</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.62</v>
+        <v>-2.33</v>
       </c>
       <c r="M63" t="n">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>172.5</v>
+        <v>171.5</v>
       </c>
       <c r="F64" t="n">
-        <v>19.02</v>
+        <v>18.91</v>
       </c>
       <c r="G64" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.88</v>
+        <v>-0.58</v>
       </c>
       <c r="M64" t="n">
-        <v>171</v>
+        <v>172.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F65" t="n">
-        <v>12.12</v>
+        <v>12.15</v>
       </c>
       <c r="G65" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.29</v>
+        <v>0.2</v>
       </c>
       <c r="M65" t="n">
-        <v>48</v>
+        <v>49.1</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>157.5</v>
+        <v>157</v>
       </c>
       <c r="F66" t="n">
-        <v>16.54</v>
+        <v>16.49</v>
       </c>
       <c r="G66" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1.25</v>
+        <v>-0.32</v>
       </c>
       <c r="M66" t="n">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5833,13 +5833,13 @@
         <v>91</v>
       </c>
       <c r="E68" t="n">
-        <v>118</v>
+        <v>118.5</v>
       </c>
       <c r="F68" t="n">
-        <v>15.25</v>
+        <v>15.31</v>
       </c>
       <c r="G68" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="H68" t="n">
         <v>15</v>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M68" t="n">
         <v>118</v>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>316.5</v>
+        <v>320</v>
       </c>
       <c r="F69" t="n">
-        <v>26.75</v>
+        <v>27.05</v>
       </c>
       <c r="G69" t="n">
-        <v>6.88</v>
+        <v>6.96</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.31</v>
+        <v>1.11</v>
       </c>
       <c r="M69" t="n">
-        <v>317.5</v>
+        <v>316.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>82.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="F70" t="n">
-        <v>14.49</v>
+        <v>14.39</v>
       </c>
       <c r="G70" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.1</v>
+        <v>-0.72</v>
       </c>
       <c r="M70" t="n">
-        <v>82</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>129</v>
+        <v>129.5</v>
       </c>
       <c r="F71" t="n">
-        <v>17.97</v>
+        <v>18.04</v>
       </c>
       <c r="G71" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.98</v>
+        <v>0.39</v>
       </c>
       <c r="M71" t="n">
-        <v>126.5</v>
+        <v>129</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>256</v>
+        <v>250.5</v>
       </c>
       <c r="F72" t="n">
-        <v>16.88</v>
+        <v>16.51</v>
       </c>
       <c r="G72" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.19</v>
+        <v>-2.15</v>
       </c>
       <c r="M72" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="F73" t="n">
-        <v>44.9</v>
+        <v>47.01</v>
       </c>
       <c r="G73" t="n">
-        <v>23.98</v>
+        <v>25.11</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1.85</v>
+        <v>4.72</v>
       </c>
       <c r="M73" t="n">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="F74" t="n">
-        <v>19.68</v>
+        <v>19.32</v>
       </c>
       <c r="G74" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-0.33</v>
+        <v>-1.8</v>
       </c>
       <c r="M74" t="n">
-        <v>61.2</v>
+        <v>61</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3470</v>
+        <v>3555</v>
       </c>
       <c r="F75" t="n">
-        <v>46.25</v>
+        <v>47.39</v>
       </c>
       <c r="G75" t="n">
-        <v>24.69</v>
+        <v>25.29</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="M75" t="n">
-        <v>3390</v>
+        <v>3470</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>736</v>
+        <v>753</v>
       </c>
       <c r="F76" t="n">
-        <v>14.83</v>
+        <v>15.17</v>
       </c>
       <c r="G76" t="n">
-        <v>8.380000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.94</v>
+        <v>2.31</v>
       </c>
       <c r="M76" t="n">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2500</v>
+        <v>2475</v>
       </c>
       <c r="F77" t="n">
-        <v>28.98</v>
+        <v>28.69</v>
       </c>
       <c r="G77" t="n">
-        <v>10.08</v>
+        <v>9.98</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.63</v>
+        <v>-1</v>
       </c>
       <c r="M77" t="n">
-        <v>2460</v>
+        <v>2500</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>118.5</v>
+        <v>120</v>
       </c>
       <c r="F78" t="n">
-        <v>16.9</v>
+        <v>17.12</v>
       </c>
       <c r="G78" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-2.07</v>
+        <v>1.27</v>
       </c>
       <c r="M78" t="n">
-        <v>121</v>
+        <v>118.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="F79" t="n">
-        <v>13.55</v>
+        <v>13.68</v>
       </c>
       <c r="G79" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.39</v>
+        <v>0.91</v>
       </c>
       <c r="M79" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>25.5</v>
+        <v>25.05</v>
       </c>
       <c r="F80" t="n">
-        <v>5.12</v>
+        <v>5.03</v>
       </c>
       <c r="G80" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-1.16</v>
+        <v>-1.76</v>
       </c>
       <c r="M80" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>42.85</v>
+        <v>42</v>
       </c>
       <c r="F83" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="G83" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.82</v>
+        <v>-1.98</v>
       </c>
       <c r="M83" t="n">
-        <v>42.5</v>
+        <v>42.85</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="F84" t="n">
-        <v>23.38</v>
+        <v>23.51</v>
       </c>
       <c r="G84" t="n">
-        <v>8.960000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F85" t="n">
-        <v>23.26</v>
+        <v>23.05</v>
       </c>
       <c r="G85" t="n">
-        <v>5.12</v>
+        <v>5.08</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="M85" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F86" t="n">
-        <v>17.53</v>
+        <v>17.96</v>
       </c>
       <c r="G86" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M86" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.85</v>
+        <v>38.65</v>
       </c>
       <c r="F87" t="n">
-        <v>8.01</v>
+        <v>7.97</v>
       </c>
       <c r="G87" t="n">
         <v>1.1</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.89</v>
+        <v>-0.51</v>
       </c>
       <c r="M87" t="n">
-        <v>39.2</v>
+        <v>38.85</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="F88" t="n">
-        <v>29.69</v>
+        <v>29.77</v>
       </c>
       <c r="G88" t="n">
-        <v>15.3</v>
+        <v>15.34</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1.31</v>
+        <v>0.26</v>
       </c>
       <c r="M88" t="n">
-        <v>1915</v>
+        <v>1890</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1595</v>
+        <v>1710</v>
       </c>
       <c r="F89" t="n">
-        <v>36.79</v>
+        <v>39.44</v>
       </c>
       <c r="G89" t="n">
-        <v>11.19</v>
+        <v>12</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-0.31</v>
+        <v>7.21</v>
       </c>
       <c r="M89" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,10 +7589,10 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="F90" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G90" t="n">
         <v>2.16</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.11</v>
+        <v>-0.11</v>
       </c>
       <c r="M90" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="F92" t="n">
-        <v>7.36</v>
+        <v>7.39</v>
       </c>
       <c r="G92" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M92" t="n">
         <v>53.1</v>
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>341.5</v>
+        <v>338.5</v>
       </c>
       <c r="F93" t="n">
-        <v>14.88</v>
+        <v>14.75</v>
       </c>
       <c r="G93" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.15</v>
+        <v>-0.88</v>
       </c>
       <c r="M93" t="n">
-        <v>342</v>
+        <v>341.5</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="F94" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M94" t="n">
-        <v>2115</v>
+        <v>2105</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>180</v>
+        <v>184.5</v>
       </c>
       <c r="F95" t="n">
-        <v>14.3</v>
+        <v>14.65</v>
       </c>
       <c r="G95" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-0.28</v>
+        <v>2.5</v>
       </c>
       <c r="M95" t="n">
-        <v>180.5</v>
+        <v>180</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,10 +8170,10 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="G97" t="n">
         <v>1.1</v>
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.87</v>
+        <v>0.29</v>
       </c>
       <c r="M97" t="n">
-        <v>69.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F98" t="n">
-        <v>4.95</v>
+        <v>4.89</v>
       </c>
       <c r="G98" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-0.26</v>
+        <v>-1.31</v>
       </c>
       <c r="M98" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>34.65</v>
+        <v>34.05</v>
       </c>
       <c r="F100" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="G100" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
       <c r="M100" t="n">
         <v>34.65</v>
@@ -8490,10 +8490,10 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>200.5</v>
+        <v>200</v>
       </c>
       <c r="F101" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="G101" t="n">
         <v>2.73</v>
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="M101" t="n">
-        <v>201.5</v>
+        <v>200.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3470</v>
+        <v>3555</v>
       </c>
       <c r="F2" t="n">
-        <v>46.25</v>
+        <v>47.39</v>
       </c>
       <c r="G2" t="n">
-        <v>24.69</v>
+        <v>25.29</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3390</v>
+        <v>3470</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>736</v>
+        <v>753</v>
       </c>
       <c r="F3" t="n">
-        <v>14.83</v>
+        <v>15.17</v>
       </c>
       <c r="G3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.94</v>
+        <v>2.31</v>
       </c>
       <c r="M3" t="n">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2500</v>
+        <v>2475</v>
       </c>
       <c r="F4" t="n">
-        <v>28.98</v>
+        <v>28.69</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08</v>
+        <v>9.98</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.63</v>
+        <v>-1</v>
       </c>
       <c r="M4" t="n">
-        <v>2460</v>
+        <v>2500</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>118.5</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>16.9</v>
+        <v>17.12</v>
       </c>
       <c r="G5" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.07</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
-        <v>121</v>
+        <v>118.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.55</v>
+        <v>13.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>0.91</v>
       </c>
       <c r="M6" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.5</v>
+        <v>25.05</v>
       </c>
       <c r="F7" t="n">
-        <v>5.12</v>
+        <v>5.03</v>
       </c>
       <c r="G7" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.16</v>
+        <v>-1.76</v>
       </c>
       <c r="M7" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.85</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.82</v>
+        <v>-1.98</v>
       </c>
       <c r="M10" t="n">
-        <v>42.5</v>
+        <v>42.85</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="F11" t="n">
-        <v>23.38</v>
+        <v>23.51</v>
       </c>
       <c r="G11" t="n">
-        <v>8.960000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F12" t="n">
-        <v>23.26</v>
+        <v>23.05</v>
       </c>
       <c r="G12" t="n">
-        <v>5.12</v>
+        <v>5.08</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="M12" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F13" t="n">
-        <v>17.53</v>
+        <v>17.96</v>
       </c>
       <c r="G13" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.85</v>
+        <v>38.65</v>
       </c>
       <c r="F14" t="n">
-        <v>8.01</v>
+        <v>7.97</v>
       </c>
       <c r="G14" t="n">
         <v>1.1</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.89</v>
+        <v>-0.51</v>
       </c>
       <c r="M14" t="n">
-        <v>39.2</v>
+        <v>38.85</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="F15" t="n">
-        <v>29.69</v>
+        <v>29.77</v>
       </c>
       <c r="G15" t="n">
-        <v>15.3</v>
+        <v>15.34</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.31</v>
+        <v>0.26</v>
       </c>
       <c r="M15" t="n">
-        <v>1915</v>
+        <v>1890</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1595</v>
+        <v>1710</v>
       </c>
       <c r="F16" t="n">
-        <v>36.79</v>
+        <v>39.44</v>
       </c>
       <c r="G16" t="n">
-        <v>11.19</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-0.31</v>
+        <v>7.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,10 +9895,10 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="F17" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>2.16</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.11</v>
+        <v>-0.11</v>
       </c>
       <c r="M17" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="F19" t="n">
-        <v>7.36</v>
+        <v>7.39</v>
       </c>
       <c r="G19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M19" t="n">
         <v>53.1</v>
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>341.5</v>
+        <v>338.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.88</v>
+        <v>14.75</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.15</v>
+        <v>-0.88</v>
       </c>
       <c r="M20" t="n">
-        <v>342</v>
+        <v>341.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="F21" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="G21" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M21" t="n">
-        <v>2115</v>
+        <v>2105</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>180</v>
+        <v>184.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.3</v>
+        <v>14.65</v>
       </c>
       <c r="G22" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.28</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>180.5</v>
+        <v>180</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>157.5</v>
+        <v>157</v>
       </c>
       <c r="F2" t="n">
-        <v>16.54</v>
+        <v>16.49</v>
       </c>
       <c r="G2" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.25</v>
+        <v>-0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>118</v>
+        <v>118.5</v>
       </c>
       <c r="F4" t="n">
-        <v>15.25</v>
+        <v>15.31</v>
       </c>
       <c r="G4" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M4" t="n">
         <v>118</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>316.5</v>
+        <v>320</v>
       </c>
       <c r="F5" t="n">
-        <v>26.75</v>
+        <v>27.05</v>
       </c>
       <c r="G5" t="n">
-        <v>6.88</v>
+        <v>6.96</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.31</v>
+        <v>1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>317.5</v>
+        <v>316.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14.49</v>
+        <v>14.39</v>
       </c>
       <c r="G6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.1</v>
+        <v>-0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>82</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>129</v>
+        <v>129.5</v>
       </c>
       <c r="F7" t="n">
-        <v>17.97</v>
+        <v>18.04</v>
       </c>
       <c r="G7" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.98</v>
+        <v>0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>126.5</v>
+        <v>129</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>256</v>
+        <v>250.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.88</v>
+        <v>16.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.19</v>
+        <v>-2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="F9" t="n">
-        <v>44.9</v>
+        <v>47.01</v>
       </c>
       <c r="G9" t="n">
-        <v>23.98</v>
+        <v>25.11</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.85</v>
+        <v>4.72</v>
       </c>
       <c r="M9" t="n">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="F10" t="n">
-        <v>19.68</v>
+        <v>19.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.33</v>
+        <v>-1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>61.2</v>
+        <v>61</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="F2" t="n">
-        <v>103.7</v>
+        <v>103.03</v>
       </c>
       <c r="G2" t="n">
-        <v>27.96</v>
+        <v>27.78</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-6.95</v>
+        <v>-0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>1655</v>
+        <v>1540</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,10 +11538,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.9</v>
+        <v>40.85</v>
       </c>
       <c r="F3" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
       <c r="G3" t="n">
         <v>1.82</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>-0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5620</v>
+        <v>5415</v>
       </c>
       <c r="F5" t="n">
-        <v>120.34</v>
+        <v>115.95</v>
       </c>
       <c r="G5" t="n">
-        <v>34.62</v>
+        <v>33.36</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.14</v>
+        <v>-3.65</v>
       </c>
       <c r="M5" t="n">
-        <v>5345</v>
+        <v>5620</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.25</v>
+        <v>23.16</v>
       </c>
       <c r="G6" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="M6" t="n">
         <v>123</v>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.77</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.94</v>
+        <v>-2.86</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>172.5</v>
+        <v>172</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1230</v>
+        <v>1210</v>
       </c>
       <c r="F11" t="n">
-        <v>23.63</v>
+        <v>23.25</v>
       </c>
       <c r="G11" t="n">
-        <v>4.49</v>
+        <v>4.41</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.38</v>
+        <v>-1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>1260</v>
+        <v>1230</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.57</v>
+        <v>20.51</v>
       </c>
       <c r="G12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>-0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>283.5</v>
+        <v>287</v>
       </c>
       <c r="F13" t="n">
-        <v>33.16</v>
+        <v>33.57</v>
       </c>
       <c r="G13" t="n">
-        <v>6.71</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.35</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
-        <v>284.5</v>
+        <v>283.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.49</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>213</v>
+        <v>212.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.19</v>
+        <v>19.14</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="M15" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8385</v>
+        <v>8525</v>
       </c>
       <c r="F16" t="n">
-        <v>214.94</v>
+        <v>218.53</v>
       </c>
       <c r="G16" t="n">
-        <v>83.45</v>
+        <v>84.84</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.12</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>8375</v>
+        <v>8385</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="F2" t="n">
-        <v>60.47</v>
+        <v>60.79</v>
       </c>
       <c r="G2" t="n">
-        <v>16.8</v>
+        <v>16.89</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M2" t="n">
         <v>1900</v>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>70.8</v>
+        <v>69.3</v>
       </c>
       <c r="F3" t="n">
-        <v>20.82</v>
+        <v>20.38</v>
       </c>
       <c r="G3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>-2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>6410</v>
+        <v>6920</v>
       </c>
       <c r="F4" t="n">
-        <v>144.66</v>
+        <v>156.17</v>
       </c>
       <c r="G4" t="n">
-        <v>39.89</v>
+        <v>43.06</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>9.949999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="M4" t="n">
-        <v>5830</v>
+        <v>6410</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5020</v>
+        <v>5050</v>
       </c>
       <c r="F5" t="n">
-        <v>78.5</v>
+        <v>78.97</v>
       </c>
       <c r="G5" t="n">
-        <v>30.84</v>
+        <v>31.02</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.29</v>
+        <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>4860</v>
+        <v>5020</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F6" t="n">
-        <v>46.07</v>
+        <v>45.75</v>
       </c>
       <c r="G6" t="n">
-        <v>24.16</v>
+        <v>23.99</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.12</v>
+        <v>-0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>152</v>
+        <v>153.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.69</v>
+        <v>11.81</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.62</v>
+        <v>0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="F10" t="n">
-        <v>24.49</v>
+        <v>24.38</v>
       </c>
       <c r="G10" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.95</v>
+        <v>-0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>196.5</v>
+        <v>196</v>
       </c>
       <c r="F11" t="n">
-        <v>27.07</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13556,7 +13556,7 @@
         <v>-0.25</v>
       </c>
       <c r="M11" t="n">
-        <v>197</v>
+        <v>196.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3760</v>
+        <v>3770</v>
       </c>
       <c r="F12" t="n">
-        <v>55.15</v>
+        <v>55.29</v>
       </c>
       <c r="G12" t="n">
-        <v>5.37</v>
+        <v>5.39</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>0.27</v>
       </c>
       <c r="M12" t="n">
-        <v>3715</v>
+        <v>3760</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.9</v>
+        <v>40.85</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5620</v>
+        <v>5415</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.86</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.63</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1230</v>
+        <v>1210</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>283.5</v>
+        <v>287</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>213</v>
+        <v>212.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8385</v>
+        <v>8525</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1515</v>
+        <v>1530</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>12390</v>
+        <v>12350</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>82</v>
+        <v>81.3</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.42</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5995</v>
+        <v>5850</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2325</v>
+        <v>2295</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>18.45</v>
+        <v>18.3</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1460</v>
+        <v>1495</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>63.6</v>
+        <v>62.9</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2680</v>
+        <v>2700</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1175</v>
+        <v>1155</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-4.58</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-4.75</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3475</v>
+        <v>3310</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5185</v>
+        <v>5285</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-2.12</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>70.8</v>
+        <v>69.3</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.96</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>6410</v>
+        <v>6920</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>5020</v>
+        <v>5050</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>152</v>
+        <v>153.5</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>196.5</v>
+        <v>196</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3760</v>
+        <v>3770</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>216.5</v>
+        <v>218.5</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-1.58</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>109</v>
+        <v>110.5</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>6190</v>
+        <v>6245</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>58.4</v>
+        <v>58.8</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>165.5</v>
+        <v>166</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>234.5</v>
+        <v>243</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>185.5</v>
+        <v>183.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-2.33</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>172.5</v>
+        <v>171.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>157.5</v>
+        <v>157</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>118</v>
+        <v>118.5</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>316.5</v>
+        <v>320</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>82.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>129</v>
+        <v>129.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-2.15</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>256</v>
+        <v>250.5</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3470</v>
+        <v>3555</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>736</v>
+        <v>753</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2500</v>
+        <v>2475</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>118.5</v>
+        <v>120</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>25.5</v>
+        <v>25.05</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.98</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>42.85</v>
+        <v>42</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>38.85</v>
+        <v>38.65</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>1595</v>
+        <v>1710</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.88</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>341.5</v>
+        <v>338.5</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>180</v>
+        <v>184.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-1.73</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>34.65</v>
+        <v>34.05</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>200.5</v>
+        <v>200</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3470</v>
+        <v>3555</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>736</v>
+        <v>753</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2500</v>
+        <v>2475</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>118.5</v>
+        <v>120</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>25.5</v>
+        <v>25.05</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.98</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>42.85</v>
+        <v>42</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>38.85</v>
+        <v>38.65</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1595</v>
+        <v>1710</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.88</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>341.5</v>
+        <v>338.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>180</v>
+        <v>184.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>157.5</v>
+        <v>157</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>118</v>
+        <v>118.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>316.5</v>
+        <v>320</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>82.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>129</v>
+        <v>129.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-2.15</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>256</v>
+        <v>250.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.9</v>
+        <v>40.85</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5620</v>
+        <v>5415</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.86</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.63</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1230</v>
+        <v>1210</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>283.5</v>
+        <v>287</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>213</v>
+        <v>212.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8385</v>
+        <v>8525</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-2.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>70.8</v>
+        <v>69.3</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.96</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6410</v>
+        <v>6920</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5020</v>
+        <v>5050</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>152</v>
+        <v>153.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>196.5</v>
+        <v>196</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3760</v>
+        <v>3770</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="F2" t="n">
-        <v>103.03</v>
+        <v>106.73</v>
       </c>
       <c r="G2" t="n">
-        <v>27.78</v>
+        <v>28.78</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M2" t="n">
         <v>1530</v>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.85</v>
+        <v>40.9</v>
       </c>
       <c r="F3" t="n">
-        <v>9.48</v>
+        <v>9.49</v>
       </c>
       <c r="G3" t="n">
         <v>1.82</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M3" t="n">
         <v>40.85</v>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M4" t="n">
         <v>154.5</v>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="F5" t="n">
-        <v>115.95</v>
+        <v>111.03</v>
       </c>
       <c r="G5" t="n">
-        <v>33.36</v>
+        <v>31.94</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-4.25</v>
       </c>
       <c r="M5" t="n">
         <v>5415</v>
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122.5</v>
+        <v>121</v>
       </c>
       <c r="F6" t="n">
-        <v>23.16</v>
+        <v>22.87</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.22</v>
       </c>
       <c r="M6" t="n">
         <v>122.5</v>
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.67</v>
+        <v>25.43</v>
       </c>
       <c r="G9" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="M9" t="n">
         <v>105.5</v>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>157</v>
+        <v>155.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.78</v>
+        <v>17.61</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>6.24</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="M10" t="n">
         <v>157</v>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>164.5</v>
+        <v>167.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.51</v>
+        <v>20.89</v>
       </c>
       <c r="G12" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M12" t="n">
         <v>164.5</v>
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F13" t="n">
-        <v>33.57</v>
+        <v>32.87</v>
       </c>
       <c r="G13" t="n">
-        <v>6.8</v>
+        <v>6.66</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-2.09</v>
       </c>
       <c r="M13" t="n">
         <v>287</v>
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
-        <v>28.49</v>
+        <v>28.29</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>145</v>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>212.5</v>
+        <v>212</v>
       </c>
       <c r="F15" t="n">
-        <v>19.14</v>
+        <v>19.1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="M15" t="n">
         <v>212.5</v>
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="F16" t="n">
-        <v>218.53</v>
+        <v>203.15</v>
       </c>
       <c r="G16" t="n">
-        <v>84.84</v>
+        <v>78.87</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-7.04</v>
       </c>
       <c r="M16" t="n">
         <v>8525</v>
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="F17" t="n">
-        <v>45.27</v>
+        <v>44.38</v>
       </c>
       <c r="G17" t="n">
-        <v>9.19</v>
+        <v>9.01</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="M17" t="n">
         <v>1530</v>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="F18" t="n">
-        <v>68.09</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>34.87</v>
+        <v>34.2</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="M18" t="n">
         <v>12350</v>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="F19" t="n">
-        <v>82.56999999999999</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>16.02</v>
+        <v>15.78</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="M19" t="n">
         <v>971</v>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="F20" t="n">
-        <v>44.67</v>
+        <v>44.23</v>
       </c>
       <c r="G20" t="n">
-        <v>6.68</v>
+        <v>6.61</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.98</v>
       </c>
       <c r="M20" t="n">
         <v>81.3</v>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5850</v>
+        <v>5675</v>
       </c>
       <c r="F21" t="n">
-        <v>95.78</v>
+        <v>92.91</v>
       </c>
       <c r="G21" t="n">
-        <v>24.73</v>
+        <v>23.99</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-2.99</v>
       </c>
       <c r="M21" t="n">
         <v>5850</v>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="F22" t="n">
-        <v>58.55</v>
+        <v>55.74</v>
       </c>
       <c r="G22" t="n">
-        <v>29.47</v>
+        <v>28.06</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-4.79</v>
       </c>
       <c r="M22" t="n">
         <v>2295</v>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="F24" t="n">
-        <v>75.93000000000001</v>
+        <v>75.42</v>
       </c>
       <c r="G24" t="n">
-        <v>18.53</v>
+        <v>18.4</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="M24" t="n">
         <v>1495</v>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>62.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>76.70999999999999</v>
+        <v>84.27</v>
       </c>
       <c r="G25" t="n">
-        <v>5.23</v>
+        <v>5.75</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>62.9</v>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="F26" t="n">
-        <v>232.36</v>
+        <v>228.06</v>
       </c>
       <c r="G26" t="n">
-        <v>52.93</v>
+        <v>51.95</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-1.85</v>
       </c>
       <c r="M26" t="n">
         <v>2700</v>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="F27" t="n">
-        <v>50.58</v>
+        <v>49.71</v>
       </c>
       <c r="G27" t="n">
-        <v>7.9</v>
+        <v>7.76</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="M27" t="n">
         <v>699</v>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1155</v>
+        <v>1195</v>
       </c>
       <c r="F28" t="n">
-        <v>56.56</v>
+        <v>58.52</v>
       </c>
       <c r="G28" t="n">
-        <v>11.72</v>
+        <v>12.13</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="M28" t="n">
         <v>1155</v>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="F29" t="n">
-        <v>92.14</v>
+        <v>92.8</v>
       </c>
       <c r="G29" t="n">
-        <v>18.06</v>
+        <v>18.18</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="M29" t="n">
         <v>563</v>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3310</v>
+        <v>3140</v>
       </c>
       <c r="F30" t="n">
-        <v>78.06999999999999</v>
+        <v>74.06</v>
       </c>
       <c r="G30" t="n">
-        <v>10.76</v>
+        <v>10.21</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-5.14</v>
       </c>
       <c r="M30" t="n">
         <v>3310</v>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="F31" t="n">
-        <v>104.06</v>
+        <v>106.49</v>
       </c>
       <c r="G31" t="n">
-        <v>13.38</v>
+        <v>13.69</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M31" t="n">
         <v>513</v>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F32" t="n">
-        <v>45.73</v>
+        <v>46.23</v>
       </c>
       <c r="G32" t="n">
-        <v>11.34</v>
+        <v>11.47</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M32" t="n">
         <v>722</v>
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="F33" t="n">
-        <v>39.06</v>
+        <v>36.9</v>
       </c>
       <c r="G33" t="n">
-        <v>6.74</v>
+        <v>6.37</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-5.52</v>
       </c>
       <c r="M33" t="n">
         <v>580</v>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="F34" t="n">
-        <v>87.28</v>
+        <v>81.09</v>
       </c>
       <c r="G34" t="n">
-        <v>19.89</v>
+        <v>18.47</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>-7.1</v>
       </c>
       <c r="M34" t="n">
         <v>5285</v>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="F35" t="n">
-        <v>60.79</v>
+        <v>58.4</v>
       </c>
       <c r="G35" t="n">
-        <v>16.89</v>
+        <v>16.23</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-3.93</v>
       </c>
       <c r="M35" t="n">
         <v>1910</v>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="F36" t="n">
-        <v>20.38</v>
+        <v>20.24</v>
       </c>
       <c r="G36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-0.72</v>
       </c>
       <c r="M36" t="n">
         <v>69.3</v>
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="F37" t="n">
-        <v>156.17</v>
+        <v>155.61</v>
       </c>
       <c r="G37" t="n">
-        <v>43.06</v>
+        <v>42.91</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="M37" t="n">
         <v>6920</v>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="F38" t="n">
-        <v>78.97</v>
+        <v>76.94</v>
       </c>
       <c r="G38" t="n">
-        <v>31.02</v>
+        <v>30.22</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>-2.57</v>
       </c>
       <c r="M38" t="n">
         <v>5050</v>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="F39" t="n">
-        <v>45.75</v>
+        <v>45.03</v>
       </c>
       <c r="G39" t="n">
-        <v>23.99</v>
+        <v>23.61</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>-1.57</v>
       </c>
       <c r="M39" t="n">
         <v>699</v>
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F42" t="n">
-        <v>15.45</v>
+        <v>15.38</v>
       </c>
       <c r="G42" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M42" t="n">
         <v>106</v>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="F43" t="n">
-        <v>24.38</v>
+        <v>23.86</v>
       </c>
       <c r="G43" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="M43" t="n">
         <v>901</v>
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F44" t="n">
-        <v>27</v>
+        <v>26.72</v>
       </c>
       <c r="G44" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="M44" t="n">
         <v>196</v>
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3770</v>
+        <v>3685</v>
       </c>
       <c r="F45" t="n">
-        <v>55.29</v>
+        <v>54.05</v>
       </c>
       <c r="G45" t="n">
-        <v>5.39</v>
+        <v>5.27</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="M45" t="n">
         <v>3770</v>
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>218.5</v>
+        <v>213</v>
       </c>
       <c r="F46" t="n">
-        <v>22.25</v>
+        <v>21.69</v>
       </c>
       <c r="G46" t="n">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
       <c r="M46" t="n">
         <v>218.5</v>
@@ -4155,34 +4155,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>238</v>
+        <v>124.5</v>
       </c>
       <c r="F47" t="n">
-        <v>26.07</v>
+        <v>20.24</v>
       </c>
       <c r="G47" t="n">
-        <v>3.21</v>
+        <v>2.99</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>-15.3</v>
+        <v>11</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -4191,31 +4191,31 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M47" t="n">
-        <v>238</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>EPS單期衰退</t>
-        </is>
-      </c>
+        <v>122.5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.72</v>
+        <v>1.4</v>
       </c>
       <c r="R47" t="n">
-        <v>13.2</v>
+        <v>3.8</v>
       </c>
       <c r="S47" t="n">
-        <v>34.8</v>
+        <v>48.7</v>
       </c>
       <c r="T47" t="n">
-        <v>34.5</v>
+        <v>28.4</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
@@ -4225,19 +4225,19 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4246,20 +4246,20 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>749</v>
+        <v>232.5</v>
       </c>
       <c r="F48" t="n">
-        <v>27.16</v>
+        <v>25.47</v>
       </c>
       <c r="G48" t="n">
-        <v>7.66</v>
+        <v>3.14</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>-15.3</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4268,35 +4268,31 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-2.31</v>
       </c>
       <c r="M48" t="n">
-        <v>749</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>31.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="R48" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="S48" t="n">
-        <v>21.9</v>
+        <v>34.8</v>
       </c>
       <c r="T48" t="n">
-        <v>32.2</v>
+        <v>34.5</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -4306,19 +4302,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4327,20 +4323,20 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E49" t="n">
-        <v>110.5</v>
+        <v>760</v>
       </c>
       <c r="F49" t="n">
-        <v>20.62</v>
+        <v>27.56</v>
       </c>
       <c r="G49" t="n">
-        <v>2.56</v>
+        <v>7.77</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>186.3</v>
+        <v>27</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4349,10 +4345,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M49" t="n">
-        <v>110.5</v>
+        <v>749</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4361,28 +4357,28 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>10.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="R49" t="n">
-        <v>-3.4</v>
+        <v>3.8</v>
       </c>
       <c r="S49" t="n">
-        <v>37</v>
+        <v>21.9</v>
       </c>
       <c r="T49" t="n">
-        <v>35.8</v>
+        <v>32.2</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -4394,12 +4390,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4408,20 +4404,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>6245</v>
+        <v>110</v>
       </c>
       <c r="F50" t="n">
-        <v>33.21</v>
+        <v>20.52</v>
       </c>
       <c r="G50" t="n">
-        <v>4.26</v>
+        <v>2.55</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>186.3</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4430,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="M50" t="n">
-        <v>6245</v>
+        <v>110.5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4442,28 +4438,28 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="R50" t="n">
-        <v>6.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S50" t="n">
-        <v>41.8</v>
+        <v>37</v>
       </c>
       <c r="T50" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4475,71 +4471,73 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="E51" t="n">
-        <v>565</v>
+        <v>6020</v>
       </c>
       <c r="F51" t="n">
-        <v>25.59</v>
+        <v>32.02</v>
       </c>
       <c r="G51" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="H51" t="n">
-        <v>29.3</v>
-      </c>
+        <v>4.11</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.87</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="M51" t="n">
-        <v>565</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+        <v>6245</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P51" t="n">
-        <v>19.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.94</v>
+        <v>1.21</v>
       </c>
       <c r="R51" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="S51" t="n">
-        <v>64.90000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="T51" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.87</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4547,19 +4545,19 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4568,25 +4566,25 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E52" t="n">
-        <v>698</v>
+        <v>544</v>
       </c>
       <c r="F52" t="n">
-        <v>42.82</v>
+        <v>24.64</v>
       </c>
       <c r="G52" t="n">
-        <v>5.75</v>
+        <v>6.71</v>
       </c>
       <c r="H52" t="n">
-        <v>46.1</v>
+        <v>29.3</v>
       </c>
       <c r="I52" t="n">
-        <v>30.6</v>
+        <v>18.6</v>
       </c>
       <c r="J52" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4594,78 +4592,78 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-3.72</v>
       </c>
       <c r="M52" t="n">
-        <v>698</v>
+        <v>565</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R52" t="n">
-        <v>24.8</v>
+        <v>10.6</v>
       </c>
       <c r="S52" t="n">
-        <v>1.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>60.2</v>
+        <v>34.7</v>
       </c>
       <c r="U52" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E53" t="n">
-        <v>58.8</v>
+        <v>713</v>
       </c>
       <c r="F53" t="n">
-        <v>16.15</v>
+        <v>43.74</v>
       </c>
       <c r="G53" t="n">
-        <v>2.46</v>
+        <v>5.87</v>
       </c>
       <c r="H53" t="n">
-        <v>17.3</v>
+        <v>46.1</v>
       </c>
       <c r="I53" t="n">
-        <v>11.8</v>
+        <v>30.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4673,30 +4671,30 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M53" t="n">
-        <v>58.8</v>
+        <v>698</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>11.3</v>
+        <v>15.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="R53" t="n">
-        <v>4.4</v>
+        <v>24.8</v>
       </c>
       <c r="S53" t="n">
-        <v>768.2</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>19.4</v>
+        <v>60.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -4705,19 +4703,19 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4726,25 +4724,25 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>179</v>
+        <v>58.3</v>
       </c>
       <c r="F54" t="n">
-        <v>16.35</v>
+        <v>16.02</v>
       </c>
       <c r="G54" t="n">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="H54" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="I54" t="n">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="J54" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4752,34 +4750,34 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M54" t="n">
-        <v>179</v>
+        <v>58.8</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.03</v>
+        <v>1.15</v>
       </c>
       <c r="R54" t="n">
-        <v>30.2</v>
+        <v>4.4</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>768.2</v>
       </c>
       <c r="T54" t="n">
-        <v>16.9</v>
+        <v>19.4</v>
       </c>
       <c r="U54" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -4791,89 +4789,91 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E55" t="n">
-        <v>339</v>
+        <v>177.5</v>
       </c>
       <c r="F55" t="n">
-        <v>17.56</v>
+        <v>16.21</v>
       </c>
       <c r="G55" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>1.76</v>
+      </c>
+      <c r="H55" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I55" t="n">
-        <v>49</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
       <c r="M55" t="n">
-        <v>339</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.09</v>
+        <v>4.03</v>
       </c>
       <c r="R55" t="n">
-        <v>24.2</v>
+        <v>30.2</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>24</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4882,20 +4882,20 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E56" t="n">
-        <v>166</v>
+        <v>344.5</v>
       </c>
       <c r="F56" t="n">
-        <v>18.67</v>
+        <v>17.84</v>
       </c>
       <c r="G56" t="n">
-        <v>3.94</v>
+        <v>5.06</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>57.1</v>
+        <v>49</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M56" t="n">
-        <v>166</v>
+        <v>339</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4916,24 +4916,24 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>18.6</v>
+        <v>29.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="R56" t="n">
-        <v>11.1</v>
+        <v>24.2</v>
       </c>
       <c r="S56" t="n">
-        <v>3.6</v>
+        <v>25</v>
       </c>
       <c r="T56" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -4945,34 +4945,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E57" t="n">
-        <v>122.5</v>
+        <v>167</v>
       </c>
       <c r="F57" t="n">
-        <v>19.92</v>
+        <v>18.79</v>
       </c>
       <c r="G57" t="n">
-        <v>2.94</v>
+        <v>3.96</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>11</v>
+        <v>57.1</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M57" t="n">
-        <v>122.5</v>
+        <v>166</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4993,24 +4993,24 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>10.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.4</v>
+        <v>2.74</v>
       </c>
       <c r="R57" t="n">
-        <v>3.8</v>
+        <v>11.1</v>
       </c>
       <c r="S57" t="n">
-        <v>48.7</v>
+        <v>3.6</v>
       </c>
       <c r="T57" t="n">
-        <v>28.4</v>
+        <v>22</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5039,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="F58" t="n">
-        <v>17</v>
+        <v>16.93</v>
       </c>
       <c r="G58" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="M58" t="n">
         <v>89.09999999999999</v>
@@ -5120,13 +5120,13 @@
         <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F59" t="n">
-        <v>17.28</v>
+        <v>17.17</v>
       </c>
       <c r="G59" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="M59" t="n">
         <v>155</v>
@@ -5278,13 +5278,13 @@
         <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>183.5</v>
+        <v>185.5</v>
       </c>
       <c r="F61" t="n">
-        <v>15.49</v>
+        <v>15.65</v>
       </c>
       <c r="G61" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M61" t="n">
         <v>183.5</v>
@@ -5355,13 +5355,13 @@
         <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="F62" t="n">
-        <v>17.58</v>
+        <v>18</v>
       </c>
       <c r="G62" t="n">
-        <v>14.19</v>
+        <v>14.52</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M62" t="n">
         <v>761</v>
@@ -5436,13 +5436,13 @@
         <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F63" t="n">
-        <v>19.52</v>
+        <v>19.64</v>
       </c>
       <c r="G63" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M63" t="n">
         <v>503</v>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>171.5</v>
+        <v>174</v>
       </c>
       <c r="F64" t="n">
-        <v>18.91</v>
+        <v>19.18</v>
       </c>
       <c r="G64" t="n">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M64" t="n">
         <v>171.5</v>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.2</v>
+        <v>50.2</v>
       </c>
       <c r="F65" t="n">
-        <v>12.15</v>
+        <v>12.4</v>
       </c>
       <c r="G65" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M65" t="n">
         <v>49.2</v>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>157</v>
+        <v>158.5</v>
       </c>
       <c r="F66" t="n">
-        <v>16.49</v>
+        <v>16.65</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65</v>
+        <v>4.69</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M66" t="n">
         <v>157</v>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F67" t="n">
-        <v>20.28</v>
+        <v>20.21</v>
       </c>
       <c r="G67" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="M67" t="n">
         <v>542</v>
@@ -5833,13 +5833,13 @@
         <v>91</v>
       </c>
       <c r="E68" t="n">
-        <v>118.5</v>
+        <v>118</v>
       </c>
       <c r="F68" t="n">
-        <v>15.31</v>
+        <v>15.25</v>
       </c>
       <c r="G68" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="H68" t="n">
         <v>15</v>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M68" t="n">
         <v>118.5</v>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F69" t="n">
-        <v>27.05</v>
+        <v>26.97</v>
       </c>
       <c r="G69" t="n">
-        <v>6.96</v>
+        <v>6.93</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="M69" t="n">
         <v>320</v>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>82.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>14.39</v>
+        <v>14.49</v>
       </c>
       <c r="G70" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="M70" t="n">
         <v>82.3</v>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>129.5</v>
+        <v>131</v>
       </c>
       <c r="F71" t="n">
-        <v>18.04</v>
+        <v>18.25</v>
       </c>
       <c r="G71" t="n">
-        <v>4.47</v>
+        <v>4.53</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M71" t="n">
         <v>129.5</v>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="F73" t="n">
-        <v>47.01</v>
+        <v>47.65</v>
       </c>
       <c r="G73" t="n">
-        <v>25.11</v>
+        <v>25.45</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M73" t="n">
         <v>1110</v>
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="F74" t="n">
-        <v>19.32</v>
+        <v>19.1</v>
       </c>
       <c r="G74" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="M74" t="n">
         <v>59.9</v>
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="F75" t="n">
-        <v>47.39</v>
+        <v>45.32</v>
       </c>
       <c r="G75" t="n">
-        <v>25.29</v>
+        <v>24.19</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>-4.36</v>
       </c>
       <c r="M75" t="n">
         <v>3555</v>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="F76" t="n">
-        <v>15.17</v>
+        <v>14.75</v>
       </c>
       <c r="G76" t="n">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>-2.79</v>
       </c>
       <c r="M76" t="n">
         <v>753</v>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>120</v>
+        <v>117.5</v>
       </c>
       <c r="F78" t="n">
-        <v>17.12</v>
+        <v>16.76</v>
       </c>
       <c r="G78" t="n">
-        <v>3.79</v>
+        <v>3.71</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>-2.08</v>
       </c>
       <c r="M78" t="n">
         <v>120</v>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>110.5</v>
+        <v>110</v>
       </c>
       <c r="F79" t="n">
-        <v>13.68</v>
+        <v>13.61</v>
       </c>
       <c r="G79" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="M79" t="n">
         <v>110.5</v>
@@ -6791,10 +6791,10 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="F80" t="n">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="G80" t="n">
         <v>0.97</v>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M80" t="n">
         <v>25.05</v>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F82" t="n">
-        <v>12.83</v>
+        <v>12.76</v>
       </c>
       <c r="G82" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M82" t="n">
         <v>180</v>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="F83" t="n">
-        <v>8.84</v>
+        <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>-1.19</v>
       </c>
       <c r="M83" t="n">
         <v>42</v>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="F84" t="n">
-        <v>23.51</v>
+        <v>22.99</v>
       </c>
       <c r="G84" t="n">
-        <v>9.01</v>
+        <v>8.81</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>-2.23</v>
       </c>
       <c r="M84" t="n">
         <v>897</v>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="F85" t="n">
-        <v>23.05</v>
+        <v>22.32</v>
       </c>
       <c r="G85" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>-3.16</v>
       </c>
       <c r="M85" t="n">
         <v>538</v>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>167</v>
+        <v>163.5</v>
       </c>
       <c r="F86" t="n">
-        <v>17.96</v>
+        <v>17.58</v>
       </c>
       <c r="G86" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="M86" t="n">
         <v>167</v>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.65</v>
+        <v>38.35</v>
       </c>
       <c r="F87" t="n">
-        <v>7.97</v>
+        <v>7.91</v>
       </c>
       <c r="G87" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="M87" t="n">
         <v>38.65</v>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="F88" t="n">
-        <v>29.77</v>
+        <v>28.44</v>
       </c>
       <c r="G88" t="n">
-        <v>15.34</v>
+        <v>14.65</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>-4.49</v>
       </c>
       <c r="M88" t="n">
         <v>1895</v>
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1710</v>
+        <v>1630</v>
       </c>
       <c r="F89" t="n">
-        <v>39.44</v>
+        <v>37.59</v>
       </c>
       <c r="G89" t="n">
-        <v>12</v>
+        <v>11.44</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>-4.68</v>
       </c>
       <c r="M89" t="n">
         <v>1710</v>
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>89.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="G90" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="M90" t="n">
         <v>89.8</v>
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>56.2</v>
+        <v>55.3</v>
       </c>
       <c r="F91" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="G91" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="M91" t="n">
         <v>56.2</v>
@@ -7755,10 +7755,10 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="F92" t="n">
-        <v>7.39</v>
+        <v>7.41</v>
       </c>
       <c r="G92" t="n">
         <v>1.14</v>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="M92" t="n">
         <v>53.3</v>
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>338.5</v>
+        <v>336.5</v>
       </c>
       <c r="F93" t="n">
-        <v>14.75</v>
+        <v>14.66</v>
       </c>
       <c r="G93" t="n">
-        <v>5.36</v>
+        <v>5.32</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="M93" t="n">
         <v>338.5</v>
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="F94" t="n">
-        <v>6.78</v>
+        <v>6.73</v>
       </c>
       <c r="G94" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="M94" t="n">
         <v>2115</v>
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>184.5</v>
+        <v>185.5</v>
       </c>
       <c r="F95" t="n">
-        <v>14.65</v>
+        <v>14.73</v>
       </c>
       <c r="G95" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="M95" t="n">
         <v>184.5</v>
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F96" t="n">
-        <v>15.78</v>
+        <v>15.73</v>
       </c>
       <c r="G96" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="M96" t="n">
         <v>1480</v>
@@ -8170,13 +8170,13 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>70.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="F97" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="G97" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="M97" t="n">
         <v>70.09999999999999</v>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F98" t="n">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
       <c r="G98" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="M98" t="n">
         <v>378</v>
@@ -8328,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>23.5</v>
+        <v>23.45</v>
       </c>
       <c r="F99" t="n">
         <v>3.32</v>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="M99" t="n">
         <v>23.5</v>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>34.05</v>
+        <v>33.4</v>
       </c>
       <c r="F100" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="G100" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>-1.91</v>
       </c>
       <c r="M100" t="n">
         <v>34.05</v>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>200</v>
+        <v>199.5</v>
       </c>
       <c r="F101" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="G101" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="M101" t="n">
         <v>200</v>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="F2" t="n">
-        <v>47.39</v>
+        <v>45.32</v>
       </c>
       <c r="G2" t="n">
-        <v>25.29</v>
+        <v>24.19</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-4.36</v>
       </c>
       <c r="M2" t="n">
         <v>3555</v>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="F3" t="n">
-        <v>15.17</v>
+        <v>14.75</v>
       </c>
       <c r="G3" t="n">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-2.79</v>
       </c>
       <c r="M3" t="n">
         <v>753</v>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>117.5</v>
       </c>
       <c r="F5" t="n">
-        <v>17.12</v>
+        <v>16.76</v>
       </c>
       <c r="G5" t="n">
-        <v>3.79</v>
+        <v>3.71</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-2.08</v>
       </c>
       <c r="M5" t="n">
         <v>120</v>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>110.5</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>13.68</v>
+        <v>13.61</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="M6" t="n">
         <v>110.5</v>
@@ -9097,10 +9097,10 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="G7" t="n">
         <v>0.97</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M7" t="n">
         <v>25.05</v>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F9" t="n">
-        <v>12.83</v>
+        <v>12.76</v>
       </c>
       <c r="G9" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>180</v>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="n">
-        <v>8.84</v>
+        <v>8.74</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.19</v>
       </c>
       <c r="M10" t="n">
         <v>42</v>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="F11" t="n">
-        <v>23.51</v>
+        <v>22.99</v>
       </c>
       <c r="G11" t="n">
-        <v>9.01</v>
+        <v>8.81</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-2.23</v>
       </c>
       <c r="M11" t="n">
         <v>897</v>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="F12" t="n">
-        <v>23.05</v>
+        <v>22.32</v>
       </c>
       <c r="G12" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-3.16</v>
       </c>
       <c r="M12" t="n">
         <v>538</v>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>167</v>
+        <v>163.5</v>
       </c>
       <c r="F13" t="n">
-        <v>17.96</v>
+        <v>17.58</v>
       </c>
       <c r="G13" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="M13" t="n">
         <v>167</v>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.65</v>
+        <v>38.35</v>
       </c>
       <c r="F14" t="n">
-        <v>7.97</v>
+        <v>7.91</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="M14" t="n">
         <v>38.65</v>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="F15" t="n">
-        <v>29.77</v>
+        <v>28.44</v>
       </c>
       <c r="G15" t="n">
-        <v>15.34</v>
+        <v>14.65</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-4.49</v>
       </c>
       <c r="M15" t="n">
         <v>1895</v>
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1710</v>
+        <v>1630</v>
       </c>
       <c r="F16" t="n">
-        <v>39.44</v>
+        <v>37.59</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>11.44</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-4.68</v>
       </c>
       <c r="M16" t="n">
         <v>1710</v>
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="M17" t="n">
         <v>89.8</v>
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>56.2</v>
+        <v>55.3</v>
       </c>
       <c r="F18" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="M18" t="n">
         <v>56.2</v>
@@ -10061,10 +10061,10 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="F19" t="n">
-        <v>7.39</v>
+        <v>7.41</v>
       </c>
       <c r="G19" t="n">
         <v>1.14</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="M19" t="n">
         <v>53.3</v>
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>338.5</v>
+        <v>336.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.75</v>
+        <v>14.66</v>
       </c>
       <c r="G20" t="n">
-        <v>5.36</v>
+        <v>5.32</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="M20" t="n">
         <v>338.5</v>
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="F21" t="n">
-        <v>6.78</v>
+        <v>6.73</v>
       </c>
       <c r="G21" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="M21" t="n">
         <v>2115</v>
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>184.5</v>
+        <v>185.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.65</v>
+        <v>14.73</v>
       </c>
       <c r="G22" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="M22" t="n">
         <v>184.5</v>
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F23" t="n">
-        <v>15.78</v>
+        <v>15.73</v>
       </c>
       <c r="G23" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="M23" t="n">
         <v>1480</v>
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>157</v>
+        <v>158.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16.49</v>
+        <v>16.65</v>
       </c>
       <c r="G2" t="n">
-        <v>4.65</v>
+        <v>4.69</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M2" t="n">
         <v>157</v>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F3" t="n">
-        <v>20.28</v>
+        <v>20.21</v>
       </c>
       <c r="G3" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="M3" t="n">
         <v>542</v>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>118.5</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>15.31</v>
+        <v>15.25</v>
       </c>
       <c r="G4" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M4" t="n">
         <v>118.5</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F5" t="n">
-        <v>27.05</v>
+        <v>26.97</v>
       </c>
       <c r="G5" t="n">
-        <v>6.96</v>
+        <v>6.93</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="M5" t="n">
         <v>320</v>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>14.39</v>
+        <v>14.49</v>
       </c>
       <c r="G6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="M6" t="n">
         <v>82.3</v>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>129.5</v>
+        <v>131</v>
       </c>
       <c r="F7" t="n">
-        <v>18.04</v>
+        <v>18.25</v>
       </c>
       <c r="G7" t="n">
-        <v>4.47</v>
+        <v>4.53</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M7" t="n">
         <v>129.5</v>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="F9" t="n">
-        <v>47.01</v>
+        <v>47.65</v>
       </c>
       <c r="G9" t="n">
-        <v>25.11</v>
+        <v>25.45</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1110</v>
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="F10" t="n">
-        <v>19.32</v>
+        <v>19.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="M10" t="n">
         <v>59.9</v>
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="F2" t="n">
-        <v>103.03</v>
+        <v>106.73</v>
       </c>
       <c r="G2" t="n">
-        <v>27.78</v>
+        <v>28.78</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M2" t="n">
         <v>1530</v>
@@ -11538,10 +11538,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.85</v>
+        <v>40.9</v>
       </c>
       <c r="F3" t="n">
-        <v>9.48</v>
+        <v>9.49</v>
       </c>
       <c r="G3" t="n">
         <v>1.82</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M3" t="n">
         <v>40.85</v>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M4" t="n">
         <v>154.5</v>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="F5" t="n">
-        <v>115.95</v>
+        <v>111.03</v>
       </c>
       <c r="G5" t="n">
-        <v>33.36</v>
+        <v>31.94</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-4.25</v>
       </c>
       <c r="M5" t="n">
         <v>5415</v>
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122.5</v>
+        <v>121</v>
       </c>
       <c r="F6" t="n">
-        <v>23.16</v>
+        <v>22.87</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.22</v>
       </c>
       <c r="M6" t="n">
         <v>122.5</v>
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.67</v>
+        <v>25.43</v>
       </c>
       <c r="G9" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="M9" t="n">
         <v>105.5</v>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>157</v>
+        <v>155.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.78</v>
+        <v>17.61</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>6.24</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="M10" t="n">
         <v>157</v>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>164.5</v>
+        <v>167.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.51</v>
+        <v>20.89</v>
       </c>
       <c r="G12" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M12" t="n">
         <v>164.5</v>
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F13" t="n">
-        <v>33.57</v>
+        <v>32.87</v>
       </c>
       <c r="G13" t="n">
-        <v>6.8</v>
+        <v>6.66</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,7 +12367,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-2.09</v>
       </c>
       <c r="M13" t="n">
         <v>287</v>
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
-        <v>28.49</v>
+        <v>28.29</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>145</v>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>212.5</v>
+        <v>212</v>
       </c>
       <c r="F15" t="n">
-        <v>19.14</v>
+        <v>19.1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="M15" t="n">
         <v>212.5</v>
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="F16" t="n">
-        <v>218.53</v>
+        <v>203.15</v>
       </c>
       <c r="G16" t="n">
-        <v>84.84</v>
+        <v>78.87</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-7.04</v>
       </c>
       <c r="M16" t="n">
         <v>8525</v>
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="F2" t="n">
-        <v>60.79</v>
+        <v>58.4</v>
       </c>
       <c r="G2" t="n">
-        <v>16.89</v>
+        <v>16.23</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-3.93</v>
       </c>
       <c r="M2" t="n">
         <v>1910</v>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="F3" t="n">
-        <v>20.38</v>
+        <v>20.24</v>
       </c>
       <c r="G3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.72</v>
       </c>
       <c r="M3" t="n">
         <v>69.3</v>
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="F4" t="n">
-        <v>156.17</v>
+        <v>155.61</v>
       </c>
       <c r="G4" t="n">
-        <v>43.06</v>
+        <v>42.91</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="M4" t="n">
         <v>6920</v>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="F5" t="n">
-        <v>78.97</v>
+        <v>76.94</v>
       </c>
       <c r="G5" t="n">
-        <v>31.02</v>
+        <v>30.22</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-2.57</v>
       </c>
       <c r="M5" t="n">
         <v>5050</v>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="F6" t="n">
-        <v>45.75</v>
+        <v>45.03</v>
       </c>
       <c r="G6" t="n">
-        <v>23.99</v>
+        <v>23.61</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,7 +13146,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.57</v>
       </c>
       <c r="M6" t="n">
         <v>699</v>
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.45</v>
+        <v>15.38</v>
       </c>
       <c r="G9" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
         <v>106</v>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="F10" t="n">
-        <v>24.38</v>
+        <v>23.86</v>
       </c>
       <c r="G10" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="M10" t="n">
         <v>901</v>
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>26.72</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="M11" t="n">
         <v>196</v>
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3770</v>
+        <v>3685</v>
       </c>
       <c r="F12" t="n">
-        <v>55.29</v>
+        <v>54.05</v>
       </c>
       <c r="G12" t="n">
-        <v>5.39</v>
+        <v>5.27</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="M12" t="n">
         <v>3770</v>

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1585</v>
+        <v>1605</v>
       </c>
       <c r="F2" t="n">
-        <v>106.73</v>
+        <v>108.08</v>
       </c>
       <c r="G2" t="n">
-        <v>28.78</v>
+        <v>29.14</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.59</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.85</v>
+        <v>40.9</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -741,7 +741,7 @@
         <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5185</v>
+        <v>5125</v>
       </c>
       <c r="F5" t="n">
-        <v>111.03</v>
+        <v>109.74</v>
       </c>
       <c r="G5" t="n">
-        <v>31.94</v>
+        <v>31.57</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-4.25</v>
+        <v>-1.16</v>
       </c>
       <c r="M5" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>121</v>
+        <v>119.5</v>
       </c>
       <c r="F6" t="n">
-        <v>22.87</v>
+        <v>22.59</v>
       </c>
       <c r="G6" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.22</v>
+        <v>-1.24</v>
       </c>
       <c r="M6" t="n">
-        <v>122.5</v>
+        <v>121</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="M7" t="n">
         <v>102</v>
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F8" t="n">
-        <v>21.94</v>
+        <v>22.07</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M8" t="n">
         <v>172</v>
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.43</v>
+        <v>25.18</v>
       </c>
       <c r="G9" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>155.5</v>
+        <v>158.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.61</v>
+        <v>17.95</v>
       </c>
       <c r="G10" t="n">
-        <v>6.24</v>
+        <v>6.36</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.96</v>
+        <v>1.93</v>
       </c>
       <c r="M10" t="n">
-        <v>157</v>
+        <v>155.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="F11" t="n">
-        <v>23.25</v>
+        <v>23.05</v>
       </c>
       <c r="G11" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="M11" t="n">
         <v>1210</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>164.5</v>
+        <v>167.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>281</v>
+        <v>279.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.87</v>
+        <v>32.69</v>
       </c>
       <c r="G13" t="n">
-        <v>6.66</v>
+        <v>6.62</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-2.09</v>
+        <v>-0.53</v>
       </c>
       <c r="M13" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.29</v>
+        <v>28.19</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>212</v>
+        <v>212.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.1</v>
+        <v>19.14</v>
       </c>
       <c r="G15" t="n">
-        <v>5.38</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.24</v>
+        <v>0.24</v>
       </c>
       <c r="M15" t="n">
-        <v>212.5</v>
+        <v>212</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7925</v>
+        <v>8040</v>
       </c>
       <c r="F16" t="n">
-        <v>203.15</v>
+        <v>206.1</v>
       </c>
       <c r="G16" t="n">
-        <v>78.87</v>
+        <v>80.02</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-7.04</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1500</v>
+        <v>1490</v>
       </c>
       <c r="F17" t="n">
-        <v>44.38</v>
+        <v>44.08</v>
       </c>
       <c r="G17" t="n">
-        <v>9.01</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-1.96</v>
+        <v>-0.67</v>
       </c>
       <c r="M17" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12115</v>
+        <v>12055</v>
       </c>
       <c r="F18" t="n">
-        <v>66.79000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>34.2</v>
+        <v>34.03</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.9</v>
+        <v>-0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="F19" t="n">
-        <v>81.29000000000001</v>
+        <v>81.89</v>
       </c>
       <c r="G19" t="n">
-        <v>15.78</v>
+        <v>15.89</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.54</v>
+        <v>0.73</v>
       </c>
       <c r="M19" t="n">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>44.23</v>
+        <v>44.51</v>
       </c>
       <c r="G20" t="n">
-        <v>6.61</v>
+        <v>6.66</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.98</v>
+        <v>0.62</v>
       </c>
       <c r="M20" t="n">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5675</v>
+        <v>5930</v>
       </c>
       <c r="F21" t="n">
-        <v>92.91</v>
+        <v>97.09</v>
       </c>
       <c r="G21" t="n">
-        <v>23.99</v>
+        <v>25.07</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.99</v>
+        <v>4.49</v>
       </c>
       <c r="M21" t="n">
-        <v>5850</v>
+        <v>5675</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2185</v>
+        <v>2135</v>
       </c>
       <c r="F22" t="n">
-        <v>55.74</v>
+        <v>54.46</v>
       </c>
       <c r="G22" t="n">
-        <v>28.06</v>
+        <v>27.41</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-4.79</v>
+        <v>-2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.3</v>
+        <v>18.65</v>
       </c>
       <c r="F23" t="n">
-        <v>41.59</v>
+        <v>42.39</v>
       </c>
       <c r="G23" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
         <v>18.3</v>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1485</v>
+        <v>1520</v>
       </c>
       <c r="F24" t="n">
-        <v>75.42</v>
+        <v>77.2</v>
       </c>
       <c r="G24" t="n">
-        <v>18.4</v>
+        <v>18.84</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-0.67</v>
+        <v>2.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>69.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F25" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="G25" t="n">
-        <v>5.75</v>
+        <v>5.72</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.859999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="M25" t="n">
-        <v>62.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2650</v>
+        <v>2695</v>
       </c>
       <c r="F26" t="n">
-        <v>228.06</v>
+        <v>231.93</v>
       </c>
       <c r="G26" t="n">
-        <v>51.95</v>
+        <v>52.83</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-1.85</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="F27" t="n">
-        <v>49.71</v>
+        <v>50.87</v>
       </c>
       <c r="G27" t="n">
-        <v>7.76</v>
+        <v>7.94</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-1.72</v>
+        <v>2.33</v>
       </c>
       <c r="M27" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1195</v>
+        <v>1215</v>
       </c>
       <c r="F28" t="n">
-        <v>58.52</v>
+        <v>59.5</v>
       </c>
       <c r="G28" t="n">
-        <v>12.13</v>
+        <v>12.33</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.46</v>
+        <v>1.67</v>
       </c>
       <c r="M28" t="n">
-        <v>1155</v>
+        <v>1195</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="F29" t="n">
-        <v>92.8</v>
+        <v>93.13</v>
       </c>
       <c r="G29" t="n">
-        <v>18.18</v>
+        <v>18.25</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.71</v>
+        <v>0.35</v>
       </c>
       <c r="M29" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3140</v>
+        <v>3065</v>
       </c>
       <c r="F30" t="n">
-        <v>74.06</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>10.21</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-5.14</v>
+        <v>-2.39</v>
       </c>
       <c r="M30" t="n">
-        <v>3310</v>
+        <v>3140</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F31" t="n">
-        <v>106.49</v>
+        <v>106.09</v>
       </c>
       <c r="G31" t="n">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.34</v>
+        <v>-0.38</v>
       </c>
       <c r="M31" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="F32" t="n">
-        <v>46.23</v>
+        <v>45.98</v>
       </c>
       <c r="G32" t="n">
-        <v>11.47</v>
+        <v>11.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.11</v>
+        <v>-0.55</v>
       </c>
       <c r="M32" t="n">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-5.52</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4910</v>
+        <v>4920</v>
       </c>
       <c r="F34" t="n">
-        <v>81.09</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>18.47</v>
+        <v>18.51</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-7.1</v>
+        <v>0.2</v>
       </c>
       <c r="M34" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1835</v>
+        <v>1890</v>
       </c>
       <c r="F35" t="n">
-        <v>58.4</v>
+        <v>60.15</v>
       </c>
       <c r="G35" t="n">
-        <v>16.23</v>
+        <v>16.72</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-3.93</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="F36" t="n">
-        <v>20.24</v>
+        <v>20.5</v>
       </c>
       <c r="G36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-0.72</v>
+        <v>1.31</v>
       </c>
       <c r="M36" t="n">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>6895</v>
+        <v>6800</v>
       </c>
       <c r="F37" t="n">
-        <v>155.61</v>
+        <v>153.46</v>
       </c>
       <c r="G37" t="n">
-        <v>42.91</v>
+        <v>42.32</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-0.36</v>
+        <v>-1.38</v>
       </c>
       <c r="M37" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>4920</v>
+        <v>4935</v>
       </c>
       <c r="F38" t="n">
-        <v>76.94</v>
+        <v>77.17</v>
       </c>
       <c r="G38" t="n">
-        <v>30.22</v>
+        <v>30.31</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-2.57</v>
+        <v>0.3</v>
       </c>
       <c r="M38" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="F39" t="n">
-        <v>45.03</v>
+        <v>45.35</v>
       </c>
       <c r="G39" t="n">
-        <v>23.61</v>
+        <v>23.78</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-1.57</v>
+        <v>0.73</v>
       </c>
       <c r="M39" t="n">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>11.92</v>
+        <v>11.93</v>
       </c>
       <c r="G40" t="n">
         <v>1.67</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M40" t="n">
         <v>97</v>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="F41" t="n">
-        <v>11.81</v>
+        <v>11.77</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="M41" t="n">
         <v>153.5</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="F43" t="n">
-        <v>23.86</v>
+        <v>24.08</v>
       </c>
       <c r="G43" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-2.11</v>
+        <v>0.91</v>
       </c>
       <c r="M43" t="n">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>194</v>
+        <v>197.5</v>
       </c>
       <c r="F44" t="n">
-        <v>26.72</v>
+        <v>27.2</v>
       </c>
       <c r="G44" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-1.02</v>
+        <v>1.8</v>
       </c>
       <c r="M44" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3685</v>
+        <v>3740</v>
       </c>
       <c r="F45" t="n">
-        <v>54.05</v>
+        <v>54.85</v>
       </c>
       <c r="G45" t="n">
-        <v>5.27</v>
+        <v>5.34</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-2.25</v>
+        <v>1.49</v>
       </c>
       <c r="M45" t="n">
-        <v>3770</v>
+        <v>3685</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,10 +4095,10 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>213</v>
+        <v>213.5</v>
       </c>
       <c r="F46" t="n">
-        <v>21.69</v>
+        <v>21.74</v>
       </c>
       <c r="G46" t="n">
         <v>3.68</v>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-2.52</v>
+        <v>0.23</v>
       </c>
       <c r="M46" t="n">
-        <v>218.5</v>
+        <v>213</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>124.5</v>
+        <v>123.5</v>
       </c>
       <c r="F47" t="n">
-        <v>20.24</v>
+        <v>20.08</v>
       </c>
       <c r="G47" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.63</v>
+        <v>-0.8</v>
       </c>
       <c r="M47" t="n">
-        <v>122.5</v>
+        <v>124.5</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4249,13 +4249,13 @@
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>232.5</v>
+        <v>236</v>
       </c>
       <c r="F48" t="n">
-        <v>25.47</v>
+        <v>25.85</v>
       </c>
       <c r="G48" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-2.31</v>
+        <v>1.51</v>
       </c>
       <c r="M48" t="n">
-        <v>238</v>
+        <v>232.5</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4323,21 +4323,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E49" t="n">
-        <v>760</v>
+        <v>519</v>
       </c>
       <c r="F49" t="n">
-        <v>27.56</v>
+        <v>20.14</v>
       </c>
       <c r="G49" t="n">
-        <v>7.77</v>
+        <v>5.55</v>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="n">
-        <v>27</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
@@ -4345,10 +4343,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.47</v>
+        <v>2.57</v>
       </c>
       <c r="M49" t="n">
-        <v>749</v>
+        <v>506</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4357,23 +4355,23 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>31.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q49" t="n">
         <v>1.5</v>
       </c>
       <c r="R49" t="n">
-        <v>3.8</v>
+        <v>-6.1</v>
       </c>
       <c r="S49" t="n">
-        <v>21.9</v>
+        <v>730.1</v>
       </c>
       <c r="T49" t="n">
-        <v>32.2</v>
+        <v>45.2</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
@@ -4390,12 +4388,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4404,20 +4402,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>110</v>
+        <v>760</v>
       </c>
       <c r="F50" t="n">
-        <v>20.52</v>
+        <v>27.56</v>
       </c>
       <c r="G50" t="n">
-        <v>2.55</v>
+        <v>7.77</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>186.3</v>
+        <v>27</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4426,10 +4424,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>110.5</v>
+        <v>760</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4438,28 +4436,28 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>10.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="R50" t="n">
-        <v>-3.4</v>
+        <v>3.8</v>
       </c>
       <c r="S50" t="n">
-        <v>37</v>
+        <v>21.9</v>
       </c>
       <c r="T50" t="n">
-        <v>35.8</v>
+        <v>32.2</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4471,12 +4469,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4485,20 +4483,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>6020</v>
+        <v>114.5</v>
       </c>
       <c r="F51" t="n">
-        <v>32.02</v>
+        <v>21.36</v>
       </c>
       <c r="G51" t="n">
-        <v>4.11</v>
+        <v>2.65</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>186.3</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4507,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-3.6</v>
+        <v>4.09</v>
       </c>
       <c r="M51" t="n">
-        <v>6245</v>
+        <v>110</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4519,28 +4517,28 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="R51" t="n">
-        <v>6.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S51" t="n">
-        <v>41.8</v>
+        <v>37</v>
       </c>
       <c r="T51" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4552,71 +4550,73 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>544</v>
+        <v>5945</v>
       </c>
       <c r="F52" t="n">
-        <v>24.64</v>
+        <v>31.62</v>
       </c>
       <c r="G52" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H52" t="n">
-        <v>29.3</v>
-      </c>
+        <v>4.06</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.87</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-3.72</v>
+        <v>-1.25</v>
       </c>
       <c r="M52" t="n">
-        <v>565</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+        <v>6020</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>毛利壓歷史低檔</t>
+        </is>
+      </c>
       <c r="P52" t="n">
-        <v>19.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.94</v>
+        <v>1.21</v>
       </c>
       <c r="R52" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="S52" t="n">
-        <v>64.90000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="T52" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.87</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4624,19 +4624,19 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4645,25 +4645,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>713</v>
+        <v>585</v>
       </c>
       <c r="F53" t="n">
-        <v>43.74</v>
+        <v>26.49</v>
       </c>
       <c r="G53" t="n">
-        <v>5.87</v>
+        <v>7.22</v>
       </c>
       <c r="H53" t="n">
-        <v>46.1</v>
+        <v>29.3</v>
       </c>
       <c r="I53" t="n">
-        <v>30.6</v>
+        <v>18.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4671,78 +4671,78 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.15</v>
+        <v>7.54</v>
       </c>
       <c r="M53" t="n">
-        <v>698</v>
+        <v>544</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R53" t="n">
-        <v>24.8</v>
+        <v>10.6</v>
       </c>
       <c r="S53" t="n">
-        <v>1.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>60.2</v>
+        <v>34.7</v>
       </c>
       <c r="U53" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E54" t="n">
-        <v>58.3</v>
+        <v>707</v>
       </c>
       <c r="F54" t="n">
-        <v>16.02</v>
+        <v>43.37</v>
       </c>
       <c r="G54" t="n">
-        <v>2.44</v>
+        <v>5.82</v>
       </c>
       <c r="H54" t="n">
-        <v>17.3</v>
+        <v>46.1</v>
       </c>
       <c r="I54" t="n">
-        <v>11.8</v>
+        <v>30.6</v>
       </c>
       <c r="J54" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4750,30 +4750,30 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="M54" t="n">
-        <v>58.8</v>
+        <v>713</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>11.3</v>
+        <v>15.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="R54" t="n">
-        <v>4.4</v>
+        <v>24.8</v>
       </c>
       <c r="S54" t="n">
-        <v>768.2</v>
+        <v>1.5</v>
       </c>
       <c r="T54" t="n">
-        <v>19.4</v>
+        <v>60.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4803,25 +4803,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>177.5</v>
+        <v>59.2</v>
       </c>
       <c r="F55" t="n">
-        <v>16.21</v>
+        <v>16.26</v>
       </c>
       <c r="G55" t="n">
-        <v>1.76</v>
+        <v>2.47</v>
       </c>
       <c r="H55" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="I55" t="n">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="J55" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4829,34 +4829,34 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.84</v>
+        <v>1.54</v>
       </c>
       <c r="M55" t="n">
-        <v>179</v>
+        <v>58.3</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.03</v>
+        <v>1.15</v>
       </c>
       <c r="R55" t="n">
-        <v>30.2</v>
+        <v>4.4</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>768.2</v>
       </c>
       <c r="T55" t="n">
-        <v>16.9</v>
+        <v>19.4</v>
       </c>
       <c r="U55" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -4868,89 +4868,91 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>344.5</v>
+        <v>177</v>
       </c>
       <c r="F56" t="n">
-        <v>17.84</v>
+        <v>16.16</v>
       </c>
       <c r="G56" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>1.76</v>
+      </c>
+      <c r="H56" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I56" t="n">
-        <v>49</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.62</v>
+        <v>-0.28</v>
       </c>
       <c r="M56" t="n">
-        <v>339</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>177.5</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.09</v>
+        <v>4.03</v>
       </c>
       <c r="R56" t="n">
-        <v>24.2</v>
+        <v>30.2</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>24</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4959,20 +4961,20 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>167</v>
+        <v>349</v>
       </c>
       <c r="F57" t="n">
-        <v>18.79</v>
+        <v>18.07</v>
       </c>
       <c r="G57" t="n">
-        <v>3.96</v>
+        <v>5.12</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>57.1</v>
+        <v>49</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4981,10 +4983,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.6</v>
+        <v>1.31</v>
       </c>
       <c r="M57" t="n">
-        <v>166</v>
+        <v>344.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4993,24 +4995,24 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>18.6</v>
+        <v>29.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="R57" t="n">
-        <v>11.1</v>
+        <v>24.2</v>
       </c>
       <c r="S57" t="n">
-        <v>3.6</v>
+        <v>25</v>
       </c>
       <c r="T57" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5022,34 +5024,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>88.7</v>
+        <v>168</v>
       </c>
       <c r="F58" t="n">
-        <v>16.93</v>
+        <v>18.9</v>
       </c>
       <c r="G58" t="n">
-        <v>1.73</v>
+        <v>3.99</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>11.3</v>
+        <v>57.1</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5058,35 +5060,31 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-0.45</v>
+        <v>0.6</v>
       </c>
       <c r="M58" t="n">
-        <v>89.09999999999999</v>
+        <v>167</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>9.5</v>
+        <v>18.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.99</v>
+        <v>2.74</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="S58" t="n">
-        <v>-2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T58" t="n">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
@@ -5103,12 +5101,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5117,20 +5115,20 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>154</v>
+        <v>91.5</v>
       </c>
       <c r="F59" t="n">
-        <v>17.17</v>
+        <v>17.46</v>
       </c>
       <c r="G59" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5139,10 +5137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-0.65</v>
+        <v>3.16</v>
       </c>
       <c r="M59" t="n">
-        <v>155</v>
+        <v>88.7</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5151,23 +5149,23 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>ROE5低</t>
+          <t>月營收轉負-3%</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>5.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="R59" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>14.6</v>
+        <v>-2.7</v>
       </c>
       <c r="T59" t="n">
-        <v>34.2</v>
+        <v>20.3</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
@@ -5184,12 +5182,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5198,20 +5196,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>243</v>
+        <v>157.5</v>
       </c>
       <c r="F60" t="n">
-        <v>15.1</v>
+        <v>17.56</v>
       </c>
       <c r="G60" t="n">
-        <v>5.49</v>
+        <v>1.73</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5220,36 +5218,40 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M60" t="n">
-        <v>243</v>
+        <v>154</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P60" t="n">
-        <v>30.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="R60" t="n">
-        <v>20.4</v>
+        <v>22.1</v>
       </c>
       <c r="S60" t="n">
-        <v>812.4</v>
+        <v>14.6</v>
       </c>
       <c r="T60" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5261,12 +5263,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5275,20 +5277,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>185.5</v>
+        <v>243.5</v>
       </c>
       <c r="F61" t="n">
-        <v>15.65</v>
+        <v>15.13</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86</v>
+        <v>5.5</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>49.2</v>
+        <v>9.6</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -5297,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.09</v>
+        <v>0.21</v>
       </c>
       <c r="M61" t="n">
-        <v>183.5</v>
+        <v>243</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5309,24 +5311,24 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>14.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>20.4</v>
       </c>
       <c r="S61" t="n">
-        <v>10.3</v>
+        <v>812.4</v>
       </c>
       <c r="T61" t="n">
-        <v>20.2</v>
+        <v>34.6</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5338,12 +5340,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5352,20 +5354,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>779</v>
+        <v>185</v>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>15.61</v>
       </c>
       <c r="G62" t="n">
-        <v>14.52</v>
+        <v>1.86</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>-8.1</v>
+        <v>49.2</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5374,35 +5376,31 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.37</v>
+        <v>-0.27</v>
       </c>
       <c r="M62" t="n">
-        <v>761</v>
+        <v>185.5</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>94.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="R62" t="n">
-        <v>18.2</v>
+        <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="T62" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
@@ -5419,33 +5417,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>506</v>
+        <v>788</v>
       </c>
       <c r="F63" t="n">
-        <v>19.64</v>
+        <v>18.21</v>
       </c>
       <c r="G63" t="n">
-        <v>5.41</v>
+        <v>14.69</v>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>-8.1</v>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.6</v>
+        <v>1.16</v>
       </c>
       <c r="M63" t="n">
-        <v>503</v>
+        <v>779</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>17.9</v>
+        <v>94.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="R63" t="n">
-        <v>-6.1</v>
+        <v>18.2</v>
       </c>
       <c r="S63" t="n">
-        <v>730.1</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>45.2</v>
+        <v>19.6</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>174</v>
+        <v>179.5</v>
       </c>
       <c r="F64" t="n">
-        <v>19.18</v>
+        <v>19.79</v>
       </c>
       <c r="G64" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.46</v>
+        <v>3.16</v>
       </c>
       <c r="M64" t="n">
-        <v>171.5</v>
+        <v>174</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="F65" t="n">
-        <v>12.4</v>
+        <v>12.44</v>
       </c>
       <c r="G65" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.03</v>
+        <v>0.4</v>
       </c>
       <c r="M65" t="n">
-        <v>49.2</v>
+        <v>50.2</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="F66" t="n">
-        <v>16.65</v>
+        <v>16.49</v>
       </c>
       <c r="G66" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="M66" t="n">
-        <v>157</v>
+        <v>158.5</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="F67" t="n">
-        <v>20.21</v>
+        <v>20.77</v>
       </c>
       <c r="G67" t="n">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.37</v>
+        <v>2.78</v>
       </c>
       <c r="M67" t="n">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>118.5</v>
+        <v>118</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F69" t="n">
-        <v>26.97</v>
+        <v>27.56</v>
       </c>
       <c r="G69" t="n">
-        <v>6.93</v>
+        <v>7.09</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.31</v>
+        <v>2.19</v>
       </c>
       <c r="M69" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>82.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>14.49</v>
+        <v>14.58</v>
       </c>
       <c r="G70" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="M70" t="n">
-        <v>82.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F71" t="n">
-        <v>18.25</v>
+        <v>18.94</v>
       </c>
       <c r="G71" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.16</v>
+        <v>3.82</v>
       </c>
       <c r="M71" t="n">
-        <v>129.5</v>
+        <v>131</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>250.5</v>
+        <v>251.5</v>
       </c>
       <c r="F72" t="n">
-        <v>16.51</v>
+        <v>16.58</v>
       </c>
       <c r="G72" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M72" t="n">
         <v>250.5</v>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="F73" t="n">
-        <v>47.65</v>
+        <v>48.07</v>
       </c>
       <c r="G73" t="n">
-        <v>25.45</v>
+        <v>25.67</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.35</v>
+        <v>0.89</v>
       </c>
       <c r="M73" t="n">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="F74" t="n">
-        <v>19.1</v>
+        <v>19.19</v>
       </c>
       <c r="G74" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.17</v>
+        <v>0.51</v>
       </c>
       <c r="M74" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3400</v>
+        <v>3435</v>
       </c>
       <c r="F75" t="n">
-        <v>45.32</v>
+        <v>45.79</v>
       </c>
       <c r="G75" t="n">
-        <v>24.19</v>
+        <v>24.44</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-4.36</v>
+        <v>1.03</v>
       </c>
       <c r="M75" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="F76" t="n">
-        <v>14.75</v>
+        <v>15.23</v>
       </c>
       <c r="G76" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-2.79</v>
+        <v>3.28</v>
       </c>
       <c r="M76" t="n">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2475</v>
+        <v>2480</v>
       </c>
       <c r="F77" t="n">
-        <v>28.69</v>
+        <v>28.75</v>
       </c>
       <c r="G77" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M77" t="n">
         <v>2475</v>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>117.5</v>
+        <v>120</v>
       </c>
       <c r="F78" t="n">
-        <v>16.76</v>
+        <v>17.12</v>
       </c>
       <c r="G78" t="n">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-2.08</v>
+        <v>2.13</v>
       </c>
       <c r="M78" t="n">
-        <v>120</v>
+        <v>117.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="F79" t="n">
-        <v>13.61</v>
+        <v>13.68</v>
       </c>
       <c r="G79" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.45</v>
+        <v>0.45</v>
       </c>
       <c r="M79" t="n">
-        <v>110.5</v>
+        <v>110</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="F80" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="G80" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="M80" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="F81" t="n">
-        <v>12.15</v>
+        <v>12.1</v>
       </c>
       <c r="G81" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M81" t="n">
         <v>105.5</v>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F82" t="n">
-        <v>12.76</v>
+        <v>12.83</v>
       </c>
       <c r="G82" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>41.5</v>
+        <v>42.85</v>
       </c>
       <c r="F83" t="n">
-        <v>8.74</v>
+        <v>9.02</v>
       </c>
       <c r="G83" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.19</v>
+        <v>3.25</v>
       </c>
       <c r="M83" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>877</v>
+        <v>836</v>
       </c>
       <c r="F84" t="n">
-        <v>22.99</v>
+        <v>21.91</v>
       </c>
       <c r="G84" t="n">
-        <v>8.81</v>
+        <v>8.4</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-2.23</v>
+        <v>-4.68</v>
       </c>
       <c r="M84" t="n">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F85" t="n">
-        <v>22.32</v>
+        <v>22.49</v>
       </c>
       <c r="G85" t="n">
-        <v>4.92</v>
+        <v>4.95</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-3.16</v>
+        <v>0.77</v>
       </c>
       <c r="M85" t="n">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>163.5</v>
+        <v>160.5</v>
       </c>
       <c r="F86" t="n">
-        <v>17.58</v>
+        <v>17.26</v>
       </c>
       <c r="G86" t="n">
-        <v>4.44</v>
+        <v>4.36</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-2.1</v>
+        <v>-1.83</v>
       </c>
       <c r="M86" t="n">
-        <v>167</v>
+        <v>163.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.35</v>
+        <v>38.95</v>
       </c>
       <c r="F87" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.78</v>
+        <v>1.56</v>
       </c>
       <c r="M87" t="n">
-        <v>38.65</v>
+        <v>38.35</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1810</v>
+        <v>1775</v>
       </c>
       <c r="F88" t="n">
-        <v>28.44</v>
+        <v>27.89</v>
       </c>
       <c r="G88" t="n">
-        <v>14.65</v>
+        <v>14.37</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-4.49</v>
+        <v>-1.93</v>
       </c>
       <c r="M88" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1630</v>
+        <v>1530</v>
       </c>
       <c r="F89" t="n">
-        <v>37.59</v>
+        <v>35.29</v>
       </c>
       <c r="G89" t="n">
-        <v>11.44</v>
+        <v>10.74</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-4.68</v>
+        <v>-6.13</v>
       </c>
       <c r="M89" t="n">
-        <v>1710</v>
+        <v>1630</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,10 +7589,10 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="F90" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="G90" t="n">
         <v>2.14</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.78</v>
+        <v>0.11</v>
       </c>
       <c r="M90" t="n">
-        <v>89.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>55.3</v>
+        <v>55.4</v>
       </c>
       <c r="F91" t="n">
-        <v>8.33</v>
+        <v>8.34</v>
       </c>
       <c r="G91" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-1.6</v>
+        <v>0.18</v>
       </c>
       <c r="M91" t="n">
-        <v>56.2</v>
+        <v>55.3</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>53.4</v>
+        <v>54.4</v>
       </c>
       <c r="F92" t="n">
-        <v>7.41</v>
+        <v>7.55</v>
       </c>
       <c r="G92" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.19</v>
+        <v>1.87</v>
       </c>
       <c r="M92" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>336.5</v>
+        <v>333.5</v>
       </c>
       <c r="F93" t="n">
-        <v>14.66</v>
+        <v>14.53</v>
       </c>
       <c r="G93" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.59</v>
+        <v>-0.89</v>
       </c>
       <c r="M93" t="n">
-        <v>338.5</v>
+        <v>336.5</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="F94" t="n">
-        <v>6.73</v>
+        <v>6.7</v>
       </c>
       <c r="G94" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-0.71</v>
+        <v>-0.48</v>
       </c>
       <c r="M94" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>185.5</v>
+        <v>184.5</v>
       </c>
       <c r="F95" t="n">
-        <v>14.73</v>
+        <v>14.65</v>
       </c>
       <c r="G95" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.54</v>
+        <v>-0.54</v>
       </c>
       <c r="M95" t="n">
-        <v>184.5</v>
+        <v>185.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="F96" t="n">
-        <v>15.73</v>
+        <v>15.57</v>
       </c>
       <c r="G96" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-0.34</v>
+        <v>-1.02</v>
       </c>
       <c r="M96" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,7 +8170,7 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F97" t="n">
         <v>4.88</v>
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.57</v>
+        <v>-0.14</v>
       </c>
       <c r="M97" t="n">
-        <v>70.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>377</v>
+        <v>377.5</v>
       </c>
       <c r="F98" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="G98" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-0.26</v>
+        <v>0.13</v>
       </c>
       <c r="M98" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>23.45</v>
+        <v>23.3</v>
       </c>
       <c r="F99" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="G99" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-0.21</v>
+        <v>-0.64</v>
       </c>
       <c r="M99" t="n">
-        <v>23.5</v>
+        <v>23.45</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>33.4</v>
+        <v>33.45</v>
       </c>
       <c r="F100" t="n">
         <v>3.6</v>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-1.91</v>
+        <v>0.15</v>
       </c>
       <c r="M100" t="n">
-        <v>34.05</v>
+        <v>33.4</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>199.5</v>
+        <v>202</v>
       </c>
       <c r="F101" t="n">
-        <v>4.96</v>
+        <v>5.02</v>
       </c>
       <c r="G101" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-0.25</v>
+        <v>1.25</v>
       </c>
       <c r="M101" t="n">
-        <v>200</v>
+        <v>199.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3400</v>
+        <v>3435</v>
       </c>
       <c r="F2" t="n">
-        <v>45.32</v>
+        <v>45.79</v>
       </c>
       <c r="G2" t="n">
-        <v>24.19</v>
+        <v>24.44</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-4.36</v>
+        <v>1.03</v>
       </c>
       <c r="M2" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="F3" t="n">
-        <v>14.75</v>
+        <v>15.23</v>
       </c>
       <c r="G3" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-2.79</v>
+        <v>3.28</v>
       </c>
       <c r="M3" t="n">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2475</v>
+        <v>2480</v>
       </c>
       <c r="F4" t="n">
-        <v>28.69</v>
+        <v>28.75</v>
       </c>
       <c r="G4" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
         <v>2475</v>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>117.5</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>16.76</v>
+        <v>17.12</v>
       </c>
       <c r="G5" t="n">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.08</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>120</v>
+        <v>117.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.61</v>
+        <v>13.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.45</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>110.5</v>
+        <v>110</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="F7" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>12.15</v>
+        <v>12.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M8" t="n">
         <v>105.5</v>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F9" t="n">
-        <v>12.76</v>
+        <v>12.83</v>
       </c>
       <c r="G9" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>42.85</v>
       </c>
       <c r="F10" t="n">
-        <v>8.74</v>
+        <v>9.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.19</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>877</v>
+        <v>836</v>
       </c>
       <c r="F11" t="n">
-        <v>22.99</v>
+        <v>21.91</v>
       </c>
       <c r="G11" t="n">
-        <v>8.81</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.23</v>
+        <v>-4.68</v>
       </c>
       <c r="M11" t="n">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F12" t="n">
-        <v>22.32</v>
+        <v>22.49</v>
       </c>
       <c r="G12" t="n">
-        <v>4.92</v>
+        <v>4.95</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-3.16</v>
+        <v>0.77</v>
       </c>
       <c r="M12" t="n">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>163.5</v>
+        <v>160.5</v>
       </c>
       <c r="F13" t="n">
-        <v>17.58</v>
+        <v>17.26</v>
       </c>
       <c r="G13" t="n">
-        <v>4.44</v>
+        <v>4.36</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-2.1</v>
+        <v>-1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>167</v>
+        <v>163.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.35</v>
+        <v>38.95</v>
       </c>
       <c r="F14" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.78</v>
+        <v>1.56</v>
       </c>
       <c r="M14" t="n">
-        <v>38.65</v>
+        <v>38.35</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1810</v>
+        <v>1775</v>
       </c>
       <c r="F15" t="n">
-        <v>28.44</v>
+        <v>27.89</v>
       </c>
       <c r="G15" t="n">
-        <v>14.65</v>
+        <v>14.37</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-4.49</v>
+        <v>-1.93</v>
       </c>
       <c r="M15" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1630</v>
+        <v>1530</v>
       </c>
       <c r="F16" t="n">
-        <v>37.59</v>
+        <v>35.29</v>
       </c>
       <c r="G16" t="n">
-        <v>11.44</v>
+        <v>10.74</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-4.68</v>
+        <v>-6.13</v>
       </c>
       <c r="M16" t="n">
-        <v>1710</v>
+        <v>1630</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,10 +9895,10 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="F17" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="G17" t="n">
         <v>2.14</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.78</v>
+        <v>0.11</v>
       </c>
       <c r="M17" t="n">
-        <v>89.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>55.3</v>
+        <v>55.4</v>
       </c>
       <c r="F18" t="n">
-        <v>8.33</v>
+        <v>8.34</v>
       </c>
       <c r="G18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.6</v>
+        <v>0.18</v>
       </c>
       <c r="M18" t="n">
-        <v>56.2</v>
+        <v>55.3</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>53.4</v>
+        <v>54.4</v>
       </c>
       <c r="F19" t="n">
-        <v>7.41</v>
+        <v>7.55</v>
       </c>
       <c r="G19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.19</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>336.5</v>
+        <v>333.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.66</v>
+        <v>14.53</v>
       </c>
       <c r="G20" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.59</v>
+        <v>-0.89</v>
       </c>
       <c r="M20" t="n">
-        <v>338.5</v>
+        <v>336.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="F21" t="n">
-        <v>6.73</v>
+        <v>6.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-0.71</v>
+        <v>-0.48</v>
       </c>
       <c r="M21" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>185.5</v>
+        <v>184.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.73</v>
+        <v>14.65</v>
       </c>
       <c r="G22" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.54</v>
+        <v>-0.54</v>
       </c>
       <c r="M22" t="n">
-        <v>184.5</v>
+        <v>185.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="F23" t="n">
-        <v>15.73</v>
+        <v>15.57</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.34</v>
+        <v>-1.02</v>
       </c>
       <c r="M23" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="F2" t="n">
-        <v>16.65</v>
+        <v>16.49</v>
       </c>
       <c r="G2" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>157</v>
+        <v>158.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="F3" t="n">
-        <v>20.21</v>
+        <v>20.77</v>
       </c>
       <c r="G3" t="n">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.37</v>
+        <v>2.78</v>
       </c>
       <c r="M3" t="n">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>118.5</v>
+        <v>118</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F5" t="n">
-        <v>26.97</v>
+        <v>27.56</v>
       </c>
       <c r="G5" t="n">
-        <v>6.93</v>
+        <v>7.09</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.31</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>14.49</v>
+        <v>14.58</v>
       </c>
       <c r="G6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>82.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F7" t="n">
-        <v>18.25</v>
+        <v>18.94</v>
       </c>
       <c r="G7" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.16</v>
+        <v>3.82</v>
       </c>
       <c r="M7" t="n">
-        <v>129.5</v>
+        <v>131</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>250.5</v>
+        <v>251.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.51</v>
+        <v>16.58</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
         <v>250.5</v>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="F9" t="n">
-        <v>47.65</v>
+        <v>48.07</v>
       </c>
       <c r="G9" t="n">
-        <v>25.45</v>
+        <v>25.67</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>0.89</v>
       </c>
       <c r="M9" t="n">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.1</v>
+        <v>19.19</v>
       </c>
       <c r="G10" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.17</v>
+        <v>0.51</v>
       </c>
       <c r="M10" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1585</v>
+        <v>1605</v>
       </c>
       <c r="F2" t="n">
-        <v>106.73</v>
+        <v>108.08</v>
       </c>
       <c r="G2" t="n">
-        <v>28.78</v>
+        <v>29.14</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.59</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.85</v>
+        <v>40.9</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11643,7 +11643,7 @@
         <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5185</v>
+        <v>5125</v>
       </c>
       <c r="F5" t="n">
-        <v>111.03</v>
+        <v>109.74</v>
       </c>
       <c r="G5" t="n">
-        <v>31.94</v>
+        <v>31.57</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-4.25</v>
+        <v>-1.16</v>
       </c>
       <c r="M5" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>121</v>
+        <v>119.5</v>
       </c>
       <c r="F6" t="n">
-        <v>22.87</v>
+        <v>22.59</v>
       </c>
       <c r="G6" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.22</v>
+        <v>-1.24</v>
       </c>
       <c r="M6" t="n">
-        <v>122.5</v>
+        <v>121</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="M7" t="n">
         <v>102</v>
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F8" t="n">
-        <v>21.94</v>
+        <v>22.07</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M8" t="n">
         <v>172</v>
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.43</v>
+        <v>25.18</v>
       </c>
       <c r="G9" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>155.5</v>
+        <v>158.5</v>
       </c>
       <c r="F10" t="n">
-        <v>17.61</v>
+        <v>17.95</v>
       </c>
       <c r="G10" t="n">
-        <v>6.24</v>
+        <v>6.36</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.96</v>
+        <v>1.93</v>
       </c>
       <c r="M10" t="n">
-        <v>157</v>
+        <v>155.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="F11" t="n">
-        <v>23.25</v>
+        <v>23.05</v>
       </c>
       <c r="G11" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="M11" t="n">
         <v>1210</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>164.5</v>
+        <v>167.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>281</v>
+        <v>279.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.87</v>
+        <v>32.69</v>
       </c>
       <c r="G13" t="n">
-        <v>6.66</v>
+        <v>6.62</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-2.09</v>
+        <v>-0.53</v>
       </c>
       <c r="M13" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.29</v>
+        <v>28.19</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>212</v>
+        <v>212.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.1</v>
+        <v>19.14</v>
       </c>
       <c r="G15" t="n">
-        <v>5.38</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.24</v>
+        <v>0.24</v>
       </c>
       <c r="M15" t="n">
-        <v>212.5</v>
+        <v>212</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7925</v>
+        <v>8040</v>
       </c>
       <c r="F16" t="n">
-        <v>203.15</v>
+        <v>206.1</v>
       </c>
       <c r="G16" t="n">
-        <v>78.87</v>
+        <v>80.02</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-7.04</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1835</v>
+        <v>1890</v>
       </c>
       <c r="F2" t="n">
-        <v>58.4</v>
+        <v>60.15</v>
       </c>
       <c r="G2" t="n">
-        <v>16.23</v>
+        <v>16.72</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.93</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="F3" t="n">
-        <v>20.24</v>
+        <v>20.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.72</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>6895</v>
+        <v>6800</v>
       </c>
       <c r="F4" t="n">
-        <v>155.61</v>
+        <v>153.46</v>
       </c>
       <c r="G4" t="n">
-        <v>42.91</v>
+        <v>42.32</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.36</v>
+        <v>-1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4920</v>
+        <v>4935</v>
       </c>
       <c r="F5" t="n">
-        <v>76.94</v>
+        <v>77.17</v>
       </c>
       <c r="G5" t="n">
-        <v>30.22</v>
+        <v>30.31</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.57</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="F6" t="n">
-        <v>45.03</v>
+        <v>45.35</v>
       </c>
       <c r="G6" t="n">
-        <v>23.61</v>
+        <v>23.78</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.57</v>
+        <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.92</v>
+        <v>11.93</v>
       </c>
       <c r="G7" t="n">
         <v>1.67</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
         <v>97</v>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>11.81</v>
+        <v>11.77</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="M8" t="n">
         <v>153.5</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="F10" t="n">
-        <v>23.86</v>
+        <v>24.08</v>
       </c>
       <c r="G10" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.11</v>
+        <v>0.91</v>
       </c>
       <c r="M10" t="n">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>194</v>
+        <v>197.5</v>
       </c>
       <c r="F11" t="n">
-        <v>26.72</v>
+        <v>27.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.02</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3685</v>
+        <v>3740</v>
       </c>
       <c r="F12" t="n">
-        <v>54.05</v>
+        <v>54.85</v>
       </c>
       <c r="G12" t="n">
-        <v>5.27</v>
+        <v>5.34</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-2.25</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
-        <v>3770</v>
+        <v>3685</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1605</v>
+        <v>1565</v>
       </c>
       <c r="F2" t="n">
-        <v>108.08</v>
+        <v>105.39</v>
       </c>
       <c r="G2" t="n">
-        <v>29.14</v>
+        <v>28.42</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>-2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1585</v>
+        <v>1605</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>16.94</v>
       </c>
       <c r="G4" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5125</v>
+        <v>5030</v>
       </c>
       <c r="F5" t="n">
-        <v>109.74</v>
+        <v>107.71</v>
       </c>
       <c r="G5" t="n">
-        <v>31.57</v>
+        <v>30.99</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.16</v>
+        <v>-1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>5185</v>
+        <v>5125</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>119.5</v>
+        <v>122</v>
       </c>
       <c r="F6" t="n">
-        <v>22.59</v>
+        <v>23.06</v>
       </c>
       <c r="G6" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.24</v>
+        <v>2.09</v>
       </c>
       <c r="M6" t="n">
-        <v>121</v>
+        <v>119.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F8" t="n">
-        <v>22.07</v>
+        <v>22.19</v>
       </c>
       <c r="G8" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1065,7 +1065,7 @@
         <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>25.18</v>
+        <v>25.55</v>
       </c>
       <c r="G9" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.96</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158.5</v>
+        <v>164</v>
       </c>
       <c r="F10" t="n">
-        <v>17.95</v>
+        <v>18.57</v>
       </c>
       <c r="G10" t="n">
-        <v>6.36</v>
+        <v>6.58</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.93</v>
+        <v>3.47</v>
       </c>
       <c r="M10" t="n">
-        <v>155.5</v>
+        <v>158.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F11" t="n">
-        <v>23.05</v>
+        <v>22.77</v>
       </c>
       <c r="G11" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.83</v>
+        <v>-1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>279.5</v>
+        <v>284.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.69</v>
+        <v>33.27</v>
       </c>
       <c r="G13" t="n">
-        <v>6.62</v>
+        <v>6.74</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.53</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
-        <v>281</v>
+        <v>279.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>143.5</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.19</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>212</v>
+        <v>212.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8040</v>
+        <v>7900</v>
       </c>
       <c r="F16" t="n">
-        <v>206.1</v>
+        <v>202.51</v>
       </c>
       <c r="G16" t="n">
-        <v>80.02</v>
+        <v>78.62</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>-1.74</v>
       </c>
       <c r="M16" t="n">
-        <v>7925</v>
+        <v>8040</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1490</v>
+        <v>1480</v>
       </c>
       <c r="F17" t="n">
-        <v>44.08</v>
+        <v>43.79</v>
       </c>
       <c r="G17" t="n">
-        <v>8.949999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1792,7 +1792,7 @@
         <v>-0.67</v>
       </c>
       <c r="M17" t="n">
-        <v>1500</v>
+        <v>1490</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12055</v>
+        <v>11835</v>
       </c>
       <c r="F18" t="n">
-        <v>66.45999999999999</v>
+        <v>65.25</v>
       </c>
       <c r="G18" t="n">
-        <v>34.03</v>
+        <v>33.41</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-0.5</v>
+        <v>-1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>12115</v>
+        <v>12055</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>963</v>
+        <v>1000</v>
       </c>
       <c r="F19" t="n">
-        <v>81.89</v>
+        <v>85.03</v>
       </c>
       <c r="G19" t="n">
-        <v>15.89</v>
+        <v>16.5</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.73</v>
+        <v>3.84</v>
       </c>
       <c r="M19" t="n">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>44.51</v>
+        <v>44.18</v>
       </c>
       <c r="G20" t="n">
-        <v>6.66</v>
+        <v>6.61</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.62</v>
+        <v>-0.74</v>
       </c>
       <c r="M20" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5930</v>
+        <v>5770</v>
       </c>
       <c r="F21" t="n">
-        <v>97.09</v>
+        <v>94.47</v>
       </c>
       <c r="G21" t="n">
-        <v>25.07</v>
+        <v>24.39</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.49</v>
+        <v>-2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>5675</v>
+        <v>5930</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2135</v>
+        <v>2080</v>
       </c>
       <c r="F22" t="n">
-        <v>54.46</v>
+        <v>53.06</v>
       </c>
       <c r="G22" t="n">
-        <v>27.41</v>
+        <v>26.71</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.29</v>
+        <v>-2.58</v>
       </c>
       <c r="M22" t="n">
-        <v>2185</v>
+        <v>2135</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.65</v>
+        <v>18.35</v>
       </c>
       <c r="F23" t="n">
-        <v>42.39</v>
+        <v>41.7</v>
       </c>
       <c r="G23" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>-1.61</v>
       </c>
       <c r="M23" t="n">
-        <v>18.3</v>
+        <v>18.65</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="F24" t="n">
-        <v>77.2</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>18.84</v>
+        <v>19.02</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.36</v>
+        <v>0.99</v>
       </c>
       <c r="M24" t="n">
-        <v>1485</v>
+        <v>1520</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>68.7</v>
+        <v>61.9</v>
       </c>
       <c r="F25" t="n">
-        <v>83.78</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>5.72</v>
+        <v>5.15</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-0.58</v>
+        <v>-9.9</v>
       </c>
       <c r="M25" t="n">
-        <v>69.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2695</v>
+        <v>2660</v>
       </c>
       <c r="F26" t="n">
-        <v>231.93</v>
+        <v>228.92</v>
       </c>
       <c r="G26" t="n">
-        <v>52.83</v>
+        <v>52.15</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>-1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>2650</v>
+        <v>2695</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F27" t="n">
-        <v>50.87</v>
+        <v>51.37</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94</v>
+        <v>8.02</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1215</v>
+        <v>1170</v>
       </c>
       <c r="F28" t="n">
-        <v>59.5</v>
+        <v>57.3</v>
       </c>
       <c r="G28" t="n">
-        <v>12.33</v>
+        <v>11.87</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.67</v>
+        <v>-3.7</v>
       </c>
       <c r="M28" t="n">
-        <v>1195</v>
+        <v>1215</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="F29" t="n">
-        <v>93.13</v>
+        <v>91.16</v>
       </c>
       <c r="G29" t="n">
-        <v>18.25</v>
+        <v>17.86</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.35</v>
+        <v>-2.11</v>
       </c>
       <c r="M29" t="n">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3065</v>
+        <v>3000</v>
       </c>
       <c r="F30" t="n">
-        <v>72.29000000000001</v>
+        <v>70.75</v>
       </c>
       <c r="G30" t="n">
-        <v>9.970000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-2.39</v>
+        <v>-2.12</v>
       </c>
       <c r="M30" t="n">
-        <v>3140</v>
+        <v>3065</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="F31" t="n">
-        <v>106.09</v>
+        <v>104.46</v>
       </c>
       <c r="G31" t="n">
-        <v>13.64</v>
+        <v>13.43</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-0.38</v>
+        <v>-1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F32" t="n">
-        <v>45.98</v>
+        <v>45.79</v>
       </c>
       <c r="G32" t="n">
-        <v>11.4</v>
+        <v>11.36</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.55</v>
+        <v>-0.41</v>
       </c>
       <c r="M32" t="n">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>548</v>
+        <v>602</v>
       </c>
       <c r="F33" t="n">
-        <v>36.9</v>
+        <v>40.54</v>
       </c>
       <c r="G33" t="n">
-        <v>6.37</v>
+        <v>7</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="M33" t="n">
         <v>548</v>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4920</v>
+        <v>4980</v>
       </c>
       <c r="F34" t="n">
-        <v>81.26000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="G34" t="n">
-        <v>18.51</v>
+        <v>18.74</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
+        <v>1.22</v>
       </c>
       <c r="M34" t="n">
-        <v>4910</v>
+        <v>4920</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="F35" t="n">
-        <v>60.15</v>
+        <v>60.63</v>
       </c>
       <c r="G35" t="n">
-        <v>16.72</v>
+        <v>16.85</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>0.79</v>
       </c>
       <c r="M35" t="n">
-        <v>1835</v>
+        <v>1890</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>69.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>20.5</v>
+        <v>20.32</v>
       </c>
       <c r="G36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.31</v>
+        <v>-0.86</v>
       </c>
       <c r="M36" t="n">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>6800</v>
+        <v>6875</v>
       </c>
       <c r="F37" t="n">
-        <v>153.46</v>
+        <v>155.16</v>
       </c>
       <c r="G37" t="n">
-        <v>42.32</v>
+        <v>42.78</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1.38</v>
+        <v>1.1</v>
       </c>
       <c r="M37" t="n">
-        <v>6895</v>
+        <v>6800</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>4935</v>
+        <v>4975</v>
       </c>
       <c r="F38" t="n">
-        <v>77.17</v>
+        <v>77.8</v>
       </c>
       <c r="G38" t="n">
-        <v>30.31</v>
+        <v>30.56</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>4920</v>
+        <v>4935</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="F39" t="n">
-        <v>45.35</v>
+        <v>45.03</v>
       </c>
       <c r="G39" t="n">
-        <v>23.78</v>
+        <v>23.61</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="M39" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,13 +3605,13 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F40" t="n">
-        <v>11.93</v>
+        <v>11.98</v>
       </c>
       <c r="G40" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H40" t="n">
         <v>11</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="M40" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="F42" t="n">
-        <v>15.38</v>
+        <v>15.52</v>
       </c>
       <c r="G42" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="M42" t="n">
         <v>105.5</v>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="F43" t="n">
-        <v>24.08</v>
+        <v>25.7</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71</v>
+        <v>3.96</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.91</v>
+        <v>6.74</v>
       </c>
       <c r="M43" t="n">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>194</v>
+        <v>197.5</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3740</v>
+        <v>3765</v>
       </c>
       <c r="F45" t="n">
-        <v>54.85</v>
+        <v>55.22</v>
       </c>
       <c r="G45" t="n">
-        <v>5.34</v>
+        <v>5.38</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.49</v>
+        <v>0.67</v>
       </c>
       <c r="M45" t="n">
-        <v>3685</v>
+        <v>3740</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>213.5</v>
+        <v>226</v>
       </c>
       <c r="F46" t="n">
-        <v>21.74</v>
+        <v>23.01</v>
       </c>
       <c r="G46" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.23</v>
+        <v>5.85</v>
       </c>
       <c r="M46" t="n">
-        <v>213</v>
+        <v>213.5</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="F47" t="n">
-        <v>20.08</v>
+        <v>20</v>
       </c>
       <c r="G47" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>124.5</v>
+        <v>123.5</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4249,13 +4249,13 @@
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>236</v>
+        <v>235.5</v>
       </c>
       <c r="F48" t="n">
-        <v>25.85</v>
+        <v>25.79</v>
       </c>
       <c r="G48" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.51</v>
+        <v>-0.21</v>
       </c>
       <c r="M48" t="n">
-        <v>232.5</v>
+        <v>236</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4405,13 +4405,13 @@
         <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="F50" t="n">
-        <v>27.56</v>
+        <v>27.63</v>
       </c>
       <c r="G50" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="M50" t="n">
         <v>760</v>
@@ -4486,13 +4486,13 @@
         <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>114.5</v>
+        <v>115</v>
       </c>
       <c r="F51" t="n">
-        <v>21.36</v>
+        <v>21.46</v>
       </c>
       <c r="G51" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.09</v>
+        <v>0.44</v>
       </c>
       <c r="M51" t="n">
-        <v>110</v>
+        <v>114.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>5945</v>
+        <v>6205</v>
       </c>
       <c r="F52" t="n">
-        <v>31.62</v>
+        <v>33</v>
       </c>
       <c r="G52" t="n">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.25</v>
+        <v>4.37</v>
       </c>
       <c r="M52" t="n">
-        <v>6020</v>
+        <v>5945</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F53" t="n">
-        <v>26.49</v>
+        <v>27.26</v>
       </c>
       <c r="G53" t="n">
-        <v>7.22</v>
+        <v>7.42</v>
       </c>
       <c r="H53" t="n">
         <v>29.3</v>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>7.54</v>
+        <v>2.91</v>
       </c>
       <c r="M53" t="n">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4806,13 +4806,13 @@
         <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>59.2</v>
+        <v>58.9</v>
       </c>
       <c r="F55" t="n">
-        <v>16.26</v>
+        <v>16.18</v>
       </c>
       <c r="G55" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="H55" t="n">
         <v>17.3</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.54</v>
+        <v>-0.51</v>
       </c>
       <c r="M55" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>177.5</v>
+        <v>177</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4964,13 +4964,13 @@
         <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>349</v>
+        <v>346.5</v>
       </c>
       <c r="F57" t="n">
-        <v>18.07</v>
+        <v>17.94</v>
       </c>
       <c r="G57" t="n">
-        <v>5.12</v>
+        <v>5.09</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.31</v>
+        <v>-0.72</v>
       </c>
       <c r="M57" t="n">
-        <v>344.5</v>
+        <v>349</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5041,13 +5041,13 @@
         <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>168</v>
+        <v>166.5</v>
       </c>
       <c r="F58" t="n">
-        <v>18.9</v>
+        <v>18.73</v>
       </c>
       <c r="G58" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.6</v>
+        <v>-0.89</v>
       </c>
       <c r="M58" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>91.5</v>
+        <v>93.2</v>
       </c>
       <c r="F59" t="n">
-        <v>17.46</v>
+        <v>17.79</v>
       </c>
       <c r="G59" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.16</v>
+        <v>1.86</v>
       </c>
       <c r="M59" t="n">
-        <v>88.7</v>
+        <v>91.5</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>157.5</v>
+        <v>155</v>
       </c>
       <c r="F60" t="n">
-        <v>17.56</v>
+        <v>17.28</v>
       </c>
       <c r="G60" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.27</v>
+        <v>-1.59</v>
       </c>
       <c r="M60" t="n">
-        <v>154</v>
+        <v>157.5</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5280,13 +5280,13 @@
         <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>243.5</v>
+        <v>267.5</v>
       </c>
       <c r="F61" t="n">
-        <v>15.13</v>
+        <v>16.63</v>
       </c>
       <c r="G61" t="n">
-        <v>5.5</v>
+        <v>6.04</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.21</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>243</v>
+        <v>243.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5357,10 +5357,10 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="F62" t="n">
-        <v>15.61</v>
+        <v>15.65</v>
       </c>
       <c r="G62" t="n">
         <v>1.86</v>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-0.27</v>
+        <v>0.27</v>
       </c>
       <c r="M62" t="n">
-        <v>185.5</v>
+        <v>185</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5434,13 +5434,13 @@
         <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>788</v>
+        <v>814</v>
       </c>
       <c r="F63" t="n">
-        <v>18.21</v>
+        <v>18.81</v>
       </c>
       <c r="G63" t="n">
-        <v>14.69</v>
+        <v>15.18</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.16</v>
+        <v>3.3</v>
       </c>
       <c r="M63" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>179.5</v>
+        <v>180</v>
       </c>
       <c r="F64" t="n">
-        <v>19.79</v>
+        <v>19.85</v>
       </c>
       <c r="G64" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.16</v>
+        <v>0.28</v>
       </c>
       <c r="M64" t="n">
-        <v>174</v>
+        <v>179.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="F65" t="n">
-        <v>12.44</v>
+        <v>12.4</v>
       </c>
       <c r="G65" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="M65" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="F67" t="n">
-        <v>20.77</v>
+        <v>21.22</v>
       </c>
       <c r="G67" t="n">
-        <v>4.9</v>
+        <v>5.01</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="M67" t="n">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F69" t="n">
-        <v>27.56</v>
+        <v>27.9</v>
       </c>
       <c r="G69" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.19</v>
+        <v>1.23</v>
       </c>
       <c r="M69" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>83.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>14.58</v>
+        <v>14.44</v>
       </c>
       <c r="G70" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.6</v>
+        <v>-0.96</v>
       </c>
       <c r="M70" t="n">
-        <v>82.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F71" t="n">
-        <v>18.94</v>
+        <v>19.08</v>
       </c>
       <c r="G71" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.82</v>
+        <v>0.74</v>
       </c>
       <c r="M71" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>251.5</v>
+        <v>254</v>
       </c>
       <c r="F72" t="n">
-        <v>16.58</v>
+        <v>16.74</v>
       </c>
       <c r="G72" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="M72" t="n">
-        <v>250.5</v>
+        <v>251.5</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1135</v>
+        <v>1105</v>
       </c>
       <c r="F73" t="n">
-        <v>48.07</v>
+        <v>46.8</v>
       </c>
       <c r="G73" t="n">
-        <v>25.67</v>
+        <v>24.99</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.89</v>
+        <v>-2.64</v>
       </c>
       <c r="M73" t="n">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>59.5</v>
+        <v>59.7</v>
       </c>
       <c r="F74" t="n">
-        <v>19.19</v>
+        <v>19.26</v>
       </c>
       <c r="G74" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="M74" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3435</v>
+        <v>3510</v>
       </c>
       <c r="F75" t="n">
-        <v>45.79</v>
+        <v>46.79</v>
       </c>
       <c r="G75" t="n">
-        <v>24.44</v>
+        <v>24.97</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="M75" t="n">
-        <v>3400</v>
+        <v>3435</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F76" t="n">
-        <v>15.23</v>
+        <v>15.29</v>
       </c>
       <c r="G76" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.28</v>
+        <v>0.4</v>
       </c>
       <c r="M76" t="n">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2480</v>
+        <v>2510</v>
       </c>
       <c r="F77" t="n">
-        <v>28.75</v>
+        <v>29.09</v>
       </c>
       <c r="G77" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.2</v>
+        <v>1.21</v>
       </c>
       <c r="M77" t="n">
-        <v>2475</v>
+        <v>2480</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F78" t="n">
-        <v>17.12</v>
+        <v>16.98</v>
       </c>
       <c r="G78" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.13</v>
+        <v>-0.83</v>
       </c>
       <c r="M78" t="n">
-        <v>117.5</v>
+        <v>120</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>25.3</v>
+        <v>25.15</v>
       </c>
       <c r="F80" t="n">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="G80" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.2</v>
+        <v>-0.59</v>
       </c>
       <c r="M80" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="F81" t="n">
-        <v>12.1</v>
+        <v>12.15</v>
       </c>
       <c r="G81" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M81" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>180</v>
+        <v>183.5</v>
       </c>
       <c r="F82" t="n">
-        <v>12.83</v>
+        <v>13.08</v>
       </c>
       <c r="G82" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="M82" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>42.85</v>
+        <v>42.2</v>
       </c>
       <c r="F83" t="n">
-        <v>9.02</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.25</v>
+        <v>-1.52</v>
       </c>
       <c r="M83" t="n">
-        <v>41.5</v>
+        <v>42.85</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="F84" t="n">
-        <v>21.91</v>
+        <v>22.15</v>
       </c>
       <c r="G84" t="n">
-        <v>8.4</v>
+        <v>8.49</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-4.68</v>
+        <v>1.08</v>
       </c>
       <c r="M84" t="n">
-        <v>877</v>
+        <v>836</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F85" t="n">
-        <v>22.49</v>
+        <v>22.66</v>
       </c>
       <c r="G85" t="n">
-        <v>4.95</v>
+        <v>4.99</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="M85" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>160.5</v>
+        <v>164</v>
       </c>
       <c r="F86" t="n">
-        <v>17.26</v>
+        <v>17.63</v>
       </c>
       <c r="G86" t="n">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-1.83</v>
+        <v>2.18</v>
       </c>
       <c r="M86" t="n">
-        <v>163.5</v>
+        <v>160.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.95</v>
+        <v>38.8</v>
       </c>
       <c r="F87" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.56</v>
+        <v>-0.39</v>
       </c>
       <c r="M87" t="n">
-        <v>38.35</v>
+        <v>38.95</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1775</v>
+        <v>1900</v>
       </c>
       <c r="F88" t="n">
-        <v>27.89</v>
+        <v>29.85</v>
       </c>
       <c r="G88" t="n">
-        <v>14.37</v>
+        <v>15.38</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1.93</v>
+        <v>7.04</v>
       </c>
       <c r="M88" t="n">
-        <v>1810</v>
+        <v>1775</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F89" t="n">
-        <v>35.29</v>
+        <v>35.17</v>
       </c>
       <c r="G89" t="n">
-        <v>10.74</v>
+        <v>10.7</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-6.13</v>
+        <v>-0.33</v>
       </c>
       <c r="M89" t="n">
-        <v>1630</v>
+        <v>1530</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,10 +7589,10 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>89.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>8.74</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G90" t="n">
         <v>2.14</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.11</v>
+        <v>-0.34</v>
       </c>
       <c r="M90" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,10 +7672,10 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="F91" t="n">
-        <v>8.34</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G91" t="n">
         <v>1.38</v>
@@ -7698,7 +7698,7 @@
         <v>0.18</v>
       </c>
       <c r="M91" t="n">
-        <v>55.3</v>
+        <v>55.4</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,10 +7755,10 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="F92" t="n">
-        <v>7.55</v>
+        <v>7.52</v>
       </c>
       <c r="G92" t="n">
         <v>1.16</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.87</v>
+        <v>-0.37</v>
       </c>
       <c r="M92" t="n">
-        <v>53.4</v>
+        <v>54.4</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,10 +7838,10 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>333.5</v>
+        <v>334</v>
       </c>
       <c r="F93" t="n">
-        <v>14.53</v>
+        <v>14.55</v>
       </c>
       <c r="G93" t="n">
         <v>5.28</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.89</v>
+        <v>0.15</v>
       </c>
       <c r="M93" t="n">
-        <v>336.5</v>
+        <v>333.5</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2090</v>
+        <v>2110</v>
       </c>
       <c r="F94" t="n">
-        <v>6.7</v>
+        <v>6.76</v>
       </c>
       <c r="G94" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-0.48</v>
+        <v>0.96</v>
       </c>
       <c r="M94" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>184.5</v>
+        <v>190.5</v>
       </c>
       <c r="F95" t="n">
-        <v>14.65</v>
+        <v>15.13</v>
       </c>
       <c r="G95" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-0.54</v>
+        <v>3.25</v>
       </c>
       <c r="M95" t="n">
-        <v>185.5</v>
+        <v>184.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="F96" t="n">
-        <v>15.57</v>
+        <v>15.73</v>
       </c>
       <c r="G96" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-1.02</v>
+        <v>1.03</v>
       </c>
       <c r="M96" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,10 +8170,10 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>69.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="F97" t="n">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="G97" t="n">
         <v>1.09</v>
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.14</v>
+        <v>-0.43</v>
       </c>
       <c r="M97" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>377.5</v>
+        <v>380</v>
       </c>
       <c r="F98" t="n">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="G98" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.13</v>
+        <v>0.66</v>
       </c>
       <c r="M98" t="n">
-        <v>377</v>
+        <v>377.5</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="F99" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="G99" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-0.64</v>
+        <v>-0.43</v>
       </c>
       <c r="M99" t="n">
-        <v>23.45</v>
+        <v>23.3</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>33.45</v>
+        <v>33.35</v>
       </c>
       <c r="F100" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="G100" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="M100" t="n">
-        <v>33.4</v>
+        <v>33.45</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F101" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="G101" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="M101" t="n">
-        <v>199.5</v>
+        <v>202</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3435</v>
+        <v>3510</v>
       </c>
       <c r="F2" t="n">
-        <v>45.79</v>
+        <v>46.79</v>
       </c>
       <c r="G2" t="n">
-        <v>24.44</v>
+        <v>24.97</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3400</v>
+        <v>3435</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F3" t="n">
-        <v>15.23</v>
+        <v>15.29</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.28</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2480</v>
+        <v>2510</v>
       </c>
       <c r="F4" t="n">
-        <v>28.75</v>
+        <v>29.09</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
-        <v>2475</v>
+        <v>2480</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F5" t="n">
-        <v>17.12</v>
+        <v>16.98</v>
       </c>
       <c r="G5" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>-0.83</v>
       </c>
       <c r="M5" t="n">
-        <v>117.5</v>
+        <v>120</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.3</v>
+        <v>25.15</v>
       </c>
       <c r="F7" t="n">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>-0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1</v>
+        <v>12.15</v>
       </c>
       <c r="G8" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>180</v>
+        <v>183.5</v>
       </c>
       <c r="F9" t="n">
-        <v>12.83</v>
+        <v>13.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.85</v>
+        <v>42.2</v>
       </c>
       <c r="F10" t="n">
-        <v>9.02</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>-1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>41.5</v>
+        <v>42.85</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="F11" t="n">
-        <v>21.91</v>
+        <v>22.15</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>8.49</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-4.68</v>
+        <v>1.08</v>
       </c>
       <c r="M11" t="n">
-        <v>877</v>
+        <v>836</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F12" t="n">
-        <v>22.49</v>
+        <v>22.66</v>
       </c>
       <c r="G12" t="n">
-        <v>4.95</v>
+        <v>4.99</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="M12" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>160.5</v>
+        <v>164</v>
       </c>
       <c r="F13" t="n">
-        <v>17.26</v>
+        <v>17.63</v>
       </c>
       <c r="G13" t="n">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.83</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>163.5</v>
+        <v>160.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.95</v>
+        <v>38.8</v>
       </c>
       <c r="F14" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.56</v>
+        <v>-0.39</v>
       </c>
       <c r="M14" t="n">
-        <v>38.35</v>
+        <v>38.95</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1775</v>
+        <v>1900</v>
       </c>
       <c r="F15" t="n">
-        <v>27.89</v>
+        <v>29.85</v>
       </c>
       <c r="G15" t="n">
-        <v>14.37</v>
+        <v>15.38</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.93</v>
+        <v>7.04</v>
       </c>
       <c r="M15" t="n">
-        <v>1810</v>
+        <v>1775</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F16" t="n">
-        <v>35.29</v>
+        <v>35.17</v>
       </c>
       <c r="G16" t="n">
-        <v>10.74</v>
+        <v>10.7</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-6.13</v>
+        <v>-0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1630</v>
+        <v>1530</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,10 +9895,10 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>89.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>8.74</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>2.14</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.11</v>
+        <v>-0.34</v>
       </c>
       <c r="M17" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,10 +9978,10 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="F18" t="n">
-        <v>8.34</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.38</v>
@@ -10004,7 +10004,7 @@
         <v>0.18</v>
       </c>
       <c r="M18" t="n">
-        <v>55.3</v>
+        <v>55.4</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,10 +10061,10 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="F19" t="n">
-        <v>7.55</v>
+        <v>7.52</v>
       </c>
       <c r="G19" t="n">
         <v>1.16</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>-0.37</v>
       </c>
       <c r="M19" t="n">
-        <v>53.4</v>
+        <v>54.4</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,10 +10144,10 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>333.5</v>
+        <v>334</v>
       </c>
       <c r="F20" t="n">
-        <v>14.53</v>
+        <v>14.55</v>
       </c>
       <c r="G20" t="n">
         <v>5.28</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.89</v>
+        <v>0.15</v>
       </c>
       <c r="M20" t="n">
-        <v>336.5</v>
+        <v>333.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2090</v>
+        <v>2110</v>
       </c>
       <c r="F21" t="n">
-        <v>6.7</v>
+        <v>6.76</v>
       </c>
       <c r="G21" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-0.48</v>
+        <v>0.96</v>
       </c>
       <c r="M21" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>184.5</v>
+        <v>190.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.65</v>
+        <v>15.13</v>
       </c>
       <c r="G22" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-0.54</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>185.5</v>
+        <v>184.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="F23" t="n">
-        <v>15.57</v>
+        <v>15.73</v>
       </c>
       <c r="G23" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.02</v>
+        <v>1.03</v>
       </c>
       <c r="M23" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="F3" t="n">
-        <v>20.77</v>
+        <v>21.22</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>5.01</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="M3" t="n">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F5" t="n">
-        <v>27.56</v>
+        <v>27.9</v>
       </c>
       <c r="G5" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>83.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>14.58</v>
+        <v>14.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>-0.96</v>
       </c>
       <c r="M6" t="n">
-        <v>82.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F7" t="n">
-        <v>18.94</v>
+        <v>19.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.82</v>
+        <v>0.74</v>
       </c>
       <c r="M7" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>251.5</v>
+        <v>254</v>
       </c>
       <c r="F8" t="n">
-        <v>16.58</v>
+        <v>16.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>250.5</v>
+        <v>251.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1135</v>
+        <v>1105</v>
       </c>
       <c r="F9" t="n">
-        <v>48.07</v>
+        <v>46.8</v>
       </c>
       <c r="G9" t="n">
-        <v>25.67</v>
+        <v>24.99</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.89</v>
+        <v>-2.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>59.5</v>
+        <v>59.7</v>
       </c>
       <c r="F10" t="n">
-        <v>19.19</v>
+        <v>19.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="M10" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1605</v>
+        <v>1565</v>
       </c>
       <c r="F2" t="n">
-        <v>108.08</v>
+        <v>105.39</v>
       </c>
       <c r="G2" t="n">
-        <v>29.14</v>
+        <v>28.42</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>-2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1585</v>
+        <v>1605</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>16.94</v>
       </c>
       <c r="G4" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5125</v>
+        <v>5030</v>
       </c>
       <c r="F5" t="n">
-        <v>109.74</v>
+        <v>107.71</v>
       </c>
       <c r="G5" t="n">
-        <v>31.57</v>
+        <v>30.99</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.16</v>
+        <v>-1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>5185</v>
+        <v>5125</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>119.5</v>
+        <v>122</v>
       </c>
       <c r="F6" t="n">
-        <v>22.59</v>
+        <v>23.06</v>
       </c>
       <c r="G6" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.24</v>
+        <v>2.09</v>
       </c>
       <c r="M6" t="n">
-        <v>121</v>
+        <v>119.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F8" t="n">
-        <v>22.07</v>
+        <v>22.19</v>
       </c>
       <c r="G8" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11967,7 +11967,7 @@
         <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>25.18</v>
+        <v>25.55</v>
       </c>
       <c r="G9" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.96</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>158.5</v>
+        <v>164</v>
       </c>
       <c r="F10" t="n">
-        <v>17.95</v>
+        <v>18.57</v>
       </c>
       <c r="G10" t="n">
-        <v>6.36</v>
+        <v>6.58</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.93</v>
+        <v>3.47</v>
       </c>
       <c r="M10" t="n">
-        <v>155.5</v>
+        <v>158.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F11" t="n">
-        <v>23.05</v>
+        <v>22.77</v>
       </c>
       <c r="G11" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.83</v>
+        <v>-1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>279.5</v>
+        <v>284.5</v>
       </c>
       <c r="F13" t="n">
-        <v>32.69</v>
+        <v>33.27</v>
       </c>
       <c r="G13" t="n">
-        <v>6.62</v>
+        <v>6.74</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.53</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
-        <v>281</v>
+        <v>279.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>143.5</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.19</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.35</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>212</v>
+        <v>212.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8040</v>
+        <v>7900</v>
       </c>
       <c r="F16" t="n">
-        <v>206.1</v>
+        <v>202.51</v>
       </c>
       <c r="G16" t="n">
-        <v>80.02</v>
+        <v>78.62</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>-1.74</v>
       </c>
       <c r="M16" t="n">
-        <v>7925</v>
+        <v>8040</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="F2" t="n">
-        <v>60.15</v>
+        <v>60.63</v>
       </c>
       <c r="G2" t="n">
-        <v>16.72</v>
+        <v>16.85</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0.79</v>
       </c>
       <c r="M2" t="n">
-        <v>1835</v>
+        <v>1890</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>69.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>20.5</v>
+        <v>20.32</v>
       </c>
       <c r="G3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>-0.86</v>
       </c>
       <c r="M3" t="n">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>6800</v>
+        <v>6875</v>
       </c>
       <c r="F4" t="n">
-        <v>153.46</v>
+        <v>155.16</v>
       </c>
       <c r="G4" t="n">
-        <v>42.32</v>
+        <v>42.78</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.38</v>
+        <v>1.1</v>
       </c>
       <c r="M4" t="n">
-        <v>6895</v>
+        <v>6800</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4935</v>
+        <v>4975</v>
       </c>
       <c r="F5" t="n">
-        <v>77.17</v>
+        <v>77.8</v>
       </c>
       <c r="G5" t="n">
-        <v>30.31</v>
+        <v>30.56</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>4920</v>
+        <v>4935</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="F6" t="n">
-        <v>45.35</v>
+        <v>45.03</v>
       </c>
       <c r="G6" t="n">
-        <v>23.78</v>
+        <v>23.61</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.93</v>
+        <v>11.98</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.38</v>
+        <v>15.52</v>
       </c>
       <c r="G9" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="M9" t="n">
         <v>105.5</v>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="F10" t="n">
-        <v>24.08</v>
+        <v>25.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.71</v>
+        <v>3.96</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.91</v>
+        <v>6.74</v>
       </c>
       <c r="M10" t="n">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>194</v>
+        <v>197.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3740</v>
+        <v>3765</v>
       </c>
       <c r="F12" t="n">
-        <v>54.85</v>
+        <v>55.22</v>
       </c>
       <c r="G12" t="n">
-        <v>5.34</v>
+        <v>5.38</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>0.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3685</v>
+        <v>3740</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1565</v>
+        <v>1510</v>
       </c>
       <c r="F2" t="n">
-        <v>105.39</v>
+        <v>101.68</v>
       </c>
       <c r="G2" t="n">
-        <v>28.42</v>
+        <v>27.42</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.49</v>
+        <v>-3.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1605</v>
+        <v>1565</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153</v>
+        <v>153.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.33</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5030</v>
+        <v>5310</v>
       </c>
       <c r="F5" t="n">
-        <v>107.71</v>
+        <v>113.7</v>
       </c>
       <c r="G5" t="n">
-        <v>30.99</v>
+        <v>32.71</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.85</v>
+        <v>5.57</v>
       </c>
       <c r="M5" t="n">
-        <v>5125</v>
+        <v>5030</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>119.5</v>
+        <v>122</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.49</v>
+        <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>174</v>
+        <v>173.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22.19</v>
+        <v>22.13</v>
       </c>
       <c r="G8" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.58</v>
+        <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>25.55</v>
+        <v>25.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="M9" t="n">
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>164</v>
+        <v>169.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.57</v>
+        <v>19.2</v>
       </c>
       <c r="G10" t="n">
-        <v>6.58</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>158.5</v>
+        <v>164</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F11" t="n">
-        <v>22.77</v>
+        <v>22.67</v>
       </c>
       <c r="G11" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.25</v>
+        <v>-0.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>167.5</v>
+        <v>170.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.89</v>
+        <v>21.26</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
         <v>167.5</v>
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>284.5</v>
+        <v>281.5</v>
       </c>
       <c r="F13" t="n">
-        <v>33.27</v>
+        <v>32.92</v>
       </c>
       <c r="G13" t="n">
-        <v>6.74</v>
+        <v>6.67</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>-1.05</v>
       </c>
       <c r="M13" t="n">
-        <v>279.5</v>
+        <v>284.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.68</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>143.5</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>212.5</v>
+        <v>210.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.14</v>
+        <v>18.96</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.34</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>212.5</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.74</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8040</v>
+        <v>7900</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1480</v>
+        <v>1625</v>
       </c>
       <c r="F17" t="n">
-        <v>43.79</v>
+        <v>48.08</v>
       </c>
       <c r="G17" t="n">
-        <v>8.890000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>1490</v>
+        <v>1480</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="F18" t="n">
-        <v>65.25</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>33.41</v>
+        <v>34.29</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.82</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>12055</v>
+        <v>11835</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F19" t="n">
-        <v>85.03</v>
+        <v>86.31</v>
       </c>
       <c r="G19" t="n">
-        <v>16.5</v>
+        <v>16.75</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.84</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>963</v>
+        <v>1000</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>80.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="F20" t="n">
-        <v>44.18</v>
+        <v>45.71</v>
       </c>
       <c r="G20" t="n">
-        <v>6.61</v>
+        <v>6.84</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.74</v>
+        <v>3.48</v>
       </c>
       <c r="M20" t="n">
-        <v>81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5770</v>
+        <v>6070</v>
       </c>
       <c r="F21" t="n">
-        <v>94.47</v>
+        <v>99.38</v>
       </c>
       <c r="G21" t="n">
-        <v>24.39</v>
+        <v>25.66</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.7</v>
+        <v>5.2</v>
       </c>
       <c r="M21" t="n">
-        <v>5930</v>
+        <v>5770</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="F22" t="n">
-        <v>53.06</v>
+        <v>55.87</v>
       </c>
       <c r="G22" t="n">
-        <v>26.71</v>
+        <v>28.12</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.58</v>
+        <v>5.29</v>
       </c>
       <c r="M22" t="n">
-        <v>2135</v>
+        <v>2080</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.35</v>
+        <v>18.55</v>
       </c>
       <c r="F23" t="n">
-        <v>41.7</v>
+        <v>42.16</v>
       </c>
       <c r="G23" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.61</v>
+        <v>1.09</v>
       </c>
       <c r="M23" t="n">
-        <v>18.65</v>
+        <v>18.35</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1535</v>
+        <v>1620</v>
       </c>
       <c r="F24" t="n">
-        <v>77.95999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="G24" t="n">
-        <v>19.02</v>
+        <v>20.08</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.99</v>
+        <v>5.54</v>
       </c>
       <c r="M24" t="n">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="F25" t="n">
-        <v>75.48999999999999</v>
+        <v>73.41</v>
       </c>
       <c r="G25" t="n">
-        <v>5.15</v>
+        <v>5.01</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-9.9</v>
+        <v>-2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>68.7</v>
+        <v>61.9</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2660</v>
+        <v>2925</v>
       </c>
       <c r="F26" t="n">
-        <v>228.92</v>
+        <v>251.72</v>
       </c>
       <c r="G26" t="n">
-        <v>52.15</v>
+        <v>57.34</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-1.3</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>2695</v>
+        <v>2660</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F27" t="n">
-        <v>51.37</v>
+        <v>51.59</v>
       </c>
       <c r="G27" t="n">
-        <v>8.02</v>
+        <v>8.06</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="M27" t="n">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="F28" t="n">
-        <v>57.3</v>
+        <v>57.05</v>
       </c>
       <c r="G28" t="n">
-        <v>11.87</v>
+        <v>11.82</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-3.7</v>
+        <v>-0.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1215</v>
+        <v>1170</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="F29" t="n">
-        <v>91.16</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>17.86</v>
+        <v>18.76</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-2.11</v>
+        <v>5.03</v>
       </c>
       <c r="M29" t="n">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3000</v>
+        <v>3070</v>
       </c>
       <c r="F30" t="n">
-        <v>70.75</v>
+        <v>72.41</v>
       </c>
       <c r="G30" t="n">
-        <v>9.76</v>
+        <v>9.98</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-2.12</v>
+        <v>2.33</v>
       </c>
       <c r="M30" t="n">
-        <v>3065</v>
+        <v>3000</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="F31" t="n">
-        <v>104.46</v>
+        <v>110.14</v>
       </c>
       <c r="G31" t="n">
-        <v>13.43</v>
+        <v>14.16</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-1.53</v>
+        <v>5.44</v>
       </c>
       <c r="M31" t="n">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="F32" t="n">
-        <v>45.79</v>
+        <v>45.35</v>
       </c>
       <c r="G32" t="n">
-        <v>11.36</v>
+        <v>11.25</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.41</v>
+        <v>-0.97</v>
       </c>
       <c r="M32" t="n">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="F33" t="n">
-        <v>40.54</v>
+        <v>42.15</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>7.28</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>9.85</v>
+        <v>3.99</v>
       </c>
       <c r="M33" t="n">
-        <v>548</v>
+        <v>602</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="F34" t="n">
-        <v>82.25</v>
+        <v>81.75</v>
       </c>
       <c r="G34" t="n">
-        <v>18.74</v>
+        <v>18.63</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.22</v>
+        <v>-0.6</v>
       </c>
       <c r="M34" t="n">
-        <v>4920</v>
+        <v>4980</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="F35" t="n">
-        <v>60.63</v>
+        <v>59.99</v>
       </c>
       <c r="G35" t="n">
-        <v>16.85</v>
+        <v>16.67</v>
       </c>
       <c r="H35" t="n">
         <v>59.1</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.79</v>
+        <v>-1.05</v>
       </c>
       <c r="M35" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3281,13 +3281,13 @@
         <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>69.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>20.32</v>
+        <v>20.12</v>
       </c>
       <c r="G36" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>19</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-0.86</v>
+        <v>-1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>69.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
@@ -3364,13 +3364,13 @@
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="F37" t="n">
-        <v>155.16</v>
+        <v>153.46</v>
       </c>
       <c r="G37" t="n">
-        <v>42.78</v>
+        <v>42.32</v>
       </c>
       <c r="H37" t="n">
         <v>70.2</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.1</v>
+        <v>-1.09</v>
       </c>
       <c r="M37" t="n">
-        <v>6800</v>
+        <v>6875</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -3443,13 +3443,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="F38" t="n">
-        <v>77.8</v>
+        <v>81.08</v>
       </c>
       <c r="G38" t="n">
-        <v>30.56</v>
+        <v>31.85</v>
       </c>
       <c r="H38" t="n">
         <v>75.3</v>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.22</v>
       </c>
       <c r="M38" t="n">
-        <v>4935</v>
+        <v>4975</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3522,13 +3522,13 @@
         <v>89</v>
       </c>
       <c r="E39" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="F39" t="n">
-        <v>45.03</v>
+        <v>45.29</v>
       </c>
       <c r="G39" t="n">
-        <v>23.61</v>
+        <v>23.75</v>
       </c>
       <c r="H39" t="n">
         <v>47.5</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.72</v>
+        <v>0.58</v>
       </c>
       <c r="M39" t="n">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
@@ -3605,10 +3605,10 @@
         <v>80</v>
       </c>
       <c r="E40" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>11.98</v>
+        <v>11.99</v>
       </c>
       <c r="G40" t="n">
         <v>1.68</v>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="M40" t="n">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="E41" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" t="n">
-        <v>11.77</v>
+        <v>11.85</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H41" t="n">
         <v>13.4</v>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="M41" t="n">
         <v>153</v>
@@ -3767,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="E42" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F42" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G42" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H42" t="n">
         <v>16</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.95</v>
+        <v>-0.47</v>
       </c>
       <c r="M42" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3846,13 +3846,13 @@
         <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="F43" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="G43" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
         <v>21.4</v>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>6.74</v>
+        <v>1.16</v>
       </c>
       <c r="M43" t="n">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3929,13 +3929,13 @@
         <v>65</v>
       </c>
       <c r="E44" t="n">
-        <v>197.5</v>
+        <v>197</v>
       </c>
       <c r="F44" t="n">
-        <v>27.2</v>
+        <v>27.13</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="H44" t="n">
         <v>30.9</v>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="M44" t="n">
         <v>197.5</v>
@@ -4012,13 +4012,13 @@
         <v>64</v>
       </c>
       <c r="E45" t="n">
-        <v>3765</v>
+        <v>3810</v>
       </c>
       <c r="F45" t="n">
-        <v>55.22</v>
+        <v>55.88</v>
       </c>
       <c r="G45" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="H45" t="n">
         <v>51.7</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.67</v>
+        <v>1.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3740</v>
+        <v>3765</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4095,13 +4095,13 @@
         <v>79</v>
       </c>
       <c r="E46" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F46" t="n">
-        <v>23.01</v>
+        <v>23.32</v>
       </c>
       <c r="G46" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5.85</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
-        <v>213.5</v>
+        <v>226</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4172,13 +4172,13 @@
         <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F47" t="n">
-        <v>20</v>
+        <v>20.49</v>
       </c>
       <c r="G47" t="n">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-0.4</v>
+        <v>2.44</v>
       </c>
       <c r="M47" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4249,13 +4249,13 @@
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>235.5</v>
+        <v>238</v>
       </c>
       <c r="F48" t="n">
-        <v>25.79</v>
+        <v>26.07</v>
       </c>
       <c r="G48" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-0.21</v>
+        <v>1.06</v>
       </c>
       <c r="M48" t="n">
-        <v>236</v>
+        <v>235.5</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
@@ -4326,13 +4326,13 @@
         <v>62</v>
       </c>
       <c r="E49" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F49" t="n">
-        <v>20.14</v>
+        <v>20.41</v>
       </c>
       <c r="G49" t="n">
-        <v>5.55</v>
+        <v>5.63</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M49" t="n">
         <v>519</v>
@@ -4405,13 +4405,13 @@
         <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="F50" t="n">
-        <v>27.63</v>
+        <v>27.34</v>
       </c>
       <c r="G50" t="n">
-        <v>7.79</v>
+        <v>7.71</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.26</v>
+        <v>-1.05</v>
       </c>
       <c r="M50" t="n">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4486,13 +4486,13 @@
         <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F51" t="n">
-        <v>21.46</v>
+        <v>22.39</v>
       </c>
       <c r="G51" t="n">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.44</v>
+        <v>4.35</v>
       </c>
       <c r="M51" t="n">
-        <v>114.5</v>
+        <v>115</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>6205</v>
+        <v>6290</v>
       </c>
       <c r="F52" t="n">
-        <v>33</v>
+        <v>33.45</v>
       </c>
       <c r="G52" t="n">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.37</v>
+        <v>1.37</v>
       </c>
       <c r="M52" t="n">
-        <v>5945</v>
+        <v>6205</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="F53" t="n">
-        <v>27.26</v>
+        <v>27.99</v>
       </c>
       <c r="G53" t="n">
-        <v>7.42</v>
+        <v>7.62</v>
       </c>
       <c r="H53" t="n">
         <v>29.3</v>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="M53" t="n">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4727,13 +4727,13 @@
         <v>91</v>
       </c>
       <c r="E54" t="n">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="F54" t="n">
-        <v>43.37</v>
+        <v>44.23</v>
       </c>
       <c r="G54" t="n">
-        <v>5.82</v>
+        <v>5.94</v>
       </c>
       <c r="H54" t="n">
         <v>46.1</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M54" t="n">
         <v>707</v>
@@ -4806,10 +4806,10 @@
         <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>16.18</v>
+        <v>16.21</v>
       </c>
       <c r="G55" t="n">
         <v>2.46</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.51</v>
+        <v>0.17</v>
       </c>
       <c r="M55" t="n">
-        <v>59.2</v>
+        <v>58.9</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4885,13 +4885,13 @@
         <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F56" t="n">
-        <v>16.16</v>
+        <v>16.07</v>
       </c>
       <c r="G56" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H56" t="n">
         <v>15.5</v>
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M56" t="n">
         <v>177</v>
@@ -4964,13 +4964,13 @@
         <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>346.5</v>
+        <v>360</v>
       </c>
       <c r="F57" t="n">
-        <v>17.94</v>
+        <v>18.64</v>
       </c>
       <c r="G57" t="n">
-        <v>5.09</v>
+        <v>5.29</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-0.72</v>
+        <v>3.9</v>
       </c>
       <c r="M57" t="n">
-        <v>349</v>
+        <v>346.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5041,13 +5041,13 @@
         <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>166.5</v>
+        <v>167.5</v>
       </c>
       <c r="F58" t="n">
-        <v>18.73</v>
+        <v>18.84</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-0.89</v>
+        <v>0.6</v>
       </c>
       <c r="M58" t="n">
-        <v>168</v>
+        <v>166.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>93.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>17.79</v>
+        <v>17.92</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.86</v>
+        <v>0.75</v>
       </c>
       <c r="M59" t="n">
-        <v>91.5</v>
+        <v>93.2</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F60" t="n">
-        <v>17.28</v>
+        <v>17.39</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1.59</v>
+        <v>0.65</v>
       </c>
       <c r="M60" t="n">
-        <v>157.5</v>
+        <v>155</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5280,13 +5280,13 @@
         <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>267.5</v>
+        <v>264.5</v>
       </c>
       <c r="F61" t="n">
-        <v>16.63</v>
+        <v>16.44</v>
       </c>
       <c r="G61" t="n">
-        <v>6.04</v>
+        <v>5.97</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>9.859999999999999</v>
+        <v>-1.12</v>
       </c>
       <c r="M61" t="n">
-        <v>243.5</v>
+        <v>267.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5357,13 +5357,13 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>185.5</v>
+        <v>187.5</v>
       </c>
       <c r="F62" t="n">
-        <v>15.65</v>
+        <v>15.82</v>
       </c>
       <c r="G62" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="M62" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5434,13 +5434,13 @@
         <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>814</v>
+        <v>791</v>
       </c>
       <c r="F63" t="n">
-        <v>18.81</v>
+        <v>18.28</v>
       </c>
       <c r="G63" t="n">
-        <v>15.18</v>
+        <v>14.75</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.3</v>
+        <v>-2.83</v>
       </c>
       <c r="M63" t="n">
-        <v>788</v>
+        <v>814</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F64" t="n">
-        <v>19.85</v>
+        <v>19.74</v>
       </c>
       <c r="G64" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0.28</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M64" t="n">
-        <v>179.5</v>
+        <v>180</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="F65" t="n">
-        <v>12.4</v>
+        <v>12.32</v>
       </c>
       <c r="G65" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="M65" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="F66" t="n">
-        <v>16.49</v>
+        <v>16.44</v>
       </c>
       <c r="G66" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M66" t="n">
         <v>157</v>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="F67" t="n">
-        <v>21.22</v>
+        <v>21.82</v>
       </c>
       <c r="G67" t="n">
-        <v>5.01</v>
+        <v>5.15</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="M67" t="n">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5833,13 +5833,13 @@
         <v>91</v>
       </c>
       <c r="E68" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F68" t="n">
-        <v>15.25</v>
+        <v>15.18</v>
       </c>
       <c r="G68" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="H68" t="n">
         <v>15</v>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M68" t="n">
         <v>118</v>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>330</v>
+        <v>339.5</v>
       </c>
       <c r="F69" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="G69" t="n">
-        <v>7.17</v>
+        <v>7.38</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.23</v>
+        <v>2.88</v>
       </c>
       <c r="M69" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="F70" t="n">
-        <v>14.44</v>
+        <v>14.39</v>
       </c>
       <c r="G70" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-0.96</v>
+        <v>-0.36</v>
       </c>
       <c r="M70" t="n">
-        <v>83.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>137</v>
+        <v>139.5</v>
       </c>
       <c r="F71" t="n">
-        <v>19.08</v>
+        <v>19.43</v>
       </c>
       <c r="G71" t="n">
-        <v>4.73</v>
+        <v>4.82</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.74</v>
+        <v>1.82</v>
       </c>
       <c r="M71" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F72" t="n">
-        <v>16.74</v>
+        <v>16.55</v>
       </c>
       <c r="G72" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.99</v>
+        <v>-1.18</v>
       </c>
       <c r="M72" t="n">
-        <v>251.5</v>
+        <v>254</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1105</v>
+        <v>1175</v>
       </c>
       <c r="F73" t="n">
-        <v>46.8</v>
+        <v>49.77</v>
       </c>
       <c r="G73" t="n">
-        <v>24.99</v>
+        <v>26.58</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-2.64</v>
+        <v>6.33</v>
       </c>
       <c r="M73" t="n">
-        <v>1135</v>
+        <v>1105</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>59.7</v>
+        <v>59</v>
       </c>
       <c r="F74" t="n">
-        <v>19.26</v>
+        <v>19.03</v>
       </c>
       <c r="G74" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.34</v>
+        <v>-1.17</v>
       </c>
       <c r="M74" t="n">
-        <v>59.5</v>
+        <v>59.7</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="F75" t="n">
-        <v>46.79</v>
+        <v>45.85</v>
       </c>
       <c r="G75" t="n">
-        <v>24.97</v>
+        <v>24.47</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.18</v>
+        <v>-1.99</v>
       </c>
       <c r="M75" t="n">
-        <v>3435</v>
+        <v>3510</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="F76" t="n">
-        <v>15.29</v>
+        <v>15.61</v>
       </c>
       <c r="G76" t="n">
-        <v>8.640000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.4</v>
+        <v>2.11</v>
       </c>
       <c r="M76" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="F77" t="n">
-        <v>29.09</v>
+        <v>28.98</v>
       </c>
       <c r="G77" t="n">
-        <v>10.12</v>
+        <v>10.08</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.21</v>
+        <v>-0.4</v>
       </c>
       <c r="M77" t="n">
-        <v>2480</v>
+        <v>2510</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F78" t="n">
-        <v>16.98</v>
+        <v>16.83</v>
       </c>
       <c r="G78" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="M78" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>110.5</v>
+        <v>113</v>
       </c>
       <c r="F79" t="n">
-        <v>13.68</v>
+        <v>13.99</v>
       </c>
       <c r="G79" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M79" t="n">
         <v>110.5</v>
@@ -6791,10 +6791,10 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>25.15</v>
+        <v>25.05</v>
       </c>
       <c r="F80" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="G80" t="n">
         <v>0.97</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-0.59</v>
+        <v>-0.4</v>
       </c>
       <c r="M80" t="n">
-        <v>25.3</v>
+        <v>25.15</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="F81" t="n">
-        <v>12.15</v>
+        <v>12.1</v>
       </c>
       <c r="G81" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="M81" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>183.5</v>
+        <v>185</v>
       </c>
       <c r="F82" t="n">
-        <v>13.08</v>
+        <v>13.19</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.94</v>
+        <v>0.82</v>
       </c>
       <c r="M82" t="n">
-        <v>180</v>
+        <v>183.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,10 +7028,10 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>42.2</v>
+        <v>42.35</v>
       </c>
       <c r="F83" t="n">
-        <v>8.880000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="G83" t="n">
         <v>1.64</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.52</v>
+        <v>0.36</v>
       </c>
       <c r="M83" t="n">
-        <v>42.85</v>
+        <v>42.2</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="F84" t="n">
-        <v>22.15</v>
+        <v>22.04</v>
       </c>
       <c r="G84" t="n">
-        <v>8.49</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.08</v>
+        <v>-0.47</v>
       </c>
       <c r="M84" t="n">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="F85" t="n">
-        <v>22.66</v>
+        <v>23.22</v>
       </c>
       <c r="G85" t="n">
-        <v>4.99</v>
+        <v>5.11</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.76</v>
+        <v>2.46</v>
       </c>
       <c r="M85" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F86" t="n">
-        <v>17.63</v>
+        <v>17.85</v>
       </c>
       <c r="G86" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.18</v>
+        <v>1.22</v>
       </c>
       <c r="M86" t="n">
-        <v>160.5</v>
+        <v>164</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.8</v>
+        <v>39.15</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="G87" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.39</v>
+        <v>0.9</v>
       </c>
       <c r="M87" t="n">
-        <v>38.95</v>
+        <v>38.8</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="F88" t="n">
-        <v>29.85</v>
+        <v>30.87</v>
       </c>
       <c r="G88" t="n">
-        <v>15.38</v>
+        <v>15.91</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7.04</v>
+        <v>3.42</v>
       </c>
       <c r="M88" t="n">
-        <v>1775</v>
+        <v>1900</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1525</v>
+        <v>1505</v>
       </c>
       <c r="F89" t="n">
-        <v>35.17</v>
+        <v>34.71</v>
       </c>
       <c r="G89" t="n">
-        <v>10.7</v>
+        <v>10.56</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-0.33</v>
+        <v>-1.31</v>
       </c>
       <c r="M89" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>88.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F90" t="n">
-        <v>8.710000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="G90" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.34</v>
+        <v>-0.45</v>
       </c>
       <c r="M90" t="n">
-        <v>89.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>54.2</v>
+        <v>53.9</v>
       </c>
       <c r="F92" t="n">
-        <v>7.52</v>
+        <v>7.48</v>
       </c>
       <c r="G92" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.37</v>
+        <v>-0.55</v>
       </c>
       <c r="M92" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F93" t="n">
-        <v>14.55</v>
+        <v>14.47</v>
       </c>
       <c r="G93" t="n">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="M93" t="n">
-        <v>333.5</v>
+        <v>334</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="F94" t="n">
-        <v>6.76</v>
+        <v>6.68</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.96</v>
+        <v>-1.18</v>
       </c>
       <c r="M94" t="n">
-        <v>2090</v>
+        <v>2110</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="F95" t="n">
-        <v>15.13</v>
+        <v>14.81</v>
       </c>
       <c r="G95" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.25</v>
+        <v>-2.1</v>
       </c>
       <c r="M95" t="n">
-        <v>184.5</v>
+        <v>190.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="F96" t="n">
-        <v>15.73</v>
+        <v>15.57</v>
       </c>
       <c r="G96" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="M96" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,13 +8170,13 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>69.3</v>
+        <v>69</v>
       </c>
       <c r="F97" t="n">
-        <v>4.86</v>
+        <v>4.84</v>
       </c>
       <c r="G97" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8192,7 +8192,7 @@
         <v>-0.43</v>
       </c>
       <c r="M97" t="n">
-        <v>69.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F98" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="G98" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="M98" t="n">
-        <v>377.5</v>
+        <v>380</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,10 +8328,10 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="F99" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="G99" t="n">
         <v>1.3</v>
@@ -8350,7 +8350,7 @@
         <v>-0.43</v>
       </c>
       <c r="M99" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>33.45</v>
+        <v>33.35</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>201</v>
+        <v>202.5</v>
       </c>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-0.5</v>
+        <v>0.75</v>
       </c>
       <c r="M101" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="F2" t="n">
-        <v>46.79</v>
+        <v>45.85</v>
       </c>
       <c r="G2" t="n">
-        <v>24.97</v>
+        <v>24.47</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.18</v>
+        <v>-1.99</v>
       </c>
       <c r="M2" t="n">
-        <v>3435</v>
+        <v>3510</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="F3" t="n">
-        <v>15.29</v>
+        <v>15.61</v>
       </c>
       <c r="G3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>2.11</v>
       </c>
       <c r="M3" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="F4" t="n">
-        <v>29.09</v>
+        <v>28.98</v>
       </c>
       <c r="G4" t="n">
-        <v>10.12</v>
+        <v>10.08</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>-0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>2480</v>
+        <v>2510</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F5" t="n">
-        <v>16.98</v>
+        <v>16.83</v>
       </c>
       <c r="G5" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="M5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>110.5</v>
+        <v>113</v>
       </c>
       <c r="F6" t="n">
-        <v>13.68</v>
+        <v>13.99</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M6" t="n">
         <v>110.5</v>
@@ -9097,10 +9097,10 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.15</v>
+        <v>25.05</v>
       </c>
       <c r="F7" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="G7" t="n">
         <v>0.97</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.59</v>
+        <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>25.3</v>
+        <v>25.15</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>12.15</v>
+        <v>12.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>183.5</v>
+        <v>185</v>
       </c>
       <c r="F9" t="n">
-        <v>13.08</v>
+        <v>13.19</v>
       </c>
       <c r="G9" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.94</v>
+        <v>0.82</v>
       </c>
       <c r="M9" t="n">
-        <v>180</v>
+        <v>183.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,10 +9334,10 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.2</v>
+        <v>42.35</v>
       </c>
       <c r="F10" t="n">
-        <v>8.880000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="G10" t="n">
         <v>1.64</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.52</v>
+        <v>0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>42.85</v>
+        <v>42.2</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="F11" t="n">
-        <v>22.15</v>
+        <v>22.04</v>
       </c>
       <c r="G11" t="n">
-        <v>8.49</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.08</v>
+        <v>-0.47</v>
       </c>
       <c r="M11" t="n">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="F12" t="n">
-        <v>22.66</v>
+        <v>23.22</v>
       </c>
       <c r="G12" t="n">
-        <v>4.99</v>
+        <v>5.11</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.76</v>
+        <v>2.46</v>
       </c>
       <c r="M12" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F13" t="n">
-        <v>17.63</v>
+        <v>17.85</v>
       </c>
       <c r="G13" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>160.5</v>
+        <v>164</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.8</v>
+        <v>39.15</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.39</v>
+        <v>0.9</v>
       </c>
       <c r="M14" t="n">
-        <v>38.95</v>
+        <v>38.8</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="F15" t="n">
-        <v>29.85</v>
+        <v>30.87</v>
       </c>
       <c r="G15" t="n">
-        <v>15.38</v>
+        <v>15.91</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7.04</v>
+        <v>3.42</v>
       </c>
       <c r="M15" t="n">
-        <v>1775</v>
+        <v>1900</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1525</v>
+        <v>1505</v>
       </c>
       <c r="F16" t="n">
-        <v>35.17</v>
+        <v>34.71</v>
       </c>
       <c r="G16" t="n">
-        <v>10.7</v>
+        <v>10.56</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-0.33</v>
+        <v>-1.31</v>
       </c>
       <c r="M16" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F17" t="n">
-        <v>8.710000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.34</v>
+        <v>-0.45</v>
       </c>
       <c r="M17" t="n">
-        <v>89.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>54.2</v>
+        <v>53.9</v>
       </c>
       <c r="F19" t="n">
-        <v>7.52</v>
+        <v>7.48</v>
       </c>
       <c r="G19" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.37</v>
+        <v>-0.55</v>
       </c>
       <c r="M19" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F20" t="n">
-        <v>14.55</v>
+        <v>14.47</v>
       </c>
       <c r="G20" t="n">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="M20" t="n">
-        <v>333.5</v>
+        <v>334</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="F21" t="n">
-        <v>6.76</v>
+        <v>6.68</v>
       </c>
       <c r="G21" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.96</v>
+        <v>-1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>2090</v>
+        <v>2110</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="F22" t="n">
-        <v>15.13</v>
+        <v>14.81</v>
       </c>
       <c r="G22" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.25</v>
+        <v>-2.1</v>
       </c>
       <c r="M22" t="n">
-        <v>184.5</v>
+        <v>190.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="F23" t="n">
-        <v>15.73</v>
+        <v>15.57</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="M23" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16.49</v>
+        <v>16.44</v>
       </c>
       <c r="G2" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M2" t="n">
         <v>157</v>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="F3" t="n">
-        <v>21.22</v>
+        <v>21.82</v>
       </c>
       <c r="G3" t="n">
-        <v>5.01</v>
+        <v>5.15</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="M3" t="n">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F4" t="n">
-        <v>15.25</v>
+        <v>15.18</v>
       </c>
       <c r="G4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M4" t="n">
         <v>118</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>330</v>
+        <v>339.5</v>
       </c>
       <c r="F5" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="G5" t="n">
-        <v>7.17</v>
+        <v>7.38</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>2.88</v>
       </c>
       <c r="M5" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14.44</v>
+        <v>14.39</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.96</v>
+        <v>-0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>83.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>137</v>
+        <v>139.5</v>
       </c>
       <c r="F7" t="n">
-        <v>19.08</v>
+        <v>19.43</v>
       </c>
       <c r="G7" t="n">
-        <v>4.73</v>
+        <v>4.82</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.74</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F8" t="n">
-        <v>16.74</v>
+        <v>16.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.99</v>
+        <v>-1.18</v>
       </c>
       <c r="M8" t="n">
-        <v>251.5</v>
+        <v>254</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1105</v>
+        <v>1175</v>
       </c>
       <c r="F9" t="n">
-        <v>46.8</v>
+        <v>49.77</v>
       </c>
       <c r="G9" t="n">
-        <v>24.99</v>
+        <v>26.58</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-2.64</v>
+        <v>6.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1135</v>
+        <v>1105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>59.7</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>19.26</v>
+        <v>19.03</v>
       </c>
       <c r="G10" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.34</v>
+        <v>-1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>59.5</v>
+        <v>59.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1565</v>
+        <v>1510</v>
       </c>
       <c r="F2" t="n">
-        <v>105.39</v>
+        <v>101.68</v>
       </c>
       <c r="G2" t="n">
-        <v>28.42</v>
+        <v>27.42</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.49</v>
+        <v>-3.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1605</v>
+        <v>1565</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153</v>
+        <v>153.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.33</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5030</v>
+        <v>5310</v>
       </c>
       <c r="F5" t="n">
-        <v>107.71</v>
+        <v>113.7</v>
       </c>
       <c r="G5" t="n">
-        <v>30.99</v>
+        <v>32.71</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.85</v>
+        <v>5.57</v>
       </c>
       <c r="M5" t="n">
-        <v>5125</v>
+        <v>5030</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>119.5</v>
+        <v>122</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.49</v>
+        <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>174</v>
+        <v>173.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22.19</v>
+        <v>22.13</v>
       </c>
       <c r="G8" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.58</v>
+        <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>25.55</v>
+        <v>25.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="M9" t="n">
-        <v>103.5</v>
+        <v>105</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>164</v>
+        <v>169.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.57</v>
+        <v>19.2</v>
       </c>
       <c r="G10" t="n">
-        <v>6.58</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>158.5</v>
+        <v>164</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="F11" t="n">
-        <v>22.77</v>
+        <v>22.67</v>
       </c>
       <c r="G11" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.25</v>
+        <v>-0.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>167.5</v>
+        <v>170.5</v>
       </c>
       <c r="F12" t="n">
-        <v>20.89</v>
+        <v>21.26</v>
       </c>
       <c r="G12" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
         <v>167.5</v>
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>284.5</v>
+        <v>281.5</v>
       </c>
       <c r="F13" t="n">
-        <v>33.27</v>
+        <v>32.92</v>
       </c>
       <c r="G13" t="n">
-        <v>6.74</v>
+        <v>6.67</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>-1.05</v>
       </c>
       <c r="M13" t="n">
-        <v>279.5</v>
+        <v>284.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.68</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>143.5</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>212.5</v>
+        <v>210.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.14</v>
+        <v>18.96</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.34</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>212.5</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.74</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8040</v>
+        <v>7900</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="F2" t="n">
-        <v>60.63</v>
+        <v>59.99</v>
       </c>
       <c r="G2" t="n">
-        <v>16.85</v>
+        <v>16.67</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.79</v>
+        <v>-1.05</v>
       </c>
       <c r="M2" t="n">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>69.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>20.32</v>
+        <v>20.12</v>
       </c>
       <c r="G3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.86</v>
+        <v>-1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>69.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="F4" t="n">
-        <v>155.16</v>
+        <v>153.46</v>
       </c>
       <c r="G4" t="n">
-        <v>42.78</v>
+        <v>42.32</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.1</v>
+        <v>-1.09</v>
       </c>
       <c r="M4" t="n">
-        <v>6800</v>
+        <v>6875</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="F5" t="n">
-        <v>77.8</v>
+        <v>81.08</v>
       </c>
       <c r="G5" t="n">
-        <v>30.56</v>
+        <v>31.85</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.22</v>
       </c>
       <c r="M5" t="n">
-        <v>4935</v>
+        <v>4975</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="F6" t="n">
-        <v>45.03</v>
+        <v>45.29</v>
       </c>
       <c r="G6" t="n">
-        <v>23.61</v>
+        <v>23.75</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.72</v>
+        <v>0.58</v>
       </c>
       <c r="M6" t="n">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.98</v>
+        <v>11.99</v>
       </c>
       <c r="G7" t="n">
         <v>1.68</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F8" t="n">
-        <v>11.77</v>
+        <v>11.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="M8" t="n">
         <v>153</v>
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>15.52</v>
+        <v>15.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.95</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="F10" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.74</v>
+        <v>1.16</v>
       </c>
       <c r="M10" t="n">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>197.5</v>
+        <v>197</v>
       </c>
       <c r="F11" t="n">
-        <v>27.2</v>
+        <v>27.13</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="M11" t="n">
         <v>197.5</v>
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3765</v>
+        <v>3810</v>
       </c>
       <c r="F12" t="n">
-        <v>55.22</v>
+        <v>55.88</v>
       </c>
       <c r="G12" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.67</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3740</v>
+        <v>3765</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1510</v>
+        <v>1595</v>
       </c>
       <c r="F2" t="n">
-        <v>101.68</v>
+        <v>107.41</v>
       </c>
       <c r="G2" t="n">
-        <v>27.42</v>
+        <v>28.96</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.51</v>
+        <v>5.63</v>
       </c>
       <c r="M2" t="n">
-        <v>1565</v>
+        <v>1510</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>153</v>
+        <v>153.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5310</v>
+        <v>5520</v>
       </c>
       <c r="F5" t="n">
-        <v>113.7</v>
+        <v>118.2</v>
       </c>
       <c r="G5" t="n">
-        <v>32.71</v>
+        <v>34.01</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.57</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>5030</v>
+        <v>5310</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.06</v>
+        <v>23.16</v>
       </c>
       <c r="G6" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M6" t="n">
         <v>122</v>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="F8" t="n">
-        <v>22.13</v>
+        <v>21.94</v>
       </c>
       <c r="G8" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>174</v>
+        <v>173.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.95</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>169.5</v>
+        <v>167</v>
       </c>
       <c r="F10" t="n">
-        <v>19.2</v>
+        <v>18.91</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>-1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>164</v>
+        <v>169.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>170.5</v>
+        <v>180.5</v>
       </c>
       <c r="F12" t="n">
-        <v>21.26</v>
+        <v>22.51</v>
       </c>
       <c r="G12" t="n">
-        <v>4.47</v>
+        <v>4.74</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>5.87</v>
       </c>
       <c r="M12" t="n">
-        <v>167.5</v>
+        <v>170.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>281.5</v>
+        <v>298</v>
       </c>
       <c r="F13" t="n">
-        <v>32.92</v>
+        <v>34.85</v>
       </c>
       <c r="G13" t="n">
-        <v>6.67</v>
+        <v>7.06</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.05</v>
+        <v>5.86</v>
       </c>
       <c r="M13" t="n">
-        <v>284.5</v>
+        <v>281.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>146</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.68</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>210.5</v>
+        <v>211</v>
       </c>
       <c r="F15" t="n">
-        <v>18.96</v>
+        <v>19.01</v>
       </c>
       <c r="G15" t="n">
-        <v>5.34</v>
+        <v>5.35</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="M15" t="n">
-        <v>212.5</v>
+        <v>210.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7900</v>
+        <v>8600</v>
       </c>
       <c r="F16" t="n">
-        <v>202.51</v>
+        <v>220.46</v>
       </c>
       <c r="G16" t="n">
-        <v>78.62</v>
+        <v>85.59</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>7900</v>
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1625</v>
+        <v>1705</v>
       </c>
       <c r="F17" t="n">
-        <v>48.08</v>
+        <v>50.44</v>
       </c>
       <c r="G17" t="n">
-        <v>9.76</v>
+        <v>10.24</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.800000000000001</v>
+        <v>4.92</v>
       </c>
       <c r="M17" t="n">
-        <v>1480</v>
+        <v>1625</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>12145</v>
+        <v>13355</v>
       </c>
       <c r="F18" t="n">
-        <v>66.95999999999999</v>
+        <v>73.63</v>
       </c>
       <c r="G18" t="n">
-        <v>34.29</v>
+        <v>37.7</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>1015</v>
+        <v>1040</v>
       </c>
       <c r="F19" t="n">
-        <v>86.31</v>
+        <v>88.44</v>
       </c>
       <c r="G19" t="n">
-        <v>16.75</v>
+        <v>17.16</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>83.2</v>
+        <v>85.5</v>
       </c>
       <c r="F20" t="n">
-        <v>45.71</v>
+        <v>46.98</v>
       </c>
       <c r="G20" t="n">
-        <v>6.84</v>
+        <v>7.03</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.48</v>
+        <v>2.76</v>
       </c>
       <c r="M20" t="n">
-        <v>80.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6070</v>
+        <v>6205</v>
       </c>
       <c r="F21" t="n">
-        <v>99.38</v>
+        <v>101.59</v>
       </c>
       <c r="G21" t="n">
-        <v>25.66</v>
+        <v>26.23</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.2</v>
+        <v>2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>5770</v>
+        <v>6070</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2190</v>
+        <v>2325</v>
       </c>
       <c r="F22" t="n">
-        <v>55.87</v>
+        <v>59.31</v>
       </c>
       <c r="G22" t="n">
-        <v>28.12</v>
+        <v>29.85</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.29</v>
+        <v>6.16</v>
       </c>
       <c r="M22" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.55</v>
+        <v>18.3</v>
       </c>
       <c r="F23" t="n">
-        <v>42.16</v>
+        <v>41.59</v>
       </c>
       <c r="G23" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.09</v>
+        <v>-1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>18.35</v>
+        <v>18.55</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1620</v>
+        <v>1780</v>
       </c>
       <c r="F24" t="n">
-        <v>82.28</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>20.08</v>
+        <v>22.06</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.54</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>1535</v>
+        <v>1620</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>60.2</v>
+        <v>57.8</v>
       </c>
       <c r="F25" t="n">
-        <v>73.41</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>5.01</v>
+        <v>4.81</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-2.75</v>
+        <v>-3.99</v>
       </c>
       <c r="M25" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2925</v>
+        <v>3000</v>
       </c>
       <c r="F26" t="n">
-        <v>251.72</v>
+        <v>258.18</v>
       </c>
       <c r="G26" t="n">
-        <v>57.34</v>
+        <v>58.81</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9.960000000000001</v>
+        <v>2.56</v>
       </c>
       <c r="M26" t="n">
-        <v>2660</v>
+        <v>2925</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>713</v>
+        <v>742</v>
       </c>
       <c r="F27" t="n">
-        <v>51.59</v>
+        <v>53.69</v>
       </c>
       <c r="G27" t="n">
-        <v>8.06</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.42</v>
+        <v>4.07</v>
       </c>
       <c r="M27" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1165</v>
+        <v>1190</v>
       </c>
       <c r="F28" t="n">
-        <v>57.05</v>
+        <v>58.28</v>
       </c>
       <c r="G28" t="n">
-        <v>11.82</v>
+        <v>12.08</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-0.43</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="F29" t="n">
-        <v>95.73999999999999</v>
+        <v>97.87</v>
       </c>
       <c r="G29" t="n">
-        <v>18.76</v>
+        <v>19.18</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.03</v>
+        <v>2.22</v>
       </c>
       <c r="M29" t="n">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3070</v>
+        <v>3105</v>
       </c>
       <c r="F30" t="n">
-        <v>72.41</v>
+        <v>73.23</v>
       </c>
       <c r="G30" t="n">
-        <v>9.98</v>
+        <v>10.1</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.33</v>
+        <v>1.14</v>
       </c>
       <c r="M30" t="n">
-        <v>3000</v>
+        <v>3070</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F31" t="n">
-        <v>110.14</v>
+        <v>111.16</v>
       </c>
       <c r="G31" t="n">
-        <v>14.16</v>
+        <v>14.29</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.44</v>
+        <v>0.92</v>
       </c>
       <c r="M31" t="n">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="F32" t="n">
-        <v>45.35</v>
+        <v>46.87</v>
       </c>
       <c r="G32" t="n">
-        <v>11.25</v>
+        <v>11.62</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.97</v>
+        <v>3.35</v>
       </c>
       <c r="M32" t="n">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3104,34 +3104,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>4950</v>
+        <v>6730</v>
       </c>
       <c r="F34" t="n">
-        <v>81.75</v>
+        <v>35.79</v>
       </c>
       <c r="G34" t="n">
-        <v>18.63</v>
+        <v>4.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>16.8</v>
+        <v>9</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-0.6</v>
+        <v>7</v>
       </c>
       <c r="M34" t="n">
-        <v>4980</v>
+        <v>6290</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3152,23 +3152,23 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>25.3</v>
+        <v>11.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="R34" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>41.8</v>
       </c>
       <c r="T34" t="n">
-        <v>61.7</v>
+        <v>32.9</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
@@ -3185,71 +3185,73 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>1885</v>
+        <v>5165</v>
       </c>
       <c r="F35" t="n">
-        <v>59.99</v>
+        <v>85.3</v>
       </c>
       <c r="G35" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="H35" t="n">
-        <v>59.1</v>
-      </c>
+        <v>19.43</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.32</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1.05</v>
+        <v>4.34</v>
       </c>
       <c r="M35" t="n">
-        <v>1905</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+        <v>4950</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️存貨爆衝(存57%vs營5%)</t>
+        </is>
+      </c>
       <c r="P35" t="n">
-        <v>22.3</v>
+        <v>25.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R35" t="n">
-        <v>15.2</v>
+        <v>4.8</v>
       </c>
       <c r="S35" t="n">
-        <v>43.7</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.32</v>
-      </c>
+        <v>61.7</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -3257,19 +3259,19 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3278,25 +3280,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>68.40000000000001</v>
+        <v>2005</v>
       </c>
       <c r="F36" t="n">
-        <v>20.12</v>
+        <v>63.81</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>17.73</v>
       </c>
       <c r="H36" t="n">
-        <v>19</v>
+        <v>59.1</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>34.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3304,55 +3306,51 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-1.01</v>
+        <v>6.37</v>
       </c>
       <c r="M36" t="n">
-        <v>69.09999999999999</v>
+        <v>1885</v>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>⚠️高槓桿(負債80%)</t>
-        </is>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>52.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="R36" t="n">
-        <v>9.699999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="S36" t="n">
-        <v>19.2</v>
+        <v>43.7</v>
       </c>
       <c r="T36" t="n">
-        <v>20.9</v>
+        <v>79.3</v>
       </c>
       <c r="U36" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3361,25 +3359,25 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>6800</v>
+        <v>68.8</v>
       </c>
       <c r="F37" t="n">
-        <v>153.46</v>
+        <v>20.24</v>
       </c>
       <c r="G37" t="n">
-        <v>42.32</v>
+        <v>1.01</v>
       </c>
       <c r="H37" t="n">
-        <v>70.2</v>
+        <v>19</v>
       </c>
       <c r="I37" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3387,51 +3385,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1.09</v>
+        <v>0.58</v>
       </c>
       <c r="M37" t="n">
-        <v>6875</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>⚠️高槓桿(負債80%)</t>
+        </is>
+      </c>
       <c r="P37" t="n">
-        <v>25</v>
+        <v>52.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.92</v>
+        <v>1.91</v>
       </c>
       <c r="R37" t="n">
-        <v>23.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S37" t="n">
-        <v>37.7</v>
+        <v>19.2</v>
       </c>
       <c r="T37" t="n">
-        <v>104.6</v>
+        <v>20.9</v>
       </c>
       <c r="U37" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3443,22 +3445,22 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>5185</v>
+        <v>7205</v>
       </c>
       <c r="F38" t="n">
-        <v>81.08</v>
+        <v>162.6</v>
       </c>
       <c r="G38" t="n">
-        <v>31.85</v>
+        <v>44.84</v>
       </c>
       <c r="H38" t="n">
-        <v>75.3</v>
+        <v>70.2</v>
       </c>
       <c r="I38" t="n">
-        <v>59.7</v>
+        <v>49</v>
       </c>
       <c r="J38" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3466,34 +3468,34 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.22</v>
+        <v>5.96</v>
       </c>
       <c r="M38" t="n">
-        <v>4975</v>
+        <v>6800</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>34.5</v>
+        <v>25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="R38" t="n">
-        <v>25.1</v>
+        <v>23.2</v>
       </c>
       <c r="S38" t="n">
-        <v>114.6</v>
+        <v>37.7</v>
       </c>
       <c r="T38" t="n">
-        <v>120.3</v>
+        <v>104.6</v>
       </c>
       <c r="U38" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -3505,12 +3507,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3519,25 +3521,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>692</v>
+        <v>5700</v>
       </c>
       <c r="F39" t="n">
-        <v>45.29</v>
+        <v>89.13</v>
       </c>
       <c r="G39" t="n">
-        <v>23.75</v>
+        <v>35.01</v>
       </c>
       <c r="H39" t="n">
-        <v>47.5</v>
+        <v>75.3</v>
       </c>
       <c r="I39" t="n">
-        <v>20.2</v>
+        <v>59.7</v>
       </c>
       <c r="J39" t="n">
-        <v>2.83</v>
+        <v>2.01</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3545,38 +3547,34 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.58</v>
+        <v>9.93</v>
       </c>
       <c r="M39" t="n">
-        <v>688</v>
+        <v>5185</v>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>月營收轉負-9%</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>53.6</v>
+        <v>34.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.12</v>
+        <v>0.76</v>
       </c>
       <c r="R39" t="n">
-        <v>28.3</v>
+        <v>25.1</v>
       </c>
       <c r="S39" t="n">
-        <v>-9.300000000000001</v>
+        <v>114.6</v>
       </c>
       <c r="T39" t="n">
-        <v>57.1</v>
+        <v>120.3</v>
       </c>
       <c r="U39" t="n">
-        <v>2.83</v>
+        <v>2.01</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -3588,12 +3586,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3602,25 +3600,25 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>97.59999999999999</v>
+        <v>691</v>
       </c>
       <c r="F40" t="n">
-        <v>11.99</v>
+        <v>45.22</v>
       </c>
       <c r="G40" t="n">
-        <v>1.68</v>
+        <v>23.71</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>47.5</v>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>20.2</v>
       </c>
       <c r="J40" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3628,75 +3626,79 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="M40" t="n">
-        <v>97.5</v>
+        <v>692</v>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>月營收轉負-9%</t>
+        </is>
+      </c>
       <c r="P40" t="n">
-        <v>17.8</v>
+        <v>53.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.11</v>
+        <v>1.12</v>
       </c>
       <c r="R40" t="n">
-        <v>5.3</v>
+        <v>28.3</v>
       </c>
       <c r="S40" t="n">
-        <v>7.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>11.6</v>
+        <v>57.1</v>
       </c>
       <c r="U40" t="n">
-        <v>2.02</v>
+        <v>2.83</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>154</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>11.85</v>
+        <v>11.93</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="H41" t="n">
-        <v>13.4</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>2.02</v>
@@ -3707,38 +3709,34 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.65</v>
+        <v>-0.51</v>
       </c>
       <c r="M41" t="n">
-        <v>153</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>⚠️存貨爆衝(存52%vs營4%)</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="R41" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="S41" t="n">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="T41" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="U41" t="n">
         <v>2.02</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -3750,12 +3748,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3764,25 +3762,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="F42" t="n">
-        <v>15.45</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
-        <v>3.75</v>
+        <v>2.09</v>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>13.4</v>
       </c>
       <c r="I42" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="J42" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3790,51 +3788,55 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.47</v>
+        <v>1.3</v>
       </c>
       <c r="M42" t="n">
-        <v>106.5</v>
+        <v>154</v>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>⚠️存貨爆衝(存52%vs營4%)</t>
+        </is>
+      </c>
       <c r="P42" t="n">
-        <v>20.6</v>
+        <v>17.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="R42" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="S42" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="T42" t="n">
-        <v>17.2</v>
+        <v>14.4</v>
       </c>
       <c r="U42" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3843,25 +3845,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>961</v>
+        <v>106.5</v>
       </c>
       <c r="F43" t="n">
-        <v>26</v>
+        <v>15.52</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="H43" t="n">
-        <v>21.4</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J43" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3869,38 +3871,34 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.16</v>
+        <v>0.47</v>
       </c>
       <c r="M43" t="n">
-        <v>950</v>
+        <v>106</v>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>毛利壓歷史低檔</t>
-        </is>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>14.3</v>
+        <v>20.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="R43" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="S43" t="n">
-        <v>30.2</v>
+        <v>1.4</v>
       </c>
       <c r="T43" t="n">
-        <v>23.4</v>
+        <v>17.2</v>
       </c>
       <c r="U43" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -3912,12 +3910,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3926,25 +3924,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>197</v>
+        <v>1055</v>
       </c>
       <c r="F44" t="n">
-        <v>27.13</v>
+        <v>28.54</v>
       </c>
       <c r="G44" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="H44" t="n">
-        <v>30.9</v>
+        <v>21.4</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3952,34 +3950,34 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-0.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>197.5</v>
+        <v>961</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>含金量0.5差</t>
+          <t>毛利壓歷史低檔</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.49</v>
+        <v>2.02</v>
       </c>
       <c r="R44" t="n">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
-        <v>8.4</v>
+        <v>30.2</v>
       </c>
       <c r="T44" t="n">
-        <v>36.5</v>
+        <v>23.4</v>
       </c>
       <c r="U44" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -3988,46 +3986,46 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>3810</v>
+        <v>196</v>
       </c>
       <c r="F45" t="n">
-        <v>55.88</v>
+        <v>27</v>
       </c>
       <c r="G45" t="n">
-        <v>5.44</v>
+        <v>2.64</v>
       </c>
       <c r="H45" t="n">
-        <v>51.7</v>
+        <v>30.9</v>
       </c>
       <c r="I45" t="n">
-        <v>23.4</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4035,132 +4033,138 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.2</v>
+        <v>-0.51</v>
       </c>
       <c r="M45" t="n">
-        <v>3765</v>
+        <v>197</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>含金量0.3差、月營收轉負-34%</t>
+          <t>含金量0.5差</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>12.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.26</v>
+        <v>0.49</v>
       </c>
       <c r="R45" t="n">
-        <v>31.2</v>
+        <v>7.6</v>
       </c>
       <c r="S45" t="n">
-        <v>-33.5</v>
+        <v>8.4</v>
       </c>
       <c r="T45" t="n">
-        <v>63.8</v>
+        <v>36.5</v>
       </c>
       <c r="U45" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>229</v>
+        <v>3950</v>
       </c>
       <c r="F46" t="n">
-        <v>23.32</v>
+        <v>57.93</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>5.64</v>
+      </c>
+      <c r="H46" t="n">
+        <v>51.7</v>
+      </c>
       <c r="I46" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.73</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3810</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>含金量0.3差、月營收轉負-34%</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R46" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
           <t>🟠偏貴</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M46" t="n">
-        <v>226</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S46" t="n">
-        <v>30</v>
-      </c>
-      <c r="T46" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4169,20 +4173,20 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E47" t="n">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="F47" t="n">
-        <v>20.49</v>
+        <v>23.12</v>
       </c>
       <c r="G47" t="n">
-        <v>3.03</v>
+        <v>3.92</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>24.9</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -4191,10 +4195,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.44</v>
+        <v>-0.87</v>
       </c>
       <c r="M47" t="n">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4203,19 +4207,19 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>10.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="R47" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="S47" t="n">
-        <v>48.7</v>
+        <v>30</v>
       </c>
       <c r="T47" t="n">
-        <v>28.4</v>
+        <v>43.5</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
@@ -4232,34 +4236,34 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E48" t="n">
-        <v>238</v>
+        <v>128.5</v>
       </c>
       <c r="F48" t="n">
-        <v>26.07</v>
+        <v>20.89</v>
       </c>
       <c r="G48" t="n">
-        <v>3.21</v>
+        <v>3.09</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>-15.3</v>
+        <v>11</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4268,31 +4272,31 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.06</v>
+        <v>1.98</v>
       </c>
       <c r="M48" t="n">
-        <v>235.5</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>EPS單期衰退</t>
-        </is>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.72</v>
+        <v>1.4</v>
       </c>
       <c r="R48" t="n">
-        <v>13.2</v>
+        <v>3.8</v>
       </c>
       <c r="S48" t="n">
-        <v>34.8</v>
+        <v>48.7</v>
       </c>
       <c r="T48" t="n">
-        <v>34.5</v>
+        <v>28.4</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
@@ -4302,19 +4306,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4323,19 +4327,21 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>526</v>
+        <v>249.5</v>
       </c>
       <c r="F49" t="n">
-        <v>20.41</v>
+        <v>27.33</v>
       </c>
       <c r="G49" t="n">
-        <v>5.63</v>
+        <v>3.37</v>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>-15.3</v>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
@@ -4343,35 +4349,31 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.35</v>
+        <v>4.83</v>
       </c>
       <c r="M49" t="n">
-        <v>519</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>17.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="R49" t="n">
-        <v>-6.1</v>
+        <v>13.2</v>
       </c>
       <c r="S49" t="n">
-        <v>730.1</v>
+        <v>34.8</v>
       </c>
       <c r="T49" t="n">
-        <v>45.2</v>
+        <v>34.5</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
@@ -4381,19 +4383,19 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4402,21 +4404,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E50" t="n">
-        <v>754</v>
+        <v>530</v>
       </c>
       <c r="F50" t="n">
-        <v>27.34</v>
+        <v>20.57</v>
       </c>
       <c r="G50" t="n">
-        <v>7.71</v>
+        <v>5.67</v>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="n">
-        <v>27</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-1.05</v>
+        <v>0.76</v>
       </c>
       <c r="M50" t="n">
-        <v>762</v>
+        <v>526</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4436,23 +4436,23 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>31.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q50" t="n">
         <v>1.5</v>
       </c>
       <c r="R50" t="n">
-        <v>3.8</v>
+        <v>-6.1</v>
       </c>
       <c r="S50" t="n">
-        <v>21.9</v>
+        <v>730.1</v>
       </c>
       <c r="T50" t="n">
-        <v>32.2</v>
+        <v>45.2</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4469,12 +4469,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4483,20 +4483,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>120</v>
+        <v>755</v>
       </c>
       <c r="F51" t="n">
-        <v>22.39</v>
+        <v>27.37</v>
       </c>
       <c r="G51" t="n">
-        <v>2.78</v>
+        <v>7.72</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>186.3</v>
+        <v>27</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.35</v>
+        <v>0.13</v>
       </c>
       <c r="M51" t="n">
-        <v>115</v>
+        <v>754</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4517,28 +4517,28 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>10.7</v>
+        <v>31.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>-3.4</v>
+        <v>3.8</v>
       </c>
       <c r="S51" t="n">
-        <v>37</v>
+        <v>21.9</v>
       </c>
       <c r="T51" t="n">
-        <v>35.8</v>
+        <v>32.2</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4550,12 +4550,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4564,20 +4564,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E52" t="n">
-        <v>6290</v>
+        <v>129</v>
       </c>
       <c r="F52" t="n">
-        <v>33.45</v>
+        <v>24.07</v>
       </c>
       <c r="G52" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>186.3</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.37</v>
+        <v>7.5</v>
       </c>
       <c r="M52" t="n">
-        <v>6205</v>
+        <v>120</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4598,28 +4598,28 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>毛利壓歷史低檔</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="R52" t="n">
-        <v>6.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S52" t="n">
-        <v>41.8</v>
+        <v>37</v>
       </c>
       <c r="T52" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4648,13 +4648,13 @@
         <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>618</v>
+        <v>679</v>
       </c>
       <c r="F53" t="n">
-        <v>27.99</v>
+        <v>30.75</v>
       </c>
       <c r="G53" t="n">
-        <v>7.62</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H53" t="n">
         <v>29.3</v>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.66</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4727,13 +4727,13 @@
         <v>91</v>
       </c>
       <c r="E54" t="n">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="F54" t="n">
-        <v>44.23</v>
+        <v>45.64</v>
       </c>
       <c r="G54" t="n">
-        <v>5.94</v>
+        <v>6.12</v>
       </c>
       <c r="H54" t="n">
         <v>46.1</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.98</v>
+        <v>3.19</v>
       </c>
       <c r="M54" t="n">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4806,13 +4806,13 @@
         <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="F55" t="n">
-        <v>16.21</v>
+        <v>16.24</v>
       </c>
       <c r="G55" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="H55" t="n">
         <v>17.3</v>
@@ -4832,7 +4832,7 @@
         <v>0.17</v>
       </c>
       <c r="M55" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4885,13 +4885,13 @@
         <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F56" t="n">
-        <v>16.07</v>
+        <v>16.16</v>
       </c>
       <c r="G56" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H56" t="n">
         <v>15.5</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="M56" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4964,13 +4964,13 @@
         <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>360</v>
+        <v>376.5</v>
       </c>
       <c r="F57" t="n">
-        <v>18.64</v>
+        <v>19.5</v>
       </c>
       <c r="G57" t="n">
-        <v>5.29</v>
+        <v>5.53</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.9</v>
+        <v>4.58</v>
       </c>
       <c r="M57" t="n">
-        <v>346.5</v>
+        <v>360</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5041,13 +5041,13 @@
         <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>167.5</v>
+        <v>166.5</v>
       </c>
       <c r="F58" t="n">
-        <v>18.84</v>
+        <v>18.73</v>
       </c>
       <c r="G58" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="M58" t="n">
-        <v>166.5</v>
+        <v>167.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>93.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="F59" t="n">
-        <v>17.92</v>
+        <v>18.26</v>
       </c>
       <c r="G59" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0.75</v>
+        <v>1.92</v>
       </c>
       <c r="M59" t="n">
-        <v>93.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F60" t="n">
-        <v>17.39</v>
+        <v>17.5</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="M60" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5280,13 +5280,13 @@
         <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>264.5</v>
+        <v>275</v>
       </c>
       <c r="F61" t="n">
-        <v>16.44</v>
+        <v>17.09</v>
       </c>
       <c r="G61" t="n">
-        <v>5.97</v>
+        <v>6.21</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-1.12</v>
+        <v>3.97</v>
       </c>
       <c r="M61" t="n">
-        <v>267.5</v>
+        <v>264.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5357,13 +5357,13 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>187.5</v>
+        <v>188.5</v>
       </c>
       <c r="F62" t="n">
-        <v>15.82</v>
+        <v>15.91</v>
       </c>
       <c r="G62" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.08</v>
+        <v>0.53</v>
       </c>
       <c r="M62" t="n">
-        <v>185.5</v>
+        <v>187.5</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5434,13 +5434,13 @@
         <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="F63" t="n">
-        <v>18.28</v>
+        <v>18.35</v>
       </c>
       <c r="G63" t="n">
-        <v>14.75</v>
+        <v>14.8</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-2.83</v>
+        <v>0.38</v>
       </c>
       <c r="M63" t="n">
-        <v>814</v>
+        <v>791</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F64" t="n">
-        <v>19.74</v>
+        <v>19.96</v>
       </c>
       <c r="G64" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="M64" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="F65" t="n">
-        <v>12.32</v>
+        <v>12.2</v>
       </c>
       <c r="G65" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="M65" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>156.5</v>
+        <v>154</v>
       </c>
       <c r="F66" t="n">
-        <v>16.44</v>
+        <v>16.18</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.32</v>
+        <v>-1.6</v>
       </c>
       <c r="M66" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="F67" t="n">
-        <v>21.82</v>
+        <v>23.2</v>
       </c>
       <c r="G67" t="n">
-        <v>5.15</v>
+        <v>5.47</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.82</v>
+        <v>6.35</v>
       </c>
       <c r="M67" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>339.5</v>
+        <v>345</v>
       </c>
       <c r="F69" t="n">
-        <v>28.7</v>
+        <v>29.16</v>
       </c>
       <c r="G69" t="n">
-        <v>7.38</v>
+        <v>7.5</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="M69" t="n">
-        <v>330</v>
+        <v>339.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="F70" t="n">
-        <v>14.39</v>
+        <v>14.37</v>
       </c>
       <c r="G70" t="n">
         <v>2.03</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-0.36</v>
+        <v>-0.12</v>
       </c>
       <c r="M70" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>139.5</v>
+        <v>140</v>
       </c>
       <c r="F71" t="n">
-        <v>19.43</v>
+        <v>19.5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.82</v>
+        <v>0.36</v>
       </c>
       <c r="M71" t="n">
-        <v>137</v>
+        <v>139.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F72" t="n">
-        <v>16.55</v>
+        <v>16.74</v>
       </c>
       <c r="G72" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M72" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
       <c r="F73" t="n">
-        <v>49.77</v>
+        <v>47.65</v>
       </c>
       <c r="G73" t="n">
-        <v>26.58</v>
+        <v>25.45</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>6.33</v>
+        <v>-4.26</v>
       </c>
       <c r="M73" t="n">
-        <v>1105</v>
+        <v>1175</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>59</v>
+        <v>58.3</v>
       </c>
       <c r="F74" t="n">
-        <v>19.03</v>
+        <v>18.81</v>
       </c>
       <c r="G74" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.17</v>
+        <v>-1.19</v>
       </c>
       <c r="M74" t="n">
-        <v>59.7</v>
+        <v>59</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3440</v>
+        <v>3585</v>
       </c>
       <c r="F75" t="n">
-        <v>45.85</v>
+        <v>47.79</v>
       </c>
       <c r="G75" t="n">
-        <v>24.47</v>
+        <v>25.5</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.99</v>
+        <v>4.22</v>
       </c>
       <c r="M75" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="F76" t="n">
-        <v>15.61</v>
+        <v>15.91</v>
       </c>
       <c r="G76" t="n">
-        <v>8.82</v>
+        <v>8.99</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="M76" t="n">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2500</v>
+        <v>2575</v>
       </c>
       <c r="F77" t="n">
-        <v>28.98</v>
+        <v>29.85</v>
       </c>
       <c r="G77" t="n">
-        <v>10.08</v>
+        <v>10.38</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-0.4</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F78" t="n">
-        <v>16.83</v>
+        <v>16.76</v>
       </c>
       <c r="G78" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="M78" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>110.5</v>
+        <v>113</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>25.05</v>
+        <v>24.8</v>
       </c>
       <c r="F80" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="G80" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="M80" t="n">
-        <v>25.15</v>
+        <v>25.05</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F81" t="n">
-        <v>12.1</v>
+        <v>11.98</v>
       </c>
       <c r="G81" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.47</v>
+        <v>-0.95</v>
       </c>
       <c r="M81" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>183.5</v>
       </c>
       <c r="F82" t="n">
-        <v>13.19</v>
+        <v>13.08</v>
       </c>
       <c r="G82" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>183.5</v>
+        <v>185</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>42.35</v>
+        <v>41.9</v>
       </c>
       <c r="F83" t="n">
-        <v>8.92</v>
+        <v>8.82</v>
       </c>
       <c r="G83" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.36</v>
+        <v>-1.06</v>
       </c>
       <c r="M83" t="n">
-        <v>42.2</v>
+        <v>42.35</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="F84" t="n">
-        <v>22.04</v>
+        <v>23.33</v>
       </c>
       <c r="G84" t="n">
-        <v>8.449999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.47</v>
+        <v>5.83</v>
       </c>
       <c r="M84" t="n">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="F85" t="n">
-        <v>23.22</v>
+        <v>23.86</v>
       </c>
       <c r="G85" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.46</v>
+        <v>2.77</v>
       </c>
       <c r="M85" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>166</v>
+        <v>169.5</v>
       </c>
       <c r="F86" t="n">
-        <v>17.85</v>
+        <v>18.23</v>
       </c>
       <c r="G86" t="n">
-        <v>4.51</v>
+        <v>4.61</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="M86" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>39.15</v>
+        <v>38.9</v>
       </c>
       <c r="F87" t="n">
-        <v>8.07</v>
+        <v>8.02</v>
       </c>
       <c r="G87" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.9</v>
+        <v>-0.64</v>
       </c>
       <c r="M87" t="n">
-        <v>38.8</v>
+        <v>39.15</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>1965</v>
+        <v>2075</v>
       </c>
       <c r="F88" t="n">
-        <v>30.87</v>
+        <v>32.6</v>
       </c>
       <c r="G88" t="n">
-        <v>15.91</v>
+        <v>16.8</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.42</v>
+        <v>5.6</v>
       </c>
       <c r="M88" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1505</v>
+        <v>1550</v>
       </c>
       <c r="F89" t="n">
-        <v>34.71</v>
+        <v>35.75</v>
       </c>
       <c r="G89" t="n">
-        <v>10.56</v>
+        <v>10.88</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-1.31</v>
+        <v>2.99</v>
       </c>
       <c r="M89" t="n">
-        <v>1525</v>
+        <v>1505</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="F90" t="n">
-        <v>8.67</v>
+        <v>8.65</v>
       </c>
       <c r="G90" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.45</v>
+        <v>-0.23</v>
       </c>
       <c r="M90" t="n">
-        <v>88.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>55.5</v>
+        <v>54.4</v>
       </c>
       <c r="F91" t="n">
-        <v>8.359999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="G91" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>-1.98</v>
       </c>
       <c r="M91" t="n">
         <v>55.5</v>
@@ -7755,10 +7755,10 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="F92" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
       <c r="G92" t="n">
         <v>1.15</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.55</v>
+        <v>0.19</v>
       </c>
       <c r="M92" t="n">
-        <v>54.2</v>
+        <v>53.9</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F93" t="n">
-        <v>14.47</v>
+        <v>14.42</v>
       </c>
       <c r="G93" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="M93" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2085</v>
+        <v>2150</v>
       </c>
       <c r="F94" t="n">
-        <v>6.68</v>
+        <v>6.89</v>
       </c>
       <c r="G94" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-1.18</v>
+        <v>3.12</v>
       </c>
       <c r="M94" t="n">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>186.5</v>
+        <v>189.5</v>
       </c>
       <c r="F95" t="n">
-        <v>14.81</v>
+        <v>15.05</v>
       </c>
       <c r="G95" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-2.1</v>
+        <v>1.61</v>
       </c>
       <c r="M95" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="F96" t="n">
-        <v>15.57</v>
+        <v>15.73</v>
       </c>
       <c r="G96" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-1.02</v>
+        <v>1.03</v>
       </c>
       <c r="M96" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,13 +8170,13 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>69</v>
+        <v>68.5</v>
       </c>
       <c r="F97" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="G97" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.43</v>
+        <v>-0.72</v>
       </c>
       <c r="M97" t="n">
-        <v>69.3</v>
+        <v>69</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F98" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="G98" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0.53</v>
+        <v>-1.05</v>
       </c>
       <c r="M98" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>23.1</v>
+        <v>22.65</v>
       </c>
       <c r="F99" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="G99" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-0.43</v>
+        <v>-1.95</v>
       </c>
       <c r="M99" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>33.35</v>
+        <v>32</v>
       </c>
       <c r="F100" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="G100" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>-4.05</v>
       </c>
       <c r="M100" t="n">
         <v>33.35</v>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>202.5</v>
+        <v>200.5</v>
       </c>
       <c r="F101" t="n">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="G101" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.75</v>
+        <v>-0.99</v>
       </c>
       <c r="M101" t="n">
-        <v>201</v>
+        <v>202.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3440</v>
+        <v>3585</v>
       </c>
       <c r="F2" t="n">
-        <v>45.85</v>
+        <v>47.79</v>
       </c>
       <c r="G2" t="n">
-        <v>24.47</v>
+        <v>25.5</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.99</v>
+        <v>4.22</v>
       </c>
       <c r="M2" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="F3" t="n">
-        <v>15.61</v>
+        <v>15.91</v>
       </c>
       <c r="G3" t="n">
-        <v>8.82</v>
+        <v>8.99</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="M3" t="n">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2500</v>
+        <v>2575</v>
       </c>
       <c r="F4" t="n">
-        <v>28.98</v>
+        <v>29.85</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08</v>
+        <v>10.38</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.4</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F5" t="n">
-        <v>16.83</v>
+        <v>16.76</v>
       </c>
       <c r="G5" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>110.5</v>
+        <v>113</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25.05</v>
+        <v>24.8</v>
       </c>
       <c r="F7" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>25.15</v>
+        <v>25.05</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1</v>
+        <v>11.98</v>
       </c>
       <c r="G8" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.47</v>
+        <v>-0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>183.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.19</v>
+        <v>13.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>183.5</v>
+        <v>185</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42.35</v>
+        <v>41.9</v>
       </c>
       <c r="F10" t="n">
-        <v>8.92</v>
+        <v>8.82</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.36</v>
+        <v>-1.06</v>
       </c>
       <c r="M10" t="n">
-        <v>42.2</v>
+        <v>42.35</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="F11" t="n">
-        <v>22.04</v>
+        <v>23.33</v>
       </c>
       <c r="G11" t="n">
-        <v>8.449999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.47</v>
+        <v>5.83</v>
       </c>
       <c r="M11" t="n">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="F12" t="n">
-        <v>23.22</v>
+        <v>23.86</v>
       </c>
       <c r="G12" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.46</v>
+        <v>2.77</v>
       </c>
       <c r="M12" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>166</v>
+        <v>169.5</v>
       </c>
       <c r="F13" t="n">
-        <v>17.85</v>
+        <v>18.23</v>
       </c>
       <c r="G13" t="n">
-        <v>4.51</v>
+        <v>4.61</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>39.15</v>
+        <v>38.9</v>
       </c>
       <c r="F14" t="n">
-        <v>8.07</v>
+        <v>8.02</v>
       </c>
       <c r="G14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.9</v>
+        <v>-0.64</v>
       </c>
       <c r="M14" t="n">
-        <v>38.8</v>
+        <v>39.15</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>1965</v>
+        <v>2075</v>
       </c>
       <c r="F15" t="n">
-        <v>30.87</v>
+        <v>32.6</v>
       </c>
       <c r="G15" t="n">
-        <v>15.91</v>
+        <v>16.8</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.42</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1505</v>
+        <v>1550</v>
       </c>
       <c r="F16" t="n">
-        <v>34.71</v>
+        <v>35.75</v>
       </c>
       <c r="G16" t="n">
-        <v>10.56</v>
+        <v>10.88</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.31</v>
+        <v>2.99</v>
       </c>
       <c r="M16" t="n">
-        <v>1525</v>
+        <v>1505</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="F17" t="n">
-        <v>8.67</v>
+        <v>8.65</v>
       </c>
       <c r="G17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.45</v>
+        <v>-0.23</v>
       </c>
       <c r="M17" t="n">
-        <v>88.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>55.5</v>
+        <v>54.4</v>
       </c>
       <c r="F18" t="n">
-        <v>8.359999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="G18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.98</v>
       </c>
       <c r="M18" t="n">
         <v>55.5</v>
@@ -10061,10 +10061,10 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
       <c r="G19" t="n">
         <v>1.15</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.55</v>
+        <v>0.19</v>
       </c>
       <c r="M19" t="n">
-        <v>54.2</v>
+        <v>53.9</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F20" t="n">
-        <v>14.47</v>
+        <v>14.42</v>
       </c>
       <c r="G20" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="M20" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2085</v>
+        <v>2150</v>
       </c>
       <c r="F21" t="n">
-        <v>6.68</v>
+        <v>6.89</v>
       </c>
       <c r="G21" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.18</v>
+        <v>3.12</v>
       </c>
       <c r="M21" t="n">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>186.5</v>
+        <v>189.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.81</v>
+        <v>15.05</v>
       </c>
       <c r="G22" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.1</v>
+        <v>1.61</v>
       </c>
       <c r="M22" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="F23" t="n">
-        <v>15.57</v>
+        <v>15.73</v>
       </c>
       <c r="G23" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.02</v>
+        <v>1.03</v>
       </c>
       <c r="M23" t="n">
-        <v>1475</v>
+        <v>1460</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>156.5</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>16.44</v>
+        <v>16.18</v>
       </c>
       <c r="G2" t="n">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.32</v>
+        <v>-1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="F3" t="n">
-        <v>21.82</v>
+        <v>23.2</v>
       </c>
       <c r="G3" t="n">
-        <v>5.15</v>
+        <v>5.47</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.82</v>
+        <v>6.35</v>
       </c>
       <c r="M3" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>339.5</v>
+        <v>345</v>
       </c>
       <c r="F5" t="n">
-        <v>28.7</v>
+        <v>29.16</v>
       </c>
       <c r="G5" t="n">
-        <v>7.38</v>
+        <v>7.5</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>330</v>
+        <v>339.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,10 +10923,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="F6" t="n">
-        <v>14.39</v>
+        <v>14.37</v>
       </c>
       <c r="G6" t="n">
         <v>2.03</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.36</v>
+        <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>139.5</v>
+        <v>140</v>
       </c>
       <c r="F7" t="n">
-        <v>19.43</v>
+        <v>19.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>137</v>
+        <v>139.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F8" t="n">
-        <v>16.55</v>
+        <v>16.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
       <c r="F9" t="n">
-        <v>49.77</v>
+        <v>47.65</v>
       </c>
       <c r="G9" t="n">
-        <v>26.58</v>
+        <v>25.45</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.33</v>
+        <v>-4.26</v>
       </c>
       <c r="M9" t="n">
-        <v>1105</v>
+        <v>1175</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>58.3</v>
       </c>
       <c r="F10" t="n">
-        <v>19.03</v>
+        <v>18.81</v>
       </c>
       <c r="G10" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.17</v>
+        <v>-1.19</v>
       </c>
       <c r="M10" t="n">
-        <v>59.7</v>
+        <v>59</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1510</v>
+        <v>1595</v>
       </c>
       <c r="F2" t="n">
-        <v>101.68</v>
+        <v>107.41</v>
       </c>
       <c r="G2" t="n">
-        <v>27.42</v>
+        <v>28.96</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.51</v>
+        <v>5.63</v>
       </c>
       <c r="M2" t="n">
-        <v>1565</v>
+        <v>1510</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>153</v>
+        <v>153.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5310</v>
+        <v>5520</v>
       </c>
       <c r="F5" t="n">
-        <v>113.7</v>
+        <v>118.2</v>
       </c>
       <c r="G5" t="n">
-        <v>32.71</v>
+        <v>34.01</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.57</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>5030</v>
+        <v>5310</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.06</v>
+        <v>23.16</v>
       </c>
       <c r="G6" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M6" t="n">
         <v>122</v>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="F8" t="n">
-        <v>22.13</v>
+        <v>21.94</v>
       </c>
       <c r="G8" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>174</v>
+        <v>173.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.95</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>169.5</v>
+        <v>167</v>
       </c>
       <c r="F10" t="n">
-        <v>19.2</v>
+        <v>18.91</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>-1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>164</v>
+        <v>169.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>170.5</v>
+        <v>180.5</v>
       </c>
       <c r="F12" t="n">
-        <v>21.26</v>
+        <v>22.51</v>
       </c>
       <c r="G12" t="n">
-        <v>4.47</v>
+        <v>4.74</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>5.87</v>
       </c>
       <c r="M12" t="n">
-        <v>167.5</v>
+        <v>170.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>281.5</v>
+        <v>298</v>
       </c>
       <c r="F13" t="n">
-        <v>32.92</v>
+        <v>34.85</v>
       </c>
       <c r="G13" t="n">
-        <v>6.67</v>
+        <v>7.06</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-1.05</v>
+        <v>5.86</v>
       </c>
       <c r="M13" t="n">
-        <v>284.5</v>
+        <v>281.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>146</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.68</v>
+        <v>28.59</v>
       </c>
       <c r="G14" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.34</v>
+        <v>-0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>210.5</v>
+        <v>211</v>
       </c>
       <c r="F15" t="n">
-        <v>18.96</v>
+        <v>19.01</v>
       </c>
       <c r="G15" t="n">
-        <v>5.34</v>
+        <v>5.35</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="M15" t="n">
-        <v>212.5</v>
+        <v>210.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>7900</v>
+        <v>8600</v>
       </c>
       <c r="F16" t="n">
-        <v>202.51</v>
+        <v>220.46</v>
       </c>
       <c r="G16" t="n">
-        <v>78.62</v>
+        <v>85.59</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>7900</v>
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1885</v>
+        <v>2005</v>
       </c>
       <c r="F2" t="n">
-        <v>59.99</v>
+        <v>63.81</v>
       </c>
       <c r="G2" t="n">
-        <v>16.67</v>
+        <v>17.73</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.05</v>
+        <v>6.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="F3" t="n">
-        <v>20.12</v>
+        <v>20.24</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.01</v>
+        <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>69.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>6800</v>
+        <v>7205</v>
       </c>
       <c r="F4" t="n">
-        <v>153.46</v>
+        <v>162.6</v>
       </c>
       <c r="G4" t="n">
-        <v>42.32</v>
+        <v>44.84</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.09</v>
+        <v>5.96</v>
       </c>
       <c r="M4" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5185</v>
+        <v>5700</v>
       </c>
       <c r="F5" t="n">
-        <v>81.08</v>
+        <v>89.13</v>
       </c>
       <c r="G5" t="n">
-        <v>31.85</v>
+        <v>35.01</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.22</v>
+        <v>9.93</v>
       </c>
       <c r="M5" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F6" t="n">
-        <v>45.29</v>
+        <v>45.22</v>
       </c>
       <c r="G6" t="n">
-        <v>23.75</v>
+        <v>23.71</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.58</v>
+        <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.99</v>
+        <v>11.93</v>
       </c>
       <c r="G7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.1</v>
+        <v>-0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F8" t="n">
-        <v>11.85</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.65</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.45</v>
+        <v>15.52</v>
       </c>
       <c r="G9" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>961</v>
+        <v>1055</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>28.54</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.16</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F11" t="n">
-        <v>27.13</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.25</v>
+        <v>-0.51</v>
       </c>
       <c r="M11" t="n">
-        <v>197.5</v>
+        <v>197</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3810</v>
+        <v>3950</v>
       </c>
       <c r="F12" t="n">
-        <v>55.88</v>
+        <v>57.93</v>
       </c>
       <c r="G12" t="n">
-        <v>5.44</v>
+        <v>5.64</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>3.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3765</v>
+        <v>3810</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="n">
-        <v>107.41</v>
+        <v>107.74</v>
       </c>
       <c r="G2" t="n">
-        <v>28.96</v>
+        <v>29.05</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.63</v>
+        <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1510</v>
+        <v>1595</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>16.94</v>
       </c>
       <c r="G4" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="M4" t="n">
         <v>153.5</v>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="F5" t="n">
-        <v>118.2</v>
+        <v>121.41</v>
       </c>
       <c r="G5" t="n">
-        <v>34.01</v>
+        <v>34.93</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>2.72</v>
       </c>
       <c r="M5" t="n">
-        <v>5310</v>
+        <v>5520</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>23.16</v>
+        <v>23.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -903,7 +903,7 @@
         <v>0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.36</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.49</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>172.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.94</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.86</v>
+        <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.67</v>
+        <v>25.43</v>
       </c>
       <c r="G9" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>-0.95</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>167</v>
+        <v>175.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.91</v>
+        <v>19.88</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>7.05</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.47</v>
+        <v>5.09</v>
       </c>
       <c r="M10" t="n">
-        <v>169.5</v>
+        <v>167</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1180</v>
+        <v>1195</v>
       </c>
       <c r="F11" t="n">
-        <v>22.67</v>
+        <v>22.96</v>
       </c>
       <c r="G11" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
         <v>1180</v>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>180.5</v>
+        <v>182</v>
       </c>
       <c r="F12" t="n">
-        <v>22.51</v>
+        <v>22.69</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.87</v>
+        <v>0.83</v>
       </c>
       <c r="M12" t="n">
-        <v>170.5</v>
+        <v>180.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F13" t="n">
-        <v>34.85</v>
+        <v>34.97</v>
       </c>
       <c r="G13" t="n">
-        <v>7.06</v>
+        <v>7.08</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.86</v>
+        <v>0.34</v>
       </c>
       <c r="M13" t="n">
-        <v>281.5</v>
+        <v>298</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>146</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>211</v>
+        <v>210.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.01</v>
+        <v>18.96</v>
       </c>
       <c r="G15" t="n">
-        <v>5.35</v>
+        <v>5.34</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.24</v>
+        <v>-0.24</v>
       </c>
       <c r="M15" t="n">
-        <v>210.5</v>
+        <v>211</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8600</v>
+        <v>8375</v>
       </c>
       <c r="F16" t="n">
-        <v>220.46</v>
+        <v>214.69</v>
       </c>
       <c r="G16" t="n">
-        <v>85.59</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.859999999999999</v>
+        <v>-2.62</v>
       </c>
       <c r="M16" t="n">
-        <v>7900</v>
+        <v>8600</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1705</v>
+        <v>1650</v>
       </c>
       <c r="F17" t="n">
-        <v>50.44</v>
+        <v>48.82</v>
       </c>
       <c r="G17" t="n">
-        <v>10.24</v>
+        <v>9.91</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.92</v>
+        <v>-3.23</v>
       </c>
       <c r="M17" t="n">
-        <v>1625</v>
+        <v>1705</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>13355</v>
+        <v>13100</v>
       </c>
       <c r="F18" t="n">
-        <v>73.63</v>
+        <v>72.22</v>
       </c>
       <c r="G18" t="n">
-        <v>37.7</v>
+        <v>36.98</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>9.960000000000001</v>
+        <v>-1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>12145</v>
+        <v>13355</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="F19" t="n">
-        <v>88.44</v>
+        <v>87.59</v>
       </c>
       <c r="G19" t="n">
-        <v>17.16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.46</v>
+        <v>-0.96</v>
       </c>
       <c r="M19" t="n">
-        <v>1015</v>
+        <v>1040</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>85.5</v>
+        <v>85</v>
       </c>
       <c r="F20" t="n">
-        <v>46.98</v>
+        <v>46.7</v>
       </c>
       <c r="G20" t="n">
-        <v>7.03</v>
+        <v>6.98</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.76</v>
+        <v>-0.58</v>
       </c>
       <c r="M20" t="n">
-        <v>83.2</v>
+        <v>85.5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6205</v>
+        <v>6130</v>
       </c>
       <c r="F21" t="n">
-        <v>101.59</v>
+        <v>100.36</v>
       </c>
       <c r="G21" t="n">
-        <v>26.23</v>
+        <v>25.92</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.22</v>
+        <v>-1.21</v>
       </c>
       <c r="M21" t="n">
-        <v>6070</v>
+        <v>6205</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="F22" t="n">
-        <v>59.31</v>
+        <v>59.95</v>
       </c>
       <c r="G22" t="n">
-        <v>29.85</v>
+        <v>30.17</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.16</v>
+        <v>1.08</v>
       </c>
       <c r="M22" t="n">
-        <v>2190</v>
+        <v>2325</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>18.55</v>
+        <v>18.3</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1780</v>
+        <v>1755</v>
       </c>
       <c r="F24" t="n">
-        <v>90.40000000000001</v>
+        <v>89.13</v>
       </c>
       <c r="G24" t="n">
-        <v>22.06</v>
+        <v>21.75</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9.880000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>1620</v>
+        <v>1780</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>57.8</v>
+        <v>58.3</v>
       </c>
       <c r="F25" t="n">
-        <v>70.48999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-3.99</v>
+        <v>0.87</v>
       </c>
       <c r="M25" t="n">
-        <v>60.2</v>
+        <v>57.8</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>3000</v>
+        <v>2920</v>
       </c>
       <c r="F26" t="n">
-        <v>258.18</v>
+        <v>251.29</v>
       </c>
       <c r="G26" t="n">
-        <v>58.81</v>
+        <v>57.24</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.56</v>
+        <v>-2.67</v>
       </c>
       <c r="M26" t="n">
-        <v>2925</v>
+        <v>3000</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="F27" t="n">
-        <v>53.69</v>
+        <v>53.84</v>
       </c>
       <c r="G27" t="n">
-        <v>8.380000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.07</v>
+        <v>0.27</v>
       </c>
       <c r="M27" t="n">
-        <v>713</v>
+        <v>742</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1190</v>
+        <v>1175</v>
       </c>
       <c r="F28" t="n">
-        <v>58.28</v>
+        <v>57.54</v>
       </c>
       <c r="G28" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>-1.26</v>
       </c>
       <c r="M28" t="n">
-        <v>1165</v>
+        <v>1190</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="F29" t="n">
-        <v>97.87</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>19.18</v>
+        <v>18.22</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.22</v>
+        <v>-5.02</v>
       </c>
       <c r="M29" t="n">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3105</v>
+        <v>3055</v>
       </c>
       <c r="F30" t="n">
-        <v>73.23</v>
+        <v>72.05</v>
       </c>
       <c r="G30" t="n">
-        <v>10.1</v>
+        <v>9.93</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>-1.61</v>
       </c>
       <c r="M30" t="n">
-        <v>3070</v>
+        <v>3105</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="F31" t="n">
-        <v>111.16</v>
+        <v>107.71</v>
       </c>
       <c r="G31" t="n">
-        <v>14.29</v>
+        <v>13.85</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.92</v>
+        <v>-3.1</v>
       </c>
       <c r="M31" t="n">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F32" t="n">
-        <v>46.87</v>
+        <v>46.74</v>
       </c>
       <c r="G32" t="n">
-        <v>11.62</v>
+        <v>11.59</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.35</v>
+        <v>-0.27</v>
       </c>
       <c r="M32" t="n">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F33" t="n">
-        <v>42.15</v>
+        <v>42.09</v>
       </c>
       <c r="G33" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="M33" t="n">
         <v>626</v>
@@ -3121,13 +3121,13 @@
         <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>6730</v>
+        <v>6855</v>
       </c>
       <c r="F34" t="n">
-        <v>35.79</v>
+        <v>36.46</v>
       </c>
       <c r="G34" t="n">
-        <v>4.6</v>
+        <v>4.68</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7</v>
+        <v>1.86</v>
       </c>
       <c r="M34" t="n">
-        <v>6290</v>
+        <v>6730</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>5165</v>
+        <v>4920</v>
       </c>
       <c r="F35" t="n">
-        <v>85.3</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>19.43</v>
+        <v>18.51</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.34</v>
+        <v>-4.74</v>
       </c>
       <c r="M35" t="n">
-        <v>4950</v>
+        <v>5165</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="F36" t="n">
-        <v>63.81</v>
+        <v>65.25</v>
       </c>
       <c r="G36" t="n">
-        <v>17.73</v>
+        <v>18.13</v>
       </c>
       <c r="H36" t="n">
         <v>59.1</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.37</v>
+        <v>2.24</v>
       </c>
       <c r="M36" t="n">
-        <v>1885</v>
+        <v>2005</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="F37" t="n">
-        <v>20.24</v>
+        <v>20.21</v>
       </c>
       <c r="G37" t="n">
         <v>1.01</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.58</v>
+        <v>-0.15</v>
       </c>
       <c r="M37" t="n">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
@@ -3445,13 +3445,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="F38" t="n">
-        <v>162.6</v>
+        <v>159.78</v>
       </c>
       <c r="G38" t="n">
-        <v>44.84</v>
+        <v>44.06</v>
       </c>
       <c r="H38" t="n">
         <v>70.2</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.96</v>
+        <v>-1.73</v>
       </c>
       <c r="M38" t="n">
-        <v>6800</v>
+        <v>7205</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3524,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>5700</v>
+        <v>5995</v>
       </c>
       <c r="F39" t="n">
-        <v>89.13</v>
+        <v>93.75</v>
       </c>
       <c r="G39" t="n">
-        <v>35.01</v>
+        <v>36.82</v>
       </c>
       <c r="H39" t="n">
         <v>75.3</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>9.93</v>
+        <v>5.18</v>
       </c>
       <c r="M39" t="n">
-        <v>5185</v>
+        <v>5700</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3603,13 +3603,13 @@
         <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="F40" t="n">
-        <v>45.22</v>
+        <v>45.55</v>
       </c>
       <c r="G40" t="n">
-        <v>23.71</v>
+        <v>23.88</v>
       </c>
       <c r="H40" t="n">
         <v>47.5</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-0.14</v>
+        <v>0.72</v>
       </c>
       <c r="M40" t="n">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
@@ -3686,10 +3686,10 @@
         <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="F41" t="n">
-        <v>11.93</v>
+        <v>11.92</v>
       </c>
       <c r="G41" t="n">
         <v>1.67</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-0.51</v>
+        <v>-0.1</v>
       </c>
       <c r="M41" t="n">
-        <v>97.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3927,13 +3927,13 @@
         <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="F44" t="n">
-        <v>28.54</v>
+        <v>28.27</v>
       </c>
       <c r="G44" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="H44" t="n">
         <v>21.4</v>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>9.779999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="M44" t="n">
-        <v>961</v>
+        <v>1055</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4010,13 +4010,13 @@
         <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F45" t="n">
-        <v>27</v>
+        <v>27.13</v>
       </c>
       <c r="G45" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="H45" t="n">
         <v>30.9</v>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-0.51</v>
+        <v>0.51</v>
       </c>
       <c r="M45" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4093,13 +4093,13 @@
         <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>3950</v>
+        <v>4180</v>
       </c>
       <c r="F46" t="n">
-        <v>57.93</v>
+        <v>61.31</v>
       </c>
       <c r="G46" t="n">
-        <v>5.64</v>
+        <v>5.97</v>
       </c>
       <c r="H46" t="n">
         <v>51.7</v>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.67</v>
+        <v>5.82</v>
       </c>
       <c r="M46" t="n">
-        <v>3810</v>
+        <v>3950</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4176,13 +4176,13 @@
         <v>79</v>
       </c>
       <c r="E47" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F47" t="n">
-        <v>23.12</v>
+        <v>23.22</v>
       </c>
       <c r="G47" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-0.87</v>
+        <v>0.44</v>
       </c>
       <c r="M47" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4253,13 +4253,13 @@
         <v>78</v>
       </c>
       <c r="E48" t="n">
-        <v>128.5</v>
+        <v>131.5</v>
       </c>
       <c r="F48" t="n">
-        <v>20.89</v>
+        <v>21.38</v>
       </c>
       <c r="G48" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="M48" t="n">
-        <v>126</v>
+        <v>128.5</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4330,13 +4330,13 @@
         <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>249.5</v>
+        <v>256</v>
       </c>
       <c r="F49" t="n">
-        <v>27.33</v>
+        <v>28.04</v>
       </c>
       <c r="G49" t="n">
-        <v>3.37</v>
+        <v>3.46</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.83</v>
+        <v>2.61</v>
       </c>
       <c r="M49" t="n">
-        <v>238</v>
+        <v>249.5</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
@@ -4407,13 +4407,13 @@
         <v>62</v>
       </c>
       <c r="E50" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="F50" t="n">
-        <v>20.57</v>
+        <v>20.37</v>
       </c>
       <c r="G50" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.76</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4567,13 +4567,13 @@
         <v>60</v>
       </c>
       <c r="E52" t="n">
-        <v>129</v>
+        <v>127.5</v>
       </c>
       <c r="F52" t="n">
-        <v>24.07</v>
+        <v>23.79</v>
       </c>
       <c r="G52" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>7.5</v>
+        <v>-1.16</v>
       </c>
       <c r="M52" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="F53" t="n">
-        <v>30.75</v>
+        <v>30.03</v>
       </c>
       <c r="G53" t="n">
-        <v>8.369999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="H53" t="n">
         <v>29.3</v>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>9.869999999999999</v>
+        <v>-2.36</v>
       </c>
       <c r="M53" t="n">
-        <v>618</v>
+        <v>679</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4727,13 +4727,13 @@
         <v>91</v>
       </c>
       <c r="E54" t="n">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="F54" t="n">
-        <v>45.64</v>
+        <v>46.75</v>
       </c>
       <c r="G54" t="n">
-        <v>6.12</v>
+        <v>6.27</v>
       </c>
       <c r="H54" t="n">
         <v>46.1</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.19</v>
+        <v>2.42</v>
       </c>
       <c r="M54" t="n">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4806,13 +4806,13 @@
         <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>59.1</v>
+        <v>58.9</v>
       </c>
       <c r="F55" t="n">
-        <v>16.24</v>
+        <v>16.18</v>
       </c>
       <c r="G55" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="H55" t="n">
         <v>17.3</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.17</v>
+        <v>-0.34</v>
       </c>
       <c r="M55" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4885,13 +4885,13 @@
         <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>177</v>
+        <v>176.5</v>
       </c>
       <c r="F56" t="n">
-        <v>16.16</v>
+        <v>16.12</v>
       </c>
       <c r="G56" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H56" t="n">
         <v>15.5</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
       <c r="M56" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4964,13 +4964,13 @@
         <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>376.5</v>
+        <v>370.5</v>
       </c>
       <c r="F57" t="n">
-        <v>19.5</v>
+        <v>19.19</v>
       </c>
       <c r="G57" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.58</v>
+        <v>-1.59</v>
       </c>
       <c r="M57" t="n">
-        <v>360</v>
+        <v>376.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5041,13 +5041,13 @@
         <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>166.5</v>
+        <v>167</v>
       </c>
       <c r="F58" t="n">
-        <v>18.73</v>
+        <v>18.79</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M58" t="n">
-        <v>167.5</v>
+        <v>166.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="F59" t="n">
-        <v>18.26</v>
+        <v>18.66</v>
       </c>
       <c r="G59" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="M59" t="n">
-        <v>93.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>157</v>
+        <v>155.5</v>
       </c>
       <c r="F60" t="n">
-        <v>17.5</v>
+        <v>17.34</v>
       </c>
       <c r="G60" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.64</v>
+        <v>-0.96</v>
       </c>
       <c r="M60" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5280,13 +5280,13 @@
         <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="F61" t="n">
-        <v>17.09</v>
+        <v>18.15</v>
       </c>
       <c r="G61" t="n">
-        <v>6.21</v>
+        <v>6.6</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.97</v>
+        <v>6.18</v>
       </c>
       <c r="M61" t="n">
-        <v>264.5</v>
+        <v>275</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>187.5</v>
+        <v>188.5</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5434,13 +5434,13 @@
         <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="F63" t="n">
-        <v>18.35</v>
+        <v>18.02</v>
       </c>
       <c r="G63" t="n">
-        <v>14.8</v>
+        <v>14.54</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.38</v>
+        <v>-1.76</v>
       </c>
       <c r="M63" t="n">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>181</v>
+        <v>177.5</v>
       </c>
       <c r="F64" t="n">
-        <v>19.96</v>
+        <v>19.57</v>
       </c>
       <c r="G64" t="n">
-        <v>4.94</v>
+        <v>4.84</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.12</v>
+        <v>-1.93</v>
       </c>
       <c r="M64" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.4</v>
+        <v>49.65</v>
       </c>
       <c r="F65" t="n">
-        <v>12.2</v>
+        <v>12.26</v>
       </c>
       <c r="G65" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-1</v>
+        <v>0.51</v>
       </c>
       <c r="M65" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F66" t="n">
-        <v>16.18</v>
+        <v>16.28</v>
       </c>
       <c r="G66" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1.6</v>
+        <v>0.65</v>
       </c>
       <c r="M66" t="n">
-        <v>156.5</v>
+        <v>154</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F67" t="n">
-        <v>23.2</v>
+        <v>23.17</v>
       </c>
       <c r="G67" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>6.35</v>
+        <v>-0.16</v>
       </c>
       <c r="M67" t="n">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="F69" t="n">
-        <v>29.16</v>
+        <v>30.85</v>
       </c>
       <c r="G69" t="n">
-        <v>7.5</v>
+        <v>7.93</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.62</v>
+        <v>5.8</v>
       </c>
       <c r="M69" t="n">
-        <v>339.5</v>
+        <v>345</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="F70" t="n">
-        <v>14.37</v>
+        <v>14.48</v>
       </c>
       <c r="G70" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-0.12</v>
+        <v>0.73</v>
       </c>
       <c r="M70" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>140</v>
+        <v>140.5</v>
       </c>
       <c r="F71" t="n">
-        <v>19.5</v>
+        <v>19.57</v>
       </c>
       <c r="G71" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6096,7 +6096,7 @@
         <v>0.36</v>
       </c>
       <c r="M71" t="n">
-        <v>139.5</v>
+        <v>140</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F72" t="n">
-        <v>16.74</v>
+        <v>16.88</v>
       </c>
       <c r="G72" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.2</v>
+        <v>0.79</v>
       </c>
       <c r="M72" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="F73" t="n">
-        <v>47.65</v>
+        <v>47.01</v>
       </c>
       <c r="G73" t="n">
-        <v>25.45</v>
+        <v>25.11</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-4.26</v>
+        <v>-1.33</v>
       </c>
       <c r="M73" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>58.3</v>
+        <v>58.6</v>
       </c>
       <c r="F74" t="n">
-        <v>18.81</v>
+        <v>18.9</v>
       </c>
       <c r="G74" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.19</v>
+        <v>0.51</v>
       </c>
       <c r="M74" t="n">
-        <v>59</v>
+        <v>58.3</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="F75" t="n">
-        <v>47.79</v>
+        <v>49.12</v>
       </c>
       <c r="G75" t="n">
-        <v>25.5</v>
+        <v>26.21</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>4.22</v>
+        <v>2.79</v>
       </c>
       <c r="M75" t="n">
-        <v>3440</v>
+        <v>3585</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="F76" t="n">
-        <v>15.91</v>
+        <v>16.02</v>
       </c>
       <c r="G76" t="n">
-        <v>8.99</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.94</v>
+        <v>0.63</v>
       </c>
       <c r="M76" t="n">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="F77" t="n">
-        <v>29.85</v>
+        <v>29.96</v>
       </c>
       <c r="G77" t="n">
-        <v>10.38</v>
+        <v>10.42</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3</v>
+        <v>0.39</v>
       </c>
       <c r="M77" t="n">
-        <v>2500</v>
+        <v>2575</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>113</v>
+        <v>116.5</v>
       </c>
       <c r="F79" t="n">
-        <v>13.99</v>
+        <v>14.42</v>
       </c>
       <c r="G79" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M79" t="n">
         <v>113</v>
@@ -6791,10 +6791,10 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>24.8</v>
+        <v>24.75</v>
       </c>
       <c r="F80" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="G80" t="n">
         <v>0.96</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="M80" t="n">
-        <v>25.05</v>
+        <v>24.8</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>183.5</v>
+        <v>181</v>
       </c>
       <c r="F82" t="n">
-        <v>13.08</v>
+        <v>12.9</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.36</v>
       </c>
       <c r="M82" t="n">
-        <v>185</v>
+        <v>183.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>41.9</v>
+        <v>41.55</v>
       </c>
       <c r="F83" t="n">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="G83" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.06</v>
+        <v>-0.84</v>
       </c>
       <c r="M83" t="n">
-        <v>42.35</v>
+        <v>41.9</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="F84" t="n">
-        <v>23.33</v>
+        <v>23.2</v>
       </c>
       <c r="G84" t="n">
-        <v>8.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>5.83</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="F85" t="n">
-        <v>23.86</v>
+        <v>24.81</v>
       </c>
       <c r="G85" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.77</v>
+        <v>3.95</v>
       </c>
       <c r="M85" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>169.5</v>
+        <v>173</v>
       </c>
       <c r="F86" t="n">
-        <v>18.23</v>
+        <v>18.6</v>
       </c>
       <c r="G86" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="M86" t="n">
-        <v>166</v>
+        <v>169.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.9</v>
+        <v>38.95</v>
       </c>
       <c r="F87" t="n">
-        <v>8.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.64</v>
+        <v>0.13</v>
       </c>
       <c r="M87" t="n">
-        <v>39.15</v>
+        <v>38.9</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="F88" t="n">
-        <v>32.6</v>
+        <v>32.21</v>
       </c>
       <c r="G88" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>5.6</v>
+        <v>-1.2</v>
       </c>
       <c r="M88" t="n">
-        <v>1965</v>
+        <v>2075</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F89" t="n">
-        <v>35.75</v>
+        <v>35.29</v>
       </c>
       <c r="G89" t="n">
-        <v>10.88</v>
+        <v>10.74</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.99</v>
+        <v>-1.29</v>
       </c>
       <c r="M89" t="n">
-        <v>1505</v>
+        <v>1550</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>88.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>8.65</v>
+        <v>8.66</v>
       </c>
       <c r="G90" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.23</v>
+        <v>0.11</v>
       </c>
       <c r="M90" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>54.4</v>
+        <v>52.8</v>
       </c>
       <c r="F91" t="n">
-        <v>8.19</v>
+        <v>7.95</v>
       </c>
       <c r="G91" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-1.98</v>
+        <v>-2.94</v>
       </c>
       <c r="M91" t="n">
-        <v>55.5</v>
+        <v>54.4</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>54</v>
+        <v>53.2</v>
       </c>
       <c r="F92" t="n">
-        <v>7.49</v>
+        <v>7.38</v>
       </c>
       <c r="G92" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0.19</v>
+        <v>-1.48</v>
       </c>
       <c r="M92" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>331</v>
+        <v>333.5</v>
       </c>
       <c r="F93" t="n">
-        <v>14.42</v>
+        <v>14.53</v>
       </c>
       <c r="G93" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.3</v>
+        <v>0.76</v>
       </c>
       <c r="M93" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="F94" t="n">
-        <v>6.89</v>
+        <v>7.34</v>
       </c>
       <c r="G94" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.12</v>
+        <v>6.51</v>
       </c>
       <c r="M94" t="n">
-        <v>2085</v>
+        <v>2150</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>186.5</v>
+        <v>189.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F96" t="n">
-        <v>15.73</v>
+        <v>15.68</v>
       </c>
       <c r="G96" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.03</v>
+        <v>-0.34</v>
       </c>
       <c r="M96" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>69</v>
+        <v>68.5</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="F98" t="n">
-        <v>4.89</v>
+        <v>4.78</v>
       </c>
       <c r="G98" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-1.05</v>
+        <v>-2.12</v>
       </c>
       <c r="M98" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>22.65</v>
+        <v>22.4</v>
       </c>
       <c r="F99" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="G99" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-1.95</v>
+        <v>-1.1</v>
       </c>
       <c r="M99" t="n">
-        <v>23.1</v>
+        <v>22.65</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>32</v>
+        <v>31.2</v>
       </c>
       <c r="F100" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="G100" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-4.05</v>
+        <v>-2.5</v>
       </c>
       <c r="M100" t="n">
-        <v>33.35</v>
+        <v>32</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>200.5</v>
+        <v>201</v>
       </c>
       <c r="F101" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="G101" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-0.99</v>
+        <v>0.25</v>
       </c>
       <c r="M101" t="n">
-        <v>202.5</v>
+        <v>200.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="F2" t="n">
-        <v>47.79</v>
+        <v>49.12</v>
       </c>
       <c r="G2" t="n">
-        <v>25.5</v>
+        <v>26.21</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.22</v>
+        <v>2.79</v>
       </c>
       <c r="M2" t="n">
-        <v>3440</v>
+        <v>3585</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="F3" t="n">
-        <v>15.91</v>
+        <v>16.02</v>
       </c>
       <c r="G3" t="n">
-        <v>8.99</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.94</v>
+        <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="F4" t="n">
-        <v>29.85</v>
+        <v>29.96</v>
       </c>
       <c r="G4" t="n">
-        <v>10.38</v>
+        <v>10.42</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>2500</v>
+        <v>2575</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>113</v>
+        <v>116.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.99</v>
+        <v>14.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
         <v>113</v>
@@ -9097,10 +9097,10 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>24.8</v>
+        <v>24.75</v>
       </c>
       <c r="F7" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="G7" t="n">
         <v>0.96</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>25.05</v>
+        <v>24.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>183.5</v>
+        <v>181</v>
       </c>
       <c r="F9" t="n">
-        <v>13.08</v>
+        <v>12.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>185</v>
+        <v>183.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.9</v>
+        <v>41.55</v>
       </c>
       <c r="F10" t="n">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.06</v>
+        <v>-0.84</v>
       </c>
       <c r="M10" t="n">
-        <v>42.35</v>
+        <v>41.9</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="F11" t="n">
-        <v>23.33</v>
+        <v>23.2</v>
       </c>
       <c r="G11" t="n">
-        <v>8.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.83</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="F12" t="n">
-        <v>23.86</v>
+        <v>24.81</v>
       </c>
       <c r="G12" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.77</v>
+        <v>3.95</v>
       </c>
       <c r="M12" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>169.5</v>
+        <v>173</v>
       </c>
       <c r="F13" t="n">
-        <v>18.23</v>
+        <v>18.6</v>
       </c>
       <c r="G13" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="M13" t="n">
-        <v>166</v>
+        <v>169.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.9</v>
+        <v>38.95</v>
       </c>
       <c r="F14" t="n">
-        <v>8.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.64</v>
+        <v>0.13</v>
       </c>
       <c r="M14" t="n">
-        <v>39.15</v>
+        <v>38.9</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="F15" t="n">
-        <v>32.6</v>
+        <v>32.21</v>
       </c>
       <c r="G15" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>-1.2</v>
       </c>
       <c r="M15" t="n">
-        <v>1965</v>
+        <v>2075</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F16" t="n">
-        <v>35.75</v>
+        <v>35.29</v>
       </c>
       <c r="G16" t="n">
-        <v>10.88</v>
+        <v>10.74</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.99</v>
+        <v>-1.29</v>
       </c>
       <c r="M16" t="n">
-        <v>1505</v>
+        <v>1550</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>8.65</v>
+        <v>8.66</v>
       </c>
       <c r="G17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.23</v>
+        <v>0.11</v>
       </c>
       <c r="M17" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>54.4</v>
+        <v>52.8</v>
       </c>
       <c r="F18" t="n">
-        <v>8.19</v>
+        <v>7.95</v>
       </c>
       <c r="G18" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.98</v>
+        <v>-2.94</v>
       </c>
       <c r="M18" t="n">
-        <v>55.5</v>
+        <v>54.4</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>53.2</v>
       </c>
       <c r="F19" t="n">
-        <v>7.49</v>
+        <v>7.38</v>
       </c>
       <c r="G19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.19</v>
+        <v>-1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>331</v>
+        <v>333.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.42</v>
+        <v>14.53</v>
       </c>
       <c r="G20" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.3</v>
+        <v>0.76</v>
       </c>
       <c r="M20" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="F21" t="n">
-        <v>6.89</v>
+        <v>7.34</v>
       </c>
       <c r="G21" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.12</v>
+        <v>6.51</v>
       </c>
       <c r="M21" t="n">
-        <v>2085</v>
+        <v>2150</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>186.5</v>
+        <v>189.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F23" t="n">
-        <v>15.73</v>
+        <v>15.68</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.03</v>
+        <v>-0.34</v>
       </c>
       <c r="M23" t="n">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F2" t="n">
-        <v>16.18</v>
+        <v>16.28</v>
       </c>
       <c r="G2" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.6</v>
+        <v>0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>156.5</v>
+        <v>154</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F3" t="n">
-        <v>23.2</v>
+        <v>23.17</v>
       </c>
       <c r="G3" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.35</v>
+        <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="F5" t="n">
-        <v>29.16</v>
+        <v>30.85</v>
       </c>
       <c r="G5" t="n">
-        <v>7.5</v>
+        <v>7.93</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>339.5</v>
+        <v>345</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="F6" t="n">
-        <v>14.37</v>
+        <v>14.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.12</v>
+        <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>140.5</v>
       </c>
       <c r="F7" t="n">
-        <v>19.5</v>
+        <v>19.57</v>
       </c>
       <c r="G7" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11028,7 +11028,7 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>139.5</v>
+        <v>140</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F8" t="n">
-        <v>16.74</v>
+        <v>16.88</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="F9" t="n">
-        <v>47.65</v>
+        <v>47.01</v>
       </c>
       <c r="G9" t="n">
-        <v>25.45</v>
+        <v>25.11</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-4.26</v>
+        <v>-1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>58.3</v>
+        <v>58.6</v>
       </c>
       <c r="F10" t="n">
-        <v>18.81</v>
+        <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.19</v>
+        <v>0.51</v>
       </c>
       <c r="M10" t="n">
-        <v>59</v>
+        <v>58.3</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="n">
-        <v>107.41</v>
+        <v>107.74</v>
       </c>
       <c r="G2" t="n">
-        <v>28.96</v>
+        <v>29.05</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.63</v>
+        <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1510</v>
+        <v>1595</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>16.94</v>
       </c>
       <c r="G4" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="M4" t="n">
         <v>153.5</v>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="F5" t="n">
-        <v>118.2</v>
+        <v>121.41</v>
       </c>
       <c r="G5" t="n">
-        <v>34.01</v>
+        <v>34.93</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>2.72</v>
       </c>
       <c r="M5" t="n">
-        <v>5310</v>
+        <v>5520</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>23.16</v>
+        <v>23.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11805,7 +11805,7 @@
         <v>0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.36</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.49</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>172.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.94</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.86</v>
+        <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.67</v>
+        <v>25.43</v>
       </c>
       <c r="G9" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>-0.95</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>167</v>
+        <v>175.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.91</v>
+        <v>19.88</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>7.05</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.47</v>
+        <v>5.09</v>
       </c>
       <c r="M10" t="n">
-        <v>169.5</v>
+        <v>167</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1180</v>
+        <v>1195</v>
       </c>
       <c r="F11" t="n">
-        <v>22.67</v>
+        <v>22.96</v>
       </c>
       <c r="G11" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
         <v>1180</v>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>180.5</v>
+        <v>182</v>
       </c>
       <c r="F12" t="n">
-        <v>22.51</v>
+        <v>22.69</v>
       </c>
       <c r="G12" t="n">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.87</v>
+        <v>0.83</v>
       </c>
       <c r="M12" t="n">
-        <v>170.5</v>
+        <v>180.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F13" t="n">
-        <v>34.85</v>
+        <v>34.97</v>
       </c>
       <c r="G13" t="n">
-        <v>7.06</v>
+        <v>7.08</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.86</v>
+        <v>0.34</v>
       </c>
       <c r="M13" t="n">
-        <v>281.5</v>
+        <v>298</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>146</v>
+        <v>145.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>211</v>
+        <v>210.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.01</v>
+        <v>18.96</v>
       </c>
       <c r="G15" t="n">
-        <v>5.35</v>
+        <v>5.34</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.24</v>
+        <v>-0.24</v>
       </c>
       <c r="M15" t="n">
-        <v>210.5</v>
+        <v>211</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8600</v>
+        <v>8375</v>
       </c>
       <c r="F16" t="n">
-        <v>220.46</v>
+        <v>214.69</v>
       </c>
       <c r="G16" t="n">
-        <v>85.59</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.859999999999999</v>
+        <v>-2.62</v>
       </c>
       <c r="M16" t="n">
-        <v>7900</v>
+        <v>8600</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="F2" t="n">
-        <v>63.81</v>
+        <v>65.25</v>
       </c>
       <c r="G2" t="n">
-        <v>17.73</v>
+        <v>18.13</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6.37</v>
+        <v>2.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1885</v>
+        <v>2005</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,10 +12882,10 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="F3" t="n">
-        <v>20.24</v>
+        <v>20.21</v>
       </c>
       <c r="G3" t="n">
         <v>1.01</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.58</v>
+        <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="F4" t="n">
-        <v>162.6</v>
+        <v>159.78</v>
       </c>
       <c r="G4" t="n">
-        <v>44.84</v>
+        <v>44.06</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5.96</v>
+        <v>-1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>6800</v>
+        <v>7205</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5700</v>
+        <v>5995</v>
       </c>
       <c r="F5" t="n">
-        <v>89.13</v>
+        <v>93.75</v>
       </c>
       <c r="G5" t="n">
-        <v>35.01</v>
+        <v>36.82</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9.93</v>
+        <v>5.18</v>
       </c>
       <c r="M5" t="n">
-        <v>5185</v>
+        <v>5700</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="F6" t="n">
-        <v>45.22</v>
+        <v>45.55</v>
       </c>
       <c r="G6" t="n">
-        <v>23.71</v>
+        <v>23.88</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.14</v>
+        <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>11.93</v>
+        <v>11.92</v>
       </c>
       <c r="G7" t="n">
         <v>1.67</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.51</v>
+        <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>97.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="F10" t="n">
-        <v>28.54</v>
+        <v>28.27</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9.779999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="M10" t="n">
-        <v>961</v>
+        <v>1055</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>27.13</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.51</v>
+        <v>0.51</v>
       </c>
       <c r="M11" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>3950</v>
+        <v>4180</v>
       </c>
       <c r="F12" t="n">
-        <v>57.93</v>
+        <v>61.31</v>
       </c>
       <c r="G12" t="n">
-        <v>5.64</v>
+        <v>5.97</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.67</v>
+        <v>5.82</v>
       </c>
       <c r="M12" t="n">
-        <v>3810</v>
+        <v>3950</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1600</v>
+        <v>1645</v>
       </c>
       <c r="F2" t="n">
-        <v>107.74</v>
+        <v>110.77</v>
       </c>
       <c r="G2" t="n">
-        <v>29.05</v>
+        <v>29.87</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.31</v>
+        <v>2.81</v>
       </c>
       <c r="M2" t="n">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.9</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>9.49</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10.02</v>
       </c>
       <c r="M3" t="n">
         <v>40.9</v>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.33</v>
+        <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5670</v>
+        <v>5530</v>
       </c>
       <c r="F5" t="n">
-        <v>121.41</v>
+        <v>118.42</v>
       </c>
       <c r="G5" t="n">
-        <v>34.93</v>
+        <v>34.07</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.72</v>
+        <v>-2.47</v>
       </c>
       <c r="M5" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.25</v>
+        <v>23.16</v>
       </c>
       <c r="G6" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.41</v>
+        <v>-0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172.5</v>
+        <v>173.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>22.13</v>
       </c>
       <c r="G8" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>172</v>
+        <v>172.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>104.5</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>25.43</v>
+        <v>25.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.95</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>175.5</v>
+        <v>178</v>
       </c>
       <c r="F10" t="n">
-        <v>19.88</v>
+        <v>20.16</v>
       </c>
       <c r="G10" t="n">
-        <v>7.05</v>
+        <v>7.15</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.09</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>167</v>
+        <v>175.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1195</v>
+        <v>1230</v>
       </c>
       <c r="F11" t="n">
-        <v>22.96</v>
+        <v>23.63</v>
       </c>
       <c r="G11" t="n">
-        <v>4.36</v>
+        <v>4.49</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>2.93</v>
       </c>
       <c r="M11" t="n">
-        <v>1180</v>
+        <v>1195</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F12" t="n">
-        <v>22.69</v>
+        <v>22.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.83</v>
+        <v>-2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>180.5</v>
+        <v>182</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F13" t="n">
-        <v>34.97</v>
+        <v>35.09</v>
       </c>
       <c r="G13" t="n">
-        <v>7.08</v>
+        <v>7.11</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>210.5</v>
+        <v>213.5</v>
       </c>
       <c r="F15" t="n">
-        <v>18.96</v>
+        <v>19.23</v>
       </c>
       <c r="G15" t="n">
-        <v>5.34</v>
+        <v>5.42</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.24</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>211</v>
+        <v>210.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8375</v>
+        <v>8460</v>
       </c>
       <c r="F16" t="n">
-        <v>214.69</v>
+        <v>216.87</v>
       </c>
       <c r="G16" t="n">
-        <v>83.34999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-2.62</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>8600</v>
+        <v>8375</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1650</v>
+        <v>1815</v>
       </c>
       <c r="F17" t="n">
-        <v>48.82</v>
+        <v>53.7</v>
       </c>
       <c r="G17" t="n">
-        <v>9.91</v>
+        <v>10.9</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-3.23</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>1705</v>
+        <v>1650</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>13100</v>
+        <v>11790</v>
       </c>
       <c r="F18" t="n">
-        <v>72.22</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>36.98</v>
+        <v>33.29</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.91</v>
+        <v>-10</v>
       </c>
       <c r="M18" t="n">
-        <v>13355</v>
+        <v>13100</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="F19" t="n">
-        <v>87.59</v>
+        <v>86.73</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>16.83</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="M19" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>46.7</v>
+        <v>49.45</v>
       </c>
       <c r="G20" t="n">
-        <v>6.98</v>
+        <v>7.4</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-0.58</v>
+        <v>5.88</v>
       </c>
       <c r="M20" t="n">
-        <v>85.5</v>
+        <v>85</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6130</v>
+        <v>5520</v>
       </c>
       <c r="F21" t="n">
-        <v>100.36</v>
+        <v>90.37</v>
       </c>
       <c r="G21" t="n">
-        <v>25.92</v>
+        <v>23.34</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1.21</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>6205</v>
+        <v>6130</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="F22" t="n">
-        <v>59.95</v>
+        <v>61.22</v>
       </c>
       <c r="G22" t="n">
-        <v>30.17</v>
+        <v>30.82</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.08</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.3</v>
+        <v>18.65</v>
       </c>
       <c r="F23" t="n">
-        <v>41.59</v>
+        <v>42.39</v>
       </c>
       <c r="G23" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
         <v>18.3</v>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1755</v>
+        <v>1720</v>
       </c>
       <c r="F24" t="n">
-        <v>89.13</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>21.75</v>
+        <v>21.32</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1.4</v>
+        <v>-1.99</v>
       </c>
       <c r="M24" t="n">
-        <v>1780</v>
+        <v>1755</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>58.3</v>
+        <v>58.9</v>
       </c>
       <c r="F25" t="n">
-        <v>71.09999999999999</v>
+        <v>71.83</v>
       </c>
       <c r="G25" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.87</v>
+        <v>1.03</v>
       </c>
       <c r="M25" t="n">
-        <v>57.8</v>
+        <v>58.3</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2920</v>
+        <v>3140</v>
       </c>
       <c r="F26" t="n">
-        <v>251.29</v>
+        <v>270.22</v>
       </c>
       <c r="G26" t="n">
-        <v>57.24</v>
+        <v>61.56</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-2.67</v>
+        <v>7.53</v>
       </c>
       <c r="M26" t="n">
-        <v>3000</v>
+        <v>2920</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="F27" t="n">
-        <v>53.84</v>
+        <v>52.97</v>
       </c>
       <c r="G27" t="n">
-        <v>8.41</v>
+        <v>8.27</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.27</v>
+        <v>-1.61</v>
       </c>
       <c r="M27" t="n">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="n">
-        <v>57.54</v>
+        <v>59.01</v>
       </c>
       <c r="G28" t="n">
-        <v>11.92</v>
+        <v>12.23</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-1.26</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>1190</v>
+        <v>1175</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="F29" t="n">
-        <v>92.95999999999999</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>18.22</v>
+        <v>18.57</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-5.02</v>
+        <v>1.94</v>
       </c>
       <c r="M29" t="n">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3055</v>
+        <v>3020</v>
       </c>
       <c r="F30" t="n">
-        <v>72.05</v>
+        <v>71.23</v>
       </c>
       <c r="G30" t="n">
-        <v>9.93</v>
+        <v>9.82</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-1.61</v>
+        <v>-1.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3105</v>
+        <v>3055</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F31" t="n">
-        <v>107.71</v>
+        <v>108.52</v>
       </c>
       <c r="G31" t="n">
-        <v>13.85</v>
+        <v>13.95</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-3.1</v>
+        <v>0.75</v>
       </c>
       <c r="M31" t="n">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="F32" t="n">
-        <v>46.74</v>
+        <v>46.42</v>
       </c>
       <c r="G32" t="n">
-        <v>11.59</v>
+        <v>11.51</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.27</v>
+        <v>-0.68</v>
       </c>
       <c r="M32" t="n">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="F33" t="n">
-        <v>42.09</v>
+        <v>43.57</v>
       </c>
       <c r="G33" t="n">
-        <v>7.27</v>
+        <v>7.52</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-0.16</v>
+        <v>3.52</v>
       </c>
       <c r="M33" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>6855</v>
+        <v>6845</v>
       </c>
       <c r="F34" t="n">
-        <v>36.46</v>
+        <v>36.41</v>
       </c>
       <c r="G34" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.86</v>
+        <v>-0.15</v>
       </c>
       <c r="M34" t="n">
-        <v>6730</v>
+        <v>6855</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>4920</v>
+        <v>4835</v>
       </c>
       <c r="F35" t="n">
-        <v>81.26000000000001</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>18.51</v>
+        <v>18.19</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-4.74</v>
+        <v>-1.73</v>
       </c>
       <c r="M35" t="n">
-        <v>5165</v>
+        <v>4920</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>2050</v>
+        <v>1990</v>
       </c>
       <c r="F36" t="n">
-        <v>65.25</v>
+        <v>63.34</v>
       </c>
       <c r="G36" t="n">
-        <v>18.13</v>
+        <v>17.6</v>
       </c>
       <c r="H36" t="n">
         <v>59.1</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.24</v>
+        <v>-2.93</v>
       </c>
       <c r="M36" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -3362,13 +3362,13 @@
         <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>20.21</v>
+        <v>20.62</v>
       </c>
       <c r="G37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="H37" t="n">
         <v>19</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-0.15</v>
+        <v>2.04</v>
       </c>
       <c r="M37" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
@@ -3445,13 +3445,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>7080</v>
+        <v>6805</v>
       </c>
       <c r="F38" t="n">
-        <v>159.78</v>
+        <v>153.58</v>
       </c>
       <c r="G38" t="n">
-        <v>44.06</v>
+        <v>42.35</v>
       </c>
       <c r="H38" t="n">
         <v>70.2</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-1.73</v>
+        <v>-3.88</v>
       </c>
       <c r="M38" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3524,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>5995</v>
+        <v>5950</v>
       </c>
       <c r="F39" t="n">
-        <v>93.75</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>36.82</v>
+        <v>36.55</v>
       </c>
       <c r="H39" t="n">
         <v>75.3</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.18</v>
+        <v>-0.75</v>
       </c>
       <c r="M39" t="n">
-        <v>5700</v>
+        <v>5995</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3603,13 +3603,13 @@
         <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F40" t="n">
-        <v>45.55</v>
+        <v>45.94</v>
       </c>
       <c r="G40" t="n">
-        <v>23.88</v>
+        <v>24.09</v>
       </c>
       <c r="H40" t="n">
         <v>47.5</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="M40" t="n">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
@@ -3686,13 +3686,13 @@
         <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="F41" t="n">
-        <v>11.92</v>
+        <v>11.89</v>
       </c>
       <c r="G41" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H41" t="n">
         <v>11</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="M41" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3765,13 +3765,13 @@
         <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" t="n">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="G42" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H42" t="n">
         <v>13.4</v>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="M42" t="n">
         <v>156</v>
@@ -3927,13 +3927,13 @@
         <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>1045</v>
+        <v>1085</v>
       </c>
       <c r="F44" t="n">
-        <v>28.27</v>
+        <v>29.36</v>
       </c>
       <c r="G44" t="n">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="H44" t="n">
         <v>21.4</v>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-0.95</v>
+        <v>3.83</v>
       </c>
       <c r="M44" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4010,13 +4010,13 @@
         <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>197</v>
+        <v>199.5</v>
       </c>
       <c r="F45" t="n">
-        <v>27.13</v>
+        <v>27.48</v>
       </c>
       <c r="G45" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="H45" t="n">
         <v>30.9</v>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.51</v>
+        <v>1.27</v>
       </c>
       <c r="M45" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4093,13 +4093,13 @@
         <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>4180</v>
+        <v>4190</v>
       </c>
       <c r="F46" t="n">
-        <v>61.31</v>
+        <v>61.45</v>
       </c>
       <c r="G46" t="n">
-        <v>5.97</v>
+        <v>5.99</v>
       </c>
       <c r="H46" t="n">
         <v>51.7</v>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5.82</v>
+        <v>0.24</v>
       </c>
       <c r="M46" t="n">
-        <v>3950</v>
+        <v>4180</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4176,13 +4176,13 @@
         <v>79</v>
       </c>
       <c r="E47" t="n">
-        <v>228</v>
+        <v>243.5</v>
       </c>
       <c r="F47" t="n">
-        <v>23.22</v>
+        <v>24.8</v>
       </c>
       <c r="G47" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0.44</v>
+        <v>6.8</v>
       </c>
       <c r="M47" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>128.5</v>
+        <v>131.5</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4330,13 +4330,13 @@
         <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>256</v>
+        <v>257.5</v>
       </c>
       <c r="F49" t="n">
-        <v>28.04</v>
+        <v>28.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.61</v>
+        <v>0.59</v>
       </c>
       <c r="M49" t="n">
-        <v>249.5</v>
+        <v>256</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
@@ -4390,12 +4390,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4404,19 +4404,21 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>525</v>
+        <v>741</v>
       </c>
       <c r="F50" t="n">
-        <v>20.37</v>
+        <v>26.87</v>
       </c>
       <c r="G50" t="n">
-        <v>5.62</v>
+        <v>7.57</v>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>27</v>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
@@ -4424,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.85</v>
       </c>
       <c r="M50" t="n">
-        <v>530</v>
+        <v>755</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4436,23 +4438,23 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>17.9</v>
+        <v>31.7</v>
       </c>
       <c r="Q50" t="n">
         <v>1.5</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.1</v>
+        <v>3.8</v>
       </c>
       <c r="S50" t="n">
-        <v>730.1</v>
+        <v>21.9</v>
       </c>
       <c r="T50" t="n">
-        <v>45.2</v>
+        <v>32.2</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4469,12 +4471,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4483,20 +4485,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>755</v>
+        <v>140</v>
       </c>
       <c r="F51" t="n">
-        <v>27.37</v>
+        <v>26.12</v>
       </c>
       <c r="G51" t="n">
-        <v>7.72</v>
+        <v>3.25</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>186.3</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4505,10 +4507,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>755</v>
+        <v>127.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4517,28 +4519,28 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>31.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="R51" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S51" t="n">
-        <v>21.9</v>
+        <v>37</v>
       </c>
       <c r="T51" t="n">
-        <v>32.2</v>
+        <v>35.8</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4550,93 +4552,91 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E52" t="n">
-        <v>127.5</v>
+        <v>670</v>
       </c>
       <c r="F52" t="n">
-        <v>23.79</v>
+        <v>30.34</v>
       </c>
       <c r="G52" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>8.26</v>
+      </c>
+      <c r="H52" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I52" t="n">
-        <v>186.3</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.16</v>
+        <v>1.06</v>
       </c>
       <c r="M52" t="n">
-        <v>129</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>10.7</v>
+        <v>19.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.4</v>
+        <v>10.6</v>
       </c>
       <c r="S52" t="n">
-        <v>37</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4645,25 +4645,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E53" t="n">
-        <v>663</v>
+        <v>743</v>
       </c>
       <c r="F53" t="n">
-        <v>30.03</v>
+        <v>45.58</v>
       </c>
       <c r="G53" t="n">
-        <v>8.18</v>
+        <v>6.12</v>
       </c>
       <c r="H53" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I53" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4671,78 +4671,78 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-2.36</v>
+        <v>-2.49</v>
       </c>
       <c r="M53" t="n">
-        <v>679</v>
+        <v>762</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R53" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S53" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>762</v>
+        <v>60.3</v>
       </c>
       <c r="F54" t="n">
-        <v>46.75</v>
+        <v>16.57</v>
       </c>
       <c r="G54" t="n">
-        <v>6.27</v>
+        <v>2.52</v>
       </c>
       <c r="H54" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I54" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J54" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4750,30 +4750,30 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="M54" t="n">
-        <v>744</v>
+        <v>58.9</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R54" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S54" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T54" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U54" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4803,25 +4803,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E55" t="n">
-        <v>58.9</v>
+        <v>178</v>
       </c>
       <c r="F55" t="n">
-        <v>16.18</v>
+        <v>16.26</v>
       </c>
       <c r="G55" t="n">
-        <v>2.46</v>
+        <v>1.77</v>
       </c>
       <c r="H55" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I55" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J55" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4829,34 +4829,34 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.34</v>
+        <v>0.85</v>
       </c>
       <c r="M55" t="n">
-        <v>59.1</v>
+        <v>176.5</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R55" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S55" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U55" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -4868,91 +4868,89 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E56" t="n">
-        <v>176.5</v>
+        <v>377</v>
       </c>
       <c r="F56" t="n">
-        <v>16.12</v>
+        <v>19.52</v>
       </c>
       <c r="G56" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>49</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
         <v>1.75</v>
       </c>
-      <c r="H56" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>🟡未來合理</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="M56" t="n">
-        <v>177</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
+        <v>370.5</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.03</v>
+        <v>1.09</v>
       </c>
       <c r="R56" t="n">
-        <v>30.2</v>
+        <v>24.2</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4961,20 +4959,20 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E57" t="n">
-        <v>370.5</v>
+        <v>168</v>
       </c>
       <c r="F57" t="n">
-        <v>19.19</v>
+        <v>18.9</v>
       </c>
       <c r="G57" t="n">
-        <v>5.44</v>
+        <v>3.99</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>49</v>
+        <v>57.1</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4983,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-1.59</v>
+        <v>0.6</v>
       </c>
       <c r="M57" t="n">
-        <v>376.5</v>
+        <v>167</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4995,24 +4993,24 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>29.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="R57" t="n">
-        <v>24.2</v>
+        <v>11.1</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="T57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5024,34 +5022,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>167</v>
+        <v>96.8</v>
       </c>
       <c r="F58" t="n">
-        <v>18.79</v>
+        <v>18.47</v>
       </c>
       <c r="G58" t="n">
-        <v>3.96</v>
+        <v>1.89</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>57.1</v>
+        <v>11.3</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5060,31 +5058,35 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.3</v>
+        <v>-1.02</v>
       </c>
       <c r="M58" t="n">
-        <v>166.5</v>
+        <v>97.8</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P58" t="n">
-        <v>18.6</v>
+        <v>9.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.74</v>
+        <v>1.99</v>
       </c>
       <c r="R58" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>3.6</v>
+        <v>-2.7</v>
       </c>
       <c r="T58" t="n">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
@@ -5101,12 +5103,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5115,20 +5117,20 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>97.8</v>
+        <v>159.5</v>
       </c>
       <c r="F59" t="n">
-        <v>18.66</v>
+        <v>17.78</v>
       </c>
       <c r="G59" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5137,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.19</v>
+        <v>2.57</v>
       </c>
       <c r="M59" t="n">
-        <v>95.7</v>
+        <v>155.5</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5149,23 +5151,23 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="S59" t="n">
-        <v>-2.7</v>
+        <v>14.6</v>
       </c>
       <c r="T59" t="n">
-        <v>20.3</v>
+        <v>34.2</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
@@ -5182,12 +5184,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5196,20 +5198,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>155.5</v>
+        <v>295</v>
       </c>
       <c r="F60" t="n">
-        <v>17.34</v>
+        <v>18.33</v>
       </c>
       <c r="G60" t="n">
-        <v>1.71</v>
+        <v>6.66</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5218,40 +5220,36 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-0.96</v>
+        <v>1.03</v>
       </c>
       <c r="M60" t="n">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>5.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="R60" t="n">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
       <c r="S60" t="n">
-        <v>14.6</v>
+        <v>812.4</v>
       </c>
       <c r="T60" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5263,12 +5261,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5277,20 +5275,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>292</v>
+        <v>186.5</v>
       </c>
       <c r="F61" t="n">
-        <v>18.15</v>
+        <v>15.74</v>
       </c>
       <c r="G61" t="n">
-        <v>6.6</v>
+        <v>1.87</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>9.6</v>
+        <v>49.2</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -5299,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6.18</v>
+        <v>-1.06</v>
       </c>
       <c r="M61" t="n">
-        <v>275</v>
+        <v>188.5</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5311,24 +5309,24 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>30.7</v>
+        <v>14.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R61" t="n">
-        <v>20.4</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>812.4</v>
+        <v>10.3</v>
       </c>
       <c r="T61" t="n">
-        <v>34.6</v>
+        <v>20.2</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5340,12 +5338,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5354,20 +5352,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>188.5</v>
+        <v>780</v>
       </c>
       <c r="F62" t="n">
-        <v>15.91</v>
+        <v>18.02</v>
       </c>
       <c r="G62" t="n">
-        <v>1.89</v>
+        <v>14.54</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>49.2</v>
+        <v>-8.1</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5379,28 +5377,32 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>188.5</v>
+        <v>780</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P62" t="n">
-        <v>14.4</v>
+        <v>94.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>18.2</v>
       </c>
       <c r="S62" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="T62" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
@@ -5417,35 +5419,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>780</v>
+        <v>514</v>
       </c>
       <c r="F63" t="n">
-        <v>18.02</v>
+        <v>19.95</v>
       </c>
       <c r="G63" t="n">
-        <v>14.54</v>
+        <v>5.5</v>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
-        <v>-8.1</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1.76</v>
+        <v>-2.1</v>
       </c>
       <c r="M63" t="n">
-        <v>794</v>
+        <v>525</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>94.5</v>
+        <v>17.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="R63" t="n">
-        <v>18.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>730.1</v>
       </c>
       <c r="T63" t="n">
-        <v>19.6</v>
+        <v>45.2</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>177.5</v>
+        <v>179.5</v>
       </c>
       <c r="F64" t="n">
-        <v>19.57</v>
+        <v>19.79</v>
       </c>
       <c r="G64" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1.93</v>
+        <v>1.13</v>
       </c>
       <c r="M64" t="n">
-        <v>181</v>
+        <v>177.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.65</v>
+        <v>49.4</v>
       </c>
       <c r="F65" t="n">
-        <v>12.26</v>
+        <v>12.2</v>
       </c>
       <c r="G65" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="M65" t="n">
-        <v>49.4</v>
+        <v>49.65</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="F67" t="n">
-        <v>23.17</v>
+        <v>22.64</v>
       </c>
       <c r="G67" t="n">
-        <v>5.46</v>
+        <v>5.34</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.16</v>
+        <v>-2.26</v>
       </c>
       <c r="M67" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5833,13 +5833,13 @@
         <v>91</v>
       </c>
       <c r="E68" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
       <c r="F68" t="n">
-        <v>15.18</v>
+        <v>15.25</v>
       </c>
       <c r="G68" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="H68" t="n">
         <v>15</v>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="M68" t="n">
         <v>117.5</v>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F69" t="n">
-        <v>30.85</v>
+        <v>31.36</v>
       </c>
       <c r="G69" t="n">
-        <v>7.93</v>
+        <v>8.07</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.8</v>
+        <v>1.64</v>
       </c>
       <c r="M69" t="n">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>82.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>14.48</v>
+        <v>14.62</v>
       </c>
       <c r="G70" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="M70" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>140.5</v>
+        <v>139.5</v>
       </c>
       <c r="F71" t="n">
-        <v>19.57</v>
+        <v>19.43</v>
       </c>
       <c r="G71" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.36</v>
+        <v>-0.71</v>
       </c>
       <c r="M71" t="n">
-        <v>140</v>
+        <v>140.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F72" t="n">
-        <v>16.88</v>
+        <v>16.61</v>
       </c>
       <c r="G72" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.79</v>
+        <v>-1.56</v>
       </c>
       <c r="M72" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="F73" t="n">
-        <v>47.01</v>
+        <v>46.59</v>
       </c>
       <c r="G73" t="n">
-        <v>25.11</v>
+        <v>24.88</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1.33</v>
+        <v>-0.9</v>
       </c>
       <c r="M73" t="n">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="F74" t="n">
-        <v>18.9</v>
+        <v>18.74</v>
       </c>
       <c r="G74" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.51</v>
+        <v>-0.85</v>
       </c>
       <c r="M74" t="n">
-        <v>58.3</v>
+        <v>58.6</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3685</v>
+        <v>3545</v>
       </c>
       <c r="F75" t="n">
-        <v>49.12</v>
+        <v>47.25</v>
       </c>
       <c r="G75" t="n">
-        <v>26.21</v>
+        <v>25.22</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.79</v>
+        <v>-3.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="F76" t="n">
-        <v>16.02</v>
+        <v>15.85</v>
       </c>
       <c r="G76" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.63</v>
+        <v>-1.01</v>
       </c>
       <c r="M76" t="n">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>117.5</v>
+        <v>115.5</v>
       </c>
       <c r="F78" t="n">
-        <v>16.76</v>
+        <v>16.48</v>
       </c>
       <c r="G78" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="M78" t="n">
         <v>117.5</v>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>116.5</v>
+        <v>118</v>
       </c>
       <c r="F79" t="n">
-        <v>14.42</v>
+        <v>14.6</v>
       </c>
       <c r="G79" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="M79" t="n">
-        <v>113</v>
+        <v>116.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6791,10 +6791,10 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>24.75</v>
+        <v>24.8</v>
       </c>
       <c r="F80" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="G80" t="n">
         <v>0.96</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="M80" t="n">
-        <v>24.8</v>
+        <v>24.75</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F81" t="n">
-        <v>11.98</v>
+        <v>12.1</v>
       </c>
       <c r="G81" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M81" t="n">
         <v>104</v>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F82" t="n">
-        <v>12.9</v>
+        <v>13.11</v>
       </c>
       <c r="G82" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-1.36</v>
+        <v>1.66</v>
       </c>
       <c r="M82" t="n">
-        <v>183.5</v>
+        <v>181</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>41.55</v>
+        <v>41.95</v>
       </c>
       <c r="F83" t="n">
-        <v>8.75</v>
+        <v>8.83</v>
       </c>
       <c r="G83" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-0.84</v>
+        <v>0.96</v>
       </c>
       <c r="M83" t="n">
-        <v>41.9</v>
+        <v>41.55</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="F84" t="n">
-        <v>23.2</v>
+        <v>22.86</v>
       </c>
       <c r="G84" t="n">
-        <v>8.890000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.47</v>
       </c>
       <c r="M84" t="n">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F85" t="n">
-        <v>24.81</v>
+        <v>24.94</v>
       </c>
       <c r="G85" t="n">
-        <v>5.46</v>
+        <v>5.49</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.95</v>
+        <v>0.52</v>
       </c>
       <c r="M85" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>173</v>
+        <v>171.5</v>
       </c>
       <c r="F86" t="n">
-        <v>18.6</v>
+        <v>18.44</v>
       </c>
       <c r="G86" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.06</v>
+        <v>-0.87</v>
       </c>
       <c r="M86" t="n">
-        <v>169.5</v>
+        <v>173</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.95</v>
+        <v>39.3</v>
       </c>
       <c r="F87" t="n">
-        <v>8.029999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="G87" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.13</v>
+        <v>0.9</v>
       </c>
       <c r="M87" t="n">
-        <v>38.9</v>
+        <v>38.95</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="F88" t="n">
-        <v>32.21</v>
+        <v>31.66</v>
       </c>
       <c r="G88" t="n">
-        <v>16.6</v>
+        <v>16.31</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1.2</v>
+        <v>-1.71</v>
       </c>
       <c r="M88" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F89" t="n">
-        <v>35.29</v>
+        <v>35.17</v>
       </c>
       <c r="G89" t="n">
-        <v>10.74</v>
+        <v>10.7</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-1.29</v>
+        <v>-0.33</v>
       </c>
       <c r="M89" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>88.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="F90" t="n">
-        <v>8.66</v>
+        <v>8.81</v>
       </c>
       <c r="G90" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.11</v>
+        <v>1.81</v>
       </c>
       <c r="M90" t="n">
-        <v>88.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="F91" t="n">
-        <v>7.95</v>
+        <v>8.01</v>
       </c>
       <c r="G91" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-2.94</v>
+        <v>0.76</v>
       </c>
       <c r="M91" t="n">
-        <v>54.4</v>
+        <v>52.8</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-1.48</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>54</v>
+        <v>53.2</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>333.5</v>
+        <v>335</v>
       </c>
       <c r="F93" t="n">
-        <v>14.53</v>
+        <v>14.6</v>
       </c>
       <c r="G93" t="n">
-        <v>5.28</v>
+        <v>5.3</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="M93" t="n">
-        <v>331</v>
+        <v>333.5</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2290</v>
+        <v>2240</v>
       </c>
       <c r="F94" t="n">
-        <v>7.34</v>
+        <v>7.18</v>
       </c>
       <c r="G94" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>6.51</v>
+        <v>-2.18</v>
       </c>
       <c r="M94" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>189.5</v>
+        <v>185</v>
       </c>
       <c r="F95" t="n">
-        <v>15.05</v>
+        <v>14.69</v>
       </c>
       <c r="G95" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
       <c r="M95" t="n">
         <v>189.5</v>
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="F96" t="n">
-        <v>15.68</v>
+        <v>15.52</v>
       </c>
       <c r="G96" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-0.34</v>
+        <v>-1.02</v>
       </c>
       <c r="M96" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,10 +8170,10 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="G97" t="n">
         <v>1.07</v>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="M97" t="n">
         <v>68.5</v>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F98" t="n">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="G98" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-2.12</v>
+        <v>-1.35</v>
       </c>
       <c r="M98" t="n">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>22.4</v>
+        <v>22.55</v>
       </c>
       <c r="F99" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="G99" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>-1.1</v>
+        <v>0.67</v>
       </c>
       <c r="M99" t="n">
-        <v>22.65</v>
+        <v>22.4</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>31.2</v>
+        <v>31.35</v>
       </c>
       <c r="F100" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="G100" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-2.5</v>
+        <v>0.48</v>
       </c>
       <c r="M100" t="n">
-        <v>32</v>
+        <v>31.2</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="G101" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M101" t="n">
-        <v>200.5</v>
+        <v>201</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3685</v>
+        <v>3545</v>
       </c>
       <c r="F2" t="n">
-        <v>49.12</v>
+        <v>47.25</v>
       </c>
       <c r="G2" t="n">
-        <v>26.21</v>
+        <v>25.22</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.79</v>
+        <v>-3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="F3" t="n">
-        <v>16.02</v>
+        <v>15.85</v>
       </c>
       <c r="G3" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.63</v>
+        <v>-1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>117.5</v>
+        <v>115.5</v>
       </c>
       <c r="F5" t="n">
-        <v>16.76</v>
+        <v>16.48</v>
       </c>
       <c r="G5" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="M5" t="n">
         <v>117.5</v>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>116.5</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>14.42</v>
+        <v>14.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>113</v>
+        <v>116.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,10 +9097,10 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>24.75</v>
+        <v>24.8</v>
       </c>
       <c r="F7" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="G7" t="n">
         <v>0.96</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>24.8</v>
+        <v>24.75</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>11.98</v>
+        <v>12.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M8" t="n">
         <v>104</v>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F9" t="n">
-        <v>12.9</v>
+        <v>13.11</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.36</v>
+        <v>1.66</v>
       </c>
       <c r="M9" t="n">
-        <v>183.5</v>
+        <v>181</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.55</v>
+        <v>41.95</v>
       </c>
       <c r="F10" t="n">
-        <v>8.75</v>
+        <v>8.83</v>
       </c>
       <c r="G10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.84</v>
+        <v>0.96</v>
       </c>
       <c r="M10" t="n">
-        <v>41.9</v>
+        <v>41.55</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="F11" t="n">
-        <v>23.2</v>
+        <v>22.86</v>
       </c>
       <c r="G11" t="n">
-        <v>8.890000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F12" t="n">
-        <v>24.81</v>
+        <v>24.94</v>
       </c>
       <c r="G12" t="n">
-        <v>5.46</v>
+        <v>5.49</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.95</v>
+        <v>0.52</v>
       </c>
       <c r="M12" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>173</v>
+        <v>171.5</v>
       </c>
       <c r="F13" t="n">
-        <v>18.6</v>
+        <v>18.44</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.06</v>
+        <v>-0.87</v>
       </c>
       <c r="M13" t="n">
-        <v>169.5</v>
+        <v>173</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.95</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="n">
-        <v>8.029999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.13</v>
+        <v>0.9</v>
       </c>
       <c r="M14" t="n">
-        <v>38.9</v>
+        <v>38.95</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="F15" t="n">
-        <v>32.21</v>
+        <v>31.66</v>
       </c>
       <c r="G15" t="n">
-        <v>16.6</v>
+        <v>16.31</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.2</v>
+        <v>-1.71</v>
       </c>
       <c r="M15" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F16" t="n">
-        <v>35.29</v>
+        <v>35.17</v>
       </c>
       <c r="G16" t="n">
-        <v>10.74</v>
+        <v>10.7</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.29</v>
+        <v>-0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>88.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>8.66</v>
+        <v>8.81</v>
       </c>
       <c r="G17" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.11</v>
+        <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>88.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="F18" t="n">
-        <v>7.95</v>
+        <v>8.01</v>
       </c>
       <c r="G18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-2.94</v>
+        <v>0.76</v>
       </c>
       <c r="M18" t="n">
-        <v>54.4</v>
+        <v>52.8</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.48</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>54</v>
+        <v>53.2</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>333.5</v>
+        <v>335</v>
       </c>
       <c r="F20" t="n">
-        <v>14.53</v>
+        <v>14.6</v>
       </c>
       <c r="G20" t="n">
-        <v>5.28</v>
+        <v>5.3</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="M20" t="n">
-        <v>331</v>
+        <v>333.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2290</v>
+        <v>2240</v>
       </c>
       <c r="F21" t="n">
-        <v>7.34</v>
+        <v>7.18</v>
       </c>
       <c r="G21" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.51</v>
+        <v>-2.18</v>
       </c>
       <c r="M21" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>189.5</v>
+        <v>185</v>
       </c>
       <c r="F22" t="n">
-        <v>15.05</v>
+        <v>14.69</v>
       </c>
       <c r="G22" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-2.37</v>
       </c>
       <c r="M22" t="n">
         <v>189.5</v>
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="F23" t="n">
-        <v>15.68</v>
+        <v>15.52</v>
       </c>
       <c r="G23" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.34</v>
+        <v>-1.02</v>
       </c>
       <c r="M23" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="F3" t="n">
-        <v>23.17</v>
+        <v>22.64</v>
       </c>
       <c r="G3" t="n">
-        <v>5.46</v>
+        <v>5.34</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.16</v>
+        <v>-2.26</v>
       </c>
       <c r="M3" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>15.18</v>
+        <v>15.25</v>
       </c>
       <c r="G4" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="M4" t="n">
         <v>117.5</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F5" t="n">
-        <v>30.85</v>
+        <v>31.36</v>
       </c>
       <c r="G5" t="n">
-        <v>7.93</v>
+        <v>8.07</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>82.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>14.48</v>
+        <v>14.62</v>
       </c>
       <c r="G6" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="M6" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>140.5</v>
+        <v>139.5</v>
       </c>
       <c r="F7" t="n">
-        <v>19.57</v>
+        <v>19.43</v>
       </c>
       <c r="G7" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.36</v>
+        <v>-0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>140</v>
+        <v>140.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F8" t="n">
-        <v>16.88</v>
+        <v>16.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.79</v>
+        <v>-1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="F9" t="n">
-        <v>47.01</v>
+        <v>46.59</v>
       </c>
       <c r="G9" t="n">
-        <v>25.11</v>
+        <v>24.88</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.33</v>
+        <v>-0.9</v>
       </c>
       <c r="M9" t="n">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="F10" t="n">
-        <v>18.9</v>
+        <v>18.74</v>
       </c>
       <c r="G10" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.51</v>
+        <v>-0.85</v>
       </c>
       <c r="M10" t="n">
-        <v>58.3</v>
+        <v>58.6</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1600</v>
+        <v>1645</v>
       </c>
       <c r="F2" t="n">
-        <v>107.74</v>
+        <v>110.77</v>
       </c>
       <c r="G2" t="n">
-        <v>29.05</v>
+        <v>29.87</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.31</v>
+        <v>2.81</v>
       </c>
       <c r="M2" t="n">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>40.9</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>9.49</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10.02</v>
       </c>
       <c r="M3" t="n">
         <v>40.9</v>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.33</v>
+        <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5670</v>
+        <v>5530</v>
       </c>
       <c r="F5" t="n">
-        <v>121.41</v>
+        <v>118.42</v>
       </c>
       <c r="G5" t="n">
-        <v>34.93</v>
+        <v>34.07</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.72</v>
+        <v>-2.47</v>
       </c>
       <c r="M5" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.25</v>
+        <v>23.16</v>
       </c>
       <c r="G6" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.41</v>
+        <v>-0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>102</v>
+        <v>103.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>172.5</v>
+        <v>173.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>22.13</v>
       </c>
       <c r="G8" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>172</v>
+        <v>172.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>104.5</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>25.43</v>
+        <v>25.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.95</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>175.5</v>
+        <v>178</v>
       </c>
       <c r="F10" t="n">
-        <v>19.88</v>
+        <v>20.16</v>
       </c>
       <c r="G10" t="n">
-        <v>7.05</v>
+        <v>7.15</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.09</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>167</v>
+        <v>175.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1195</v>
+        <v>1230</v>
       </c>
       <c r="F11" t="n">
-        <v>22.96</v>
+        <v>23.63</v>
       </c>
       <c r="G11" t="n">
-        <v>4.36</v>
+        <v>4.49</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>2.93</v>
       </c>
       <c r="M11" t="n">
-        <v>1180</v>
+        <v>1195</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F12" t="n">
-        <v>22.69</v>
+        <v>22.07</v>
       </c>
       <c r="G12" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.83</v>
+        <v>-2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>180.5</v>
+        <v>182</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F13" t="n">
-        <v>34.97</v>
+        <v>35.09</v>
       </c>
       <c r="G13" t="n">
-        <v>7.08</v>
+        <v>7.11</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>210.5</v>
+        <v>213.5</v>
       </c>
       <c r="F15" t="n">
-        <v>18.96</v>
+        <v>19.23</v>
       </c>
       <c r="G15" t="n">
-        <v>5.34</v>
+        <v>5.42</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.24</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>211</v>
+        <v>210.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8375</v>
+        <v>8460</v>
       </c>
       <c r="F16" t="n">
-        <v>214.69</v>
+        <v>216.87</v>
       </c>
       <c r="G16" t="n">
-        <v>83.34999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-2.62</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>8600</v>
+        <v>8375</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>2050</v>
+        <v>1990</v>
       </c>
       <c r="F2" t="n">
-        <v>65.25</v>
+        <v>63.34</v>
       </c>
       <c r="G2" t="n">
-        <v>18.13</v>
+        <v>17.6</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.24</v>
+        <v>-2.93</v>
       </c>
       <c r="M2" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>20.21</v>
+        <v>20.62</v>
       </c>
       <c r="G3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.15</v>
+        <v>2.04</v>
       </c>
       <c r="M3" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>7080</v>
+        <v>6805</v>
       </c>
       <c r="F4" t="n">
-        <v>159.78</v>
+        <v>153.58</v>
       </c>
       <c r="G4" t="n">
-        <v>44.06</v>
+        <v>42.35</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.73</v>
+        <v>-3.88</v>
       </c>
       <c r="M4" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5995</v>
+        <v>5950</v>
       </c>
       <c r="F5" t="n">
-        <v>93.75</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>36.82</v>
+        <v>36.55</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.18</v>
+        <v>-0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>5700</v>
+        <v>5995</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F6" t="n">
-        <v>45.55</v>
+        <v>45.94</v>
       </c>
       <c r="G6" t="n">
-        <v>23.88</v>
+        <v>24.09</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="M6" t="n">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="F7" t="n">
-        <v>11.92</v>
+        <v>11.89</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="M8" t="n">
         <v>156</v>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>1045</v>
+        <v>1085</v>
       </c>
       <c r="F10" t="n">
-        <v>28.27</v>
+        <v>29.36</v>
       </c>
       <c r="G10" t="n">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.95</v>
+        <v>3.83</v>
       </c>
       <c r="M10" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>197</v>
+        <v>199.5</v>
       </c>
       <c r="F11" t="n">
-        <v>27.13</v>
+        <v>27.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.51</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4180</v>
+        <v>4190</v>
       </c>
       <c r="F12" t="n">
-        <v>61.31</v>
+        <v>61.45</v>
       </c>
       <c r="G12" t="n">
-        <v>5.97</v>
+        <v>5.99</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.82</v>
+        <v>0.24</v>
       </c>
       <c r="M12" t="n">
-        <v>3950</v>
+        <v>4180</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="F2" t="n">
-        <v>110.77</v>
+        <v>115.15</v>
       </c>
       <c r="G2" t="n">
-        <v>29.87</v>
+        <v>31.05</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.81</v>
+        <v>3.95</v>
       </c>
       <c r="M2" t="n">
-        <v>1600</v>
+        <v>1645</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10.02</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.9</v>
+        <v>45</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="F5" t="n">
-        <v>118.42</v>
+        <v>119.38</v>
       </c>
       <c r="G5" t="n">
-        <v>34.07</v>
+        <v>34.35</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>5670</v>
+        <v>5530</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122.5</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>23.16</v>
+        <v>23.44</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.41</v>
+        <v>1.22</v>
       </c>
       <c r="M6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>28.36</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="M7" t="n">
         <v>103.5</v>
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173.5</v>
+        <v>171.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22.13</v>
+        <v>21.88</v>
       </c>
       <c r="G8" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.58</v>
+        <v>-1.15</v>
       </c>
       <c r="M8" t="n">
-        <v>172.5</v>
+        <v>173.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>104.5</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
-        <v>20.16</v>
+        <v>19.93</v>
       </c>
       <c r="G10" t="n">
-        <v>7.15</v>
+        <v>7.07</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>-1.12</v>
       </c>
       <c r="M10" t="n">
-        <v>175.5</v>
+        <v>178</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1230</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="n">
-        <v>23.63</v>
+        <v>23.15</v>
       </c>
       <c r="G11" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.93</v>
+        <v>-2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>1195</v>
+        <v>1230</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="F12" t="n">
-        <v>22.07</v>
+        <v>21.88</v>
       </c>
       <c r="G12" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-2.75</v>
+        <v>-0.85</v>
       </c>
       <c r="M12" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>300</v>
+        <v>297.5</v>
       </c>
       <c r="F13" t="n">
-        <v>35.09</v>
+        <v>34.8</v>
       </c>
       <c r="G13" t="n">
-        <v>7.11</v>
+        <v>7.05</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>-0.83</v>
       </c>
       <c r="M13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.78</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>145.5</v>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>213.5</v>
+        <v>213</v>
       </c>
       <c r="F15" t="n">
-        <v>19.23</v>
+        <v>19.19</v>
       </c>
       <c r="G15" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>-0.23</v>
       </c>
       <c r="M15" t="n">
-        <v>210.5</v>
+        <v>213.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="F16" t="n">
-        <v>216.87</v>
+        <v>214.3</v>
       </c>
       <c r="G16" t="n">
-        <v>84.2</v>
+        <v>83.2</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>-1.18</v>
       </c>
       <c r="M16" t="n">
-        <v>8375</v>
+        <v>8460</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1815</v>
+        <v>1785</v>
       </c>
       <c r="F17" t="n">
-        <v>53.7</v>
+        <v>52.81</v>
       </c>
       <c r="G17" t="n">
-        <v>10.9</v>
+        <v>10.72</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>-1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>1650</v>
+        <v>1815</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>11790</v>
+        <v>10615</v>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>58.52</v>
       </c>
       <c r="G18" t="n">
-        <v>33.29</v>
+        <v>29.97</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-10</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>13100</v>
+        <v>11790</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="F19" t="n">
-        <v>86.73</v>
+        <v>85.88</v>
       </c>
       <c r="G19" t="n">
-        <v>16.83</v>
+        <v>16.67</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="M19" t="n">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>49.45</v>
+        <v>51.87</v>
       </c>
       <c r="G20" t="n">
-        <v>7.4</v>
+        <v>7.76</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.88</v>
+        <v>4.89</v>
       </c>
       <c r="M20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5520</v>
+        <v>5615</v>
       </c>
       <c r="F21" t="n">
-        <v>90.37</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>23.34</v>
+        <v>23.74</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-9.949999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>6130</v>
+        <v>5520</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2400</v>
+        <v>2330</v>
       </c>
       <c r="F22" t="n">
-        <v>61.22</v>
+        <v>59.44</v>
       </c>
       <c r="G22" t="n">
-        <v>30.82</v>
+        <v>29.92</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>-2.92</v>
       </c>
       <c r="M22" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.65</v>
+        <v>18.7</v>
       </c>
       <c r="F23" t="n">
-        <v>42.39</v>
+        <v>42.5</v>
       </c>
       <c r="G23" t="n">
         <v>1.72</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>0.27</v>
       </c>
       <c r="M23" t="n">
-        <v>18.3</v>
+        <v>18.65</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="F24" t="n">
-        <v>87.34999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="G24" t="n">
-        <v>21.32</v>
+        <v>21.56</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1.99</v>
+        <v>1.16</v>
       </c>
       <c r="M24" t="n">
-        <v>1755</v>
+        <v>1720</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>58.9</v>
+        <v>64.7</v>
       </c>
       <c r="F25" t="n">
-        <v>71.83</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>4.9</v>
+        <v>5.38</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.03</v>
+        <v>9.85</v>
       </c>
       <c r="M25" t="n">
-        <v>58.3</v>
+        <v>58.9</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>3140</v>
+        <v>2960</v>
       </c>
       <c r="F26" t="n">
-        <v>270.22</v>
+        <v>254.73</v>
       </c>
       <c r="G26" t="n">
-        <v>61.56</v>
+        <v>58.03</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>7.53</v>
+        <v>-5.73</v>
       </c>
       <c r="M26" t="n">
-        <v>2920</v>
+        <v>3140</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F27" t="n">
-        <v>52.97</v>
+        <v>53.84</v>
       </c>
       <c r="G27" t="n">
-        <v>8.27</v>
+        <v>8.41</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-1.61</v>
+        <v>1.64</v>
       </c>
       <c r="M27" t="n">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="F28" t="n">
-        <v>59.01</v>
+        <v>58.52</v>
       </c>
       <c r="G28" t="n">
-        <v>12.23</v>
+        <v>12.13</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>-0.83</v>
       </c>
       <c r="M28" t="n">
-        <v>1175</v>
+        <v>1205</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="F29" t="n">
-        <v>94.76000000000001</v>
+        <v>92.47</v>
       </c>
       <c r="G29" t="n">
-        <v>18.57</v>
+        <v>18.12</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.94</v>
+        <v>-2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3020</v>
+        <v>3320</v>
       </c>
       <c r="F30" t="n">
-        <v>71.23</v>
+        <v>78.3</v>
       </c>
       <c r="G30" t="n">
-        <v>9.82</v>
+        <v>10.8</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-1.15</v>
+        <v>9.93</v>
       </c>
       <c r="M30" t="n">
-        <v>3055</v>
+        <v>3020</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="F31" t="n">
-        <v>108.52</v>
+        <v>105.88</v>
       </c>
       <c r="G31" t="n">
-        <v>13.95</v>
+        <v>13.62</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.75</v>
+        <v>-2.43</v>
       </c>
       <c r="M31" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="F32" t="n">
-        <v>46.42</v>
+        <v>46.04</v>
       </c>
       <c r="G32" t="n">
-        <v>11.51</v>
+        <v>11.42</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.68</v>
+        <v>-0.82</v>
       </c>
       <c r="M32" t="n">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="F33" t="n">
-        <v>43.57</v>
+        <v>42.76</v>
       </c>
       <c r="G33" t="n">
-        <v>7.52</v>
+        <v>7.38</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.52</v>
+        <v>-1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>6845</v>
+        <v>6660</v>
       </c>
       <c r="F34" t="n">
-        <v>36.41</v>
+        <v>35.42</v>
       </c>
       <c r="G34" t="n">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-0.15</v>
+        <v>-2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>6855</v>
+        <v>6845</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="F35" t="n">
-        <v>79.84999999999999</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>18.19</v>
+        <v>17.65</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1.73</v>
+        <v>-3</v>
       </c>
       <c r="M35" t="n">
-        <v>4920</v>
+        <v>4835</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>1990</v>
+        <v>1965</v>
       </c>
       <c r="F36" t="n">
-        <v>63.34</v>
+        <v>62.54</v>
       </c>
       <c r="G36" t="n">
-        <v>17.6</v>
+        <v>17.38</v>
       </c>
       <c r="H36" t="n">
         <v>59.1</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-2.93</v>
+        <v>-1.26</v>
       </c>
       <c r="M36" t="n">
-        <v>2050</v>
+        <v>1990</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -3362,13 +3362,13 @@
         <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>70.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="F37" t="n">
-        <v>20.62</v>
+        <v>20.44</v>
       </c>
       <c r="G37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H37" t="n">
         <v>19</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.04</v>
+        <v>-0.86</v>
       </c>
       <c r="M37" t="n">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
@@ -3445,13 +3445,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>6805</v>
+        <v>7165</v>
       </c>
       <c r="F38" t="n">
-        <v>153.58</v>
+        <v>161.7</v>
       </c>
       <c r="G38" t="n">
-        <v>42.35</v>
+        <v>44.59</v>
       </c>
       <c r="H38" t="n">
         <v>70.2</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-3.88</v>
+        <v>5.29</v>
       </c>
       <c r="M38" t="n">
-        <v>7080</v>
+        <v>6805</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3524,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="F39" t="n">
-        <v>93.04000000000001</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>36.55</v>
+        <v>36.86</v>
       </c>
       <c r="H39" t="n">
         <v>75.3</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-0.75</v>
+        <v>0.84</v>
       </c>
       <c r="M39" t="n">
-        <v>5995</v>
+        <v>5950</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3603,13 +3603,13 @@
         <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="F40" t="n">
-        <v>45.94</v>
+        <v>45.29</v>
       </c>
       <c r="G40" t="n">
-        <v>24.09</v>
+        <v>23.75</v>
       </c>
       <c r="H40" t="n">
         <v>47.5</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.86</v>
+        <v>-1.42</v>
       </c>
       <c r="M40" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
@@ -3686,13 +3686,13 @@
         <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>11.89</v>
+        <v>11.93</v>
       </c>
       <c r="G41" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H41" t="n">
         <v>11</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-0.21</v>
+        <v>0.31</v>
       </c>
       <c r="M41" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="F42" t="n">
-        <v>12.08</v>
+        <v>12.04</v>
       </c>
       <c r="G42" t="n">
         <v>2.1</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.64</v>
+        <v>-0.32</v>
       </c>
       <c r="M42" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3927,13 +3927,13 @@
         <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="F44" t="n">
-        <v>29.36</v>
+        <v>28.68</v>
       </c>
       <c r="G44" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="H44" t="n">
         <v>21.4</v>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.83</v>
+        <v>-2.3</v>
       </c>
       <c r="M44" t="n">
-        <v>1045</v>
+        <v>1085</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4010,13 +4010,13 @@
         <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>199.5</v>
+        <v>197</v>
       </c>
       <c r="F45" t="n">
-        <v>27.48</v>
+        <v>27.13</v>
       </c>
       <c r="G45" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="H45" t="n">
         <v>30.9</v>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.27</v>
+        <v>-1.25</v>
       </c>
       <c r="M45" t="n">
-        <v>197</v>
+        <v>199.5</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4093,13 +4093,13 @@
         <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>4190</v>
+        <v>4345</v>
       </c>
       <c r="F46" t="n">
-        <v>61.45</v>
+        <v>63.73</v>
       </c>
       <c r="G46" t="n">
-        <v>5.99</v>
+        <v>6.21</v>
       </c>
       <c r="H46" t="n">
         <v>51.7</v>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.24</v>
+        <v>3.7</v>
       </c>
       <c r="M46" t="n">
-        <v>4180</v>
+        <v>4190</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>228</v>
+        <v>243.5</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4253,13 +4253,13 @@
         <v>78</v>
       </c>
       <c r="E48" t="n">
-        <v>131.5</v>
+        <v>130.5</v>
       </c>
       <c r="F48" t="n">
-        <v>21.38</v>
+        <v>21.22</v>
       </c>
       <c r="G48" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="M48" t="n">
         <v>131.5</v>
@@ -4313,34 +4313,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E49" t="n">
-        <v>257.5</v>
+        <v>105</v>
       </c>
       <c r="F49" t="n">
-        <v>28.2</v>
+        <v>20.04</v>
       </c>
       <c r="G49" t="n">
-        <v>3.48</v>
+        <v>2.05</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>-15.3</v>
+        <v>11.3</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4349,53 +4349,57 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>256</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
+        <v>96.8</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>月營收轉負-3%</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.72</v>
+        <v>1.99</v>
       </c>
       <c r="R49" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>34.8</v>
+        <v>-2.7</v>
       </c>
       <c r="T49" t="n">
-        <v>34.5</v>
+        <v>20.3</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4404,20 +4408,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E50" t="n">
-        <v>741</v>
+        <v>256.5</v>
       </c>
       <c r="F50" t="n">
-        <v>26.87</v>
+        <v>28.09</v>
       </c>
       <c r="G50" t="n">
-        <v>7.57</v>
+        <v>3.46</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>-15.3</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -4426,35 +4430,31 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-1.85</v>
+        <v>-0.39</v>
       </c>
       <c r="M50" t="n">
-        <v>755</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>257.5</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>31.7</v>
+        <v>9.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="R50" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="S50" t="n">
-        <v>21.9</v>
+        <v>34.8</v>
       </c>
       <c r="T50" t="n">
-        <v>32.2</v>
+        <v>34.5</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4464,19 +4464,19 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4485,21 +4485,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E51" t="n">
-        <v>140</v>
+        <v>532</v>
       </c>
       <c r="F51" t="n">
-        <v>26.12</v>
+        <v>20.64</v>
       </c>
       <c r="G51" t="n">
-        <v>3.25</v>
+        <v>5.69</v>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="n">
-        <v>186.3</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
@@ -4507,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>9.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="M51" t="n">
-        <v>127.5</v>
+        <v>514</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4519,28 +4517,28 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>10.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>-3.4</v>
+        <v>-6.1</v>
       </c>
       <c r="S51" t="n">
-        <v>37</v>
+        <v>730.1</v>
       </c>
       <c r="T51" t="n">
-        <v>35.8</v>
+        <v>45.2</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4552,71 +4550,73 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>670</v>
+        <v>749</v>
       </c>
       <c r="F52" t="n">
-        <v>30.34</v>
+        <v>27.16</v>
       </c>
       <c r="G52" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="H52" t="n">
-        <v>29.3</v>
-      </c>
+        <v>7.66</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.87</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="M52" t="n">
-        <v>663</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+        <v>741</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P52" t="n">
-        <v>19.2</v>
+        <v>31.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="R52" t="n">
-        <v>10.6</v>
+        <v>3.8</v>
       </c>
       <c r="S52" t="n">
-        <v>64.90000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="T52" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.87</v>
-      </c>
+        <v>32.2</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>🔴過熱</t>
@@ -4624,78 +4624,80 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="E53" t="n">
-        <v>743</v>
+        <v>154</v>
       </c>
       <c r="F53" t="n">
-        <v>45.58</v>
+        <v>28.73</v>
       </c>
       <c r="G53" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="H53" t="n">
-        <v>46.1</v>
-      </c>
+        <v>3.57</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.97</v>
-      </c>
+        <v>186.3</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-2.49</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
-        <v>762</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
+        </is>
+      </c>
       <c r="P53" t="n">
-        <v>15.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R53" t="n">
-        <v>24.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S53" t="n">
-        <v>1.5</v>
+        <v>37</v>
       </c>
       <c r="T53" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.97</v>
-      </c>
+        <v>35.8</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>🟠偏貴</t>
@@ -4703,46 +4705,46 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E54" t="n">
-        <v>60.3</v>
+        <v>674</v>
       </c>
       <c r="F54" t="n">
-        <v>16.57</v>
+        <v>30.53</v>
       </c>
       <c r="G54" t="n">
-        <v>2.52</v>
+        <v>8.31</v>
       </c>
       <c r="H54" t="n">
-        <v>17.3</v>
+        <v>29.3</v>
       </c>
       <c r="I54" t="n">
-        <v>11.8</v>
+        <v>18.6</v>
       </c>
       <c r="J54" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4750,78 +4752,78 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.38</v>
+        <v>0.6</v>
       </c>
       <c r="M54" t="n">
-        <v>58.9</v>
+        <v>670</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>11.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="R54" t="n">
-        <v>4.4</v>
+        <v>10.6</v>
       </c>
       <c r="S54" t="n">
-        <v>768.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T54" t="n">
-        <v>19.4</v>
+        <v>34.7</v>
       </c>
       <c r="U54" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E55" t="n">
-        <v>178</v>
+        <v>736</v>
       </c>
       <c r="F55" t="n">
-        <v>16.26</v>
+        <v>45.15</v>
       </c>
       <c r="G55" t="n">
-        <v>1.77</v>
+        <v>6.06</v>
       </c>
       <c r="H55" t="n">
-        <v>15.5</v>
+        <v>46.1</v>
       </c>
       <c r="I55" t="n">
-        <v>8.6</v>
+        <v>30.6</v>
       </c>
       <c r="J55" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4829,227 +4831,231 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.85</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>176.5</v>
+        <v>743</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>10.8</v>
+        <v>15.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.03</v>
+        <v>1.83</v>
       </c>
       <c r="R55" t="n">
-        <v>30.2</v>
+        <v>24.8</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="T55" t="n">
-        <v>16.9</v>
+        <v>60.2</v>
       </c>
       <c r="U55" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E56" t="n">
-        <v>377</v>
+        <v>61.1</v>
       </c>
       <c r="F56" t="n">
-        <v>19.52</v>
+        <v>16.79</v>
       </c>
       <c r="G56" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>2.55</v>
+      </c>
+      <c r="H56" t="n">
+        <v>17.3</v>
+      </c>
       <c r="I56" t="n">
-        <v>49</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.64</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="M56" t="n">
-        <v>370.5</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>60.3</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>29.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="R56" t="n">
-        <v>24.2</v>
+        <v>4.4</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>768.2</v>
       </c>
       <c r="T56" t="n">
-        <v>24</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.64</v>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E57" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F57" t="n">
-        <v>18.9</v>
+        <v>16.26</v>
       </c>
       <c r="G57" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>1.77</v>
+      </c>
+      <c r="H57" t="n">
+        <v>15.5</v>
+      </c>
       <c r="I57" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.95</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>167</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>18.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.74</v>
+        <v>4.03</v>
       </c>
       <c r="R57" t="n">
-        <v>11.1</v>
+        <v>30.2</v>
       </c>
       <c r="S57" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="T57" t="n">
-        <v>22</v>
-      </c>
-      <c r="U57" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.95</v>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E58" t="n">
-        <v>96.8</v>
+        <v>375.5</v>
       </c>
       <c r="F58" t="n">
-        <v>18.47</v>
+        <v>19.45</v>
       </c>
       <c r="G58" t="n">
-        <v>1.89</v>
+        <v>5.51</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>11.3</v>
+        <v>49</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5058,40 +5064,36 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-1.02</v>
+        <v>-0.4</v>
       </c>
       <c r="M58" t="n">
-        <v>97.8</v>
+        <v>377</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>月營收轉負-3%</t>
-        </is>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>9.5</v>
+        <v>29.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.99</v>
+        <v>1.09</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="S58" t="n">
-        <v>-2.7</v>
+        <v>25</v>
       </c>
       <c r="T58" t="n">
-        <v>20.3</v>
+        <v>24</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5103,34 +5105,34 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E59" t="n">
-        <v>159.5</v>
+        <v>167</v>
       </c>
       <c r="F59" t="n">
-        <v>17.78</v>
+        <v>18.79</v>
       </c>
       <c r="G59" t="n">
-        <v>1.75</v>
+        <v>3.96</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>12.4</v>
+        <v>57.1</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5139,35 +5141,31 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.57</v>
+        <v>-0.6</v>
       </c>
       <c r="M59" t="n">
-        <v>155.5</v>
+        <v>168</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>5.4</v>
+        <v>18.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="R59" t="n">
-        <v>22.1</v>
+        <v>11.1</v>
       </c>
       <c r="S59" t="n">
-        <v>14.6</v>
+        <v>3.6</v>
       </c>
       <c r="T59" t="n">
-        <v>34.2</v>
+        <v>22</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
@@ -5184,12 +5182,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5198,20 +5196,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>295</v>
+        <v>159.5</v>
       </c>
       <c r="F60" t="n">
-        <v>18.33</v>
+        <v>17.78</v>
       </c>
       <c r="G60" t="n">
-        <v>6.66</v>
+        <v>1.75</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5220,36 +5218,40 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>292</v>
+        <v>159.5</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>ROE5低</t>
+        </is>
+      </c>
       <c r="P60" t="n">
-        <v>30.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="R60" t="n">
-        <v>20.4</v>
+        <v>22.1</v>
       </c>
       <c r="S60" t="n">
-        <v>812.4</v>
+        <v>14.6</v>
       </c>
       <c r="T60" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5261,12 +5263,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5275,20 +5277,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>186.5</v>
+        <v>308</v>
       </c>
       <c r="F61" t="n">
-        <v>15.74</v>
+        <v>19.14</v>
       </c>
       <c r="G61" t="n">
-        <v>1.87</v>
+        <v>6.96</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>49.2</v>
+        <v>9.6</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -5297,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-1.06</v>
+        <v>4.41</v>
       </c>
       <c r="M61" t="n">
-        <v>188.5</v>
+        <v>295</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5309,24 +5311,24 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>14.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>20.4</v>
       </c>
       <c r="S61" t="n">
-        <v>10.3</v>
+        <v>812.4</v>
       </c>
       <c r="T61" t="n">
-        <v>20.2</v>
+        <v>34.6</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5338,12 +5340,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5352,20 +5354,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>780</v>
+        <v>187</v>
       </c>
       <c r="F62" t="n">
-        <v>18.02</v>
+        <v>15.78</v>
       </c>
       <c r="G62" t="n">
-        <v>14.54</v>
+        <v>1.88</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>-8.1</v>
+        <v>49.2</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5374,35 +5376,31 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="M62" t="n">
-        <v>780</v>
+        <v>186.5</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>94.5</v>
+        <v>14.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="R62" t="n">
-        <v>18.2</v>
+        <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="T62" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
@@ -5419,33 +5417,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>514</v>
+        <v>788</v>
       </c>
       <c r="F63" t="n">
-        <v>19.95</v>
+        <v>18.21</v>
       </c>
       <c r="G63" t="n">
-        <v>5.5</v>
+        <v>14.69</v>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>-8.1</v>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-2.1</v>
+        <v>1.03</v>
       </c>
       <c r="M63" t="n">
-        <v>525</v>
+        <v>780</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>17.9</v>
+        <v>94.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="R63" t="n">
-        <v>-6.1</v>
+        <v>18.2</v>
       </c>
       <c r="S63" t="n">
-        <v>730.1</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>45.2</v>
+        <v>19.6</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>179.5</v>
+        <v>177</v>
       </c>
       <c r="F64" t="n">
-        <v>19.79</v>
+        <v>19.51</v>
       </c>
       <c r="G64" t="n">
-        <v>4.9</v>
+        <v>4.83</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.13</v>
+        <v>-1.39</v>
       </c>
       <c r="M64" t="n">
-        <v>177.5</v>
+        <v>179.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,10 +5594,10 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F65" t="n">
-        <v>12.2</v>
+        <v>12.17</v>
       </c>
       <c r="G65" t="n">
         <v>2.15</v>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="M65" t="n">
-        <v>49.65</v>
+        <v>49.4</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="F67" t="n">
-        <v>22.64</v>
+        <v>22.31</v>
       </c>
       <c r="G67" t="n">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-2.26</v>
+        <v>-1.49</v>
       </c>
       <c r="M67" t="n">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>371</v>
+        <v>381.5</v>
       </c>
       <c r="F69" t="n">
-        <v>31.36</v>
+        <v>32.25</v>
       </c>
       <c r="G69" t="n">
-        <v>8.07</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.64</v>
+        <v>2.83</v>
       </c>
       <c r="M69" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="F70" t="n">
-        <v>14.62</v>
+        <v>14.63</v>
       </c>
       <c r="G70" t="n">
         <v>2.07</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.97</v>
+        <v>0.12</v>
       </c>
       <c r="M70" t="n">
-        <v>82.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>140.5</v>
+        <v>139.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F72" t="n">
-        <v>16.61</v>
+        <v>16.41</v>
       </c>
       <c r="G72" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.56</v>
+        <v>-1.19</v>
       </c>
       <c r="M72" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="F73" t="n">
-        <v>46.59</v>
+        <v>45.74</v>
       </c>
       <c r="G73" t="n">
-        <v>24.88</v>
+        <v>24.43</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-0.9</v>
+        <v>-1.82</v>
       </c>
       <c r="M73" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="F74" t="n">
-        <v>18.74</v>
+        <v>18.55</v>
       </c>
       <c r="G74" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-0.85</v>
+        <v>-1.03</v>
       </c>
       <c r="M74" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="F75" t="n">
-        <v>47.25</v>
+        <v>45.85</v>
       </c>
       <c r="G75" t="n">
-        <v>25.22</v>
+        <v>24.47</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-3.8</v>
+        <v>-2.96</v>
       </c>
       <c r="M75" t="n">
-        <v>3685</v>
+        <v>3545</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="F76" t="n">
-        <v>15.85</v>
+        <v>15.67</v>
       </c>
       <c r="G76" t="n">
-        <v>8.960000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1.01</v>
+        <v>-1.14</v>
       </c>
       <c r="M76" t="n">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="F77" t="n">
-        <v>29.96</v>
+        <v>29.56</v>
       </c>
       <c r="G77" t="n">
-        <v>10.42</v>
+        <v>10.28</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="M77" t="n">
         <v>2585</v>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>115.5</v>
+        <v>114.5</v>
       </c>
       <c r="F78" t="n">
-        <v>16.48</v>
+        <v>16.33</v>
       </c>
       <c r="G78" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-1.7</v>
+        <v>-0.87</v>
       </c>
       <c r="M78" t="n">
-        <v>117.5</v>
+        <v>115.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F79" t="n">
-        <v>14.6</v>
+        <v>14.54</v>
       </c>
       <c r="G79" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.29</v>
+        <v>-0.42</v>
       </c>
       <c r="M79" t="n">
-        <v>116.5</v>
+        <v>118</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="F80" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="G80" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="M80" t="n">
-        <v>24.75</v>
+        <v>24.8</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="F81" t="n">
-        <v>12.1</v>
+        <v>12.27</v>
       </c>
       <c r="G81" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.96</v>
+        <v>1.43</v>
       </c>
       <c r="M81" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F82" t="n">
-        <v>13.11</v>
+        <v>13.19</v>
       </c>
       <c r="G82" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.66</v>
+        <v>0.54</v>
       </c>
       <c r="M82" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>41.95</v>
+        <v>41.4</v>
       </c>
       <c r="F83" t="n">
-        <v>8.83</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.96</v>
+        <v>-1.31</v>
       </c>
       <c r="M83" t="n">
-        <v>41.55</v>
+        <v>41.95</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F84" t="n">
-        <v>22.86</v>
+        <v>22.91</v>
       </c>
       <c r="G84" t="n">
-        <v>8.76</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-1.47</v>
+        <v>0.23</v>
       </c>
       <c r="M84" t="n">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>171.5</v>
+        <v>168</v>
       </c>
       <c r="F86" t="n">
-        <v>18.44</v>
+        <v>18.06</v>
       </c>
       <c r="G86" t="n">
-        <v>4.66</v>
+        <v>4.57</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="M86" t="n">
-        <v>173</v>
+        <v>171.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>39.3</v>
+        <v>38.1</v>
       </c>
       <c r="F87" t="n">
-        <v>8.1</v>
+        <v>7.86</v>
       </c>
       <c r="G87" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.9</v>
+        <v>-3.05</v>
       </c>
       <c r="M87" t="n">
-        <v>38.95</v>
+        <v>39.3</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="F88" t="n">
-        <v>31.66</v>
+        <v>32.52</v>
       </c>
       <c r="G88" t="n">
-        <v>16.31</v>
+        <v>16.76</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1.71</v>
+        <v>2.73</v>
       </c>
       <c r="M88" t="n">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="F89" t="n">
-        <v>35.17</v>
+        <v>35.06</v>
       </c>
       <c r="G89" t="n">
-        <v>10.7</v>
+        <v>10.67</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7532,7 +7532,7 @@
         <v>-0.33</v>
       </c>
       <c r="M89" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>8.81</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="M90" t="n">
-        <v>88.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>53.2</v>
+        <v>56.1</v>
       </c>
       <c r="F91" t="n">
-        <v>8.01</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0.76</v>
+        <v>5.45</v>
       </c>
       <c r="M91" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
       <c r="F92" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="G92" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="M92" t="n">
         <v>53.2</v>
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>335</v>
+        <v>325.5</v>
       </c>
       <c r="F93" t="n">
-        <v>14.6</v>
+        <v>14.18</v>
       </c>
       <c r="G93" t="n">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.45</v>
+        <v>-2.84</v>
       </c>
       <c r="M93" t="n">
-        <v>333.5</v>
+        <v>335</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-2.18</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>2290</v>
+        <v>2240</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="F95" t="n">
-        <v>14.69</v>
+        <v>14.97</v>
       </c>
       <c r="G95" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-2.37</v>
+        <v>1.89</v>
       </c>
       <c r="M95" t="n">
-        <v>189.5</v>
+        <v>185</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1455</v>
+        <v>1490</v>
       </c>
       <c r="F96" t="n">
-        <v>15.52</v>
+        <v>15.89</v>
       </c>
       <c r="G96" t="n">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-1.02</v>
+        <v>2.41</v>
       </c>
       <c r="M96" t="n">
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,13 +8170,13 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>68.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="F97" t="n">
-        <v>4.79</v>
+        <v>4.91</v>
       </c>
       <c r="G97" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.15</v>
+        <v>2.34</v>
       </c>
       <c r="M97" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>365</v>
+        <v>362.5</v>
       </c>
       <c r="F98" t="n">
-        <v>4.72</v>
+        <v>4.69</v>
       </c>
       <c r="G98" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-1.35</v>
+        <v>-0.68</v>
       </c>
       <c r="M98" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>22.55</v>
+        <v>22.85</v>
       </c>
       <c r="F99" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="G99" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="M99" t="n">
-        <v>22.4</v>
+        <v>22.55</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>31.35</v>
+        <v>31.65</v>
       </c>
       <c r="F100" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="G100" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="M100" t="n">
-        <v>31.2</v>
+        <v>31.35</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>202</v>
+        <v>199.5</v>
       </c>
       <c r="F101" t="n">
-        <v>5.02</v>
+        <v>4.96</v>
       </c>
       <c r="G101" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0.5</v>
+        <v>-1.24</v>
       </c>
       <c r="M101" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="F2" t="n">
-        <v>47.25</v>
+        <v>45.85</v>
       </c>
       <c r="G2" t="n">
-        <v>25.22</v>
+        <v>24.47</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.8</v>
+        <v>-2.96</v>
       </c>
       <c r="M2" t="n">
-        <v>3685</v>
+        <v>3545</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="F3" t="n">
-        <v>15.85</v>
+        <v>15.67</v>
       </c>
       <c r="G3" t="n">
-        <v>8.960000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.01</v>
+        <v>-1.14</v>
       </c>
       <c r="M3" t="n">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="F4" t="n">
-        <v>29.96</v>
+        <v>29.56</v>
       </c>
       <c r="G4" t="n">
-        <v>10.42</v>
+        <v>10.28</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="M4" t="n">
         <v>2585</v>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>115.5</v>
+        <v>114.5</v>
       </c>
       <c r="F5" t="n">
-        <v>16.48</v>
+        <v>16.33</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-1.7</v>
+        <v>-0.87</v>
       </c>
       <c r="M5" t="n">
-        <v>117.5</v>
+        <v>115.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F6" t="n">
-        <v>14.6</v>
+        <v>14.54</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>-0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>116.5</v>
+        <v>118</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="F7" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="G7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>24.75</v>
+        <v>24.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1</v>
+        <v>12.27</v>
       </c>
       <c r="G8" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.96</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F9" t="n">
-        <v>13.11</v>
+        <v>13.19</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.66</v>
+        <v>0.54</v>
       </c>
       <c r="M9" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.95</v>
+        <v>41.4</v>
       </c>
       <c r="F10" t="n">
-        <v>8.83</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.96</v>
+        <v>-1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>41.55</v>
+        <v>41.95</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F11" t="n">
-        <v>22.86</v>
+        <v>22.91</v>
       </c>
       <c r="G11" t="n">
-        <v>8.76</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.47</v>
+        <v>0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>171.5</v>
+        <v>168</v>
       </c>
       <c r="F13" t="n">
-        <v>18.44</v>
+        <v>18.06</v>
       </c>
       <c r="G13" t="n">
-        <v>4.66</v>
+        <v>4.57</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>173</v>
+        <v>171.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>38.1</v>
       </c>
       <c r="F14" t="n">
-        <v>8.1</v>
+        <v>7.86</v>
       </c>
       <c r="G14" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.9</v>
+        <v>-3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>38.95</v>
+        <v>39.3</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="F15" t="n">
-        <v>31.66</v>
+        <v>32.52</v>
       </c>
       <c r="G15" t="n">
-        <v>16.31</v>
+        <v>16.76</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1.71</v>
+        <v>2.73</v>
       </c>
       <c r="M15" t="n">
-        <v>2050</v>
+        <v>2015</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="F16" t="n">
-        <v>35.17</v>
+        <v>35.06</v>
       </c>
       <c r="G16" t="n">
-        <v>10.7</v>
+        <v>10.67</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9838,7 +9838,7 @@
         <v>-0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>8.81</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>88.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>53.2</v>
+        <v>56.1</v>
       </c>
       <c r="F18" t="n">
-        <v>8.01</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.76</v>
+        <v>5.45</v>
       </c>
       <c r="M18" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="G19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="M19" t="n">
         <v>53.2</v>
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>335</v>
+        <v>325.5</v>
       </c>
       <c r="F20" t="n">
-        <v>14.6</v>
+        <v>14.18</v>
       </c>
       <c r="G20" t="n">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.45</v>
+        <v>-2.84</v>
       </c>
       <c r="M20" t="n">
-        <v>333.5</v>
+        <v>335</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-2.18</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2290</v>
+        <v>2240</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.69</v>
+        <v>14.97</v>
       </c>
       <c r="G22" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.37</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>189.5</v>
+        <v>185</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1455</v>
+        <v>1490</v>
       </c>
       <c r="F23" t="n">
-        <v>15.52</v>
+        <v>15.89</v>
       </c>
       <c r="G23" t="n">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.02</v>
+        <v>2.41</v>
       </c>
       <c r="M23" t="n">
-        <v>1470</v>
+        <v>1455</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="F3" t="n">
-        <v>22.64</v>
+        <v>22.31</v>
       </c>
       <c r="G3" t="n">
-        <v>5.34</v>
+        <v>5.26</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-2.26</v>
+        <v>-1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>371</v>
+        <v>381.5</v>
       </c>
       <c r="F5" t="n">
-        <v>31.36</v>
+        <v>32.25</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.64</v>
+        <v>2.83</v>
       </c>
       <c r="M5" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,10 +10923,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="F6" t="n">
-        <v>14.62</v>
+        <v>14.63</v>
       </c>
       <c r="G6" t="n">
         <v>2.07</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.97</v>
+        <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>82.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>140.5</v>
+        <v>139.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F8" t="n">
-        <v>16.61</v>
+        <v>16.41</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.56</v>
+        <v>-1.19</v>
       </c>
       <c r="M8" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="F9" t="n">
-        <v>46.59</v>
+        <v>45.74</v>
       </c>
       <c r="G9" t="n">
-        <v>24.88</v>
+        <v>24.43</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.9</v>
+        <v>-1.82</v>
       </c>
       <c r="M9" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18.74</v>
+        <v>18.55</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.85</v>
+        <v>-1.03</v>
       </c>
       <c r="M10" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="F2" t="n">
-        <v>110.77</v>
+        <v>115.15</v>
       </c>
       <c r="G2" t="n">
-        <v>29.87</v>
+        <v>31.05</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.81</v>
+        <v>3.95</v>
       </c>
       <c r="M2" t="n">
-        <v>1600</v>
+        <v>1645</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10.02</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>40.9</v>
+        <v>45</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05</v>
+        <v>17.11</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="F5" t="n">
-        <v>118.42</v>
+        <v>119.38</v>
       </c>
       <c r="G5" t="n">
-        <v>34.07</v>
+        <v>34.35</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-2.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>5670</v>
+        <v>5530</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>122.5</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>23.16</v>
+        <v>23.44</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.41</v>
+        <v>1.22</v>
       </c>
       <c r="M6" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="F7" t="n">
-        <v>28.36</v>
+        <v>28.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="M7" t="n">
         <v>103.5</v>
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>173.5</v>
+        <v>171.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22.13</v>
+        <v>21.88</v>
       </c>
       <c r="G8" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.58</v>
+        <v>-1.15</v>
       </c>
       <c r="M8" t="n">
-        <v>172.5</v>
+        <v>173.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>104.5</v>
+        <v>106</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
-        <v>20.16</v>
+        <v>19.93</v>
       </c>
       <c r="G10" t="n">
-        <v>7.15</v>
+        <v>7.07</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>-1.12</v>
       </c>
       <c r="M10" t="n">
-        <v>175.5</v>
+        <v>178</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1230</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="n">
-        <v>23.63</v>
+        <v>23.15</v>
       </c>
       <c r="G11" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.93</v>
+        <v>-2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>1195</v>
+        <v>1230</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="F12" t="n">
-        <v>22.07</v>
+        <v>21.88</v>
       </c>
       <c r="G12" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-2.75</v>
+        <v>-0.85</v>
       </c>
       <c r="M12" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>300</v>
+        <v>297.5</v>
       </c>
       <c r="F13" t="n">
-        <v>35.09</v>
+        <v>34.8</v>
       </c>
       <c r="G13" t="n">
-        <v>7.11</v>
+        <v>7.05</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>-0.83</v>
       </c>
       <c r="M13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="F14" t="n">
-        <v>28.59</v>
+        <v>28.78</v>
       </c>
       <c r="G14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>145.5</v>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>213.5</v>
+        <v>213</v>
       </c>
       <c r="F15" t="n">
-        <v>19.23</v>
+        <v>19.19</v>
       </c>
       <c r="G15" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>-0.23</v>
       </c>
       <c r="M15" t="n">
-        <v>210.5</v>
+        <v>213.5</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="F16" t="n">
-        <v>216.87</v>
+        <v>214.3</v>
       </c>
       <c r="G16" t="n">
-        <v>84.2</v>
+        <v>83.2</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>-1.18</v>
       </c>
       <c r="M16" t="n">
-        <v>8375</v>
+        <v>8460</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1990</v>
+        <v>1965</v>
       </c>
       <c r="F2" t="n">
-        <v>63.34</v>
+        <v>62.54</v>
       </c>
       <c r="G2" t="n">
-        <v>17.6</v>
+        <v>17.38</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.93</v>
+        <v>-1.26</v>
       </c>
       <c r="M2" t="n">
-        <v>2050</v>
+        <v>1990</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>70.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="F3" t="n">
-        <v>20.62</v>
+        <v>20.44</v>
       </c>
       <c r="G3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.04</v>
+        <v>-0.86</v>
       </c>
       <c r="M3" t="n">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>6805</v>
+        <v>7165</v>
       </c>
       <c r="F4" t="n">
-        <v>153.58</v>
+        <v>161.7</v>
       </c>
       <c r="G4" t="n">
-        <v>42.35</v>
+        <v>44.59</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-3.88</v>
+        <v>5.29</v>
       </c>
       <c r="M4" t="n">
-        <v>7080</v>
+        <v>6805</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="F5" t="n">
-        <v>93.04000000000001</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>36.55</v>
+        <v>36.86</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.75</v>
+        <v>0.84</v>
       </c>
       <c r="M5" t="n">
-        <v>5995</v>
+        <v>5950</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="F6" t="n">
-        <v>45.94</v>
+        <v>45.29</v>
       </c>
       <c r="G6" t="n">
-        <v>24.09</v>
+        <v>23.75</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.86</v>
+        <v>-1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11.89</v>
+        <v>11.93</v>
       </c>
       <c r="G7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.21</v>
+        <v>0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,10 +13285,10 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="F8" t="n">
-        <v>12.08</v>
+        <v>12.04</v>
       </c>
       <c r="G8" t="n">
         <v>2.1</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.64</v>
+        <v>-0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="F10" t="n">
-        <v>29.36</v>
+        <v>28.68</v>
       </c>
       <c r="G10" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.83</v>
+        <v>-2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1045</v>
+        <v>1085</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>199.5</v>
+        <v>197</v>
       </c>
       <c r="F11" t="n">
-        <v>27.48</v>
+        <v>27.13</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>-1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>197</v>
+        <v>199.5</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4190</v>
+        <v>4345</v>
       </c>
       <c r="F12" t="n">
-        <v>61.45</v>
+        <v>63.73</v>
       </c>
       <c r="G12" t="n">
-        <v>5.99</v>
+        <v>6.21</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.24</v>
+        <v>3.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4180</v>
+        <v>4190</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>122.5</v>
+        <v>124</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.15</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>173.5</v>
+        <v>171.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.03</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1230</v>
+        <v>1205</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>300</v>
+        <v>297.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>213.5</v>
+        <v>213</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1815</v>
+        <v>1785</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-9.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>11790</v>
+        <v>10615</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>90</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5520</v>
+        <v>5615</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2400</v>
+        <v>2330</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>18.65</v>
+        <v>18.7</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>58.9</v>
+        <v>64.7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-5.73</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3140</v>
+        <v>2960</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-2.42</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9.93</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3020</v>
+        <v>3320</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-2.43</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-1.85</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-2.7</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6845</v>
+        <v>6660</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1990</v>
+        <v>1965</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>70.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6805</v>
+        <v>7165</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-1.42</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>199.5</v>
+        <v>197</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4190</v>
+        <v>4345</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>131.5</v>
+        <v>130.5</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>8.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>96.8</v>
+        <v>105</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>257.5</v>
+        <v>256.5</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>60.3</v>
+        <v>61.1</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>377</v>
+        <v>375.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>186.5</v>
+        <v>187</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1.39</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>179.5</v>
+        <v>177</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1.49</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>371</v>
+        <v>381.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.19</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1.82</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-2.96</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>115.5</v>
+        <v>114.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>41.95</v>
+        <v>41.4</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>171.5</v>
+        <v>168</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-3.05</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>39.3</v>
+        <v>38.1</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>53.2</v>
+        <v>56.1</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-2.84</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>335</v>
+        <v>325.5</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1455</v>
+        <v>1490</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>68.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>365</v>
+        <v>362.5</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>22.55</v>
+        <v>22.85</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>31.35</v>
+        <v>31.65</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>202</v>
+        <v>199.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-2.96</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>115.5</v>
+        <v>114.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9199,10 +9199,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.31</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>41.95</v>
+        <v>41.4</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>171.5</v>
+        <v>168</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-3.05</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>39.3</v>
+        <v>38.1</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>53.2</v>
+        <v>56.1</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>53.2</v>
+        <v>53</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.84</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>335</v>
+        <v>325.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1455</v>
+        <v>1490</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.49</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>371</v>
+        <v>381.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.19</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-1.82</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>122.5</v>
+        <v>124</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.15</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>173.5</v>
+        <v>171.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-2.03</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1230</v>
+        <v>1205</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>300</v>
+        <v>297.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12450,10 +12450,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>213.5</v>
+        <v>213</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1990</v>
+        <v>1965</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>70.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6805</v>
+        <v>7165</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.42</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>157</v>
+        <v>156.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>199.5</v>
+        <v>197</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4190</v>
+        <v>4345</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="F2" t="n">
-        <v>115.15</v>
+        <v>115.82</v>
       </c>
       <c r="G2" t="n">
-        <v>31.05</v>
+        <v>31.23</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M2" t="n">
         <v>1710</v>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="F3" t="n">
-        <v>9.390000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>45</v>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M4" t="n">
         <v>154.5</v>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5575</v>
+        <v>6130</v>
       </c>
       <c r="F5" t="n">
-        <v>119.38</v>
+        <v>131.26</v>
       </c>
       <c r="G5" t="n">
-        <v>34.35</v>
+        <v>37.76</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>5575</v>
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>121.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44</v>
+        <v>22.97</v>
       </c>
       <c r="G6" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-2.02</v>
       </c>
       <c r="M6" t="n">
         <v>124</v>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>28.77</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M7" t="n">
         <v>102.5</v>
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>171.5</v>
+        <v>171</v>
       </c>
       <c r="F8" t="n">
-        <v>21.88</v>
+        <v>21.81</v>
       </c>
       <c r="G8" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="M8" t="n">
         <v>171.5</v>
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
         <v>106</v>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>176</v>
+        <v>174.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.93</v>
+        <v>19.76</v>
       </c>
       <c r="G10" t="n">
-        <v>7.07</v>
+        <v>7.01</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M10" t="n">
         <v>176</v>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="F11" t="n">
-        <v>23.15</v>
+        <v>23.25</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M11" t="n">
         <v>1205</v>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>175.5</v>
+        <v>174</v>
       </c>
       <c r="F12" t="n">
-        <v>21.88</v>
+        <v>21.7</v>
       </c>
       <c r="G12" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M12" t="n">
         <v>175.5</v>
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>297.5</v>
+        <v>288</v>
       </c>
       <c r="F13" t="n">
-        <v>34.8</v>
+        <v>33.68</v>
       </c>
       <c r="G13" t="n">
-        <v>7.05</v>
+        <v>6.82</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-3.19</v>
       </c>
       <c r="M13" t="n">
         <v>297.5</v>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F15" t="n">
-        <v>19.19</v>
+        <v>19.46</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.48</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>213</v>
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8360</v>
+        <v>8100</v>
       </c>
       <c r="F16" t="n">
-        <v>214.3</v>
+        <v>207.64</v>
       </c>
       <c r="G16" t="n">
-        <v>83.2</v>
+        <v>80.61</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-3.11</v>
       </c>
       <c r="M16" t="n">
         <v>8360</v>
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1785</v>
+        <v>1725</v>
       </c>
       <c r="F17" t="n">
-        <v>52.81</v>
+        <v>51.04</v>
       </c>
       <c r="G17" t="n">
-        <v>10.72</v>
+        <v>10.36</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-3.36</v>
       </c>
       <c r="M17" t="n">
         <v>1785</v>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>10615</v>
+        <v>10580</v>
       </c>
       <c r="F18" t="n">
-        <v>58.52</v>
+        <v>58.33</v>
       </c>
       <c r="G18" t="n">
-        <v>29.97</v>
+        <v>29.87</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="M18" t="n">
         <v>10615</v>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="F19" t="n">
-        <v>85.88</v>
+        <v>85.03</v>
       </c>
       <c r="G19" t="n">
-        <v>16.67</v>
+        <v>16.5</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="M19" t="n">
         <v>1010</v>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>94.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="F20" t="n">
-        <v>51.87</v>
+        <v>52.2</v>
       </c>
       <c r="G20" t="n">
-        <v>7.76</v>
+        <v>7.81</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="M20" t="n">
         <v>94.40000000000001</v>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5615</v>
+        <v>6025</v>
       </c>
       <c r="F21" t="n">
-        <v>91.93000000000001</v>
+        <v>98.64</v>
       </c>
       <c r="G21" t="n">
-        <v>23.74</v>
+        <v>25.47</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
         <v>5615</v>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2330</v>
+        <v>2365</v>
       </c>
       <c r="F22" t="n">
-        <v>59.44</v>
+        <v>60.33</v>
       </c>
       <c r="G22" t="n">
-        <v>29.92</v>
+        <v>30.37</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
         <v>2330</v>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="F24" t="n">
-        <v>88.37</v>
+        <v>88.12</v>
       </c>
       <c r="G24" t="n">
-        <v>21.56</v>
+        <v>21.5</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="M24" t="n">
         <v>1740</v>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>64.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>78.90000000000001</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>5.38</v>
+        <v>5.92</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>64.7</v>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2960</v>
+        <v>3025</v>
       </c>
       <c r="F26" t="n">
-        <v>254.73</v>
+        <v>260.33</v>
       </c>
       <c r="G26" t="n">
-        <v>58.03</v>
+        <v>59.3</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
         <v>2960</v>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="F27" t="n">
-        <v>53.84</v>
+        <v>55.14</v>
       </c>
       <c r="G27" t="n">
-        <v>8.41</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
         <v>744</v>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="F28" t="n">
-        <v>58.52</v>
+        <v>58.03</v>
       </c>
       <c r="G28" t="n">
-        <v>12.13</v>
+        <v>12.03</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
       <c r="M28" t="n">
         <v>1195</v>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F29" t="n">
-        <v>92.47</v>
+        <v>95.25</v>
       </c>
       <c r="G29" t="n">
-        <v>18.12</v>
+        <v>18.67</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M29" t="n">
         <v>565</v>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3320</v>
+        <v>3420</v>
       </c>
       <c r="F30" t="n">
-        <v>78.3</v>
+        <v>80.66</v>
       </c>
       <c r="G30" t="n">
-        <v>10.8</v>
+        <v>11.12</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M30" t="n">
         <v>3320</v>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F31" t="n">
-        <v>105.88</v>
+        <v>105.27</v>
       </c>
       <c r="G31" t="n">
-        <v>13.62</v>
+        <v>13.54</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="M31" t="n">
         <v>522</v>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="F32" t="n">
-        <v>46.04</v>
+        <v>45.66</v>
       </c>
       <c r="G32" t="n">
-        <v>11.42</v>
+        <v>11.32</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="M32" t="n">
         <v>727</v>
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F33" t="n">
-        <v>42.76</v>
+        <v>42.83</v>
       </c>
       <c r="G33" t="n">
-        <v>7.38</v>
+        <v>7.39</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="M33" t="n">
         <v>635</v>
@@ -3121,13 +3121,13 @@
         <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>6660</v>
+        <v>7325</v>
       </c>
       <c r="F34" t="n">
-        <v>35.42</v>
+        <v>38.96</v>
       </c>
       <c r="G34" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>9.98</v>
       </c>
       <c r="M34" t="n">
         <v>6660</v>
@@ -3202,13 +3202,13 @@
         <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>4690</v>
+        <v>4625</v>
       </c>
       <c r="F35" t="n">
-        <v>77.45999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="G35" t="n">
-        <v>17.65</v>
+        <v>17.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="M35" t="n">
         <v>4690</v>
@@ -3283,13 +3283,13 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>1965</v>
+        <v>1900</v>
       </c>
       <c r="F36" t="n">
-        <v>62.54</v>
+        <v>60.47</v>
       </c>
       <c r="G36" t="n">
-        <v>17.38</v>
+        <v>16.8</v>
       </c>
       <c r="H36" t="n">
         <v>59.1</v>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-3.31</v>
       </c>
       <c r="M36" t="n">
         <v>1965</v>
@@ -3362,13 +3362,13 @@
         <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>69.5</v>
+        <v>72.3</v>
       </c>
       <c r="F37" t="n">
-        <v>20.44</v>
+        <v>21.26</v>
       </c>
       <c r="G37" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H37" t="n">
         <v>19</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="M37" t="n">
         <v>69.5</v>
@@ -3445,13 +3445,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>7165</v>
+        <v>7160</v>
       </c>
       <c r="F38" t="n">
-        <v>161.7</v>
+        <v>161.59</v>
       </c>
       <c r="G38" t="n">
-        <v>44.59</v>
+        <v>44.56</v>
       </c>
       <c r="H38" t="n">
         <v>70.2</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>7165</v>
@@ -3524,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>6000</v>
+        <v>6150</v>
       </c>
       <c r="F39" t="n">
-        <v>93.81999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="G39" t="n">
-        <v>36.86</v>
+        <v>37.78</v>
       </c>
       <c r="H39" t="n">
         <v>75.3</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
         <v>6000</v>
@@ -3603,13 +3603,13 @@
         <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="F40" t="n">
-        <v>45.29</v>
+        <v>47.38</v>
       </c>
       <c r="G40" t="n">
-        <v>23.75</v>
+        <v>24.85</v>
       </c>
       <c r="H40" t="n">
         <v>47.5</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M40" t="n">
         <v>692</v>
@@ -3686,10 +3686,10 @@
         <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>11.93</v>
+        <v>11.97</v>
       </c>
       <c r="G41" t="n">
         <v>1.67</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="M41" t="n">
         <v>97.09999999999999</v>
@@ -3765,10 +3765,10 @@
         <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>156.5</v>
+        <v>157</v>
       </c>
       <c r="F42" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="G42" t="n">
         <v>2.1</v>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M42" t="n">
         <v>156.5</v>
@@ -3848,13 +3848,13 @@
         <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="F43" t="n">
-        <v>15.52</v>
+        <v>15.67</v>
       </c>
       <c r="G43" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
         <v>16</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>106.5</v>
@@ -3927,13 +3927,13 @@
         <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="F44" t="n">
-        <v>28.68</v>
+        <v>28.95</v>
       </c>
       <c r="G44" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="H44" t="n">
         <v>21.4</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>1060</v>
@@ -4010,13 +4010,13 @@
         <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F45" t="n">
-        <v>27.13</v>
+        <v>28.1</v>
       </c>
       <c r="G45" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="H45" t="n">
         <v>30.9</v>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M45" t="n">
         <v>197</v>
@@ -4093,13 +4093,13 @@
         <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>4345</v>
+        <v>4395</v>
       </c>
       <c r="F46" t="n">
-        <v>63.73</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>6.21</v>
+        <v>6.28</v>
       </c>
       <c r="H46" t="n">
         <v>51.7</v>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M46" t="n">
         <v>4345</v>
@@ -4253,13 +4253,13 @@
         <v>78</v>
       </c>
       <c r="E48" t="n">
-        <v>130.5</v>
+        <v>128.5</v>
       </c>
       <c r="F48" t="n">
-        <v>21.22</v>
+        <v>20.89</v>
       </c>
       <c r="G48" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1.53</v>
       </c>
       <c r="M48" t="n">
         <v>130.5</v>
@@ -4313,34 +4313,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>105</v>
+        <v>263.5</v>
       </c>
       <c r="F49" t="n">
-        <v>20.04</v>
+        <v>28.86</v>
       </c>
       <c r="G49" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>11.3</v>
+        <v>-15.3</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4349,57 +4349,53 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M49" t="n">
-        <v>105</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>256.5</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>EPS單期衰退</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.99</v>
+        <v>0.72</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="S49" t="n">
-        <v>-2.7</v>
+        <v>34.8</v>
       </c>
       <c r="T49" t="n">
-        <v>20.3</v>
+        <v>34.5</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>⏸ 成長為負(-15%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4408,21 +4404,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50" t="n">
-        <v>256.5</v>
+        <v>527</v>
       </c>
       <c r="F50" t="n">
-        <v>28.09</v>
+        <v>20.45</v>
       </c>
       <c r="G50" t="n">
-        <v>3.46</v>
+        <v>5.64</v>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="n">
-        <v>-15.3</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
@@ -4430,31 +4424,35 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>256.5</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
+        <v>532</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS單期衰退</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>9.4</v>
+        <v>17.9</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="R50" t="n">
-        <v>13.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S50" t="n">
-        <v>34.8</v>
+        <v>730.1</v>
       </c>
       <c r="T50" t="n">
-        <v>34.5</v>
+        <v>45.2</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4464,19 +4462,19 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>⏸ 成長為負(-15%)</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4485,19 +4483,21 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>532</v>
+        <v>746</v>
       </c>
       <c r="F51" t="n">
-        <v>20.64</v>
+        <v>27.05</v>
       </c>
       <c r="G51" t="n">
-        <v>5.69</v>
+        <v>7.63</v>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>27</v>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="M51" t="n">
-        <v>532</v>
+        <v>749</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4517,23 +4517,23 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>17.9</v>
+        <v>31.7</v>
       </c>
       <c r="Q51" t="n">
         <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>-6.1</v>
+        <v>3.8</v>
       </c>
       <c r="S51" t="n">
-        <v>730.1</v>
+        <v>21.9</v>
       </c>
       <c r="T51" t="n">
-        <v>45.2</v>
+        <v>32.2</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
@@ -4550,12 +4550,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4564,20 +4564,20 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E52" t="n">
-        <v>749</v>
+        <v>148.5</v>
       </c>
       <c r="F52" t="n">
-        <v>27.16</v>
+        <v>27.71</v>
       </c>
       <c r="G52" t="n">
-        <v>7.66</v>
+        <v>3.44</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>186.3</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-3.57</v>
       </c>
       <c r="M52" t="n">
-        <v>749</v>
+        <v>154</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4598,28 +4598,28 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>31.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="R52" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S52" t="n">
-        <v>21.9</v>
+        <v>37</v>
       </c>
       <c r="T52" t="n">
-        <v>32.2</v>
+        <v>35.8</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4631,93 +4631,91 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E53" t="n">
-        <v>154</v>
+        <v>657</v>
       </c>
       <c r="F53" t="n">
-        <v>28.73</v>
+        <v>29.76</v>
       </c>
       <c r="G53" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>8.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I53" t="n">
-        <v>186.3</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
       <c r="M53" t="n">
-        <v>154</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>10.7</v>
+        <v>19.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R53" t="n">
-        <v>-3.4</v>
+        <v>10.6</v>
       </c>
       <c r="S53" t="n">
-        <v>37</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="U53" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4726,25 +4724,25 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E54" t="n">
-        <v>674</v>
+        <v>755</v>
       </c>
       <c r="F54" t="n">
-        <v>30.53</v>
+        <v>46.32</v>
       </c>
       <c r="G54" t="n">
-        <v>8.31</v>
+        <v>6.22</v>
       </c>
       <c r="H54" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I54" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J54" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4752,78 +4750,78 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M54" t="n">
-        <v>674</v>
+        <v>736</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R54" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S54" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T54" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U54" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E55" t="n">
-        <v>736</v>
+        <v>59.8</v>
       </c>
       <c r="F55" t="n">
-        <v>45.15</v>
+        <v>16.43</v>
       </c>
       <c r="G55" t="n">
-        <v>6.06</v>
+        <v>2.5</v>
       </c>
       <c r="H55" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I55" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J55" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4831,30 +4829,30 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-2.13</v>
       </c>
       <c r="M55" t="n">
-        <v>736</v>
+        <v>61.1</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R55" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S55" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T55" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U55" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -4863,19 +4861,19 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4884,25 +4882,25 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E56" t="n">
-        <v>61.1</v>
+        <v>179.5</v>
       </c>
       <c r="F56" t="n">
-        <v>16.79</v>
+        <v>16.39</v>
       </c>
       <c r="G56" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="H56" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I56" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J56" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4910,34 +4908,34 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="M56" t="n">
-        <v>61.1</v>
+        <v>178</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R56" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S56" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U56" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -4949,91 +4947,89 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>178</v>
+        <v>368.5</v>
       </c>
       <c r="F57" t="n">
-        <v>16.26</v>
+        <v>19.08</v>
       </c>
       <c r="G57" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="H57" t="n">
-        <v>15.5</v>
-      </c>
+        <v>5.41</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.95</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-1.86</v>
       </c>
       <c r="M57" t="n">
-        <v>178</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
+        <v>375.5</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.03</v>
+        <v>1.09</v>
       </c>
       <c r="R57" t="n">
-        <v>30.2</v>
+        <v>24.2</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5042,20 +5038,20 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E58" t="n">
-        <v>375.5</v>
+        <v>169</v>
       </c>
       <c r="F58" t="n">
-        <v>19.45</v>
+        <v>19.01</v>
       </c>
       <c r="G58" t="n">
-        <v>5.51</v>
+        <v>4.01</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>49</v>
+        <v>57.1</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5064,10 +5060,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M58" t="n">
-        <v>375.5</v>
+        <v>167</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5076,24 +5072,24 @@
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>29.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="R58" t="n">
-        <v>24.2</v>
+        <v>11.1</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="T58" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5105,34 +5101,34 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>167</v>
+        <v>100.5</v>
       </c>
       <c r="F59" t="n">
-        <v>18.79</v>
+        <v>19.18</v>
       </c>
       <c r="G59" t="n">
-        <v>3.96</v>
+        <v>1.96</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>57.1</v>
+        <v>11.3</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5141,31 +5137,35 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="M59" t="n">
+        <v>105</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="M59" t="n">
-        <v>167</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R59" t="n">
-        <v>11.1</v>
-      </c>
       <c r="S59" t="n">
-        <v>3.6</v>
+        <v>-2.7</v>
       </c>
       <c r="T59" t="n">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
@@ -5199,13 +5199,13 @@
         <v>77</v>
       </c>
       <c r="E60" t="n">
-        <v>159.5</v>
+        <v>157</v>
       </c>
       <c r="F60" t="n">
-        <v>17.78</v>
+        <v>17.5</v>
       </c>
       <c r="G60" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-1.57</v>
       </c>
       <c r="M60" t="n">
         <v>159.5</v>
@@ -5280,13 +5280,13 @@
         <v>76</v>
       </c>
       <c r="E61" t="n">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="F61" t="n">
-        <v>19.14</v>
+        <v>18.58</v>
       </c>
       <c r="G61" t="n">
-        <v>6.96</v>
+        <v>6.75</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-2.92</v>
       </c>
       <c r="M61" t="n">
         <v>308</v>
@@ -5434,13 +5434,13 @@
         <v>66</v>
       </c>
       <c r="E63" t="n">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="F63" t="n">
-        <v>18.21</v>
+        <v>18.41</v>
       </c>
       <c r="G63" t="n">
-        <v>14.69</v>
+        <v>14.86</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M63" t="n">
         <v>788</v>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F64" t="n">
-        <v>19.51</v>
+        <v>19.18</v>
       </c>
       <c r="G64" t="n">
-        <v>4.83</v>
+        <v>4.75</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>-1.69</v>
       </c>
       <c r="M64" t="n">
         <v>177</v>
@@ -5594,10 +5594,10 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="F65" t="n">
-        <v>12.17</v>
+        <v>12.2</v>
       </c>
       <c r="G65" t="n">
         <v>2.15</v>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M65" t="n">
         <v>49.3</v>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>155</v>
+        <v>155.5</v>
       </c>
       <c r="F66" t="n">
-        <v>16.28</v>
+        <v>16.33</v>
       </c>
       <c r="G66" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M66" t="n">
         <v>155</v>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F67" t="n">
-        <v>22.31</v>
+        <v>22.19</v>
       </c>
       <c r="G67" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="M67" t="n">
         <v>596</v>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>381.5</v>
+        <v>390.5</v>
       </c>
       <c r="F69" t="n">
-        <v>32.25</v>
+        <v>33.01</v>
       </c>
       <c r="G69" t="n">
-        <v>8.289999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M69" t="n">
         <v>381.5</v>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>83.7</v>
+        <v>80</v>
       </c>
       <c r="F70" t="n">
-        <v>14.63</v>
+        <v>13.99</v>
       </c>
       <c r="G70" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>-4.42</v>
       </c>
       <c r="M70" t="n">
         <v>83.7</v>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>139.5</v>
+        <v>136</v>
       </c>
       <c r="F71" t="n">
-        <v>19.43</v>
+        <v>18.94</v>
       </c>
       <c r="G71" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>-2.51</v>
       </c>
       <c r="M71" t="n">
         <v>139.5</v>
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>249</v>
+        <v>244.5</v>
       </c>
       <c r="F72" t="n">
-        <v>16.41</v>
+        <v>16.12</v>
       </c>
       <c r="G72" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>-1.81</v>
       </c>
       <c r="M72" t="n">
         <v>249</v>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="F73" t="n">
-        <v>45.74</v>
+        <v>45.53</v>
       </c>
       <c r="G73" t="n">
-        <v>24.43</v>
+        <v>24.32</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="M73" t="n">
         <v>1080</v>
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>57.5</v>
+        <v>58.1</v>
       </c>
       <c r="F74" t="n">
-        <v>18.55</v>
+        <v>18.74</v>
       </c>
       <c r="G74" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M74" t="n">
         <v>57.5</v>
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3440</v>
+        <v>3385</v>
       </c>
       <c r="F75" t="n">
-        <v>45.85</v>
+        <v>45.12</v>
       </c>
       <c r="G75" t="n">
-        <v>24.47</v>
+        <v>24.08</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="M75" t="n">
         <v>3440</v>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>778</v>
+        <v>750</v>
       </c>
       <c r="F76" t="n">
-        <v>15.67</v>
+        <v>15.11</v>
       </c>
       <c r="G76" t="n">
-        <v>8.85</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="M76" t="n">
         <v>778</v>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2550</v>
+        <v>2540</v>
       </c>
       <c r="F77" t="n">
-        <v>29.56</v>
+        <v>29.44</v>
       </c>
       <c r="G77" t="n">
-        <v>10.28</v>
+        <v>10.24</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M77" t="n">
         <v>2550</v>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>114.5</v>
+        <v>119.5</v>
       </c>
       <c r="F78" t="n">
-        <v>16.33</v>
+        <v>17.05</v>
       </c>
       <c r="G78" t="n">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="M78" t="n">
         <v>114.5</v>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="F79" t="n">
-        <v>14.54</v>
+        <v>14.67</v>
       </c>
       <c r="G79" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M79" t="n">
         <v>117.5</v>
@@ -6791,13 +6791,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="F80" t="n">
-        <v>4.96</v>
+        <v>5.02</v>
       </c>
       <c r="G80" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M80" t="n">
         <v>24.7</v>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="F82" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="G82" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="M82" t="n">
         <v>185</v>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="F83" t="n">
-        <v>8.720000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="G83" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M83" t="n">
         <v>41.4</v>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="F84" t="n">
-        <v>22.91</v>
+        <v>22.57</v>
       </c>
       <c r="G84" t="n">
-        <v>8.779999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="M84" t="n">
         <v>874</v>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F85" t="n">
-        <v>24.94</v>
+        <v>24.81</v>
       </c>
       <c r="G85" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="M85" t="n">
         <v>582</v>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>168</v>
+        <v>168.5</v>
       </c>
       <c r="F86" t="n">
-        <v>18.06</v>
+        <v>18.12</v>
       </c>
       <c r="G86" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M86" t="n">
         <v>168</v>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.1</v>
+        <v>38.95</v>
       </c>
       <c r="F87" t="n">
-        <v>7.86</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M87" t="n">
         <v>38.1</v>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>2070</v>
+        <v>2130</v>
       </c>
       <c r="F88" t="n">
-        <v>32.52</v>
+        <v>33.46</v>
       </c>
       <c r="G88" t="n">
-        <v>16.76</v>
+        <v>17.24</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M88" t="n">
         <v>2070</v>
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1520</v>
+        <v>1540</v>
       </c>
       <c r="F89" t="n">
-        <v>35.06</v>
+        <v>35.52</v>
       </c>
       <c r="G89" t="n">
-        <v>10.67</v>
+        <v>10.81</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M89" t="n">
         <v>1520</v>
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>91.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>8.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G90" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="M90" t="n">
         <v>91.40000000000001</v>
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="F91" t="n">
-        <v>8.449999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>-1.07</v>
       </c>
       <c r="M91" t="n">
         <v>56.1</v>
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="F92" t="n">
-        <v>7.35</v>
+        <v>7.28</v>
       </c>
       <c r="G92" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M92" t="n">
         <v>53</v>
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>325.5</v>
+        <v>322</v>
       </c>
       <c r="F93" t="n">
-        <v>14.18</v>
+        <v>14.03</v>
       </c>
       <c r="G93" t="n">
-        <v>5.15</v>
+        <v>5.09</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="M93" t="n">
         <v>325.5</v>
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2240</v>
+        <v>2275</v>
       </c>
       <c r="F94" t="n">
-        <v>7.18</v>
+        <v>7.29</v>
       </c>
       <c r="G94" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M94" t="n">
         <v>2240</v>
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>188.5</v>
+        <v>189.5</v>
       </c>
       <c r="F95" t="n">
-        <v>14.97</v>
+        <v>15.05</v>
       </c>
       <c r="G95" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M95" t="n">
         <v>188.5</v>
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1490</v>
+        <v>1540</v>
       </c>
       <c r="F96" t="n">
-        <v>15.89</v>
+        <v>16.42</v>
       </c>
       <c r="G96" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="M96" t="n">
         <v>1490</v>
@@ -8170,13 +8170,13 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="G97" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="M97" t="n">
         <v>70</v>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>362.5</v>
+        <v>367.5</v>
       </c>
       <c r="F98" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="G98" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M98" t="n">
         <v>362.5</v>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>22.85</v>
+        <v>23</v>
       </c>
       <c r="F99" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="M99" t="n">
         <v>22.85</v>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>31.65</v>
+        <v>32.05</v>
       </c>
       <c r="F100" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="G100" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M100" t="n">
         <v>31.65</v>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>199.5</v>
+        <v>197</v>
       </c>
       <c r="F101" t="n">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="G101" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="M101" t="n">
         <v>199.5</v>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3440</v>
+        <v>3385</v>
       </c>
       <c r="F2" t="n">
-        <v>45.85</v>
+        <v>45.12</v>
       </c>
       <c r="G2" t="n">
-        <v>24.47</v>
+        <v>24.08</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="M2" t="n">
         <v>3440</v>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>778</v>
+        <v>750</v>
       </c>
       <c r="F3" t="n">
-        <v>15.67</v>
+        <v>15.11</v>
       </c>
       <c r="G3" t="n">
-        <v>8.85</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="M3" t="n">
         <v>778</v>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2550</v>
+        <v>2540</v>
       </c>
       <c r="F4" t="n">
-        <v>29.56</v>
+        <v>29.44</v>
       </c>
       <c r="G4" t="n">
-        <v>10.28</v>
+        <v>10.24</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M4" t="n">
         <v>2550</v>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>114.5</v>
+        <v>119.5</v>
       </c>
       <c r="F5" t="n">
-        <v>16.33</v>
+        <v>17.05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="M5" t="n">
         <v>114.5</v>
@@ -9018,13 +9018,13 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="F6" t="n">
-        <v>14.54</v>
+        <v>14.67</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H6" t="n">
         <v>12.3</v>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M6" t="n">
         <v>117.5</v>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>4.96</v>
+        <v>5.02</v>
       </c>
       <c r="G7" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M7" t="n">
         <v>24.7</v>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="G9" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="M9" t="n">
         <v>185</v>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>8.720000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>41.4</v>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="F11" t="n">
-        <v>22.91</v>
+        <v>22.57</v>
       </c>
       <c r="G11" t="n">
-        <v>8.779999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="M11" t="n">
         <v>874</v>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F12" t="n">
-        <v>24.94</v>
+        <v>24.81</v>
       </c>
       <c r="G12" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="M12" t="n">
         <v>582</v>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>168</v>
+        <v>168.5</v>
       </c>
       <c r="F13" t="n">
-        <v>18.06</v>
+        <v>18.12</v>
       </c>
       <c r="G13" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
         <v>168</v>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.1</v>
+        <v>38.95</v>
       </c>
       <c r="F14" t="n">
-        <v>7.86</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
         <v>38.1</v>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2070</v>
+        <v>2130</v>
       </c>
       <c r="F15" t="n">
-        <v>32.52</v>
+        <v>33.46</v>
       </c>
       <c r="G15" t="n">
-        <v>16.76</v>
+        <v>17.24</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
         <v>2070</v>
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1520</v>
+        <v>1540</v>
       </c>
       <c r="F16" t="n">
-        <v>35.06</v>
+        <v>35.52</v>
       </c>
       <c r="G16" t="n">
-        <v>10.67</v>
+        <v>10.81</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
         <v>1520</v>
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>91.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>8.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="M17" t="n">
         <v>91.40000000000001</v>
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="F18" t="n">
-        <v>8.449999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.07</v>
       </c>
       <c r="M18" t="n">
         <v>56.1</v>
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="F19" t="n">
-        <v>7.35</v>
+        <v>7.28</v>
       </c>
       <c r="G19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>53</v>
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>325.5</v>
+        <v>322</v>
       </c>
       <c r="F20" t="n">
-        <v>14.18</v>
+        <v>14.03</v>
       </c>
       <c r="G20" t="n">
-        <v>5.15</v>
+        <v>5.09</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="M20" t="n">
         <v>325.5</v>
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2240</v>
+        <v>2275</v>
       </c>
       <c r="F21" t="n">
-        <v>7.18</v>
+        <v>7.29</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M21" t="n">
         <v>2240</v>
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>188.5</v>
+        <v>189.5</v>
       </c>
       <c r="F22" t="n">
-        <v>14.97</v>
+        <v>15.05</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M22" t="n">
         <v>188.5</v>
@@ -10393,13 +10393,13 @@
         <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>1490</v>
+        <v>1540</v>
       </c>
       <c r="F23" t="n">
-        <v>15.89</v>
+        <v>16.42</v>
       </c>
       <c r="G23" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="H23" t="n">
         <v>11.9</v>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="M23" t="n">
         <v>1490</v>
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>155</v>
+        <v>155.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16.28</v>
+        <v>16.33</v>
       </c>
       <c r="G2" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M2" t="n">
         <v>155</v>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F3" t="n">
-        <v>22.31</v>
+        <v>22.19</v>
       </c>
       <c r="G3" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="M3" t="n">
         <v>596</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>381.5</v>
+        <v>390.5</v>
       </c>
       <c r="F5" t="n">
-        <v>32.25</v>
+        <v>33.01</v>
       </c>
       <c r="G5" t="n">
-        <v>8.289999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M5" t="n">
         <v>381.5</v>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>83.7</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>14.63</v>
+        <v>13.99</v>
       </c>
       <c r="G6" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-4.42</v>
       </c>
       <c r="M6" t="n">
         <v>83.7</v>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>139.5</v>
+        <v>136</v>
       </c>
       <c r="F7" t="n">
-        <v>19.43</v>
+        <v>18.94</v>
       </c>
       <c r="G7" t="n">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-2.51</v>
       </c>
       <c r="M7" t="n">
         <v>139.5</v>
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>249</v>
+        <v>244.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.41</v>
+        <v>16.12</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.81</v>
       </c>
       <c r="M8" t="n">
         <v>249</v>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="F9" t="n">
-        <v>45.74</v>
+        <v>45.53</v>
       </c>
       <c r="G9" t="n">
-        <v>24.43</v>
+        <v>24.32</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="M9" t="n">
         <v>1080</v>
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>57.5</v>
+        <v>58.1</v>
       </c>
       <c r="F10" t="n">
-        <v>18.55</v>
+        <v>18.74</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M10" t="n">
         <v>57.5</v>
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="F2" t="n">
-        <v>115.15</v>
+        <v>115.82</v>
       </c>
       <c r="G2" t="n">
-        <v>31.05</v>
+        <v>31.23</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M2" t="n">
         <v>1710</v>
@@ -11538,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="F3" t="n">
-        <v>9.390000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>45</v>
@@ -11617,13 +11617,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="F4" t="n">
-        <v>17.11</v>
+        <v>17.05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M4" t="n">
         <v>154.5</v>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5575</v>
+        <v>6130</v>
       </c>
       <c r="F5" t="n">
-        <v>119.38</v>
+        <v>131.26</v>
       </c>
       <c r="G5" t="n">
-        <v>34.35</v>
+        <v>37.76</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>5575</v>
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>121.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44</v>
+        <v>22.97</v>
       </c>
       <c r="G6" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-2.02</v>
       </c>
       <c r="M6" t="n">
         <v>124</v>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>28.08</v>
+        <v>28.77</v>
       </c>
       <c r="G7" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M7" t="n">
         <v>102.5</v>
@@ -11941,13 +11941,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>171.5</v>
+        <v>171</v>
       </c>
       <c r="F8" t="n">
-        <v>21.88</v>
+        <v>21.81</v>
       </c>
       <c r="G8" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="M8" t="n">
         <v>171.5</v>
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.79</v>
+        <v>25.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M9" t="n">
         <v>106</v>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>176</v>
+        <v>174.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.93</v>
+        <v>19.76</v>
       </c>
       <c r="G10" t="n">
-        <v>7.07</v>
+        <v>7.01</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M10" t="n">
         <v>176</v>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="F11" t="n">
-        <v>23.15</v>
+        <v>23.25</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M11" t="n">
         <v>1205</v>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>175.5</v>
+        <v>174</v>
       </c>
       <c r="F12" t="n">
-        <v>21.88</v>
+        <v>21.7</v>
       </c>
       <c r="G12" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M12" t="n">
         <v>175.5</v>
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>297.5</v>
+        <v>288</v>
       </c>
       <c r="F13" t="n">
-        <v>34.8</v>
+        <v>33.68</v>
       </c>
       <c r="G13" t="n">
-        <v>7.05</v>
+        <v>6.82</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,7 +12367,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-3.19</v>
       </c>
       <c r="M13" t="n">
         <v>297.5</v>
@@ -12506,13 +12506,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F15" t="n">
-        <v>19.19</v>
+        <v>19.46</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.48</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>213</v>
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8360</v>
+        <v>8100</v>
       </c>
       <c r="F16" t="n">
-        <v>214.3</v>
+        <v>207.64</v>
       </c>
       <c r="G16" t="n">
-        <v>83.2</v>
+        <v>80.61</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-3.11</v>
       </c>
       <c r="M16" t="n">
         <v>8360</v>
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1965</v>
+        <v>1900</v>
       </c>
       <c r="F2" t="n">
-        <v>62.54</v>
+        <v>60.47</v>
       </c>
       <c r="G2" t="n">
-        <v>17.38</v>
+        <v>16.8</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-3.31</v>
       </c>
       <c r="M2" t="n">
         <v>1965</v>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>69.5</v>
+        <v>72.3</v>
       </c>
       <c r="F3" t="n">
-        <v>20.44</v>
+        <v>21.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="M3" t="n">
         <v>69.5</v>
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>7165</v>
+        <v>7160</v>
       </c>
       <c r="F4" t="n">
-        <v>161.7</v>
+        <v>161.59</v>
       </c>
       <c r="G4" t="n">
-        <v>44.59</v>
+        <v>44.56</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>7165</v>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>6000</v>
+        <v>6150</v>
       </c>
       <c r="F5" t="n">
-        <v>93.81999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="G5" t="n">
-        <v>36.86</v>
+        <v>37.78</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
         <v>6000</v>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="F6" t="n">
-        <v>45.29</v>
+        <v>47.38</v>
       </c>
       <c r="G6" t="n">
-        <v>23.75</v>
+        <v>24.85</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,7 +13146,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M6" t="n">
         <v>692</v>
@@ -13206,10 +13206,10 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>11.93</v>
+        <v>11.97</v>
       </c>
       <c r="G7" t="n">
         <v>1.67</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="M7" t="n">
         <v>97.09999999999999</v>
@@ -13285,10 +13285,10 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>156.5</v>
+        <v>157</v>
       </c>
       <c r="F8" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="G8" t="n">
         <v>2.1</v>
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M8" t="n">
         <v>156.5</v>
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.52</v>
+        <v>15.67</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>106.5</v>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="F10" t="n">
-        <v>28.68</v>
+        <v>28.95</v>
       </c>
       <c r="G10" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>1060</v>
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F11" t="n">
-        <v>27.13</v>
+        <v>28.1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
         <v>197</v>
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4345</v>
+        <v>4395</v>
       </c>
       <c r="F12" t="n">
-        <v>63.73</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>6.21</v>
+        <v>6.28</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M12" t="n">
         <v>4345</v>

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="F2" t="n">
-        <v>115.82</v>
+        <v>115.49</v>
       </c>
       <c r="G2" t="n">
-        <v>31.23</v>
+        <v>31.14</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.58</v>
+        <v>-0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,13 +636,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
       <c r="F3" t="n">
-        <v>9.52</v>
+        <v>9.42</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>-1.1</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6130</v>
+        <v>5940</v>
       </c>
       <c r="F5" t="n">
-        <v>131.26</v>
+        <v>127.19</v>
       </c>
       <c r="G5" t="n">
-        <v>37.76</v>
+        <v>36.59</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9.960000000000001</v>
+        <v>-3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>5575</v>
+        <v>6130</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>121.5</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>22.97</v>
+        <v>23.63</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.53</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-2.02</v>
+        <v>2.88</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>121.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.77</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.44</v>
+        <v>-2.86</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>105</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>171.5</v>
+        <v>171</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>107.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.67</v>
+        <v>26.16</v>
       </c>
       <c r="G9" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>174.5</v>
+        <v>173</v>
       </c>
       <c r="F10" t="n">
-        <v>19.76</v>
+        <v>19.59</v>
       </c>
       <c r="G10" t="n">
-        <v>7.01</v>
+        <v>6.95</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.85</v>
+        <v>-0.86</v>
       </c>
       <c r="M10" t="n">
-        <v>176</v>
+        <v>174.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1210</v>
+        <v>1170</v>
       </c>
       <c r="F11" t="n">
-        <v>23.25</v>
+        <v>22.48</v>
       </c>
       <c r="G11" t="n">
-        <v>4.41</v>
+        <v>4.27</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.41</v>
+        <v>-3.31</v>
       </c>
       <c r="M11" t="n">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F12" t="n">
-        <v>21.7</v>
+        <v>21.45</v>
       </c>
       <c r="G12" t="n">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.85</v>
+        <v>-1.15</v>
       </c>
       <c r="M12" t="n">
-        <v>175.5</v>
+        <v>174</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="F13" t="n">
-        <v>33.68</v>
+        <v>32.28</v>
       </c>
       <c r="G13" t="n">
-        <v>6.82</v>
+        <v>6.54</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-3.19</v>
+        <v>-4.17</v>
       </c>
       <c r="M13" t="n">
-        <v>297.5</v>
+        <v>288</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>146.5</v>
+        <v>148</v>
       </c>
       <c r="F14" t="n">
-        <v>28.78</v>
+        <v>29.08</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M14" t="n">
         <v>146.5</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8100</v>
+        <v>8095</v>
       </c>
       <c r="F16" t="n">
-        <v>207.64</v>
+        <v>207.51</v>
       </c>
       <c r="G16" t="n">
-        <v>80.61</v>
+        <v>80.56</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-3.11</v>
+        <v>-0.06</v>
       </c>
       <c r="M16" t="n">
-        <v>8360</v>
+        <v>8100</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1725</v>
+        <v>1630</v>
       </c>
       <c r="F17" t="n">
-        <v>51.04</v>
+        <v>48.22</v>
       </c>
       <c r="G17" t="n">
-        <v>10.36</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-3.36</v>
+        <v>-5.51</v>
       </c>
       <c r="M17" t="n">
-        <v>1785</v>
+        <v>1725</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>10580</v>
+        <v>10060</v>
       </c>
       <c r="F18" t="n">
-        <v>58.33</v>
+        <v>55.46</v>
       </c>
       <c r="G18" t="n">
-        <v>29.87</v>
+        <v>28.4</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-0.33</v>
+        <v>-4.91</v>
       </c>
       <c r="M18" t="n">
-        <v>10615</v>
+        <v>10580</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="F19" t="n">
-        <v>85.03</v>
+        <v>80.78</v>
       </c>
       <c r="G19" t="n">
-        <v>16.5</v>
+        <v>15.68</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.99</v>
+        <v>-5</v>
       </c>
       <c r="M19" t="n">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>95</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>52.2</v>
+        <v>50.88</v>
       </c>
       <c r="G20" t="n">
-        <v>7.81</v>
+        <v>7.61</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.64</v>
+        <v>-2.53</v>
       </c>
       <c r="M20" t="n">
-        <v>94.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>6025</v>
+        <v>5700</v>
       </c>
       <c r="F21" t="n">
-        <v>98.64</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>25.47</v>
+        <v>24.1</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>-5.39</v>
       </c>
       <c r="M21" t="n">
-        <v>5615</v>
+        <v>6025</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2365</v>
+        <v>2200</v>
       </c>
       <c r="F22" t="n">
-        <v>60.33</v>
+        <v>56.12</v>
       </c>
       <c r="G22" t="n">
-        <v>30.37</v>
+        <v>28.25</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>-6.98</v>
       </c>
       <c r="M22" t="n">
-        <v>2330</v>
+        <v>2365</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="F23" t="n">
-        <v>42.5</v>
+        <v>41.7</v>
       </c>
       <c r="G23" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="M23" t="n">
         <v>18.7</v>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1735</v>
+        <v>1655</v>
       </c>
       <c r="F24" t="n">
-        <v>88.12</v>
+        <v>84.05</v>
       </c>
       <c r="G24" t="n">
-        <v>21.5</v>
+        <v>20.51</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-0.29</v>
+        <v>-4.61</v>
       </c>
       <c r="M24" t="n">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>71.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>86.70999999999999</v>
+        <v>80.61</v>
       </c>
       <c r="G25" t="n">
-        <v>5.92</v>
+        <v>5.5</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>9.890000000000001</v>
+        <v>-7.03</v>
       </c>
       <c r="M25" t="n">
-        <v>64.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>3025</v>
+        <v>2725</v>
       </c>
       <c r="F26" t="n">
-        <v>260.33</v>
+        <v>234.51</v>
       </c>
       <c r="G26" t="n">
-        <v>59.3</v>
+        <v>53.42</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>-9.92</v>
       </c>
       <c r="M26" t="n">
-        <v>2960</v>
+        <v>3025</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>762</v>
+        <v>740</v>
       </c>
       <c r="F27" t="n">
-        <v>55.14</v>
+        <v>53.55</v>
       </c>
       <c r="G27" t="n">
-        <v>8.609999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.42</v>
+        <v>-2.89</v>
       </c>
       <c r="M27" t="n">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="F28" t="n">
-        <v>58.03</v>
+        <v>57.05</v>
       </c>
       <c r="G28" t="n">
-        <v>12.03</v>
+        <v>11.82</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-0.84</v>
+        <v>-1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>582</v>
+        <v>535</v>
       </c>
       <c r="F29" t="n">
-        <v>95.25</v>
+        <v>87.56</v>
       </c>
       <c r="G29" t="n">
-        <v>18.67</v>
+        <v>17.16</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.01</v>
+        <v>-8.08</v>
       </c>
       <c r="M29" t="n">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3420</v>
+        <v>3275</v>
       </c>
       <c r="F30" t="n">
-        <v>80.66</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>11.12</v>
+        <v>10.65</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.01</v>
+        <v>-4.24</v>
       </c>
       <c r="M30" t="n">
-        <v>3320</v>
+        <v>3420</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>519</v>
+        <v>473</v>
       </c>
       <c r="F31" t="n">
-        <v>105.27</v>
+        <v>95.94</v>
       </c>
       <c r="G31" t="n">
-        <v>13.54</v>
+        <v>12.34</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-0.57</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F32" t="n">
-        <v>45.66</v>
+        <v>45.47</v>
       </c>
       <c r="G32" t="n">
-        <v>11.32</v>
+        <v>11.28</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.83</v>
+        <v>-0.42</v>
       </c>
       <c r="M32" t="n">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>636</v>
+        <v>599</v>
       </c>
       <c r="F33" t="n">
-        <v>42.83</v>
+        <v>40.34</v>
       </c>
       <c r="G33" t="n">
-        <v>7.39</v>
+        <v>6.96</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.16</v>
+        <v>-5.82</v>
       </c>
       <c r="M33" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>7325</v>
+        <v>7275</v>
       </c>
       <c r="F34" t="n">
-        <v>38.96</v>
+        <v>38.69</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>9.98</v>
+        <v>-0.68</v>
       </c>
       <c r="M34" t="n">
-        <v>6660</v>
+        <v>7325</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>4625</v>
+        <v>4525</v>
       </c>
       <c r="F35" t="n">
-        <v>76.38</v>
+        <v>74.73</v>
       </c>
       <c r="G35" t="n">
-        <v>17.4</v>
+        <v>17.03</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1.39</v>
+        <v>-2.16</v>
       </c>
       <c r="M35" t="n">
-        <v>4690</v>
+        <v>4625</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>1900</v>
+        <v>1775</v>
       </c>
       <c r="F36" t="n">
-        <v>60.47</v>
+        <v>56.49</v>
       </c>
       <c r="G36" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="H36" t="n">
         <v>59.1</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-3.31</v>
+        <v>-6.58</v>
       </c>
       <c r="M36" t="n">
-        <v>1965</v>
+        <v>1900</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -3362,13 +3362,13 @@
         <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>72.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>21.26</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H37" t="n">
         <v>19</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.03</v>
+        <v>-1.24</v>
       </c>
       <c r="M37" t="n">
-        <v>69.5</v>
+        <v>72.3</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
@@ -3445,13 +3445,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>7160</v>
+        <v>6990</v>
       </c>
       <c r="F38" t="n">
-        <v>161.59</v>
+        <v>157.75</v>
       </c>
       <c r="G38" t="n">
-        <v>44.56</v>
+        <v>43.5</v>
       </c>
       <c r="H38" t="n">
         <v>70.2</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.37</v>
       </c>
       <c r="M38" t="n">
-        <v>7165</v>
+        <v>7160</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3524,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>6150</v>
+        <v>5545</v>
       </c>
       <c r="F39" t="n">
-        <v>96.17</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>37.78</v>
+        <v>34.06</v>
       </c>
       <c r="H39" t="n">
         <v>75.3</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>-9.84</v>
       </c>
       <c r="M39" t="n">
-        <v>6000</v>
+        <v>6150</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3603,13 +3603,13 @@
         <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>724</v>
+        <v>663</v>
       </c>
       <c r="F40" t="n">
-        <v>47.38</v>
+        <v>43.39</v>
       </c>
       <c r="G40" t="n">
-        <v>24.85</v>
+        <v>22.75</v>
       </c>
       <c r="H40" t="n">
         <v>47.5</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.62</v>
+        <v>-8.43</v>
       </c>
       <c r="M40" t="n">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
@@ -3686,13 +3686,13 @@
         <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="F41" t="n">
-        <v>11.97</v>
+        <v>11.98</v>
       </c>
       <c r="G41" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H41" t="n">
         <v>11</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="M41" t="n">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3765,13 +3765,13 @@
         <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" t="n">
-        <v>12.08</v>
+        <v>12.15</v>
       </c>
       <c r="G42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H42" t="n">
         <v>13.4</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="M42" t="n">
-        <v>156.5</v>
+        <v>157</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3848,13 +3848,13 @@
         <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="F43" t="n">
-        <v>15.67</v>
+        <v>15.74</v>
       </c>
       <c r="G43" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="H43" t="n">
         <v>16</v>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="M43" t="n">
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3927,13 +3927,13 @@
         <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>1070</v>
+        <v>1175</v>
       </c>
       <c r="F44" t="n">
-        <v>28.95</v>
+        <v>31.79</v>
       </c>
       <c r="G44" t="n">
-        <v>4.46</v>
+        <v>4.9</v>
       </c>
       <c r="H44" t="n">
         <v>21.4</v>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="M44" t="n">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4010,13 +4010,13 @@
         <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>204</v>
+        <v>198.5</v>
       </c>
       <c r="F45" t="n">
-        <v>28.1</v>
+        <v>27.34</v>
       </c>
       <c r="G45" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="H45" t="n">
         <v>30.9</v>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.55</v>
+        <v>-2.7</v>
       </c>
       <c r="M45" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4093,13 +4093,13 @@
         <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>4395</v>
+        <v>4055</v>
       </c>
       <c r="F46" t="n">
-        <v>64.45999999999999</v>
+        <v>59.47</v>
       </c>
       <c r="G46" t="n">
-        <v>6.28</v>
+        <v>5.79</v>
       </c>
       <c r="H46" t="n">
         <v>51.7</v>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.15</v>
+        <v>-7.74</v>
       </c>
       <c r="M46" t="n">
-        <v>4345</v>
+        <v>4395</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4176,13 +4176,13 @@
         <v>79</v>
       </c>
       <c r="E47" t="n">
-        <v>243.5</v>
+        <v>235.5</v>
       </c>
       <c r="F47" t="n">
-        <v>24.8</v>
+        <v>23.98</v>
       </c>
       <c r="G47" t="n">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>-3.29</v>
       </c>
       <c r="M47" t="n">
         <v>243.5</v>
@@ -4253,13 +4253,13 @@
         <v>78</v>
       </c>
       <c r="E48" t="n">
-        <v>128.5</v>
+        <v>127</v>
       </c>
       <c r="F48" t="n">
-        <v>20.89</v>
+        <v>20.65</v>
       </c>
       <c r="G48" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-1.53</v>
+        <v>-1.17</v>
       </c>
       <c r="M48" t="n">
-        <v>130.5</v>
+        <v>128.5</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4330,13 +4330,13 @@
         <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>263.5</v>
+        <v>246.5</v>
       </c>
       <c r="F49" t="n">
-        <v>28.86</v>
+        <v>27</v>
       </c>
       <c r="G49" t="n">
-        <v>3.56</v>
+        <v>3.33</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.73</v>
+        <v>-6.45</v>
       </c>
       <c r="M49" t="n">
-        <v>256.5</v>
+        <v>263.5</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
@@ -4390,12 +4390,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4404,19 +4404,21 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>527</v>
+        <v>758</v>
       </c>
       <c r="F50" t="n">
-        <v>20.45</v>
+        <v>27.48</v>
       </c>
       <c r="G50" t="n">
-        <v>5.64</v>
+        <v>7.75</v>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>27</v>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
@@ -4424,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="M50" t="n">
-        <v>532</v>
+        <v>746</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4436,23 +4438,23 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EPS資料不足、營收5年萎縮-6%</t>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>17.9</v>
+        <v>31.7</v>
       </c>
       <c r="Q50" t="n">
         <v>1.5</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.1</v>
+        <v>3.8</v>
       </c>
       <c r="S50" t="n">
-        <v>730.1</v>
+        <v>21.9</v>
       </c>
       <c r="T50" t="n">
-        <v>45.2</v>
+        <v>32.2</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
@@ -4469,12 +4471,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4483,20 +4485,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>746</v>
+        <v>140</v>
       </c>
       <c r="F51" t="n">
-        <v>27.05</v>
+        <v>26.12</v>
       </c>
       <c r="G51" t="n">
-        <v>7.63</v>
+        <v>3.25</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>186.3</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -4505,10 +4507,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-0.4</v>
+        <v>-5.72</v>
       </c>
       <c r="M51" t="n">
-        <v>749</v>
+        <v>148.5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4517,28 +4519,28 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS單期衰退、營收5年萎縮-3%</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>31.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="R51" t="n">
-        <v>3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="S51" t="n">
-        <v>21.9</v>
+        <v>37</v>
       </c>
       <c r="T51" t="n">
-        <v>32.2</v>
+        <v>35.8</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4550,93 +4552,91 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E52" t="n">
-        <v>148.5</v>
+        <v>641</v>
       </c>
       <c r="F52" t="n">
-        <v>27.71</v>
+        <v>29.03</v>
       </c>
       <c r="G52" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>7.91</v>
+      </c>
+      <c r="H52" t="n">
+        <v>29.3</v>
+      </c>
       <c r="I52" t="n">
-        <v>186.3</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-3.57</v>
+        <v>-2.44</v>
       </c>
       <c r="M52" t="n">
-        <v>154</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、營收5年萎縮-3%</t>
-        </is>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>10.7</v>
+        <v>19.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.4</v>
+        <v>10.6</v>
       </c>
       <c r="S52" t="n">
-        <v>37</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
+        <v>34.7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4645,25 +4645,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E53" t="n">
-        <v>657</v>
+        <v>710</v>
       </c>
       <c r="F53" t="n">
-        <v>29.76</v>
+        <v>43.56</v>
       </c>
       <c r="G53" t="n">
-        <v>8.1</v>
+        <v>5.84</v>
       </c>
       <c r="H53" t="n">
-        <v>29.3</v>
+        <v>46.1</v>
       </c>
       <c r="I53" t="n">
-        <v>18.6</v>
+        <v>30.6</v>
       </c>
       <c r="J53" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4671,78 +4671,78 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-2.52</v>
+        <v>-5.96</v>
       </c>
       <c r="M53" t="n">
-        <v>674</v>
+        <v>755</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R53" t="n">
-        <v>10.6</v>
+        <v>24.8</v>
       </c>
       <c r="S53" t="n">
-        <v>64.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>34.7</v>
+        <v>60.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>755</v>
+        <v>58.2</v>
       </c>
       <c r="F54" t="n">
-        <v>46.32</v>
+        <v>15.99</v>
       </c>
       <c r="G54" t="n">
-        <v>6.22</v>
+        <v>2.43</v>
       </c>
       <c r="H54" t="n">
-        <v>46.1</v>
+        <v>17.3</v>
       </c>
       <c r="I54" t="n">
-        <v>30.6</v>
+        <v>11.8</v>
       </c>
       <c r="J54" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4750,30 +4750,30 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.58</v>
+        <v>-2.68</v>
       </c>
       <c r="M54" t="n">
-        <v>736</v>
+        <v>59.8</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>15.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R54" t="n">
-        <v>24.8</v>
+        <v>4.4</v>
       </c>
       <c r="S54" t="n">
-        <v>1.5</v>
+        <v>768.2</v>
       </c>
       <c r="T54" t="n">
-        <v>60.2</v>
+        <v>19.4</v>
       </c>
       <c r="U54" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟡未來合理</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4803,25 +4803,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E55" t="n">
-        <v>59.8</v>
+        <v>178.5</v>
       </c>
       <c r="F55" t="n">
-        <v>16.43</v>
+        <v>16.3</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="H55" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="I55" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="J55" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4829,34 +4829,34 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-2.13</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>61.1</v>
+        <v>179.5</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.15</v>
+        <v>4.03</v>
       </c>
       <c r="R55" t="n">
-        <v>4.4</v>
+        <v>30.2</v>
       </c>
       <c r="S55" t="n">
-        <v>768.2</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>19.4</v>
+        <v>16.9</v>
       </c>
       <c r="U55" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -4868,91 +4868,89 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E56" t="n">
-        <v>179.5</v>
+        <v>363</v>
       </c>
       <c r="F56" t="n">
-        <v>16.39</v>
+        <v>18.8</v>
       </c>
       <c r="G56" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H56" t="n">
-        <v>15.5</v>
-      </c>
+        <v>5.33</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.95</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.84</v>
+        <v>-1.49</v>
       </c>
       <c r="M56" t="n">
-        <v>178</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
+        <v>368.5</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.03</v>
+        <v>1.09</v>
       </c>
       <c r="R56" t="n">
-        <v>30.2</v>
+        <v>24.2</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.95</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4961,20 +4959,20 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E57" t="n">
-        <v>368.5</v>
+        <v>165.5</v>
       </c>
       <c r="F57" t="n">
-        <v>19.08</v>
+        <v>18.62</v>
       </c>
       <c r="G57" t="n">
-        <v>5.41</v>
+        <v>3.93</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>49</v>
+        <v>57.1</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -4983,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-1.86</v>
+        <v>-2.07</v>
       </c>
       <c r="M57" t="n">
-        <v>375.5</v>
+        <v>169</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4995,24 +4993,24 @@
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>29.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="R57" t="n">
-        <v>24.2</v>
+        <v>11.1</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="T57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5024,34 +5022,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>169</v>
+        <v>97.2</v>
       </c>
       <c r="F58" t="n">
-        <v>19.01</v>
+        <v>18.55</v>
       </c>
       <c r="G58" t="n">
-        <v>4.01</v>
+        <v>1.89</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>57.1</v>
+        <v>11.3</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5060,31 +5058,35 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.2</v>
+        <v>-3.28</v>
       </c>
       <c r="M58" t="n">
-        <v>167</v>
+        <v>100.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>月營收轉負-3%</t>
+        </is>
+      </c>
       <c r="P58" t="n">
-        <v>18.6</v>
+        <v>9.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.74</v>
+        <v>1.99</v>
       </c>
       <c r="R58" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>3.6</v>
+        <v>-2.7</v>
       </c>
       <c r="T58" t="n">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
@@ -5101,12 +5103,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5115,20 +5117,20 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>100.5</v>
+        <v>154</v>
       </c>
       <c r="F59" t="n">
-        <v>19.18</v>
+        <v>17.17</v>
       </c>
       <c r="G59" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5137,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-4.29</v>
+        <v>-1.91</v>
       </c>
       <c r="M59" t="n">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5149,23 +5151,23 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>月營收轉負-3%</t>
+          <t>ROE5低</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="S59" t="n">
-        <v>-2.7</v>
+        <v>14.6</v>
       </c>
       <c r="T59" t="n">
-        <v>20.3</v>
+        <v>34.2</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
@@ -5182,12 +5184,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5196,20 +5198,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>157</v>
+        <v>293</v>
       </c>
       <c r="F60" t="n">
-        <v>17.5</v>
+        <v>18.21</v>
       </c>
       <c r="G60" t="n">
-        <v>1.73</v>
+        <v>6.62</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5218,40 +5220,36 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1.57</v>
+        <v>-2.01</v>
       </c>
       <c r="M60" t="n">
-        <v>159.5</v>
+        <v>299</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>ROE5低</t>
-        </is>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>5.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="R60" t="n">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
       <c r="S60" t="n">
-        <v>14.6</v>
+        <v>812.4</v>
       </c>
       <c r="T60" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -5263,12 +5261,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5277,20 +5275,20 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>299</v>
+        <v>186</v>
       </c>
       <c r="F61" t="n">
-        <v>18.58</v>
+        <v>15.7</v>
       </c>
       <c r="G61" t="n">
-        <v>6.75</v>
+        <v>1.87</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>9.6</v>
+        <v>49.2</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -5299,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-2.92</v>
+        <v>-0.53</v>
       </c>
       <c r="M61" t="n">
-        <v>308</v>
+        <v>187</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5311,24 +5309,24 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>30.7</v>
+        <v>14.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R61" t="n">
-        <v>20.4</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>812.4</v>
+        <v>10.3</v>
       </c>
       <c r="T61" t="n">
-        <v>34.6</v>
+        <v>20.2</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟠偏貴</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -5340,12 +5338,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5354,20 +5352,20 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>187</v>
+        <v>797</v>
       </c>
       <c r="F62" t="n">
-        <v>15.78</v>
+        <v>18.41</v>
       </c>
       <c r="G62" t="n">
-        <v>1.88</v>
+        <v>14.86</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>49.2</v>
+        <v>-8.1</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -5379,28 +5377,32 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>187</v>
+        <v>797</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
       <c r="P62" t="n">
-        <v>14.4</v>
+        <v>94.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>18.2</v>
       </c>
       <c r="S62" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="T62" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
@@ -5417,35 +5419,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>797</v>
+        <v>488</v>
       </c>
       <c r="F63" t="n">
-        <v>18.41</v>
+        <v>18.94</v>
       </c>
       <c r="G63" t="n">
-        <v>14.86</v>
+        <v>5.22</v>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
-        <v>-8.1</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.14</v>
+        <v>-7.4</v>
       </c>
       <c r="M63" t="n">
-        <v>788</v>
+        <v>527</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5465,28 +5465,28 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS資料不足、營收5年萎縮-6%</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>94.5</v>
+        <v>17.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="R63" t="n">
-        <v>18.2</v>
+        <v>-6.1</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>730.1</v>
       </c>
       <c r="T63" t="n">
-        <v>19.6</v>
+        <v>45.2</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>174</v>
+        <v>161.5</v>
       </c>
       <c r="F64" t="n">
-        <v>19.18</v>
+        <v>17.81</v>
       </c>
       <c r="G64" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1.69</v>
+        <v>-7.18</v>
       </c>
       <c r="M64" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F65" t="n">
-        <v>12.2</v>
+        <v>12.22</v>
       </c>
       <c r="G65" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5616,7 +5616,7 @@
         <v>0.2</v>
       </c>
       <c r="M65" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>155.5</v>
+        <v>158</v>
       </c>
       <c r="F66" t="n">
-        <v>16.33</v>
+        <v>16.6</v>
       </c>
       <c r="G66" t="n">
-        <v>4.6</v>
+        <v>4.68</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.32</v>
+        <v>1.61</v>
       </c>
       <c r="M66" t="n">
-        <v>155</v>
+        <v>155.5</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F67" t="n">
-        <v>22.19</v>
+        <v>22.27</v>
       </c>
       <c r="G67" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-0.5</v>
+        <v>0.34</v>
       </c>
       <c r="M67" t="n">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5833,13 +5833,13 @@
         <v>91</v>
       </c>
       <c r="E68" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F68" t="n">
-        <v>15.25</v>
+        <v>15.18</v>
       </c>
       <c r="G68" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="H68" t="n">
         <v>15</v>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M68" t="n">
         <v>118</v>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>390.5</v>
+        <v>360.5</v>
       </c>
       <c r="F69" t="n">
-        <v>33.01</v>
+        <v>30.47</v>
       </c>
       <c r="G69" t="n">
-        <v>8.49</v>
+        <v>7.84</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.36</v>
+        <v>-7.68</v>
       </c>
       <c r="M69" t="n">
-        <v>381.5</v>
+        <v>390.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>80</v>
+        <v>79.7</v>
       </c>
       <c r="F70" t="n">
-        <v>13.99</v>
+        <v>13.93</v>
       </c>
       <c r="G70" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-4.42</v>
+        <v>-0.37</v>
       </c>
       <c r="M70" t="n">
-        <v>83.7</v>
+        <v>80</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>136</v>
+        <v>135.5</v>
       </c>
       <c r="F71" t="n">
-        <v>18.94</v>
+        <v>18.87</v>
       </c>
       <c r="G71" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-2.51</v>
+        <v>-0.37</v>
       </c>
       <c r="M71" t="n">
-        <v>139.5</v>
+        <v>136</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>244.5</v>
+        <v>240</v>
       </c>
       <c r="F72" t="n">
-        <v>16.12</v>
+        <v>15.82</v>
       </c>
       <c r="G72" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.81</v>
+        <v>-1.84</v>
       </c>
       <c r="M72" t="n">
-        <v>249</v>
+        <v>244.5</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>1075</v>
+        <v>991</v>
       </c>
       <c r="F73" t="n">
-        <v>45.53</v>
+        <v>41.97</v>
       </c>
       <c r="G73" t="n">
-        <v>24.32</v>
+        <v>22.42</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-0.46</v>
+        <v>-7.81</v>
       </c>
       <c r="M73" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>58.1</v>
+        <v>57.3</v>
       </c>
       <c r="F74" t="n">
-        <v>18.74</v>
+        <v>18.48</v>
       </c>
       <c r="G74" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.04</v>
+        <v>-1.38</v>
       </c>
       <c r="M74" t="n">
-        <v>57.5</v>
+        <v>58.1</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3385</v>
+        <v>3280</v>
       </c>
       <c r="F75" t="n">
-        <v>45.12</v>
+        <v>43.72</v>
       </c>
       <c r="G75" t="n">
-        <v>24.08</v>
+        <v>23.33</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.6</v>
+        <v>-3.1</v>
       </c>
       <c r="M75" t="n">
-        <v>3440</v>
+        <v>3385</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="F76" t="n">
-        <v>15.11</v>
+        <v>14.46</v>
       </c>
       <c r="G76" t="n">
-        <v>8.539999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-3.6</v>
+        <v>-4.27</v>
       </c>
       <c r="M76" t="n">
-        <v>778</v>
+        <v>750</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6554,13 +6554,13 @@
         <v>100</v>
       </c>
       <c r="E77" t="n">
-        <v>2540</v>
+        <v>2490</v>
       </c>
       <c r="F77" t="n">
-        <v>29.44</v>
+        <v>28.86</v>
       </c>
       <c r="G77" t="n">
-        <v>10.24</v>
+        <v>10.04</v>
       </c>
       <c r="H77" t="n">
         <v>23.6</v>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-0.39</v>
+        <v>-1.97</v>
       </c>
       <c r="M77" t="n">
-        <v>2550</v>
+        <v>2540</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>119.5</v>
+        <v>120</v>
       </c>
       <c r="F78" t="n">
-        <v>17.05</v>
+        <v>17.12</v>
       </c>
       <c r="G78" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.37</v>
+        <v>0.42</v>
       </c>
       <c r="M78" t="n">
-        <v>114.5</v>
+        <v>119.5</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         <v>94</v>
       </c>
       <c r="E80" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="F80" t="n">
-        <v>5.02</v>
+        <v>4.94</v>
       </c>
       <c r="G80" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.21</v>
+        <v>-1.6</v>
       </c>
       <c r="M80" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F81" t="n">
-        <v>12.27</v>
+        <v>12.21</v>
       </c>
       <c r="G81" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M81" t="n">
         <v>106.5</v>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>185.5</v>
+        <v>183.5</v>
       </c>
       <c r="F82" t="n">
-        <v>13.22</v>
+        <v>13.08</v>
       </c>
       <c r="G82" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.27</v>
+        <v>-1.08</v>
       </c>
       <c r="M82" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F83" t="n">
-        <v>8.84</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="M83" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>861</v>
+        <v>838</v>
       </c>
       <c r="F84" t="n">
-        <v>22.57</v>
+        <v>21.97</v>
       </c>
       <c r="G84" t="n">
-        <v>8.65</v>
+        <v>8.42</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-1.49</v>
+        <v>-2.67</v>
       </c>
       <c r="M84" t="n">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F85" t="n">
-        <v>24.81</v>
+        <v>24.51</v>
       </c>
       <c r="G85" t="n">
-        <v>5.46</v>
+        <v>5.4</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-0.52</v>
+        <v>-1.21</v>
       </c>
       <c r="M85" t="n">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>168.5</v>
+        <v>168</v>
       </c>
       <c r="F86" t="n">
-        <v>18.12</v>
+        <v>18.06</v>
       </c>
       <c r="G86" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="M86" t="n">
-        <v>168</v>
+        <v>168.5</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.95</v>
+        <v>38.65</v>
       </c>
       <c r="F87" t="n">
-        <v>8.029999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="G87" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.23</v>
+        <v>-0.77</v>
       </c>
       <c r="M87" t="n">
-        <v>38.1</v>
+        <v>38.95</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="F88" t="n">
-        <v>33.46</v>
+        <v>32.05</v>
       </c>
       <c r="G88" t="n">
-        <v>17.24</v>
+        <v>16.52</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.9</v>
+        <v>-4.23</v>
       </c>
       <c r="M88" t="n">
-        <v>2070</v>
+        <v>2130</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1540</v>
+        <v>1475</v>
       </c>
       <c r="F89" t="n">
-        <v>35.52</v>
+        <v>34.02</v>
       </c>
       <c r="G89" t="n">
-        <v>10.81</v>
+        <v>10.35</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.32</v>
+        <v>-4.22</v>
       </c>
       <c r="M89" t="n">
-        <v>1520</v>
+        <v>1540</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>90.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="F90" t="n">
-        <v>8.9</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-0.55</v>
+        <v>-2.09</v>
       </c>
       <c r="M90" t="n">
-        <v>91.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>55.5</v>
+        <v>54.4</v>
       </c>
       <c r="F91" t="n">
-        <v>8.359999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="G91" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-1.07</v>
+        <v>-1.98</v>
       </c>
       <c r="M91" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>52.5</v>
+        <v>51.4</v>
       </c>
       <c r="F92" t="n">
-        <v>7.28</v>
+        <v>7.13</v>
       </c>
       <c r="G92" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.1</v>
       </c>
       <c r="M92" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7838,13 +7838,13 @@
         <v>65</v>
       </c>
       <c r="E93" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F93" t="n">
-        <v>14.03</v>
+        <v>14.07</v>
       </c>
       <c r="G93" t="n">
-        <v>5.09</v>
+        <v>5.11</v>
       </c>
       <c r="H93" t="n">
         <v>13.2</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1.08</v>
+        <v>0.31</v>
       </c>
       <c r="M93" t="n">
-        <v>325.5</v>
+        <v>322</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2275</v>
+        <v>2195</v>
       </c>
       <c r="F94" t="n">
-        <v>7.29</v>
+        <v>7.04</v>
       </c>
       <c r="G94" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.56</v>
+        <v>-3.52</v>
       </c>
       <c r="M94" t="n">
-        <v>2240</v>
+        <v>2275</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8004,13 +8004,13 @@
         <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>189.5</v>
+        <v>187</v>
       </c>
       <c r="F95" t="n">
-        <v>15.05</v>
+        <v>14.85</v>
       </c>
       <c r="G95" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="H95" t="n">
         <v>10</v>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.53</v>
+        <v>-1.32</v>
       </c>
       <c r="M95" t="n">
-        <v>188.5</v>
+        <v>189.5</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1490</v>
+        <v>1540</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
@@ -8170,7 +8170,7 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>69.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="F97" t="n">
         <v>4.88</v>
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>-0.57</v>
+        <v>0.14</v>
       </c>
       <c r="M97" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>367.5</v>
+        <v>363</v>
       </c>
       <c r="F98" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="G98" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.38</v>
+        <v>-1.22</v>
       </c>
       <c r="M98" t="n">
-        <v>362.5</v>
+        <v>367.5</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>23</v>
+        <v>23.05</v>
       </c>
       <c r="F99" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="G99" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.66</v>
+        <v>0.22</v>
       </c>
       <c r="M99" t="n">
-        <v>22.85</v>
+        <v>23</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>32.05</v>
+        <v>31.8</v>
       </c>
       <c r="F100" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="G100" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.26</v>
+        <v>-0.78</v>
       </c>
       <c r="M100" t="n">
-        <v>31.65</v>
+        <v>32.05</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>197</v>
+        <v>189.5</v>
       </c>
       <c r="F101" t="n">
-        <v>4.9</v>
+        <v>4.71</v>
       </c>
       <c r="G101" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-1.25</v>
+        <v>-3.81</v>
       </c>
       <c r="M101" t="n">
-        <v>199.5</v>
+        <v>197</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3385</v>
+        <v>3280</v>
       </c>
       <c r="F2" t="n">
-        <v>45.12</v>
+        <v>43.72</v>
       </c>
       <c r="G2" t="n">
-        <v>24.08</v>
+        <v>23.33</v>
       </c>
       <c r="H2" t="n">
         <v>24.6</v>
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.6</v>
+        <v>-3.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3440</v>
+        <v>3385</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="F3" t="n">
-        <v>15.11</v>
+        <v>14.46</v>
       </c>
       <c r="G3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="H3" t="n">
         <v>14.2</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-3.6</v>
+        <v>-4.27</v>
       </c>
       <c r="M3" t="n">
-        <v>778</v>
+        <v>750</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>2540</v>
+        <v>2490</v>
       </c>
       <c r="F4" t="n">
-        <v>29.44</v>
+        <v>28.86</v>
       </c>
       <c r="G4" t="n">
-        <v>10.24</v>
+        <v>10.04</v>
       </c>
       <c r="H4" t="n">
         <v>23.6</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.39</v>
+        <v>-1.97</v>
       </c>
       <c r="M4" t="n">
-        <v>2550</v>
+        <v>2540</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -8939,13 +8939,13 @@
         <v>97</v>
       </c>
       <c r="E5" t="n">
-        <v>119.5</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>17.05</v>
+        <v>17.12</v>
       </c>
       <c r="G5" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="H5" t="n">
         <v>12.4</v>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.37</v>
+        <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>114.5</v>
+        <v>119.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -9097,13 +9097,13 @@
         <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="F7" t="n">
-        <v>5.02</v>
+        <v>4.94</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.21</v>
+        <v>-1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -9176,13 +9176,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
-        <v>12.27</v>
+        <v>12.21</v>
       </c>
       <c r="G8" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
         <v>10.7</v>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="M8" t="n">
         <v>106.5</v>
@@ -9255,13 +9255,13 @@
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>185.5</v>
+        <v>183.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13.22</v>
+        <v>13.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="H9" t="n">
         <v>11.4</v>
@@ -9278,10 +9278,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.27</v>
+        <v>-1.08</v>
       </c>
       <c r="M9" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -9334,13 +9334,13 @@
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>8.84</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="M10" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -9413,13 +9413,13 @@
         <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>861</v>
+        <v>838</v>
       </c>
       <c r="F11" t="n">
-        <v>22.57</v>
+        <v>21.97</v>
       </c>
       <c r="G11" t="n">
-        <v>8.65</v>
+        <v>8.42</v>
       </c>
       <c r="H11" t="n">
         <v>25</v>
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-1.49</v>
+        <v>-2.67</v>
       </c>
       <c r="M11" t="n">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -9492,13 +9492,13 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="F12" t="n">
-        <v>24.81</v>
+        <v>24.51</v>
       </c>
       <c r="G12" t="n">
-        <v>5.46</v>
+        <v>5.4</v>
       </c>
       <c r="H12" t="n">
         <v>21.2</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.52</v>
+        <v>-1.21</v>
       </c>
       <c r="M12" t="n">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -9571,13 +9571,13 @@
         <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>168.5</v>
+        <v>168</v>
       </c>
       <c r="F13" t="n">
-        <v>18.12</v>
+        <v>18.06</v>
       </c>
       <c r="G13" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="H13" t="n">
         <v>14.1</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>168</v>
+        <v>168.5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -9650,13 +9650,13 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>38.95</v>
+        <v>38.65</v>
       </c>
       <c r="F14" t="n">
-        <v>8.029999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="G14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H14" t="n">
         <v>6.2</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>-0.77</v>
       </c>
       <c r="M14" t="n">
-        <v>38.1</v>
+        <v>38.95</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -9729,13 +9729,13 @@
         <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="F15" t="n">
-        <v>33.46</v>
+        <v>32.05</v>
       </c>
       <c r="G15" t="n">
-        <v>17.24</v>
+        <v>16.52</v>
       </c>
       <c r="H15" t="n">
         <v>30.7</v>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>-4.23</v>
       </c>
       <c r="M15" t="n">
-        <v>2070</v>
+        <v>2130</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -9812,13 +9812,13 @@
         <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>1540</v>
+        <v>1475</v>
       </c>
       <c r="F16" t="n">
-        <v>35.52</v>
+        <v>34.02</v>
       </c>
       <c r="G16" t="n">
-        <v>10.81</v>
+        <v>10.35</v>
       </c>
       <c r="H16" t="n">
         <v>21.8</v>
@@ -9835,10 +9835,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>-4.22</v>
       </c>
       <c r="M16" t="n">
-        <v>1520</v>
+        <v>1540</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -9895,13 +9895,13 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>90.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>8.9</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
         <v>8.6</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-0.55</v>
+        <v>-2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>91.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
@@ -9978,13 +9978,13 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>55.5</v>
+        <v>54.4</v>
       </c>
       <c r="F18" t="n">
-        <v>8.359999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="G18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.07</v>
+        <v>-1.98</v>
       </c>
       <c r="M18" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
@@ -10061,13 +10061,13 @@
         <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>52.5</v>
+        <v>51.4</v>
       </c>
       <c r="F19" t="n">
-        <v>7.28</v>
+        <v>7.13</v>
       </c>
       <c r="G19" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="H19" t="n">
         <v>10.4</v>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
@@ -10144,13 +10144,13 @@
         <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F20" t="n">
-        <v>14.03</v>
+        <v>14.07</v>
       </c>
       <c r="G20" t="n">
-        <v>5.09</v>
+        <v>5.11</v>
       </c>
       <c r="H20" t="n">
         <v>13.2</v>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1.08</v>
+        <v>0.31</v>
       </c>
       <c r="M20" t="n">
-        <v>325.5</v>
+        <v>322</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
@@ -10227,13 +10227,13 @@
         <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>2275</v>
+        <v>2195</v>
       </c>
       <c r="F21" t="n">
-        <v>7.29</v>
+        <v>7.04</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.56</v>
+        <v>-3.52</v>
       </c>
       <c r="M21" t="n">
-        <v>2240</v>
+        <v>2275</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
@@ -10310,13 +10310,13 @@
         <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>189.5</v>
+        <v>187</v>
       </c>
       <c r="F22" t="n">
-        <v>15.05</v>
+        <v>14.85</v>
       </c>
       <c r="G22" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="H22" t="n">
         <v>10</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.53</v>
+        <v>-1.32</v>
       </c>
       <c r="M22" t="n">
-        <v>188.5</v>
+        <v>189.5</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1490</v>
+        <v>1540</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
@@ -10607,13 +10607,13 @@
         <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>155.5</v>
+        <v>158</v>
       </c>
       <c r="F2" t="n">
-        <v>16.33</v>
+        <v>16.6</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>4.68</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.32</v>
+        <v>1.61</v>
       </c>
       <c r="M2" t="n">
-        <v>155</v>
+        <v>155.5</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -10686,13 +10686,13 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F3" t="n">
-        <v>22.19</v>
+        <v>22.27</v>
       </c>
       <c r="G3" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="H3" t="n">
         <v>17.9</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-0.5</v>
+        <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -10765,13 +10765,13 @@
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="F4" t="n">
-        <v>15.25</v>
+        <v>15.18</v>
       </c>
       <c r="G4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M4" t="n">
         <v>118</v>
@@ -10844,13 +10844,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>390.5</v>
+        <v>360.5</v>
       </c>
       <c r="F5" t="n">
-        <v>33.01</v>
+        <v>30.47</v>
       </c>
       <c r="G5" t="n">
-        <v>8.49</v>
+        <v>7.84</v>
       </c>
       <c r="H5" t="n">
         <v>27.5</v>
@@ -10867,10 +10867,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.36</v>
+        <v>-7.68</v>
       </c>
       <c r="M5" t="n">
-        <v>381.5</v>
+        <v>390.5</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -10923,13 +10923,13 @@
         <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>79.7</v>
       </c>
       <c r="F6" t="n">
-        <v>13.99</v>
+        <v>13.93</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H6" t="n">
         <v>16.7</v>
@@ -10946,10 +10946,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-4.42</v>
+        <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>83.7</v>
+        <v>80</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11002,13 +11002,13 @@
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>136</v>
+        <v>135.5</v>
       </c>
       <c r="F7" t="n">
-        <v>18.94</v>
+        <v>18.87</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="H7" t="n">
         <v>16.4</v>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.51</v>
+        <v>-0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>139.5</v>
+        <v>136</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11085,13 +11085,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>244.5</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>16.12</v>
+        <v>15.82</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H8" t="n">
         <v>15.3</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-1.81</v>
+        <v>-1.84</v>
       </c>
       <c r="M8" t="n">
-        <v>249</v>
+        <v>244.5</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -11164,13 +11164,13 @@
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>1075</v>
+        <v>991</v>
       </c>
       <c r="F9" t="n">
-        <v>45.53</v>
+        <v>41.97</v>
       </c>
       <c r="G9" t="n">
-        <v>24.32</v>
+        <v>22.42</v>
       </c>
       <c r="H9" t="n">
         <v>38.8</v>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.46</v>
+        <v>-7.81</v>
       </c>
       <c r="M9" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -11245,13 +11245,13 @@
         <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>58.1</v>
+        <v>57.3</v>
       </c>
       <c r="F10" t="n">
-        <v>18.74</v>
+        <v>18.48</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="H10" t="n">
         <v>21.3</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.04</v>
+        <v>-1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>57.5</v>
+        <v>58.1</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -11459,13 +11459,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="F2" t="n">
-        <v>115.82</v>
+        <v>115.49</v>
       </c>
       <c r="G2" t="n">
-        <v>31.23</v>
+        <v>31.14</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -11482,10 +11482,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.58</v>
+        <v>-0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -11538,13 +11538,13 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
       <c r="F3" t="n">
-        <v>9.52</v>
+        <v>9.42</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H3" t="n">
         <v>11.1</v>
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>-1.1</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>154.5</v>
+        <v>154</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>6130</v>
+        <v>5940</v>
       </c>
       <c r="F5" t="n">
-        <v>131.26</v>
+        <v>127.19</v>
       </c>
       <c r="G5" t="n">
-        <v>37.76</v>
+        <v>36.59</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9.960000000000001</v>
+        <v>-3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>5575</v>
+        <v>6130</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -11779,13 +11779,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>121.5</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>22.97</v>
+        <v>23.63</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.53</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -11802,10 +11802,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-2.02</v>
+        <v>2.88</v>
       </c>
       <c r="M6" t="n">
-        <v>124</v>
+        <v>121.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>28.77</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.44</v>
+        <v>-2.86</v>
       </c>
       <c r="M7" t="n">
-        <v>102.5</v>
+        <v>105</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>171.5</v>
+        <v>171</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -12024,13 +12024,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>105.5</v>
+        <v>107.5</v>
       </c>
       <c r="F9" t="n">
-        <v>25.67</v>
+        <v>26.16</v>
       </c>
       <c r="G9" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.47</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>174.5</v>
+        <v>173</v>
       </c>
       <c r="F10" t="n">
-        <v>19.76</v>
+        <v>19.59</v>
       </c>
       <c r="G10" t="n">
-        <v>7.01</v>
+        <v>6.95</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.85</v>
+        <v>-0.86</v>
       </c>
       <c r="M10" t="n">
-        <v>176</v>
+        <v>174.5</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -12182,13 +12182,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1210</v>
+        <v>1170</v>
       </c>
       <c r="F11" t="n">
-        <v>23.25</v>
+        <v>22.48</v>
       </c>
       <c r="G11" t="n">
-        <v>4.41</v>
+        <v>4.27</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.41</v>
+        <v>-3.31</v>
       </c>
       <c r="M11" t="n">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -12261,13 +12261,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F12" t="n">
-        <v>21.7</v>
+        <v>21.45</v>
       </c>
       <c r="G12" t="n">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-0.85</v>
+        <v>-1.15</v>
       </c>
       <c r="M12" t="n">
-        <v>175.5</v>
+        <v>174</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -12344,13 +12344,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="F13" t="n">
-        <v>33.68</v>
+        <v>32.28</v>
       </c>
       <c r="G13" t="n">
-        <v>6.82</v>
+        <v>6.54</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-3.19</v>
+        <v>-4.17</v>
       </c>
       <c r="M13" t="n">
-        <v>297.5</v>
+        <v>288</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -12427,13 +12427,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>146.5</v>
+        <v>148</v>
       </c>
       <c r="F14" t="n">
-        <v>28.78</v>
+        <v>29.08</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M14" t="n">
         <v>146.5</v>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -12589,13 +12589,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8100</v>
+        <v>8095</v>
       </c>
       <c r="F16" t="n">
-        <v>207.64</v>
+        <v>207.51</v>
       </c>
       <c r="G16" t="n">
-        <v>80.61</v>
+        <v>80.56</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-3.11</v>
+        <v>-0.06</v>
       </c>
       <c r="M16" t="n">
-        <v>8360</v>
+        <v>8100</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -12803,13 +12803,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>1900</v>
+        <v>1775</v>
       </c>
       <c r="F2" t="n">
-        <v>60.47</v>
+        <v>56.49</v>
       </c>
       <c r="G2" t="n">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="H2" t="n">
         <v>59.1</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.31</v>
+        <v>-6.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1965</v>
+        <v>1900</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -12882,13 +12882,13 @@
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>72.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>21.26</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H3" t="n">
         <v>19</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.03</v>
+        <v>-1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>69.5</v>
+        <v>72.3</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -12965,13 +12965,13 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>7160</v>
+        <v>6990</v>
       </c>
       <c r="F4" t="n">
-        <v>161.59</v>
+        <v>157.75</v>
       </c>
       <c r="G4" t="n">
-        <v>44.56</v>
+        <v>43.5</v>
       </c>
       <c r="H4" t="n">
         <v>70.2</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.37</v>
       </c>
       <c r="M4" t="n">
-        <v>7165</v>
+        <v>7160</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -13044,13 +13044,13 @@
         <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>6150</v>
+        <v>5545</v>
       </c>
       <c r="F5" t="n">
-        <v>96.17</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>37.78</v>
+        <v>34.06</v>
       </c>
       <c r="H5" t="n">
         <v>75.3</v>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>-9.84</v>
       </c>
       <c r="M5" t="n">
-        <v>6000</v>
+        <v>6150</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -13123,13 +13123,13 @@
         <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>724</v>
+        <v>663</v>
       </c>
       <c r="F6" t="n">
-        <v>47.38</v>
+        <v>43.39</v>
       </c>
       <c r="G6" t="n">
-        <v>24.85</v>
+        <v>22.75</v>
       </c>
       <c r="H6" t="n">
         <v>47.5</v>
@@ -13146,10 +13146,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.62</v>
+        <v>-8.43</v>
       </c>
       <c r="M6" t="n">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -13206,13 +13206,13 @@
         <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11.97</v>
+        <v>11.98</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -13285,13 +13285,13 @@
         <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F8" t="n">
-        <v>12.08</v>
+        <v>12.15</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
         <v>13.4</v>
@@ -13308,10 +13308,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>156.5</v>
+        <v>157</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -13368,13 +13368,13 @@
         <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>15.67</v>
+        <v>15.74</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="H9" t="n">
         <v>16</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -13447,13 +13447,13 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>1070</v>
+        <v>1175</v>
       </c>
       <c r="F10" t="n">
-        <v>28.95</v>
+        <v>31.79</v>
       </c>
       <c r="G10" t="n">
-        <v>4.46</v>
+        <v>4.9</v>
       </c>
       <c r="H10" t="n">
         <v>21.4</v>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="M10" t="n">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -13530,13 +13530,13 @@
         <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>204</v>
+        <v>198.5</v>
       </c>
       <c r="F11" t="n">
-        <v>28.1</v>
+        <v>27.34</v>
       </c>
       <c r="G11" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="n">
         <v>30.9</v>
@@ -13553,10 +13553,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>-2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -13613,13 +13613,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>4395</v>
+        <v>4055</v>
       </c>
       <c r="F12" t="n">
-        <v>64.45999999999999</v>
+        <v>59.47</v>
       </c>
       <c r="G12" t="n">
-        <v>6.28</v>
+        <v>5.79</v>
       </c>
       <c r="H12" t="n">
         <v>51.7</v>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.15</v>
+        <v>-7.74</v>
       </c>
       <c r="M12" t="n">
-        <v>4345</v>
+        <v>4395</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">

--- a/data/台股PE監看表.xlsx
+++ b/data/台股PE監看表.xlsx
@@ -557,13 +557,13 @@
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>1715</v>
+        <v>1685</v>
       </c>
       <c r="F2" t="n">
-        <v>115.49</v>
+        <v>113.47</v>
       </c>
       <c r="G2" t="n">
-        <v>31.14</v>
+        <v>30.6</v>
       </c>
       <c r="H2" t="n">
         <v>92.59999999999999</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.29</v>
+        <v>-1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -636,10 +636,10 @@
         <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>9.42</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>1.89</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.1</v>
+        <v>-0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -715,13 +715,13 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>155.5</v>
       </c>
       <c r="F4" t="n">
-        <v>17.05</v>
+        <v>17.22</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="H4" t="n">
         <v>15.7</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="M4" t="n">
         <v>154</v>
@@ -794,13 +794,13 @@
         <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="F5" t="n">
-        <v>127.19</v>
+        <v>126.02</v>
       </c>
       <c r="G5" t="n">
-        <v>36.59</v>
+        <v>36.26</v>
       </c>
       <c r="H5" t="n">
         <v>107.9</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-3.1</v>
+        <v>-0.93</v>
       </c>
       <c r="M5" t="n">
-        <v>6130</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>126.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.63</v>
+        <v>23.91</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53</v>
+        <v>4.58</v>
       </c>
       <c r="H6" t="n">
         <v>22.9</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.88</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>121.5</v>
+        <v>125</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -956,13 +956,13 @@
         <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.22</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="H7" t="n">
         <v>35.8</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.86</v>
+        <v>0.98</v>
       </c>
       <c r="M7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -1039,13 +1039,13 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>171</v>
+        <v>173.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.81</v>
+        <v>22.13</v>
       </c>
       <c r="G8" t="n">
-        <v>4.78</v>
+        <v>4.85</v>
       </c>
       <c r="H8" t="n">
         <v>25.1</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>171</v>
@@ -1122,13 +1122,13 @@
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>26.16</v>
+        <v>26.28</v>
       </c>
       <c r="G9" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="H9" t="n">
         <v>25.9</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>105.5</v>
+        <v>107.5</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1201,13 +1201,13 @@
         <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F10" t="n">
-        <v>19.59</v>
+        <v>20.05</v>
       </c>
       <c r="G10" t="n">
-        <v>6.95</v>
+        <v>7.11</v>
       </c>
       <c r="H10" t="n">
         <v>19.1</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-0.86</v>
+        <v>2.31</v>
       </c>
       <c r="M10" t="n">
-        <v>174.5</v>
+        <v>173</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>1170</v>
+        <v>1185</v>
       </c>
       <c r="F11" t="n">
-        <v>22.48</v>
+        <v>22.77</v>
       </c>
       <c r="G11" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
       <c r="H11" t="n">
         <v>27.4</v>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-3.31</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>1210</v>
+        <v>1170</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F12" t="n">
-        <v>21.45</v>
+        <v>21.82</v>
       </c>
       <c r="G12" t="n">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="H12" t="n">
         <v>23.2</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1.15</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
@@ -1442,13 +1442,13 @@
         <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="F13" t="n">
-        <v>32.28</v>
+        <v>33.1</v>
       </c>
       <c r="G13" t="n">
-        <v>6.54</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
         <v>32.1</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-4.17</v>
+        <v>2.54</v>
       </c>
       <c r="M13" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>148</v>
+        <v>148.5</v>
       </c>
       <c r="F14" t="n">
-        <v>29.08</v>
+        <v>29.17</v>
       </c>
       <c r="G14" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="H14" t="n">
         <v>28.1</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.02</v>
+        <v>0.34</v>
       </c>
       <c r="M14" t="n">
-        <v>146.5</v>
+        <v>148</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>216</v>
+        <v>219.5</v>
       </c>
       <c r="F15" t="n">
-        <v>19.46</v>
+        <v>19.77</v>
       </c>
       <c r="G15" t="n">
-        <v>5.48</v>
+        <v>5.57</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
         <v>216</v>
@@ -1687,13 +1687,13 @@
         <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>8095</v>
+        <v>8245</v>
       </c>
       <c r="F16" t="n">
-        <v>207.51</v>
+        <v>211.36</v>
       </c>
       <c r="G16" t="n">
-        <v>80.56</v>
+        <v>82.06</v>
       </c>
       <c r="H16" t="n">
         <v>137.1</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-0.06</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>8100</v>
+        <v>8095</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="F17" t="n">
-        <v>48.22</v>
+        <v>48.52</v>
       </c>
       <c r="G17" t="n">
-        <v>9.789999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-5.51</v>
+        <v>0.61</v>
       </c>
       <c r="M17" t="n">
-        <v>1725</v>
+        <v>1630</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1847,13 +1847,13 @@
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>10060</v>
+        <v>10005</v>
       </c>
       <c r="F18" t="n">
-        <v>55.46</v>
+        <v>55.16</v>
       </c>
       <c r="G18" t="n">
-        <v>28.4</v>
+        <v>28.25</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-4.91</v>
+        <v>-0.55</v>
       </c>
       <c r="M18" t="n">
-        <v>10580</v>
+        <v>10060</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1924,13 +1924,13 @@
         <v>94</v>
       </c>
       <c r="E19" t="n">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F19" t="n">
-        <v>80.78</v>
+        <v>80.61</v>
       </c>
       <c r="G19" t="n">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-5</v>
+        <v>-0.21</v>
       </c>
       <c r="M19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>92.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>50.88</v>
+        <v>52.75</v>
       </c>
       <c r="G20" t="n">
-        <v>7.61</v>
+        <v>7.89</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-2.53</v>
+        <v>3.67</v>
       </c>
       <c r="M20" t="n">
-        <v>95</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         <v>84</v>
       </c>
       <c r="E21" t="n">
-        <v>5700</v>
+        <v>5615</v>
       </c>
       <c r="F21" t="n">
-        <v>93.31999999999999</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>24.1</v>
+        <v>23.74</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-5.39</v>
+        <v>-1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>6025</v>
+        <v>5700</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="F22" t="n">
-        <v>56.12</v>
+        <v>57.4</v>
       </c>
       <c r="G22" t="n">
-        <v>28.25</v>
+        <v>28.89</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-6.98</v>
+        <v>2.27</v>
       </c>
       <c r="M22" t="n">
-        <v>2365</v>
+        <v>2200</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>18.35</v>
+        <v>18.45</v>
       </c>
       <c r="F23" t="n">
-        <v>41.7</v>
+        <v>41.93</v>
       </c>
       <c r="G23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1.87</v>
+        <v>0.54</v>
       </c>
       <c r="M23" t="n">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2321,13 +2321,13 @@
         <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>1655</v>
+        <v>1735</v>
       </c>
       <c r="F24" t="n">
-        <v>84.05</v>
+        <v>88.12</v>
       </c>
       <c r="G24" t="n">
-        <v>20.51</v>
+        <v>21.5</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-4.61</v>
+        <v>4.83</v>
       </c>
       <c r="M24" t="n">
-        <v>1735</v>
+        <v>1655</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>66.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="F25" t="n">
-        <v>80.61</v>
+        <v>77.56</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>5.29</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-7.03</v>
+        <v>-3.78</v>
       </c>
       <c r="M25" t="n">
-        <v>71.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2483,13 +2483,13 @@
         <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>2725</v>
+        <v>2880</v>
       </c>
       <c r="F26" t="n">
-        <v>234.51</v>
+        <v>247.85</v>
       </c>
       <c r="G26" t="n">
-        <v>53.42</v>
+        <v>56.46</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-9.92</v>
+        <v>5.69</v>
       </c>
       <c r="M26" t="n">
-        <v>3025</v>
+        <v>2725</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="F27" t="n">
-        <v>53.55</v>
+        <v>54.05</v>
       </c>
       <c r="G27" t="n">
-        <v>8.359999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-2.89</v>
+        <v>0.95</v>
       </c>
       <c r="M27" t="n">
-        <v>762</v>
+        <v>740</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2643,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>1165</v>
+        <v>1190</v>
       </c>
       <c r="F28" t="n">
-        <v>57.05</v>
+        <v>58.28</v>
       </c>
       <c r="G28" t="n">
-        <v>11.82</v>
+        <v>12.08</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-1.69</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2722,13 +2722,13 @@
         <v>66</v>
       </c>
       <c r="E29" t="n">
-        <v>535</v>
+        <v>588</v>
       </c>
       <c r="F29" t="n">
-        <v>87.56</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>17.16</v>
+        <v>18.86</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-8.08</v>
+        <v>9.91</v>
       </c>
       <c r="M29" t="n">
-        <v>582</v>
+        <v>535</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>3275</v>
+        <v>3225</v>
       </c>
       <c r="F30" t="n">
-        <v>77.23999999999999</v>
+        <v>76.06</v>
       </c>
       <c r="G30" t="n">
-        <v>10.65</v>
+        <v>10.49</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-4.24</v>
+        <v>-1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3420</v>
+        <v>3275</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="F31" t="n">
-        <v>95.94</v>
+        <v>101.42</v>
       </c>
       <c r="G31" t="n">
-        <v>12.34</v>
+        <v>13.04</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-8.859999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M31" t="n">
-        <v>519</v>
+        <v>473</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="F32" t="n">
-        <v>45.47</v>
+        <v>45.22</v>
       </c>
       <c r="G32" t="n">
-        <v>11.28</v>
+        <v>11.21</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.42</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
@@ -3040,13 +3040,13 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="F33" t="n">
-        <v>40.34</v>
+        <v>42.22</v>
       </c>
       <c r="G33" t="n">
-        <v>6.96</v>
+        <v>7.29</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-5.82</v>
+        <v>4.67</v>
       </c>
       <c r="M33" t="n">
-        <v>636</v>
+        <v>599</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3121,13 +3121,13 @@
         <v>51</v>
       </c>
       <c r="E34" t="n">
-        <v>7275</v>
+        <v>6880</v>
       </c>
       <c r="F34" t="n">
-        <v>38.69</v>
+        <v>36.59</v>
       </c>
       <c r="G34" t="n">
-        <v>4.97</v>
+        <v>4.7</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-0.68</v>
+        <v>-5.43</v>
       </c>
       <c r="M34" t="n">
-        <v>7325</v>
+        <v>7275</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="F35" t="n">
-        <v>74.73</v>
+        <v>73.91</v>
       </c>
       <c r="G35" t="n">
-        <v>17.03</v>
+        <v>16.84</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-2.16</v>
+        <v>-1.1</v>
       </c>
       <c r="M35" t="n">
-        <v>4625</v>
+        <v>4525</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="F36" t="n">
-        <v>56.49</v>
+        <v>56.81</v>
       </c>
       <c r="G36" t="n">
-        <v>15.7</v>
+        <v>15.79</v>
       </c>
       <c r="H36" t="n">
         <v>59.1</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-6.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>1900</v>
+        <v>1775</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>21.06</v>
       </c>
       <c r="G37" t="n">
         <v>1.05</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1.24</v>
+        <v>0.28</v>
       </c>
       <c r="M37" t="n">
-        <v>72.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
@@ -3445,13 +3445,13 @@
         <v>90</v>
       </c>
       <c r="E38" t="n">
-        <v>6990</v>
+        <v>7070</v>
       </c>
       <c r="F38" t="n">
-        <v>157.75</v>
+        <v>159.56</v>
       </c>
       <c r="G38" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="H38" t="n">
         <v>70.2</v>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-2.37</v>
+        <v>1.14</v>
       </c>
       <c r="M38" t="n">
-        <v>7160</v>
+        <v>6990</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3524,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="E39" t="n">
-        <v>5545</v>
+        <v>5520</v>
       </c>
       <c r="F39" t="n">
-        <v>86.70999999999999</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>34.06</v>
+        <v>33.91</v>
       </c>
       <c r="H39" t="n">
         <v>75.3</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-9.84</v>
+        <v>-0.45</v>
       </c>
       <c r="M39" t="n">
-        <v>6150</v>
+        <v>5545</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -3603,13 +3603,13 @@
         <v>89</v>
       </c>
       <c r="E40" t="n">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="F40" t="n">
-        <v>43.39</v>
+        <v>45.16</v>
       </c>
       <c r="G40" t="n">
-        <v>22.75</v>
+        <v>23.68</v>
       </c>
       <c r="H40" t="n">
         <v>47.5</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-8.43</v>
+        <v>4.07</v>
       </c>
       <c r="M40" t="n">
-        <v>724</v>
+        <v>663</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
@@ -3686,13 +3686,13 @@
         <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="F41" t="n">
-        <v>11.98</v>
+        <v>12.08</v>
       </c>
       <c r="G41" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H41" t="n">
         <v>11</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0.1</v>
+        <v>0.82</v>
       </c>
       <c r="M41" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3765,13 +3765,13 @@
         <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>158</v>
+        <v>160.5</v>
       </c>
       <c r="F42" t="n">
-        <v>12.15</v>
+        <v>12.35</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H42" t="n">
         <v>13.4</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.64</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
@@ -3848,13 +3848,13 @@
         <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>108</v>
+        <v>107.5</v>
       </c>
       <c r="F43" t="n">
-        <v>15.74</v>
+        <v>15.67</v>
       </c>
       <c r="G43" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
         <v>16</v>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.47</v>
+        <v>-0.46</v>
       </c>
       <c r="M43" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3927,13 +3927,13 @@
         <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>1175</v>
+        <v>1065</v>
       </c>
       <c r="F44" t="n">
-        <v>31.79</v>
+        <v>28.81</v>
       </c>
       <c r="G44" t="n">
-        <v>4.9</v>
+        <v>4.44</v>
       </c>
       <c r="H44" t="n">
         <v>21.4</v>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>9.81</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>1070</v>
+        <v>1175</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
@@ -4010,13 +4010,13 @@
         <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>198.5</v>
+        <v>203</v>
       </c>
       <c r="F45" t="n">
-        <v>27.34</v>
+        <v>27.96</v>
       </c>
       <c r="G45" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="H45" t="n">
         <v>30.9</v>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-2.7</v>
+        <v>2.27</v>
       </c>
       <c r="M45" t="n">
-        <v>204</v>
+        <v>198.5</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -4093,13 +4093,13 @@
         <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>4055</v>
+        <v>3940</v>
       </c>
       <c r="F46" t="n">
-        <v>59.47</v>
+        <v>57.79</v>
       </c>
       <c r="G46" t="n">
-        <v>5.79</v>
+        <v>5.63</v>
       </c>
       <c r="H46" t="n">
         <v>51.7</v>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-7.74</v>
+        <v>-2.84</v>
       </c>
       <c r="M46" t="n">
-        <v>4395</v>
+        <v>4055</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -4176,13 +4176,13 @@
         <v>79</v>
       </c>
       <c r="E47" t="n">
-        <v>235.5</v>
+        <v>244</v>
       </c>
       <c r="F47" t="n">
-        <v>23.98</v>
+        <v>24.85</v>
       </c>
       <c r="G47" t="n">
-        <v>4.06</v>
+        <v>4.21</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-3.29</v>
+        <v>3.61</v>
       </c>
       <c r="M47" t="n">
-        <v>243.5</v>
+        <v>235.5</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4253,13 +4253,13 @@
         <v>78</v>
       </c>
       <c r="E48" t="n">
-        <v>127</v>
+        <v>126.5</v>
       </c>
       <c r="F48" t="n">
-        <v>20.65</v>
+        <v>20.57</v>
       </c>
       <c r="G48" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-1.17</v>
+        <v>-0.39</v>
       </c>
       <c r="M48" t="n">
-        <v>128.5</v>
+        <v>127</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4330,13 +4330,13 @@
         <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>246.5</v>
+        <v>253</v>
       </c>
       <c r="F49" t="n">
-        <v>27</v>
+        <v>27.71</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-6.45</v>
+        <v>2.64</v>
       </c>
       <c r="M49" t="n">
-        <v>263.5</v>
+        <v>246.5</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
@@ -4407,13 +4407,13 @@
         <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="F50" t="n">
-        <v>27.48</v>
+        <v>28.21</v>
       </c>
       <c r="G50" t="n">
-        <v>7.75</v>
+        <v>7.95</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.61</v>
+        <v>2.64</v>
       </c>
       <c r="M50" t="n">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4488,13 +4488,13 @@
         <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F51" t="n">
-        <v>26.12</v>
+        <v>26.31</v>
       </c>
       <c r="G51" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-5.72</v>
+        <v>0.71</v>
       </c>
       <c r="M51" t="n">
-        <v>148.5</v>
+        <v>140</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4569,13 +4569,13 @@
         <v>97</v>
       </c>
       <c r="E52" t="n">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="F52" t="n">
-        <v>29.03</v>
+        <v>29.71</v>
       </c>
       <c r="G52" t="n">
-        <v>7.91</v>
+        <v>8.09</v>
       </c>
       <c r="H52" t="n">
         <v>29.3</v>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-2.44</v>
+        <v>2.34</v>
       </c>
       <c r="M52" t="n">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -4648,13 +4648,13 @@
         <v>91</v>
       </c>
       <c r="E53" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F53" t="n">
-        <v>43.56</v>
+        <v>43.62</v>
       </c>
       <c r="G53" t="n">
-        <v>5.84</v>
+        <v>5.85</v>
       </c>
       <c r="H53" t="n">
         <v>46.1</v>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-5.96</v>
+        <v>0.14</v>
       </c>
       <c r="M53" t="n">
-        <v>755</v>
+        <v>710</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -4727,13 +4727,13 @@
         <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>58.2</v>
+        <v>59.2</v>
       </c>
       <c r="F54" t="n">
-        <v>15.99</v>
+        <v>16.26</v>
       </c>
       <c r="G54" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="H54" t="n">
         <v>17.3</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-2.68</v>
+        <v>1.72</v>
       </c>
       <c r="M54" t="n">
-        <v>59.8</v>
+        <v>58.2</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -4806,13 +4806,13 @@
         <v>77</v>
       </c>
       <c r="E55" t="n">
-        <v>178.5</v>
+        <v>182.5</v>
       </c>
       <c r="F55" t="n">
-        <v>16.3</v>
+        <v>16.67</v>
       </c>
       <c r="G55" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H55" t="n">
         <v>15.5</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="M55" t="n">
-        <v>179.5</v>
+        <v>178.5</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -4885,13 +4885,13 @@
         <v>96</v>
       </c>
       <c r="E56" t="n">
-        <v>363</v>
+        <v>375.5</v>
       </c>
       <c r="F56" t="n">
-        <v>18.8</v>
+        <v>19.45</v>
       </c>
       <c r="G56" t="n">
-        <v>5.33</v>
+        <v>5.51</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-1.49</v>
+        <v>3.44</v>
       </c>
       <c r="M56" t="n">
-        <v>368.5</v>
+        <v>363</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -4962,13 +4962,13 @@
         <v>94</v>
       </c>
       <c r="E57" t="n">
-        <v>165.5</v>
+        <v>168.5</v>
       </c>
       <c r="F57" t="n">
-        <v>18.62</v>
+        <v>18.95</v>
       </c>
       <c r="G57" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-2.07</v>
+        <v>1.81</v>
       </c>
       <c r="M57" t="n">
-        <v>169</v>
+        <v>165.5</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -5039,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="E58" t="n">
-        <v>97.2</v>
+        <v>97.8</v>
       </c>
       <c r="F58" t="n">
-        <v>18.55</v>
+        <v>18.66</v>
       </c>
       <c r="G58" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-3.28</v>
+        <v>0.62</v>
       </c>
       <c r="M58" t="n">
-        <v>100.5</v>
+        <v>97.2</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -5120,13 +5120,13 @@
         <v>77</v>
       </c>
       <c r="E59" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="F59" t="n">
-        <v>17.17</v>
+        <v>17.22</v>
       </c>
       <c r="G59" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1.91</v>
+        <v>0.32</v>
       </c>
       <c r="M59" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5201,13 +5201,13 @@
         <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>293</v>
+        <v>300.5</v>
       </c>
       <c r="F60" t="n">
-        <v>18.21</v>
+        <v>18.68</v>
       </c>
       <c r="G60" t="n">
-        <v>6.62</v>
+        <v>6.79</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-2.01</v>
+        <v>2.56</v>
       </c>
       <c r="M60" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -5278,13 +5278,13 @@
         <v>73</v>
       </c>
       <c r="E61" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F61" t="n">
-        <v>15.7</v>
+        <v>15.86</v>
       </c>
       <c r="G61" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-0.53</v>
+        <v>1.08</v>
       </c>
       <c r="M61" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         <v>66</v>
       </c>
       <c r="E62" t="n">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="F62" t="n">
-        <v>18.41</v>
+        <v>18.74</v>
       </c>
       <c r="G62" t="n">
-        <v>14.86</v>
+        <v>15.12</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M62" t="n">
         <v>797</v>
@@ -5436,13 +5436,13 @@
         <v>62</v>
       </c>
       <c r="E63" t="n">
-        <v>488</v>
+        <v>480.5</v>
       </c>
       <c r="F63" t="n">
-        <v>18.94</v>
+        <v>18.65</v>
       </c>
       <c r="G63" t="n">
-        <v>5.22</v>
+        <v>5.14</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-7.4</v>
+        <v>-1.54</v>
       </c>
       <c r="M63" t="n">
-        <v>527</v>
+        <v>488</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -5515,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="E64" t="n">
-        <v>161.5</v>
+        <v>165</v>
       </c>
       <c r="F64" t="n">
-        <v>17.81</v>
+        <v>18.19</v>
       </c>
       <c r="G64" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-7.18</v>
+        <v>2.17</v>
       </c>
       <c r="M64" t="n">
-        <v>174</v>
+        <v>161.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>49.5</v>
+        <v>49.85</v>
       </c>
       <c r="F65" t="n">
-        <v>12.22</v>
+        <v>12.31</v>
       </c>
       <c r="G65" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.2</v>
+        <v>0.71</v>
       </c>
       <c r="M65" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -5675,13 +5675,13 @@
         <v>97</v>
       </c>
       <c r="E66" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F66" t="n">
-        <v>16.6</v>
+        <v>16.81</v>
       </c>
       <c r="G66" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="H66" t="n">
         <v>14.7</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="M66" t="n">
-        <v>155.5</v>
+        <v>158</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         <v>96</v>
       </c>
       <c r="E67" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F67" t="n">
-        <v>22.27</v>
+        <v>22.31</v>
       </c>
       <c r="G67" t="n">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="H67" t="n">
         <v>17.9</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="M67" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -5833,13 +5833,13 @@
         <v>91</v>
       </c>
       <c r="E68" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
       <c r="F68" t="n">
-        <v>15.18</v>
+        <v>15.25</v>
       </c>
       <c r="G68" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="H68" t="n">
         <v>15</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-0.42</v>
+        <v>0.43</v>
       </c>
       <c r="M68" t="n">
-        <v>118</v>
+        <v>117.5</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
@@ -5912,13 +5912,13 @@
         <v>90</v>
       </c>
       <c r="E69" t="n">
-        <v>360.5</v>
+        <v>367</v>
       </c>
       <c r="F69" t="n">
-        <v>30.47</v>
+        <v>31.02</v>
       </c>
       <c r="G69" t="n">
-        <v>7.84</v>
+        <v>7.98</v>
       </c>
       <c r="H69" t="n">
         <v>27.5</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-7.68</v>
+        <v>1.8</v>
       </c>
       <c r="M69" t="n">
-        <v>390.5</v>
+        <v>360.5</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
@@ -5991,13 +5991,13 @@
         <v>87</v>
       </c>
       <c r="E70" t="n">
-        <v>79.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>13.93</v>
+        <v>13.71</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H70" t="n">
         <v>16.7</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-0.37</v>
+        <v>-1.63</v>
       </c>
       <c r="M70" t="n">
-        <v>80</v>
+        <v>79.7</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         <v>77</v>
       </c>
       <c r="E71" t="n">
-        <v>135.5</v>
+        <v>135</v>
       </c>
       <c r="F71" t="n">
-        <v>18.87</v>
+        <v>18.8</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="H71" t="n">
         <v>16.4</v>
@@ -6096,7 +6096,7 @@
         <v>-0.37</v>
       </c>
       <c r="M71" t="n">
-        <v>136</v>
+        <v>135.5</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
@@ -6153,13 +6153,13 @@
         <v>77</v>
       </c>
       <c r="E72" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F72" t="n">
-        <v>15.82</v>
+        <v>16.02</v>
       </c>
       <c r="G72" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H72" t="n">
         <v>15.3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.84</v>
+        <v>1.25</v>
       </c>
       <c r="M72" t="n">
-        <v>244.5</v>
+        <v>240</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
@@ -6232,13 +6232,13 @@
         <v>76</v>
       </c>
       <c r="E73" t="n">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="F73" t="n">
-        <v>41.97</v>
+        <v>42.27</v>
       </c>
       <c r="G73" t="n">
-        <v>22.42</v>
+        <v>22.57</v>
       </c>
       <c r="H73" t="n">
         <v>38.8</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-7.81</v>
+        <v>0.71</v>
       </c>
       <c r="M73" t="n">
-        <v>1075</v>
+        <v>991</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="E74" t="n">
-        <v>57.3</v>
+        <v>58.3</v>
       </c>
       <c r="F74" t="n">
-        <v>18.48</v>
+        <v>18.81</v>
       </c>
       <c r="G74" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="H74" t="n">
         <v>21.3</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.38</v>
+        <v>1.75</v>
       </c>
       <c r="M74" t="n">
-        <v>58.1</v>
+        <v>57.3</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
@@ -6396,13 +6396,13 @@
         <v>100</v>
       </c>
       <c r="E75" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="F75" t="n">
-        <v>43.72</v>
+        <v>44.19</v>
       </c>
       <c r="G75" t="n">
-        <v>23.33</v>
+        <v>23.58</v>
       </c>
       <c r="H75" t="n">
         <v>24.6</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-3.1</v>
+        <v>1.07</v>
       </c>
       <c r="M75" t="n">
-        <v>3385</v>
+        <v>3280</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -6475,13 +6475,13 @@
         <v>100</v>
       </c>
       <c r="E76" t="n">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F76" t="n">
-        <v>14.46</v>
+        <v>14.5</v>
       </c>
       <c r="G76" t="n">
-        <v>8.17</v>
+        <v>8.19</v>
       </c>
       <c r="H76" t="n">
         <v>14.2</v>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-4.27</v>
+        <v>0.28</v>
       </c>
       <c r="M76" t="n">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1.97</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2540</v>
+        <v>2490</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -6633,13 +6633,13 @@
         <v>97</v>
       </c>
       <c r="E78" t="n">
-        <v>120</v>
+        <v>121.5</v>
       </c>
       <c r="F78" t="n">
-        <v>17.12</v>
+        <v>17.33</v>
       </c>
       <c r="G78" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="H78" t="n">
         <v>12.4</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0.42</v>
+        <v>1.25</v>
       </c>
       <c r="M78" t="n">
-        <v>119.5</v>
+        <v>120</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         <v>94</v>
       </c>
       <c r="E79" t="n">
-        <v>118.5</v>
+        <v>120</v>
       </c>
       <c r="F79" t="n">
-        <v>14.67</v>
+        <v>14.85</v>
       </c>
       <c r="G79" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H79" t="n">
         <v>12.3</v>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M79" t="n">
         <v>118.5</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -6870,13 +6870,13 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>106</v>
+        <v>107.5</v>
       </c>
       <c r="F81" t="n">
-        <v>12.21</v>
+        <v>12.38</v>
       </c>
       <c r="G81" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H81" t="n">
         <v>10.7</v>
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-0.47</v>
+        <v>1.42</v>
       </c>
       <c r="M81" t="n">
-        <v>106.5</v>
+        <v>106</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -6949,13 +6949,13 @@
         <v>94</v>
       </c>
       <c r="E82" t="n">
-        <v>183.5</v>
+        <v>184</v>
       </c>
       <c r="F82" t="n">
-        <v>13.08</v>
+        <v>13.11</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="H82" t="n">
         <v>11.4</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-1.08</v>
+        <v>0.27</v>
       </c>
       <c r="M82" t="n">
-        <v>185.5</v>
+        <v>183.5</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         <v>92</v>
       </c>
       <c r="E83" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="F83" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H83" t="n">
         <v>7.6</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.38</v>
+        <v>0.93</v>
       </c>
       <c r="M83" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -7107,13 +7107,13 @@
         <v>90</v>
       </c>
       <c r="E84" t="n">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="F84" t="n">
-        <v>21.97</v>
+        <v>22.36</v>
       </c>
       <c r="G84" t="n">
-        <v>8.42</v>
+        <v>8.57</v>
       </c>
       <c r="H84" t="n">
         <v>25</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-2.67</v>
+        <v>1.79</v>
       </c>
       <c r="M84" t="n">
-        <v>861</v>
+        <v>838</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -7186,13 +7186,13 @@
         <v>90</v>
       </c>
       <c r="E85" t="n">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="F85" t="n">
-        <v>24.51</v>
+        <v>25.84</v>
       </c>
       <c r="G85" t="n">
-        <v>5.4</v>
+        <v>5.69</v>
       </c>
       <c r="H85" t="n">
         <v>21.2</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-1.21</v>
+        <v>5.42</v>
       </c>
       <c r="M85" t="n">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -7265,13 +7265,13 @@
         <v>90</v>
       </c>
       <c r="E86" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F86" t="n">
-        <v>18.06</v>
+        <v>18.39</v>
       </c>
       <c r="G86" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="H86" t="n">
         <v>14.1</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-0.3</v>
+        <v>1.79</v>
       </c>
       <c r="M86" t="n">
-        <v>168.5</v>
+        <v>168</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         <v>84</v>
       </c>
       <c r="E87" t="n">
-        <v>38.65</v>
+        <v>39.15</v>
       </c>
       <c r="F87" t="n">
-        <v>7.97</v>
+        <v>8.07</v>
       </c>
       <c r="G87" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H87" t="n">
         <v>6.2</v>
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.77</v>
+        <v>1.29</v>
       </c>
       <c r="M87" t="n">
-        <v>38.95</v>
+        <v>38.65</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         <v>80</v>
       </c>
       <c r="E88" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="F88" t="n">
-        <v>32.05</v>
+        <v>32.21</v>
       </c>
       <c r="G88" t="n">
-        <v>16.52</v>
+        <v>16.6</v>
       </c>
       <c r="H88" t="n">
         <v>30.7</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-4.23</v>
+        <v>0.49</v>
       </c>
       <c r="M88" t="n">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
@@ -7506,13 +7506,13 @@
         <v>80</v>
       </c>
       <c r="E89" t="n">
-        <v>1475</v>
+        <v>1490</v>
       </c>
       <c r="F89" t="n">
-        <v>34.02</v>
+        <v>34.36</v>
       </c>
       <c r="G89" t="n">
-        <v>10.35</v>
+        <v>10.46</v>
       </c>
       <c r="H89" t="n">
         <v>21.8</v>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-4.22</v>
+        <v>1.02</v>
       </c>
       <c r="M89" t="n">
-        <v>1540</v>
+        <v>1475</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
@@ -7589,13 +7589,13 @@
         <v>79</v>
       </c>
       <c r="E90" t="n">
-        <v>89</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>8.720000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="G90" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="H90" t="n">
         <v>8.6</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-2.09</v>
+        <v>0.45</v>
       </c>
       <c r="M90" t="n">
-        <v>90.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
@@ -7672,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="E91" t="n">
-        <v>54.4</v>
+        <v>54.9</v>
       </c>
       <c r="F91" t="n">
-        <v>8.19</v>
+        <v>8.27</v>
       </c>
       <c r="G91" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H91" t="n">
         <v>6.8</v>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>-1.98</v>
+        <v>0.92</v>
       </c>
       <c r="M91" t="n">
-        <v>55.5</v>
+        <v>54.4</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
@@ -7755,13 +7755,13 @@
         <v>77</v>
       </c>
       <c r="E92" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
       <c r="F92" t="n">
-        <v>7.13</v>
+        <v>7.24</v>
       </c>
       <c r="G92" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H92" t="n">
         <v>10.4</v>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-2.1</v>
+        <v>1.56</v>
       </c>
       <c r="M92" t="n">
-        <v>52.5</v>
+        <v>51.4</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
@@ -7921,13 +7921,13 @@
         <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>2195</v>
+        <v>2115</v>
       </c>
       <c r="F94" t="n">
-        <v>7.04</v>
+        <v>6.78</v>
       </c>
       <c r="G94" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="H94" t="n">
         <v>9.6</v>
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>-3.52</v>
+        <v>-3.64</v>
       </c>
       <c r="M94" t="n">
-        <v>2275</v>
+        <v>2195</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>189.5</v>
+        <v>187</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
@@ -8087,13 +8087,13 @@
         <v>60</v>
       </c>
       <c r="E96" t="n">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="F96" t="n">
-        <v>16.42</v>
+        <v>16.48</v>
       </c>
       <c r="G96" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="H96" t="n">
         <v>11.9</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M96" t="n">
         <v>1540</v>
@@ -8170,13 +8170,13 @@
         <v>79</v>
       </c>
       <c r="E97" t="n">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="F97" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="G97" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0.14</v>
+        <v>0.72</v>
       </c>
       <c r="M97" t="n">
-        <v>69.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -8247,13 +8247,13 @@
         <v>77</v>
       </c>
       <c r="E98" t="n">
-        <v>363</v>
+        <v>367.5</v>
       </c>
       <c r="F98" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="G98" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>-1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M98" t="n">
-        <v>367.5</v>
+        <v>363</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -8328,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="E99" t="n">
-        <v>23.05</v>
+        <v>22.9</v>
       </c>
       <c r="F99" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="G99" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0.22</v>
+        <v>-0.65</v>
       </c>
       <c r="M99" t="n">
-        <v>23</v>
+        <v>23.05</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>75</v>
       </c>
       <c r="E100" t="n">
-        <v>31.8</v>
+        <v>32.4</v>
       </c>
       <c r="F100" t="n">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="G100" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
@@ -8428,10 +8428,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>-0.78</v>
+        <v>1.89</v>
       </c>
       <c r="M100" t="n">
-        <v>32.05</v>
+        <v>31.8</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -8490,13 +8490,13 @@
         <v>69</v>
       </c>
       <c r="E101" t="n">
-        <v>189.5</v>
+        <v>191.5</v>
       </c>
       <c r="F101" t="n">
-        <v>4.71</v>
+        <v>4.76</v>
       </c>
       <c r="G101" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>-3.81</v>
+        <v>1.06</v>
       </c>
       <c r="M101" t="n">
-        <v>197</v>
+        <v>189.5</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -8702,13 +8702,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="F2" t="n">
-        <v>43.72</v>
+        <v>44.19</v>
       </c>
       <c r="G2" t="n">
-        <v>23.33</v>
+        <v>23.58</v>
       </c>
       <c r="H2" t="n">
 